--- a/import-files/WC-CTN-O(1).xlsx
+++ b/import-files/WC-CTN-O(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Pictures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3FAC2D-B78D-436A-8473-19AC2733B481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785F232C-5C2F-4A7D-87D9-FC2DF11BCD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Club Details" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Membership!$A$1:$T$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Membership!$A$1:$T$115</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="791">
   <si>
     <t>How To Complete/Update existing information.</t>
   </si>
@@ -670,9 +670,6 @@
     <t>earl@pnp.co.za</t>
   </si>
   <si>
-    <t>Best of Order</t>
-  </si>
-  <si>
     <t>8509085191080</t>
   </si>
   <si>
@@ -2567,9 +2564,6 @@
     <t>Roberts</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
     <t>Dooling</t>
   </si>
   <si>
@@ -2591,9 +2585,6 @@
     <t>Chesley</t>
   </si>
   <si>
-    <t>Fernando</t>
-  </si>
-  <si>
     <t>Micheal</t>
   </si>
   <si>
@@ -2609,9 +2600,6 @@
     <t>DSA-100000</t>
   </si>
   <si>
-    <t>DSA-200000</t>
-  </si>
-  <si>
     <t>DSA-300000</t>
   </si>
   <si>
@@ -2622,6 +2610,15 @@
   </si>
   <si>
     <t>DSA-600000</t>
+  </si>
+  <si>
+    <t>Guardians</t>
+  </si>
+  <si>
+    <t>Brisdel</t>
+  </si>
+  <si>
+    <t>East Side</t>
   </si>
   <si>
     <t>DSA-180519</t>
@@ -3083,6 +3080,12 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3097,12 +3100,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -4178,66 +4175,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
     </row>
     <row r="2" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>223</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
+      <c r="A2" s="45" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
     </row>
     <row r="3" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
     </row>
     <row r="6" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47" t="s">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="47"/>
+      <c r="D8" s="42"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
@@ -4268,7 +4265,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>28</v>
@@ -4280,7 +4277,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>17</v>
@@ -4312,7 +4309,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>18</v>
@@ -4330,33 +4327,33 @@
       <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="48"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47" t="s">
+      <c r="B18" s="42"/>
+      <c r="C18" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="47"/>
+      <c r="D18" s="42"/>
     </row>
     <row r="19" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>49</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4370,7 +4367,7 @@
         <v>27</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4378,13 +4375,13 @@
         <v>28</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4392,7 +4389,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>17</v>
@@ -4424,13 +4421,13 @@
         <v>18</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4438,30 +4435,30 @@
         <v>29</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="47" t="s">
+      <c r="A28" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47" t="s">
+      <c r="B28" s="42"/>
+      <c r="C28" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="47"/>
+      <c r="D28" s="42"/>
     </row>
     <row r="29" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
@@ -4474,7 +4471,7 @@
         <v>49</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4496,13 +4493,13 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4514,7 +4511,7 @@
         <v>17</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4542,13 +4539,13 @@
         <v>18</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4556,13 +4553,13 @@
         <v>29</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4573,6 +4570,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="A18:B18"/>
@@ -4581,12 +4584,6 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B26" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -4634,7 +4631,7 @@
   <sheetData>
     <row r="1" spans="1:20" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>33</v>
@@ -4673,7 +4670,7 @@
         <v>14</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O1" s="10" t="s">
         <v>15</v>
@@ -4696,7 +4693,7 @@
     </row>
     <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B2" s="34" t="s">
         <v>59</v>
@@ -4714,13 +4711,13 @@
         <v>126</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H2" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J2" s="35" t="s">
         <v>115</v>
@@ -4730,27 +4727,27 @@
       </c>
       <c r="L2" s="35"/>
       <c r="M2" s="35" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="N2" s="36">
         <v>18768</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
       <c r="R2" s="35" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="S2" s="37"/>
       <c r="T2" s="37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B3" s="34" t="s">
         <v>59</v>
@@ -4768,43 +4765,43 @@
         <v>126</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H3" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J3" s="34" t="s">
         <v>80</v>
       </c>
       <c r="K3" s="34" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L3" s="34"/>
       <c r="M3" s="35" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="N3" s="36">
         <v>21633</v>
       </c>
       <c r="O3" s="34" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P3" s="34"/>
       <c r="Q3" s="34"/>
       <c r="R3" s="35" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="S3" s="38"/>
       <c r="T3" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B4" s="34" t="s">
         <v>59</v>
@@ -4822,43 +4819,43 @@
         <v>126</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H4" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I4" s="34" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J4" s="34" t="s">
         <v>72</v>
       </c>
       <c r="K4" s="34" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="L4" s="34"/>
       <c r="M4" s="35" t="s">
+        <v>561</v>
+      </c>
+      <c r="N4" s="36" t="s">
         <v>562</v>
       </c>
-      <c r="N4" s="36" t="s">
+      <c r="O4" s="34" t="s">
         <v>563</v>
-      </c>
-      <c r="O4" s="34" t="s">
-        <v>564</v>
       </c>
       <c r="P4" s="34"/>
       <c r="Q4" s="34"/>
       <c r="R4" s="35" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="S4" s="38"/>
       <c r="T4" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B5" s="34" t="s">
         <v>59</v>
@@ -4876,23 +4873,23 @@
         <v>126</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H5" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J5" s="34" t="s">
         <v>103</v>
       </c>
       <c r="K5" s="34" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L5" s="34"/>
       <c r="M5" s="35" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="N5" s="36">
         <v>18144</v>
@@ -4902,11 +4899,13 @@
       <c r="Q5" s="34"/>
       <c r="R5" s="35"/>
       <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
+      <c r="T5" s="38" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B6" s="34" t="s">
         <v>59</v>
@@ -4924,45 +4923,45 @@
         <v>126</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H6" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I6" s="35" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J6" s="35" t="s">
         <v>71</v>
       </c>
       <c r="K6" s="35" t="s">
+        <v>523</v>
+      </c>
+      <c r="L6" s="35" t="s">
         <v>524</v>
       </c>
-      <c r="L6" s="35" t="s">
+      <c r="M6" s="35" t="s">
         <v>525</v>
-      </c>
-      <c r="M6" s="35" t="s">
-        <v>526</v>
       </c>
       <c r="N6" s="36">
         <v>34958</v>
       </c>
       <c r="O6" s="34" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="P6" s="35"/>
       <c r="Q6" s="35"/>
       <c r="R6" s="35" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="S6" s="35"/>
       <c r="T6" s="35" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>59</v>
@@ -4980,7 +4979,7 @@
         <v>126</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H7" s="34" t="s">
         <v>63</v>
@@ -4996,27 +4995,27 @@
       </c>
       <c r="L7" s="34"/>
       <c r="M7" s="35" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N7" s="36">
         <v>20787</v>
       </c>
       <c r="O7" s="34" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P7" s="34"/>
       <c r="Q7" s="34"/>
       <c r="R7" s="35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S7" s="38"/>
       <c r="T7" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>59</v>
@@ -5034,7 +5033,7 @@
         <v>126</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H8" s="34" t="s">
         <v>63</v>
@@ -5050,27 +5049,27 @@
       </c>
       <c r="L8" s="34"/>
       <c r="M8" s="35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N8" s="36">
         <v>30024</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P8" s="34"/>
       <c r="Q8" s="34"/>
       <c r="R8" s="35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S8" s="38"/>
       <c r="T8" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B9" s="34" t="s">
         <v>59</v>
@@ -5088,43 +5087,43 @@
         <v>126</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H9" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I9" s="35" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J9" s="35" t="s">
         <v>72</v>
       </c>
       <c r="K9" s="35" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L9" s="35"/>
       <c r="M9" s="35" t="s">
+        <v>681</v>
+      </c>
+      <c r="N9" s="36" t="s">
+        <v>690</v>
+      </c>
+      <c r="O9" s="34" t="s">
         <v>682</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>691</v>
-      </c>
-      <c r="O9" s="34" t="s">
-        <v>683</v>
       </c>
       <c r="P9" s="35"/>
       <c r="Q9" s="35"/>
       <c r="R9" s="35" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="S9" s="35"/>
       <c r="T9" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>59</v>
@@ -5142,43 +5141,43 @@
         <v>126</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H10" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J10" s="34" t="s">
         <v>71</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L10" s="34"/>
       <c r="M10" s="35" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="N10" s="36">
         <v>23651</v>
       </c>
       <c r="O10" s="34" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P10" s="34"/>
       <c r="Q10" s="34"/>
       <c r="R10" s="35" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="S10" s="38"/>
       <c r="T10" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>59</v>
@@ -5196,7 +5195,7 @@
         <v>126</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H11" s="34" t="s">
         <v>63</v>
@@ -5212,27 +5211,27 @@
       </c>
       <c r="L11" s="34"/>
       <c r="M11" s="35" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N11" s="36">
         <v>24982</v>
       </c>
       <c r="O11" s="34" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P11" s="34"/>
       <c r="Q11" s="34"/>
       <c r="R11" s="34" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="S11" s="35"/>
       <c r="T11" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>59</v>
@@ -5250,47 +5249,47 @@
         <v>126</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H12" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I12" s="35" t="s">
+        <v>403</v>
+      </c>
+      <c r="J12" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="K12" s="35" t="s">
         <v>404</v>
       </c>
-      <c r="J12" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="K12" s="35" t="s">
+      <c r="L12" s="35" t="s">
+        <v>404</v>
+      </c>
+      <c r="M12" s="35" t="s">
         <v>405</v>
-      </c>
-      <c r="L12" s="35" t="s">
-        <v>405</v>
-      </c>
-      <c r="M12" s="35" t="s">
-        <v>406</v>
       </c>
       <c r="N12" s="36">
         <v>26677</v>
       </c>
       <c r="O12" s="34" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="P12" s="35"/>
       <c r="Q12" s="35"/>
       <c r="R12" s="35" t="s">
+        <v>407</v>
+      </c>
+      <c r="S12" s="35" t="s">
         <v>408</v>
       </c>
-      <c r="S12" s="35" t="s">
-        <v>409</v>
-      </c>
       <c r="T12" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>59</v>
@@ -5308,43 +5307,43 @@
         <v>126</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H13" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J13" s="34" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K13" s="34" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="L13" s="34"/>
       <c r="M13" s="35" t="s">
+        <v>746</v>
+      </c>
+      <c r="N13" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="N13" s="36" t="s">
-        <v>748</v>
-      </c>
       <c r="O13" s="34" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="P13" s="34"/>
       <c r="Q13" s="34"/>
       <c r="R13" s="35" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="S13" s="39"/>
       <c r="T13" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>59</v>
@@ -5362,43 +5361,43 @@
         <v>126</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H14" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J14" s="34" t="s">
         <v>103</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="35" t="s">
+        <v>742</v>
+      </c>
+      <c r="N14" s="36" t="s">
         <v>743</v>
       </c>
-      <c r="N14" s="36" t="s">
-        <v>744</v>
-      </c>
       <c r="O14" s="34" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="P14" s="34"/>
       <c r="Q14" s="34"/>
       <c r="R14" s="35" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="S14" s="39"/>
       <c r="T14" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>59</v>
@@ -5416,43 +5415,43 @@
         <v>126</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I15" s="34" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J15" s="34" t="s">
         <v>71</v>
       </c>
       <c r="K15" s="34" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="35" t="s">
+        <v>738</v>
+      </c>
+      <c r="N15" s="36" t="s">
         <v>739</v>
       </c>
-      <c r="N15" s="36" t="s">
-        <v>740</v>
-      </c>
       <c r="O15" s="34" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="P15" s="34"/>
       <c r="Q15" s="34"/>
       <c r="R15" s="35" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="S15" s="39"/>
       <c r="T15" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>59</v>
@@ -5470,43 +5469,43 @@
         <v>126</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H16" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I16" s="34" t="s">
+        <v>452</v>
+      </c>
+      <c r="J16" s="34" t="s">
         <v>453</v>
       </c>
-      <c r="J16" s="34" t="s">
+      <c r="K16" s="34" t="s">
         <v>454</v>
-      </c>
-      <c r="K16" s="34" t="s">
-        <v>455</v>
       </c>
       <c r="L16" s="34"/>
       <c r="M16" s="35" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="N16" s="36" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="O16" s="34" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="P16" s="34"/>
       <c r="Q16" s="34"/>
       <c r="R16" s="35" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S16" s="39"/>
       <c r="T16" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B17" s="34" t="s">
         <v>59</v>
@@ -5524,7 +5523,7 @@
         <v>126</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H17" s="34" t="s">
         <v>63</v>
@@ -5540,27 +5539,27 @@
       </c>
       <c r="L17" s="34"/>
       <c r="M17" s="35" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N17" s="36">
         <v>23212</v>
       </c>
       <c r="O17" s="34" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P17" s="34"/>
       <c r="Q17" s="34"/>
       <c r="R17" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="S17" s="39"/>
       <c r="T17" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B18" s="34" t="s">
         <v>59</v>
@@ -5578,7 +5577,7 @@
         <v>126</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H18" s="34" t="s">
         <v>63</v>
@@ -5590,13 +5589,13 @@
         <v>73</v>
       </c>
       <c r="K18" s="34" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L18" s="34" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="M18" s="35" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N18" s="36">
         <v>23919</v>
@@ -5607,12 +5606,12 @@
       <c r="R18" s="35"/>
       <c r="S18" s="39"/>
       <c r="T18" s="38" t="s">
-        <v>447</v>
+        <v>786</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B19" s="34" t="s">
         <v>59</v>
@@ -5630,45 +5629,45 @@
         <v>126</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H19" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I19" s="35" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J19" s="35" t="s">
         <v>68</v>
       </c>
       <c r="K19" s="35" t="s">
+        <v>441</v>
+      </c>
+      <c r="L19" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="M19" s="35" t="s">
         <v>442</v>
-      </c>
-      <c r="L19" s="35" t="s">
-        <v>441</v>
-      </c>
-      <c r="M19" s="35" t="s">
-        <v>443</v>
       </c>
       <c r="N19" s="36">
         <v>28381</v>
       </c>
       <c r="O19" s="35" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="P19" s="35"/>
       <c r="Q19" s="35"/>
       <c r="R19" s="35" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="S19" s="37"/>
       <c r="T19" s="37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>59</v>
@@ -5686,41 +5685,41 @@
         <v>126</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H20" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I20" s="34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J20" s="34" t="s">
         <v>103</v>
       </c>
       <c r="K20" s="34" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L20" s="34"/>
       <c r="M20" s="35" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="N20" s="36">
         <v>37912</v>
       </c>
       <c r="O20" s="34" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="P20" s="34"/>
       <c r="Q20" s="34"/>
       <c r="R20" s="35"/>
       <c r="S20" s="39"/>
       <c r="T20" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>59</v>
@@ -5738,45 +5737,45 @@
         <v>126</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H21" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I21" s="34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J21" s="34" t="s">
         <v>82</v>
       </c>
       <c r="K21" s="34" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="35" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N21" s="36">
         <v>23337</v>
       </c>
       <c r="O21" s="34" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P21" s="34"/>
       <c r="Q21" s="34"/>
       <c r="R21" s="35" t="s">
+        <v>293</v>
+      </c>
+      <c r="S21" s="38" t="s">
         <v>294</v>
       </c>
-      <c r="S21" s="38" t="s">
-        <v>295</v>
-      </c>
       <c r="T21" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>59</v>
@@ -5794,23 +5793,23 @@
         <v>126</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H22" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I22" s="35" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="J22" s="35" t="s">
         <v>73</v>
       </c>
       <c r="K22" s="35" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L22" s="35"/>
       <c r="M22" s="35" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="N22" s="36">
         <v>25927</v>
@@ -5821,12 +5820,12 @@
       <c r="R22" s="35"/>
       <c r="S22" s="35"/>
       <c r="T22" s="38" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>59</v>
@@ -5844,7 +5843,7 @@
         <v>126</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H23" s="34" t="s">
         <v>63</v>
@@ -5860,25 +5859,25 @@
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="35" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N23" s="36">
         <v>21575</v>
       </c>
       <c r="O23" s="34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P23" s="34"/>
       <c r="Q23" s="34"/>
       <c r="R23" s="35"/>
       <c r="S23" s="38"/>
       <c r="T23" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="34" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B24" s="34" t="s">
         <v>59</v>
@@ -5896,43 +5895,43 @@
         <v>126</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H24" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I24" s="34" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J24" s="34" t="s">
         <v>81</v>
       </c>
       <c r="K24" s="34" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="35" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N24" s="36">
         <v>27616</v>
       </c>
       <c r="O24" s="34" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="P24" s="34"/>
       <c r="Q24" s="34"/>
       <c r="R24" s="35" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S24" s="39"/>
       <c r="T24" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B25" s="34" t="s">
         <v>59</v>
@@ -5950,43 +5949,43 @@
         <v>126</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H25" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I25" s="34" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="J25" s="34" t="s">
         <v>72</v>
       </c>
       <c r="K25" s="34" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="L25" s="34"/>
       <c r="M25" s="35" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N25" s="36" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="O25" s="34" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="P25" s="34"/>
       <c r="Q25" s="34"/>
       <c r="R25" s="35" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="S25" s="39"/>
       <c r="T25" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B26" s="34" t="s">
         <v>59</v>
@@ -6004,43 +6003,43 @@
         <v>126</v>
       </c>
       <c r="G26" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H26" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I26" s="34" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="J26" s="34" t="s">
         <v>72</v>
       </c>
       <c r="K26" s="34" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="L26" s="34"/>
       <c r="M26" s="35" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="N26" s="36" t="s">
+        <v>725</v>
+      </c>
+      <c r="O26" s="34" t="s">
         <v>726</v>
-      </c>
-      <c r="O26" s="34" t="s">
-        <v>727</v>
       </c>
       <c r="P26" s="34"/>
       <c r="Q26" s="34"/>
       <c r="R26" s="35" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="S26" s="39"/>
       <c r="T26" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B27" s="34" t="s">
         <v>59</v>
@@ -6058,7 +6057,7 @@
         <v>126</v>
       </c>
       <c r="G27" s="35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H27" s="35" t="s">
         <v>63</v>
@@ -6070,33 +6069,33 @@
         <v>70</v>
       </c>
       <c r="K27" s="35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L27" s="35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="M27" s="35" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N27" s="36">
         <v>23057</v>
       </c>
       <c r="O27" s="35" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="35" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="S27" s="37"/>
       <c r="T27" s="37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="34" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B28" s="34" t="s">
         <v>59</v>
@@ -6114,45 +6113,45 @@
         <v>126</v>
       </c>
       <c r="G28" s="35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H28" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I28" s="35" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J28" s="35" t="s">
         <v>68</v>
       </c>
       <c r="K28" s="35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L28" s="35"/>
       <c r="M28" s="35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="N28" s="36">
         <v>25256</v>
       </c>
       <c r="O28" s="35" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="35" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="S28" s="37" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="T28" s="37" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="34" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B29" s="34" t="s">
         <v>59</v>
@@ -6170,13 +6169,13 @@
         <v>126</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H29" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I29" s="35" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="J29" s="35" t="s">
         <v>73</v>
@@ -6185,30 +6184,30 @@
         <v>74</v>
       </c>
       <c r="L29" s="35" t="s">
+        <v>659</v>
+      </c>
+      <c r="M29" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="N29" s="36" t="s">
+        <v>672</v>
+      </c>
+      <c r="O29" s="34" t="s">
         <v>660</v>
-      </c>
-      <c r="M29" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="N29" s="36" t="s">
-        <v>673</v>
-      </c>
-      <c r="O29" s="34" t="s">
-        <v>661</v>
       </c>
       <c r="P29" s="35"/>
       <c r="Q29" s="35"/>
       <c r="R29" s="35" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="S29" s="35"/>
       <c r="T29" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B30" s="34" t="s">
         <v>59</v>
@@ -6226,45 +6225,45 @@
         <v>126</v>
       </c>
       <c r="G30" s="35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H30" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="J30" s="35" t="s">
         <v>103</v>
       </c>
       <c r="K30" s="35" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L30" s="35"/>
       <c r="M30" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N30" s="36">
         <v>22633</v>
       </c>
       <c r="O30" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P30" s="35"/>
       <c r="Q30" s="35"/>
       <c r="R30" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="S30" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="S30" s="35" t="s">
+      <c r="T30" s="35" t="s">
         <v>150</v>
-      </c>
-      <c r="T30" s="35" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="35" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B31" s="34" t="s">
         <v>59</v>
@@ -6282,43 +6281,43 @@
         <v>126</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H31" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I31" s="34" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="J31" s="34" t="s">
         <v>84</v>
       </c>
       <c r="K31" s="34" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="L31" s="34"/>
       <c r="M31" s="35" t="s">
+        <v>714</v>
+      </c>
+      <c r="N31" s="36" t="s">
         <v>715</v>
       </c>
-      <c r="N31" s="36" t="s">
+      <c r="O31" s="34" t="s">
         <v>716</v>
-      </c>
-      <c r="O31" s="34" t="s">
-        <v>717</v>
       </c>
       <c r="P31" s="34"/>
       <c r="Q31" s="34"/>
       <c r="R31" s="35" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="S31" s="39"/>
       <c r="T31" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B32" s="34" t="s">
         <v>59</v>
@@ -6336,7 +6335,7 @@
         <v>126</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>63</v>
@@ -6348,35 +6347,35 @@
         <v>70</v>
       </c>
       <c r="K32" s="35" t="s">
+        <v>409</v>
+      </c>
+      <c r="L32" s="35" t="s">
+        <v>409</v>
+      </c>
+      <c r="M32" s="35" t="s">
         <v>410</v>
-      </c>
-      <c r="L32" s="35" t="s">
-        <v>410</v>
-      </c>
-      <c r="M32" s="35" t="s">
-        <v>411</v>
       </c>
       <c r="N32" s="36">
         <v>30282</v>
       </c>
       <c r="O32" s="34" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P32" s="35"/>
       <c r="Q32" s="35"/>
       <c r="R32" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="S32" s="35" t="s">
         <v>413</v>
       </c>
-      <c r="S32" s="35" t="s">
-        <v>414</v>
-      </c>
       <c r="T32" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B33" s="34" t="s">
         <v>59</v>
@@ -6394,7 +6393,7 @@
         <v>126</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H33" s="34" t="s">
         <v>63</v>
@@ -6406,33 +6405,33 @@
         <v>84</v>
       </c>
       <c r="K33" s="35" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L33" s="35"/>
       <c r="M33" s="35" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N33" s="36">
         <v>27970</v>
       </c>
       <c r="O33" s="34" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P33" s="35"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="S33" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="S33" s="35" t="s">
+      <c r="T33" s="38" t="s">
         <v>204</v>
-      </c>
-      <c r="T33" s="38" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B34" s="34" t="s">
         <v>59</v>
@@ -6450,43 +6449,43 @@
         <v>126</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H34" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I34" s="35" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="J34" s="35" t="s">
         <v>103</v>
       </c>
       <c r="K34" s="35" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L34" s="35"/>
       <c r="M34" s="35" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="N34" s="36" t="s">
+        <v>558</v>
+      </c>
+      <c r="O34" s="34" t="s">
         <v>559</v>
-      </c>
-      <c r="O34" s="34" t="s">
-        <v>560</v>
       </c>
       <c r="P34" s="35"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="35" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="S34" s="35"/>
       <c r="T34" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="35" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B35" s="34" t="s">
         <v>59</v>
@@ -6504,43 +6503,43 @@
         <v>126</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="J35" s="35" t="s">
         <v>73</v>
       </c>
       <c r="K35" s="35" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L35" s="35"/>
       <c r="M35" s="35" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="N35" s="36" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="O35" s="34" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="P35" s="35"/>
       <c r="Q35" s="35"/>
       <c r="R35" s="35" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="S35" s="35"/>
       <c r="T35" s="38" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B36" s="34" t="s">
         <v>59</v>
@@ -6558,43 +6557,43 @@
         <v>126</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H36" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I36" s="34" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J36" s="34" t="s">
         <v>73</v>
       </c>
       <c r="K36" s="34" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="L36" s="34"/>
       <c r="M36" s="35" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="N36" s="36">
         <v>38935</v>
       </c>
       <c r="O36" s="34" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P36" s="34"/>
       <c r="Q36" s="34"/>
       <c r="R36" s="35" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="S36" s="39"/>
       <c r="T36" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B37" s="34" t="s">
         <v>59</v>
@@ -6612,13 +6611,13 @@
         <v>126</v>
       </c>
       <c r="G37" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H37" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I37" s="35" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J37" s="35" t="s">
         <v>73</v>
@@ -6627,30 +6626,30 @@
         <v>74</v>
       </c>
       <c r="L37" s="35" t="s">
+        <v>663</v>
+      </c>
+      <c r="M37" s="35" t="s">
         <v>664</v>
       </c>
-      <c r="M37" s="35" t="s">
-        <v>665</v>
-      </c>
       <c r="N37" s="36" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="O37" s="34" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P37" s="35"/>
       <c r="Q37" s="35"/>
       <c r="R37" s="35" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="S37" s="35"/>
       <c r="T37" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="34" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B38" s="34" t="s">
         <v>59</v>
@@ -6668,7 +6667,7 @@
         <v>126</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H38" s="34" t="s">
         <v>63</v>
@@ -6684,27 +6683,27 @@
       </c>
       <c r="L38" s="34"/>
       <c r="M38" s="35" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N38" s="36">
         <v>27347</v>
       </c>
       <c r="O38" s="34" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P38" s="34"/>
       <c r="Q38" s="34"/>
       <c r="R38" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S38" s="39"/>
       <c r="T38" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="35" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B39" s="34" t="s">
         <v>59</v>
@@ -6722,45 +6721,45 @@
         <v>126</v>
       </c>
       <c r="G39" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H39" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I39" s="34" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="J39" s="34" t="s">
         <v>70</v>
       </c>
       <c r="K39" s="34" t="s">
+        <v>706</v>
+      </c>
+      <c r="L39" s="34" t="s">
         <v>707</v>
       </c>
-      <c r="L39" s="34" t="s">
+      <c r="M39" s="35" t="s">
         <v>708</v>
       </c>
-      <c r="M39" s="35" t="s">
+      <c r="N39" s="36" t="s">
         <v>709</v>
       </c>
-      <c r="N39" s="36" t="s">
+      <c r="O39" s="34" t="s">
         <v>710</v>
-      </c>
-      <c r="O39" s="34" t="s">
-        <v>711</v>
       </c>
       <c r="P39" s="34"/>
       <c r="Q39" s="34"/>
       <c r="R39" s="35" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="S39" s="39"/>
       <c r="T39" s="38" t="s">
-        <v>168</v>
+        <v>787</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="34" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B40" s="34" t="s">
         <v>59</v>
@@ -6778,7 +6777,7 @@
         <v>126</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H40" s="34" t="s">
         <v>63</v>
@@ -6790,31 +6789,31 @@
         <v>73</v>
       </c>
       <c r="K40" s="35" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="L40" s="35"/>
       <c r="M40" s="35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N40" s="36">
         <v>22941</v>
       </c>
       <c r="O40" s="34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P40" s="35"/>
       <c r="Q40" s="35"/>
       <c r="R40" s="35" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="S40" s="35"/>
       <c r="T40" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="34" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B41" s="34" t="s">
         <v>59</v>
@@ -6832,13 +6831,13 @@
         <v>126</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I41" s="35" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J41" s="35" t="s">
         <v>84</v>
@@ -6848,27 +6847,27 @@
       </c>
       <c r="L41" s="35"/>
       <c r="M41" s="35" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="N41" s="36">
         <v>30209</v>
       </c>
       <c r="O41" s="34" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="P41" s="35"/>
       <c r="Q41" s="35"/>
       <c r="R41" s="35" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="S41" s="35"/>
       <c r="T41" s="38" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="35" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B42" s="34" t="s">
         <v>59</v>
@@ -6886,43 +6885,43 @@
         <v>126</v>
       </c>
       <c r="G42" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H42" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I42" s="35" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J42" s="35" t="s">
         <v>80</v>
       </c>
       <c r="K42" s="35" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="L42" s="35"/>
       <c r="M42" s="35" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="N42" s="36" t="s">
+        <v>651</v>
+      </c>
+      <c r="O42" s="34" t="s">
         <v>652</v>
-      </c>
-      <c r="O42" s="34" t="s">
-        <v>653</v>
       </c>
       <c r="P42" s="35"/>
       <c r="Q42" s="35"/>
       <c r="R42" s="35" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="S42" s="35"/>
       <c r="T42" s="38" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="34" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B43" s="34" t="s">
         <v>59</v>
@@ -6940,45 +6939,45 @@
         <v>126</v>
       </c>
       <c r="G43" s="35" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H43" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I43" s="35" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="J43" s="35" t="s">
         <v>80</v>
       </c>
       <c r="K43" s="35" t="s">
+        <v>577</v>
+      </c>
+      <c r="L43" s="35" t="s">
         <v>578</v>
       </c>
-      <c r="L43" s="35" t="s">
+      <c r="M43" s="35" t="s">
         <v>579</v>
-      </c>
-      <c r="M43" s="35" t="s">
-        <v>580</v>
       </c>
       <c r="N43" s="36">
         <v>23292</v>
       </c>
       <c r="O43" s="35" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
       <c r="R43" s="35" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="S43" s="35"/>
       <c r="T43" s="35" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="34" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B44" s="34" t="s">
         <v>59</v>
@@ -6996,48 +6995,48 @@
         <v>126</v>
       </c>
       <c r="G44" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H44" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I44" s="34" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J44" s="34" t="s">
         <v>80</v>
       </c>
       <c r="K44" s="34" t="s">
+        <v>587</v>
+      </c>
+      <c r="L44" s="34" t="s">
         <v>588</v>
       </c>
-      <c r="L44" s="34" t="s">
+      <c r="M44" s="35" t="s">
         <v>589</v>
-      </c>
-      <c r="M44" s="35" t="s">
-        <v>590</v>
       </c>
       <c r="N44" s="36">
         <v>29846</v>
       </c>
       <c r="O44" s="34" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P44" s="34"/>
       <c r="Q44" s="34"/>
       <c r="R44" s="35" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="S44" s="39" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="T44" s="38" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="U44" s="32"/>
     </row>
     <row r="45" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="34" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B45" s="34" t="s">
         <v>59</v>
@@ -7055,43 +7054,43 @@
         <v>126</v>
       </c>
       <c r="G45" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H45" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I45" s="34" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J45" s="34" t="s">
         <v>65</v>
       </c>
       <c r="K45" s="34" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L45" s="34"/>
       <c r="M45" s="35" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N45" s="36">
         <v>26758</v>
       </c>
       <c r="O45" s="34" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P45" s="34"/>
       <c r="Q45" s="34"/>
       <c r="R45" s="35" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="S45" s="39"/>
       <c r="T45" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="34" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B46" s="34" t="s">
         <v>59</v>
@@ -7109,13 +7108,13 @@
         <v>126</v>
       </c>
       <c r="G46" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H46" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I46" s="34" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J46" s="34" t="s">
         <v>73</v>
@@ -7125,29 +7124,29 @@
       </c>
       <c r="L46" s="34"/>
       <c r="M46" s="35" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="N46" s="36">
         <v>31066</v>
       </c>
       <c r="O46" s="34" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="P46" s="34"/>
       <c r="Q46" s="34"/>
       <c r="R46" s="35" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="S46" s="39" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="T46" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="34" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B47" s="34" t="s">
         <v>59</v>
@@ -7165,47 +7164,47 @@
         <v>126</v>
       </c>
       <c r="G47" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I47" s="34" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J47" s="34" t="s">
         <v>107</v>
       </c>
       <c r="K47" s="34" t="s">
+        <v>569</v>
+      </c>
+      <c r="L47" s="34" t="s">
         <v>570</v>
       </c>
-      <c r="L47" s="34" t="s">
+      <c r="M47" s="35" t="s">
         <v>571</v>
-      </c>
-      <c r="M47" s="35" t="s">
-        <v>572</v>
       </c>
       <c r="N47" s="36">
         <v>27169</v>
       </c>
       <c r="O47" s="34" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P47" s="34"/>
       <c r="Q47" s="34"/>
       <c r="R47" s="35" t="s">
+        <v>573</v>
+      </c>
+      <c r="S47" s="39" t="s">
         <v>574</v>
       </c>
-      <c r="S47" s="39" t="s">
-        <v>575</v>
-      </c>
       <c r="T47" s="38" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="34" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B48" s="34" t="s">
         <v>59</v>
@@ -7223,25 +7222,25 @@
         <v>126</v>
       </c>
       <c r="G48" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H48" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I48" s="34" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J48" s="34" t="s">
         <v>80</v>
       </c>
       <c r="K48" s="34" t="s">
+        <v>389</v>
+      </c>
+      <c r="L48" s="34" t="s">
+        <v>389</v>
+      </c>
+      <c r="M48" s="35" t="s">
         <v>390</v>
-      </c>
-      <c r="L48" s="34" t="s">
-        <v>390</v>
-      </c>
-      <c r="M48" s="35" t="s">
-        <v>391</v>
       </c>
       <c r="N48" s="36">
         <v>25576</v>
@@ -7252,12 +7251,12 @@
       <c r="R48" s="35"/>
       <c r="S48" s="39"/>
       <c r="T48" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="34" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B49" s="34" t="s">
         <v>59</v>
@@ -7275,7 +7274,7 @@
         <v>126</v>
       </c>
       <c r="G49" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H49" s="34" t="s">
         <v>63</v>
@@ -7287,33 +7286,33 @@
         <v>80</v>
       </c>
       <c r="K49" s="34" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="L49" s="34"/>
       <c r="M49" s="35" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N49" s="36">
         <v>23532</v>
       </c>
       <c r="O49" s="34" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P49" s="34"/>
       <c r="Q49" s="34"/>
       <c r="R49" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="S49" s="39" t="s">
         <v>299</v>
       </c>
-      <c r="S49" s="39" t="s">
-        <v>300</v>
-      </c>
       <c r="T49" s="38" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="34" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B50" s="34" t="s">
         <v>59</v>
@@ -7331,7 +7330,7 @@
         <v>126</v>
       </c>
       <c r="G50" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H50" s="34" t="s">
         <v>63</v>
@@ -7346,32 +7345,32 @@
         <v>102</v>
       </c>
       <c r="L50" s="34" t="s">
+        <v>582</v>
+      </c>
+      <c r="M50" s="35" t="s">
         <v>583</v>
-      </c>
-      <c r="M50" s="35" t="s">
-        <v>584</v>
       </c>
       <c r="N50" s="36">
         <v>24574</v>
       </c>
       <c r="O50" s="34" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P50" s="34"/>
       <c r="Q50" s="34"/>
       <c r="R50" s="35" t="s">
+        <v>585</v>
+      </c>
+      <c r="S50" s="39" t="s">
         <v>586</v>
       </c>
-      <c r="S50" s="39" t="s">
-        <v>587</v>
-      </c>
       <c r="T50" s="38" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="34" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B51" s="34" t="s">
         <v>59</v>
@@ -7389,7 +7388,7 @@
         <v>126</v>
       </c>
       <c r="G51" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H51" s="34" t="s">
         <v>63</v>
@@ -7401,33 +7400,33 @@
         <v>84</v>
       </c>
       <c r="K51" s="34" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L51" s="34" t="s">
+        <v>693</v>
+      </c>
+      <c r="M51" s="35" t="s">
         <v>694</v>
-      </c>
-      <c r="M51" s="35" t="s">
-        <v>695</v>
       </c>
       <c r="N51" s="36">
         <v>20073</v>
       </c>
       <c r="O51" s="34" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="P51" s="34"/>
       <c r="Q51" s="34"/>
       <c r="R51" s="35" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="S51" s="39"/>
       <c r="T51" s="38" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="34" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B52" s="34" t="s">
         <v>59</v>
@@ -7445,7 +7444,7 @@
         <v>126</v>
       </c>
       <c r="G52" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H52" s="34" t="s">
         <v>63</v>
@@ -7457,29 +7456,29 @@
         <v>73</v>
       </c>
       <c r="K52" s="34" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="L52" s="34"/>
       <c r="M52" s="35" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="N52" s="36">
         <v>40077</v>
       </c>
       <c r="O52" s="34" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P52" s="34"/>
       <c r="Q52" s="34"/>
       <c r="R52" s="35"/>
       <c r="S52" s="39"/>
       <c r="T52" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B53" s="34" t="s">
         <v>59</v>
@@ -7497,7 +7496,7 @@
         <v>126</v>
       </c>
       <c r="G53" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H53" s="34" t="s">
         <v>63</v>
@@ -7513,27 +7512,27 @@
       </c>
       <c r="L53" s="34"/>
       <c r="M53" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N53" s="36">
         <v>24906</v>
       </c>
       <c r="O53" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P53" s="34"/>
       <c r="Q53" s="34"/>
       <c r="R53" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S53" s="39"/>
       <c r="T53" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="34" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B54" s="34" t="s">
         <v>59</v>
@@ -7551,7 +7550,7 @@
         <v>126</v>
       </c>
       <c r="G54" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H54" s="34" t="s">
         <v>63</v>
@@ -7563,33 +7562,33 @@
         <v>70</v>
       </c>
       <c r="K54" s="34" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L54" s="34"/>
       <c r="M54" s="35" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N54" s="36">
         <v>23023</v>
       </c>
       <c r="O54" s="34" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="P54" s="34"/>
       <c r="Q54" s="34"/>
       <c r="R54" s="35" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="S54" s="39" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="T54" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="34" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B55" s="34" t="s">
         <v>59</v>
@@ -7607,7 +7606,7 @@
         <v>126</v>
       </c>
       <c r="G55" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>63</v>
@@ -7619,33 +7618,33 @@
         <v>73</v>
       </c>
       <c r="K55" s="34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L55" s="34"/>
       <c r="M55" s="35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="N55" s="36">
         <v>23467</v>
       </c>
       <c r="O55" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P55" s="34"/>
       <c r="Q55" s="34"/>
       <c r="R55" s="35" t="s">
+        <v>342</v>
+      </c>
+      <c r="S55" s="39" t="s">
         <v>343</v>
       </c>
-      <c r="S55" s="39" t="s">
-        <v>344</v>
-      </c>
       <c r="T55" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="34" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B56" s="34" t="s">
         <v>59</v>
@@ -7663,45 +7662,45 @@
         <v>126</v>
       </c>
       <c r="G56" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H56" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I56" s="34" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J56" s="34" t="s">
         <v>65</v>
       </c>
       <c r="K56" s="34" t="s">
+        <v>448</v>
+      </c>
+      <c r="L56" s="34" t="s">
         <v>449</v>
       </c>
-      <c r="L56" s="34" t="s">
+      <c r="M56" s="35" t="s">
         <v>450</v>
-      </c>
-      <c r="M56" s="35" t="s">
-        <v>451</v>
       </c>
       <c r="N56" s="36">
         <v>25972</v>
       </c>
       <c r="O56" s="34" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="P56" s="34"/>
       <c r="Q56" s="34"/>
       <c r="R56" s="35" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="S56" s="39"/>
       <c r="T56" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B57" s="34" t="s">
         <v>59</v>
@@ -7719,7 +7718,7 @@
         <v>126</v>
       </c>
       <c r="G57" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H57" s="34" t="s">
         <v>63</v>
@@ -7734,30 +7733,30 @@
         <v>128</v>
       </c>
       <c r="L57" s="34" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M57" s="35" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N57" s="36">
         <v>27622</v>
       </c>
       <c r="O57" s="34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P57" s="34"/>
       <c r="Q57" s="34"/>
       <c r="R57" s="35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="S57" s="39"/>
       <c r="T57" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="34" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B58" s="34" t="s">
         <v>59</v>
@@ -7775,7 +7774,7 @@
         <v>126</v>
       </c>
       <c r="G58" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H58" s="34" t="s">
         <v>63</v>
@@ -7787,13 +7786,13 @@
         <v>81</v>
       </c>
       <c r="K58" s="34" t="s">
+        <v>376</v>
+      </c>
+      <c r="L58" s="34" t="s">
+        <v>376</v>
+      </c>
+      <c r="M58" s="35" t="s">
         <v>377</v>
-      </c>
-      <c r="L58" s="34" t="s">
-        <v>377</v>
-      </c>
-      <c r="M58" s="35" t="s">
-        <v>378</v>
       </c>
       <c r="N58" s="36">
         <v>22700</v>
@@ -7804,12 +7803,12 @@
       <c r="R58" s="35"/>
       <c r="S58" s="39"/>
       <c r="T58" s="38" t="s">
-        <v>447</v>
+        <v>786</v>
       </c>
     </row>
     <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="34" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B59" s="34" t="s">
         <v>59</v>
@@ -7827,7 +7826,7 @@
         <v>126</v>
       </c>
       <c r="G59" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H59" s="34" t="s">
         <v>63</v>
@@ -7836,36 +7835,36 @@
         <v>104</v>
       </c>
       <c r="J59" s="34" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="K59" s="34" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="L59" s="34"/>
       <c r="M59" s="35" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N59" s="36">
         <v>30254</v>
       </c>
       <c r="O59" s="34" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P59" s="34"/>
       <c r="Q59" s="34"/>
       <c r="R59" s="35" t="s">
+        <v>308</v>
+      </c>
+      <c r="S59" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="S59" s="39" t="s">
-        <v>310</v>
-      </c>
       <c r="T59" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B60" s="34" t="s">
         <v>59</v>
@@ -7883,45 +7882,45 @@
         <v>126</v>
       </c>
       <c r="G60" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H60" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I60" s="34" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J60" s="34" t="s">
         <v>79</v>
       </c>
       <c r="K60" s="34" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L60" s="34"/>
       <c r="M60" s="35" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N60" s="36">
         <v>27776</v>
       </c>
       <c r="O60" s="34" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P60" s="34"/>
       <c r="Q60" s="34"/>
       <c r="R60" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="S60" s="39" t="s">
         <v>305</v>
       </c>
-      <c r="S60" s="39" t="s">
-        <v>306</v>
-      </c>
       <c r="T60" s="38" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="34" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B61" s="34" t="s">
         <v>59</v>
@@ -7939,7 +7938,7 @@
         <v>126</v>
       </c>
       <c r="G61" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H61" s="34" t="s">
         <v>63</v>
@@ -7957,7 +7956,7 @@
         <v>69</v>
       </c>
       <c r="M61" s="35" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N61" s="36">
         <v>30538</v>
@@ -7968,12 +7967,12 @@
       <c r="R61" s="35"/>
       <c r="S61" s="39"/>
       <c r="T61" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="34" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B62" s="34" t="s">
         <v>59</v>
@@ -7991,13 +7990,13 @@
         <v>126</v>
       </c>
       <c r="G62" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H62" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I62" s="34" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J62" s="34" t="s">
         <v>80</v>
@@ -8009,7 +8008,7 @@
         <v>92</v>
       </c>
       <c r="M62" s="35" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="N62" s="36">
         <v>25896</v>
@@ -8020,12 +8019,12 @@
       <c r="R62" s="35"/>
       <c r="S62" s="39"/>
       <c r="T62" s="38" t="s">
-        <v>447</v>
+        <v>786</v>
       </c>
     </row>
     <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="34" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B63" s="34" t="s">
         <v>59</v>
@@ -8043,43 +8042,43 @@
         <v>126</v>
       </c>
       <c r="G63" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H63" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I63" s="34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J63" s="34" t="s">
         <v>65</v>
       </c>
       <c r="K63" s="34" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L63" s="34"/>
       <c r="M63" s="35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N63" s="36">
         <v>25993</v>
       </c>
       <c r="O63" s="34" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P63" s="34"/>
       <c r="Q63" s="34"/>
       <c r="R63" s="35" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="S63" s="39"/>
       <c r="T63" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="34" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B64" s="34" t="s">
         <v>59</v>
@@ -8097,7 +8096,7 @@
         <v>126</v>
       </c>
       <c r="G64" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H64" s="34" t="s">
         <v>63</v>
@@ -8109,33 +8108,33 @@
         <v>107</v>
       </c>
       <c r="K64" s="34" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L64" s="34"/>
       <c r="M64" s="35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N64" s="36">
         <v>25881</v>
       </c>
       <c r="O64" s="34" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P64" s="34"/>
       <c r="Q64" s="34"/>
       <c r="R64" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="S64" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="S64" s="39" t="s">
-        <v>155</v>
-      </c>
       <c r="T64" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="34" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B65" s="34" t="s">
         <v>59</v>
@@ -8153,47 +8152,47 @@
         <v>126</v>
       </c>
       <c r="G65" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H65" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I65" s="34" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J65" s="34" t="s">
         <v>73</v>
       </c>
       <c r="K65" s="34" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L65" s="34" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M65" s="35" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="N65" s="36">
         <v>30157</v>
       </c>
       <c r="O65" s="34" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P65" s="34"/>
       <c r="Q65" s="34"/>
       <c r="R65" s="35" t="s">
+        <v>396</v>
+      </c>
+      <c r="S65" s="39" t="s">
         <v>397</v>
       </c>
-      <c r="S65" s="39" t="s">
-        <v>398</v>
-      </c>
       <c r="T65" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="34" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B66" s="34" t="s">
         <v>59</v>
@@ -8211,45 +8210,45 @@
         <v>126</v>
       </c>
       <c r="G66" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H66" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I66" s="34" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J66" s="34" t="s">
         <v>73</v>
       </c>
       <c r="K66" s="34" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L66" s="34"/>
       <c r="M66" s="35" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="N66" s="36">
         <v>34772</v>
       </c>
       <c r="O66" s="34" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P66" s="34"/>
       <c r="Q66" s="34"/>
       <c r="R66" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="S66" s="39" t="s">
         <v>347</v>
       </c>
-      <c r="S66" s="39" t="s">
-        <v>348</v>
-      </c>
       <c r="T66" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="34" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B67" s="34" t="s">
         <v>59</v>
@@ -8267,45 +8266,45 @@
         <v>126</v>
       </c>
       <c r="G67" s="35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H67" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I67" s="35" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J67" s="35" t="s">
         <v>77</v>
       </c>
       <c r="K67" s="35" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L67" s="35"/>
       <c r="M67" s="35" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="N67" s="36">
         <v>23605</v>
       </c>
       <c r="O67" s="35" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P67" s="35"/>
       <c r="Q67" s="35"/>
       <c r="R67" s="35" t="s">
+        <v>338</v>
+      </c>
+      <c r="S67" s="37" t="s">
         <v>339</v>
       </c>
-      <c r="S67" s="37" t="s">
-        <v>340</v>
-      </c>
       <c r="T67" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="34" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B68" s="34" t="s">
         <v>59</v>
@@ -8323,7 +8322,7 @@
         <v>126</v>
       </c>
       <c r="G68" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H68" s="34" t="s">
         <v>63</v>
@@ -8335,33 +8334,33 @@
         <v>72</v>
       </c>
       <c r="K68" s="34" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L68" s="34"/>
       <c r="M68" s="35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N68" s="36">
         <v>22431</v>
       </c>
       <c r="O68" s="34" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P68" s="34"/>
       <c r="Q68" s="34"/>
       <c r="R68" s="35" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="S68" s="39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T68" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="34" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B69" s="34" t="s">
         <v>59</v>
@@ -8379,7 +8378,7 @@
         <v>126</v>
       </c>
       <c r="G69" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H69" s="34" t="s">
         <v>63</v>
@@ -8395,27 +8394,27 @@
       </c>
       <c r="L69" s="35"/>
       <c r="M69" s="35" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N69" s="36">
         <v>23105</v>
       </c>
       <c r="O69" s="34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
       <c r="R69" s="35" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="S69" s="35"/>
       <c r="T69" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="34" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B70" s="34" t="s">
         <v>59</v>
@@ -8433,7 +8432,7 @@
         <v>126</v>
       </c>
       <c r="G70" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H70" s="34" t="s">
         <v>63</v>
@@ -8449,27 +8448,27 @@
       </c>
       <c r="L70" s="35"/>
       <c r="M70" s="35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N70" s="36">
         <v>36383</v>
       </c>
       <c r="O70" s="34" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P70" s="35"/>
       <c r="Q70" s="35"/>
       <c r="R70" s="35" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="S70" s="35"/>
       <c r="T70" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B71" s="34" t="s">
         <v>59</v>
@@ -8487,7 +8486,7 @@
         <v>126</v>
       </c>
       <c r="G71" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H71" s="34" t="s">
         <v>63</v>
@@ -8503,27 +8502,27 @@
       </c>
       <c r="L71" s="35"/>
       <c r="M71" s="35" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N71" s="36">
         <v>33831</v>
       </c>
       <c r="O71" s="34" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P71" s="35"/>
       <c r="Q71" s="35"/>
       <c r="R71" s="35" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="S71" s="35"/>
       <c r="T71" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="34" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B72" s="34" t="s">
         <v>59</v>
@@ -8541,7 +8540,7 @@
         <v>126</v>
       </c>
       <c r="G72" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H72" s="34" t="s">
         <v>63</v>
@@ -8553,31 +8552,31 @@
         <v>84</v>
       </c>
       <c r="K72" s="35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L72" s="35"/>
       <c r="M72" s="35" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N72" s="36">
         <v>30287</v>
       </c>
       <c r="O72" s="34" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P72" s="35"/>
       <c r="Q72" s="35"/>
       <c r="R72" s="35" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="S72" s="35"/>
       <c r="T72" s="38" t="s">
-        <v>168</v>
+        <v>787</v>
       </c>
     </row>
     <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="34" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B73" s="34" t="s">
         <v>59</v>
@@ -8595,7 +8594,7 @@
         <v>126</v>
       </c>
       <c r="G73" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H73" s="34" t="s">
         <v>63</v>
@@ -8611,27 +8610,27 @@
       </c>
       <c r="L73" s="35"/>
       <c r="M73" s="35" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="N73" s="36">
         <v>26138</v>
       </c>
       <c r="O73" s="34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P73" s="35"/>
       <c r="Q73" s="35"/>
       <c r="R73" s="35" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="S73" s="35"/>
       <c r="T73" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B74" s="34" t="s">
         <v>59</v>
@@ -8649,7 +8648,7 @@
         <v>126</v>
       </c>
       <c r="G74" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H74" s="34" t="s">
         <v>63</v>
@@ -8665,27 +8664,27 @@
       </c>
       <c r="L74" s="35"/>
       <c r="M74" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N74" s="36">
         <v>32984</v>
       </c>
       <c r="O74" s="34" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P74" s="35"/>
       <c r="Q74" s="35"/>
       <c r="R74" s="35" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S74" s="35"/>
       <c r="T74" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="75" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="34" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B75" s="34" t="s">
         <v>59</v>
@@ -8703,45 +8702,45 @@
         <v>126</v>
       </c>
       <c r="G75" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H75" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I75" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="J75" s="35" t="s">
         <v>103</v>
       </c>
       <c r="K75" s="35" t="s">
+        <v>528</v>
+      </c>
+      <c r="L75" s="35" t="s">
         <v>529</v>
       </c>
-      <c r="L75" s="35" t="s">
+      <c r="M75" s="35" t="s">
         <v>530</v>
-      </c>
-      <c r="M75" s="35" t="s">
-        <v>531</v>
       </c>
       <c r="N75" s="36">
         <v>23098</v>
       </c>
       <c r="O75" s="34" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="P75" s="35"/>
       <c r="Q75" s="35"/>
       <c r="R75" s="35" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="S75" s="35"/>
       <c r="T75" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="76" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="34" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B76" s="34" t="s">
         <v>59</v>
@@ -8759,45 +8758,45 @@
         <v>126</v>
       </c>
       <c r="G76" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H76" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I76" s="35" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J76" s="35" t="s">
         <v>81</v>
       </c>
       <c r="K76" s="35" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L76" s="35"/>
       <c r="M76" s="35" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N76" s="36">
         <v>25389</v>
       </c>
       <c r="O76" s="34" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P76" s="35"/>
       <c r="Q76" s="35"/>
       <c r="R76" s="35" t="s">
+        <v>430</v>
+      </c>
+      <c r="S76" s="35" t="s">
         <v>431</v>
       </c>
-      <c r="S76" s="35" t="s">
-        <v>432</v>
-      </c>
       <c r="T76" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B77" s="34" t="s">
         <v>59</v>
@@ -8815,7 +8814,7 @@
         <v>126</v>
       </c>
       <c r="G77" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H77" s="34" t="s">
         <v>63</v>
@@ -8831,27 +8830,27 @@
       </c>
       <c r="L77" s="35"/>
       <c r="M77" s="35" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N77" s="36">
         <v>29006</v>
       </c>
       <c r="O77" s="34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P77" s="35"/>
       <c r="Q77" s="35"/>
       <c r="R77" s="35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S77" s="35"/>
       <c r="T77" s="38" t="s">
-        <v>168</v>
+        <v>787</v>
       </c>
     </row>
     <row r="78" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="34" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B78" s="34" t="s">
         <v>59</v>
@@ -8869,7 +8868,7 @@
         <v>126</v>
       </c>
       <c r="G78" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H78" s="34" t="s">
         <v>63</v>
@@ -8885,27 +8884,27 @@
       </c>
       <c r="L78" s="35"/>
       <c r="M78" s="35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N78" s="36">
         <v>21024</v>
       </c>
       <c r="O78" s="34" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
       <c r="R78" s="35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="S78" s="35"/>
       <c r="T78" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="34" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B79" s="34" t="s">
         <v>59</v>
@@ -8923,7 +8922,7 @@
         <v>126</v>
       </c>
       <c r="G79" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>63</v>
@@ -8935,31 +8934,31 @@
         <v>81</v>
       </c>
       <c r="K79" s="35" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L79" s="35"/>
       <c r="M79" s="35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N79" s="36">
         <v>19757</v>
       </c>
       <c r="O79" s="34" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
       <c r="R79" s="35" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S79" s="35"/>
       <c r="T79" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="34" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B80" s="34" t="s">
         <v>59</v>
@@ -8977,43 +8976,43 @@
         <v>126</v>
       </c>
       <c r="G80" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H80" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I80" s="35" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J80" s="35" t="s">
         <v>73</v>
       </c>
       <c r="K80" s="35" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="L80" s="35"/>
       <c r="M80" s="35" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N80" s="36">
         <v>30337</v>
       </c>
       <c r="O80" s="34" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
       <c r="R80" s="35" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="S80" s="35"/>
       <c r="T80" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B81" s="34" t="s">
         <v>59</v>
@@ -9031,25 +9030,25 @@
         <v>126</v>
       </c>
       <c r="G81" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H81" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I81" s="35" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J81" s="35" t="s">
         <v>65</v>
       </c>
       <c r="K81" s="35" t="s">
+        <v>384</v>
+      </c>
+      <c r="L81" s="35" t="s">
+        <v>384</v>
+      </c>
+      <c r="M81" s="35" t="s">
         <v>385</v>
-      </c>
-      <c r="L81" s="35" t="s">
-        <v>385</v>
-      </c>
-      <c r="M81" s="35" t="s">
-        <v>386</v>
       </c>
       <c r="N81" s="36">
         <v>29821</v>
@@ -9060,12 +9059,12 @@
       <c r="R81" s="35"/>
       <c r="S81" s="35"/>
       <c r="T81" s="38" t="s">
-        <v>447</v>
+        <v>786</v>
       </c>
     </row>
     <row r="82" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B82" s="34" t="s">
         <v>59</v>
@@ -9083,7 +9082,7 @@
         <v>126</v>
       </c>
       <c r="G82" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H82" s="34" t="s">
         <v>63</v>
@@ -9116,12 +9115,12 @@
         <v>137</v>
       </c>
       <c r="T82" s="38" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="34" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B83" s="34" t="s">
         <v>59</v>
@@ -9139,25 +9138,25 @@
         <v>126</v>
       </c>
       <c r="G83" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H83" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I83" s="35" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J83" s="35" t="s">
         <v>72</v>
       </c>
       <c r="K83" s="35" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L83" s="35" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M83" s="35" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N83" s="36">
         <v>24507</v>
@@ -9166,16 +9165,16 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
       <c r="R83" s="35" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="S83" s="35"/>
       <c r="T83" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="34" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B84" s="34" t="s">
         <v>59</v>
@@ -9193,7 +9192,7 @@
         <v>126</v>
       </c>
       <c r="G84" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H84" s="34" t="s">
         <v>63</v>
@@ -9205,33 +9204,33 @@
         <v>81</v>
       </c>
       <c r="K84" s="35" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="L84" s="35"/>
       <c r="M84" s="35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N84" s="36">
         <v>29328</v>
       </c>
       <c r="O84" s="34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
       <c r="R84" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="S84" s="35" t="s">
         <v>210</v>
       </c>
-      <c r="S84" s="35" t="s">
-        <v>211</v>
-      </c>
       <c r="T84" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85" spans="1:21" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="34" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B85" s="34" t="s">
         <v>59</v>
@@ -9249,7 +9248,7 @@
         <v>126</v>
       </c>
       <c r="G85" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H85" s="34" t="s">
         <v>63</v>
@@ -9258,33 +9257,33 @@
         <v>129</v>
       </c>
       <c r="J85" s="35" t="s">
+        <v>642</v>
+      </c>
+      <c r="K85" s="35" t="s">
         <v>643</v>
-      </c>
-      <c r="K85" s="35" t="s">
-        <v>644</v>
       </c>
       <c r="L85" s="35"/>
       <c r="M85" s="35" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="N85" s="36">
         <v>40905</v>
       </c>
       <c r="O85" s="34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
       <c r="R85" s="35"/>
       <c r="S85" s="35"/>
       <c r="T85" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="U85" s="27"/>
     </row>
     <row r="86" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B86" s="34" t="s">
         <v>59</v>
@@ -9302,7 +9301,7 @@
         <v>126</v>
       </c>
       <c r="G86" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H86" s="34" t="s">
         <v>63</v>
@@ -9318,29 +9317,29 @@
       </c>
       <c r="L86" s="35"/>
       <c r="M86" s="35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N86" s="36">
         <v>27907</v>
       </c>
       <c r="O86" s="34" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
       <c r="R86" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="S86" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="S86" s="35" t="s">
-        <v>163</v>
-      </c>
       <c r="T86" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="87" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="34" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B87" s="34" t="s">
         <v>59</v>
@@ -9358,45 +9357,45 @@
         <v>126</v>
       </c>
       <c r="G87" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I87" s="35" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J87" s="35" t="s">
         <v>117</v>
       </c>
       <c r="K87" s="35" t="s">
+        <v>519</v>
+      </c>
+      <c r="L87" s="35" t="s">
         <v>520</v>
       </c>
-      <c r="L87" s="35" t="s">
+      <c r="M87" s="35" t="s">
         <v>521</v>
       </c>
-      <c r="M87" s="35" t="s">
+      <c r="N87" s="36" t="s">
+        <v>674</v>
+      </c>
+      <c r="O87" s="34" t="s">
         <v>522</v>
-      </c>
-      <c r="N87" s="36" t="s">
-        <v>675</v>
-      </c>
-      <c r="O87" s="34" t="s">
-        <v>523</v>
       </c>
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
       <c r="R87" s="35" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="S87" s="35"/>
       <c r="T87" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="88" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="34" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B88" s="34" t="s">
         <v>59</v>
@@ -9414,43 +9413,43 @@
         <v>126</v>
       </c>
       <c r="G88" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H88" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I88" s="35" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J88" s="35" t="s">
         <v>80</v>
       </c>
       <c r="K88" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L88" s="35"/>
       <c r="M88" s="35" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N88" s="36">
         <v>23497</v>
       </c>
       <c r="O88" s="34" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
       <c r="R88" s="35" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="S88" s="35"/>
       <c r="T88" s="38" t="s">
-        <v>447</v>
+        <v>786</v>
       </c>
     </row>
     <row r="89" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="34" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B89" s="34" t="s">
         <v>59</v>
@@ -9468,45 +9467,45 @@
         <v>126</v>
       </c>
       <c r="G89" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H89" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I89" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="J89" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="K89" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="J89" s="35" t="s">
-        <v>284</v>
-      </c>
-      <c r="K89" s="35" t="s">
+      <c r="L89" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="L89" s="35" t="s">
+      <c r="M89" s="35" t="s">
         <v>477</v>
-      </c>
-      <c r="M89" s="35" t="s">
-        <v>478</v>
       </c>
       <c r="N89" s="36">
         <v>24537</v>
       </c>
       <c r="O89" s="34" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
       <c r="R89" s="35" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="S89" s="35"/>
       <c r="T89" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="90" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="35" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B90" s="34" t="s">
         <v>59</v>
@@ -9524,43 +9523,43 @@
         <v>126</v>
       </c>
       <c r="G90" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I90" s="34" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="J90" s="34" t="s">
         <v>84</v>
       </c>
       <c r="K90" s="34" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="L90" s="34"/>
       <c r="M90" s="35" t="s">
+        <v>733</v>
+      </c>
+      <c r="N90" s="36" t="s">
         <v>734</v>
       </c>
-      <c r="N90" s="36" t="s">
+      <c r="O90" s="34" t="s">
         <v>735</v>
-      </c>
-      <c r="O90" s="34" t="s">
-        <v>736</v>
       </c>
       <c r="P90" s="34"/>
       <c r="Q90" s="34"/>
       <c r="R90" s="35" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="S90" s="39"/>
       <c r="T90" s="38" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="91" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="34" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B91" s="34" t="s">
         <v>59</v>
@@ -9578,7 +9577,7 @@
         <v>126</v>
       </c>
       <c r="G91" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H91" s="34" t="s">
         <v>63</v>
@@ -9594,27 +9593,27 @@
       </c>
       <c r="L91" s="35"/>
       <c r="M91" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N91" s="36">
         <v>31298</v>
       </c>
       <c r="O91" s="34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
       <c r="R91" s="35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S91" s="35"/>
       <c r="T91" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="92" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B92" s="34" t="s">
         <v>59</v>
@@ -9632,7 +9631,7 @@
         <v>126</v>
       </c>
       <c r="G92" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H92" s="34" t="s">
         <v>63</v>
@@ -9648,27 +9647,27 @@
       </c>
       <c r="L92" s="35"/>
       <c r="M92" s="35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N92" s="36">
         <v>28101</v>
       </c>
       <c r="O92" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
       <c r="R92" s="35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S92" s="35"/>
       <c r="T92" s="38" t="s">
-        <v>168</v>
+        <v>787</v>
       </c>
     </row>
     <row r="93" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="34" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B93" s="34" t="s">
         <v>59</v>
@@ -9686,7 +9685,7 @@
         <v>126</v>
       </c>
       <c r="G93" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H93" s="34" t="s">
         <v>63</v>
@@ -9698,11 +9697,11 @@
         <v>79</v>
       </c>
       <c r="K93" s="35" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L93" s="35"/>
       <c r="M93" s="35" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N93" s="36">
         <v>30156</v>
@@ -9711,16 +9710,16 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
       <c r="R93" s="35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S93" s="35"/>
       <c r="T93" s="38" t="s">
-        <v>168</v>
+        <v>787</v>
       </c>
     </row>
     <row r="94" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="34" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B94" s="34" t="s">
         <v>59</v>
@@ -9735,46 +9734,46 @@
         <v>62</v>
       </c>
       <c r="F94" s="35" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G94" s="34" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H94" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I94" s="35" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="J94" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K94" s="35" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="L94" s="35"/>
       <c r="M94" s="35" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="N94" s="36">
         <v>33667</v>
       </c>
       <c r="O94" s="34" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
       <c r="R94" s="35" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="S94" s="35"/>
       <c r="T94" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="34" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B95" s="34" t="s">
         <v>59</v>
@@ -9792,43 +9791,43 @@
         <v>126</v>
       </c>
       <c r="G95" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H95" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I95" s="35" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J95" s="35" t="s">
         <v>72</v>
       </c>
       <c r="K95" s="35" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L95" s="35"/>
       <c r="M95" s="35" t="s">
+        <v>535</v>
+      </c>
+      <c r="N95" s="36" t="s">
         <v>536</v>
       </c>
-      <c r="N95" s="36" t="s">
+      <c r="O95" s="34" t="s">
         <v>537</v>
-      </c>
-      <c r="O95" s="34" t="s">
-        <v>538</v>
       </c>
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
       <c r="R95" s="35" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="S95" s="35"/>
       <c r="T95" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="34" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B96" s="34" t="s">
         <v>59</v>
@@ -9846,47 +9845,47 @@
         <v>126</v>
       </c>
       <c r="G96" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H96" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I96" s="35" t="s">
+        <v>480</v>
+      </c>
+      <c r="J96" s="35" t="s">
+        <v>394</v>
+      </c>
+      <c r="K96" s="35" t="s">
         <v>481</v>
       </c>
-      <c r="J96" s="35" t="s">
-        <v>395</v>
-      </c>
-      <c r="K96" s="35" t="s">
+      <c r="L96" s="35" t="s">
+        <v>394</v>
+      </c>
+      <c r="M96" s="35" t="s">
         <v>482</v>
-      </c>
-      <c r="L96" s="35" t="s">
-        <v>395</v>
-      </c>
-      <c r="M96" s="35" t="s">
-        <v>483</v>
       </c>
       <c r="N96" s="36">
         <v>34298</v>
       </c>
       <c r="O96" s="34" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
       <c r="R96" s="35" t="s">
+        <v>484</v>
+      </c>
+      <c r="S96" s="35" t="s">
         <v>485</v>
       </c>
-      <c r="S96" s="35" t="s">
-        <v>486</v>
-      </c>
       <c r="T96" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="97" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="34" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B97" s="34" t="s">
         <v>59</v>
@@ -9904,45 +9903,45 @@
         <v>126</v>
       </c>
       <c r="G97" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H97" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I97" s="35" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J97" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K97" s="35" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L97" s="35"/>
       <c r="M97" s="35" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N97" s="36">
         <v>29452</v>
       </c>
       <c r="O97" s="34" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
       <c r="R97" s="35" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="S97" s="35" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="T97" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="98" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="34" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B98" s="34" t="s">
         <v>59</v>
@@ -9957,48 +9956,48 @@
         <v>62</v>
       </c>
       <c r="F98" s="35" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G98" s="34" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H98" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I98" s="35" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J98" s="35" t="s">
         <v>70</v>
       </c>
       <c r="K98" s="35" t="s">
+        <v>358</v>
+      </c>
+      <c r="L98" s="35" t="s">
+        <v>667</v>
+      </c>
+      <c r="M98" s="35" t="s">
         <v>359</v>
       </c>
-      <c r="L98" s="35" t="s">
-        <v>668</v>
-      </c>
-      <c r="M98" s="35" t="s">
+      <c r="N98" s="36" t="s">
+        <v>675</v>
+      </c>
+      <c r="O98" s="34" t="s">
         <v>360</v>
-      </c>
-      <c r="N98" s="36" t="s">
-        <v>676</v>
-      </c>
-      <c r="O98" s="34" t="s">
-        <v>361</v>
       </c>
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
       <c r="R98" s="35" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="S98" s="35"/>
       <c r="T98" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="99" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="34" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B99" s="34" t="s">
         <v>59</v>
@@ -10016,43 +10015,43 @@
         <v>126</v>
       </c>
       <c r="G99" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H99" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I99" s="35" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="J99" s="35" t="s">
         <v>71</v>
       </c>
       <c r="K99" s="35" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L99" s="35"/>
       <c r="M99" s="35" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="N99" s="36">
         <v>32200</v>
       </c>
       <c r="O99" s="34" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
       <c r="R99" s="35" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="S99" s="35"/>
       <c r="T99" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="100" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="34" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B100" s="34" t="s">
         <v>59</v>
@@ -10070,43 +10069,43 @@
         <v>126</v>
       </c>
       <c r="G100" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H100" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I100" s="35" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="J100" s="35" t="s">
         <v>65</v>
       </c>
       <c r="K100" s="35" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="L100" s="35"/>
       <c r="M100" s="35" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N100" s="36">
         <v>28570</v>
       </c>
       <c r="O100" s="34" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
       <c r="R100" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S100" s="35"/>
       <c r="T100" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="34" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B101" s="34" t="s">
         <v>59</v>
@@ -10124,43 +10123,43 @@
         <v>126</v>
       </c>
       <c r="G101" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H101" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I101" s="35" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J101" s="35" t="s">
         <v>73</v>
       </c>
       <c r="K101" s="35" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="L101" s="35"/>
       <c r="M101" s="35" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="N101" s="36">
         <v>33544</v>
       </c>
       <c r="O101" s="34" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
       <c r="R101" s="35" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="S101" s="35"/>
       <c r="T101" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="102" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="34" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B102" s="34" t="s">
         <v>59</v>
@@ -10178,7 +10177,7 @@
         <v>126</v>
       </c>
       <c r="G102" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H102" s="34" t="s">
         <v>63</v>
@@ -10190,35 +10189,35 @@
         <v>84</v>
       </c>
       <c r="K102" s="35" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L102" s="35" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M102" s="35" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N102" s="36">
         <v>25204</v>
       </c>
       <c r="O102" s="34" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
       <c r="R102" s="35" t="s">
+        <v>401</v>
+      </c>
+      <c r="S102" s="35" t="s">
         <v>402</v>
       </c>
-      <c r="S102" s="35" t="s">
-        <v>403</v>
-      </c>
       <c r="T102" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="103" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="34" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B103" s="34" t="s">
         <v>59</v>
@@ -10236,7 +10235,7 @@
         <v>126</v>
       </c>
       <c r="G103" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H103" s="34" t="s">
         <v>63</v>
@@ -10252,25 +10251,25 @@
       </c>
       <c r="L103" s="35"/>
       <c r="M103" s="35" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N103" s="36">
         <v>26134</v>
       </c>
       <c r="O103" s="34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
       <c r="R103" s="35"/>
       <c r="S103" s="35"/>
       <c r="T103" s="38" t="s">
-        <v>168</v>
+        <v>787</v>
       </c>
     </row>
     <row r="104" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="34" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B104" s="34" t="s">
         <v>59</v>
@@ -10288,45 +10287,45 @@
         <v>126</v>
       </c>
       <c r="G104" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H104" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I104" s="35" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="J104" s="35" t="s">
         <v>107</v>
       </c>
       <c r="K104" s="35" t="s">
+        <v>592</v>
+      </c>
+      <c r="L104" s="35" t="s">
         <v>593</v>
       </c>
-      <c r="L104" s="35" t="s">
+      <c r="M104" s="35" t="s">
         <v>594</v>
-      </c>
-      <c r="M104" s="35" t="s">
-        <v>595</v>
       </c>
       <c r="N104" s="36">
         <v>31906</v>
       </c>
       <c r="O104" s="34" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
       <c r="R104" s="35" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="S104" s="35"/>
       <c r="T104" s="38" t="s">
-        <v>168</v>
+        <v>787</v>
       </c>
     </row>
     <row r="105" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="34" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B105" s="34" t="s">
         <v>59</v>
@@ -10341,46 +10340,46 @@
         <v>62</v>
       </c>
       <c r="F105" s="35" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G105" s="34" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H105" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I105" s="35" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="J105" s="35" t="s">
         <v>65</v>
       </c>
       <c r="K105" s="35" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="L105" s="35"/>
       <c r="M105" s="35" t="s">
+        <v>677</v>
+      </c>
+      <c r="N105" s="36" t="s">
         <v>678</v>
       </c>
-      <c r="N105" s="36" t="s">
-        <v>679</v>
-      </c>
       <c r="O105" s="34" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
       <c r="R105" s="35" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="S105" s="35"/>
       <c r="T105" s="38" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="106" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="34" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B106" s="34" t="s">
         <v>59</v>
@@ -10398,7 +10397,7 @@
         <v>126</v>
       </c>
       <c r="G106" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H106" s="34" t="s">
         <v>63</v>
@@ -10414,27 +10413,27 @@
       </c>
       <c r="L106" s="35"/>
       <c r="M106" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="N106" s="36" t="s">
+        <v>671</v>
+      </c>
+      <c r="O106" s="34" t="s">
         <v>176</v>
-      </c>
-      <c r="N106" s="36" t="s">
-        <v>672</v>
-      </c>
-      <c r="O106" s="34" t="s">
-        <v>177</v>
       </c>
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
       <c r="R106" s="35" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S106" s="35"/>
       <c r="T106" s="38" t="s">
-        <v>447</v>
+        <v>786</v>
       </c>
     </row>
     <row r="107" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="34" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B107" s="34" t="s">
         <v>59</v>
@@ -10452,45 +10451,45 @@
         <v>126</v>
       </c>
       <c r="G107" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H107" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I107" s="35" t="s">
+        <v>684</v>
+      </c>
+      <c r="J107" s="35" t="s">
+        <v>642</v>
+      </c>
+      <c r="K107" s="35" t="s">
         <v>685</v>
       </c>
-      <c r="J107" s="35" t="s">
-        <v>643</v>
-      </c>
-      <c r="K107" s="35" t="s">
+      <c r="L107" s="35" t="s">
         <v>686</v>
       </c>
-      <c r="L107" s="35" t="s">
+      <c r="M107" s="35" t="s">
+        <v>689</v>
+      </c>
+      <c r="N107" s="36" t="s">
+        <v>691</v>
+      </c>
+      <c r="O107" s="34" t="s">
         <v>687</v>
-      </c>
-      <c r="M107" s="35" t="s">
-        <v>690</v>
-      </c>
-      <c r="N107" s="36" t="s">
-        <v>692</v>
-      </c>
-      <c r="O107" s="34" t="s">
-        <v>688</v>
       </c>
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
       <c r="R107" s="35" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="S107" s="35"/>
       <c r="T107" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="108" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="34" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B108" s="34" t="s">
         <v>59</v>
@@ -10508,7 +10507,7 @@
         <v>126</v>
       </c>
       <c r="G108" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H108" s="34" t="s">
         <v>63</v>
@@ -10520,33 +10519,33 @@
         <v>70</v>
       </c>
       <c r="K108" s="35" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L108" s="35"/>
       <c r="M108" s="35" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N108" s="36">
         <v>26766</v>
       </c>
       <c r="O108" s="34" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
       <c r="R108" s="35" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="S108" s="35" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T108" s="38" t="s">
-        <v>497</v>
+        <v>785</v>
       </c>
     </row>
     <row r="109" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="34" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B109" s="34" t="s">
         <v>59</v>
@@ -10564,7 +10563,7 @@
         <v>126</v>
       </c>
       <c r="G109" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H109" s="34" t="s">
         <v>63</v>
@@ -10580,27 +10579,27 @@
       </c>
       <c r="L109" s="35"/>
       <c r="M109" s="35" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N109" s="36">
         <v>24263</v>
       </c>
       <c r="O109" s="34" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P109" s="35"/>
       <c r="Q109" s="35"/>
       <c r="R109" s="35" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="S109" s="35"/>
       <c r="T109" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="110" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="34" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B110" s="34" t="s">
         <v>59</v>
@@ -10618,19 +10617,19 @@
         <v>126</v>
       </c>
       <c r="G110" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H110" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I110" s="35" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="J110" s="35" t="s">
         <v>70</v>
       </c>
       <c r="K110" s="35" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="L110" s="35"/>
       <c r="M110" s="35"/>
@@ -10640,11 +10639,13 @@
       <c r="Q110" s="35"/>
       <c r="R110" s="35"/>
       <c r="S110" s="35"/>
-      <c r="T110" s="38"/>
+      <c r="T110" s="38" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="111" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="34" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B111" s="34" t="s">
         <v>59</v>
@@ -10662,19 +10663,19 @@
         <v>126</v>
       </c>
       <c r="G111" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I111" s="35" t="s">
-        <v>130</v>
+        <v>713</v>
       </c>
       <c r="J111" s="35" t="s">
-        <v>770</v>
+        <v>84</v>
       </c>
       <c r="K111" s="35" t="s">
-        <v>778</v>
+        <v>727</v>
       </c>
       <c r="L111" s="35"/>
       <c r="M111" s="35"/>
@@ -10684,11 +10685,13 @@
       <c r="Q111" s="35"/>
       <c r="R111" s="35"/>
       <c r="S111" s="35"/>
-      <c r="T111" s="38"/>
+      <c r="T111" s="38" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="112" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="34" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B112" s="34" t="s">
         <v>59</v>
@@ -10706,19 +10709,19 @@
         <v>126</v>
       </c>
       <c r="G112" s="34" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H112" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I112" s="35" t="s">
-        <v>714</v>
+        <v>769</v>
       </c>
       <c r="J112" s="35" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K112" s="35" t="s">
-        <v>728</v>
+        <v>776</v>
       </c>
       <c r="L112" s="35"/>
       <c r="M112" s="35"/>
@@ -10728,11 +10731,13 @@
       <c r="Q112" s="35"/>
       <c r="R112" s="35"/>
       <c r="S112" s="35"/>
-      <c r="T112" s="38"/>
+      <c r="T112" s="38" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="113" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="34" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B113" s="34" t="s">
         <v>59</v>
@@ -10744,25 +10749,25 @@
         <v>61</v>
       </c>
       <c r="E113" s="35" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F113" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G113" s="34" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="H113" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I113" s="35" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="J113" s="35" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K113" s="35" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="L113" s="35"/>
       <c r="M113" s="35"/>
@@ -10772,11 +10777,13 @@
       <c r="Q113" s="35"/>
       <c r="R113" s="35"/>
       <c r="S113" s="35"/>
-      <c r="T113" s="38"/>
+      <c r="T113" s="38" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="114" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="34" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B114" s="34" t="s">
         <v>59</v>
@@ -10788,25 +10795,25 @@
         <v>61</v>
       </c>
       <c r="E114" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F114" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G114" s="34" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="H114" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I114" s="35" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="J114" s="35" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K114" s="35" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="L114" s="35"/>
       <c r="M114" s="35"/>
@@ -10816,64 +10823,27 @@
       <c r="Q114" s="35"/>
       <c r="R114" s="35"/>
       <c r="S114" s="35"/>
-      <c r="T114" s="38"/>
+      <c r="T114" s="38" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="115" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="34" t="s">
-        <v>788</v>
-      </c>
-      <c r="B115" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C115" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D115" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="E115" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="F115" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G115" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="H115" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="I115" s="35" t="s">
-        <v>773</v>
-      </c>
-      <c r="J115" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="K115" s="35" t="s">
-        <v>781</v>
-      </c>
-      <c r="L115" s="35"/>
-      <c r="M115" s="35"/>
-      <c r="N115" s="36"/>
-      <c r="O115" s="34"/>
-      <c r="P115" s="35"/>
-      <c r="Q115" s="35"/>
-      <c r="R115" s="35"/>
-      <c r="S115" s="35"/>
-      <c r="T115" s="38"/>
+      <c r="T115" s="38" t="s">
+        <v>787</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" sort="0"/>
-  <autoFilter ref="A1:T110" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U114">
-    <sortCondition ref="I2:I17001"/>
-    <sortCondition ref="K2:K17001"/>
+  <autoFilter ref="A1:T115" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U113">
+    <sortCondition ref="I2:I17000"/>
+    <sortCondition ref="K2:K17000"/>
   </sortState>
   <phoneticPr fontId="31" type="noConversion"/>
-  <conditionalFormatting sqref="A116:A1048576 A1">
+  <conditionalFormatting sqref="A115:A1048576 A1">
     <cfRule type="duplicateValues" dxfId="14" priority="585"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H97 H105:H115">
+  <conditionalFormatting sqref="H2:H97 H105:H114">
     <cfRule type="containsText" dxfId="13" priority="16" operator="containsText" text="Inactive - ADS">
       <formula>NOT(ISERROR(SEARCH("Inactive - ADS",H2)))</formula>
     </cfRule>
@@ -10893,15 +10863,15 @@
       <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H101)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1 M116:M65095">
+  <conditionalFormatting sqref="M1 M115:M65094">
     <cfRule type="expression" dxfId="9" priority="582" stopIfTrue="1">
       <formula>LEN(M1)&lt;&gt;13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M97">
-    <cfRule type="duplicateValues" dxfId="8" priority="652"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="661"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M115">
+  <conditionalFormatting sqref="M2:M114">
     <cfRule type="expression" dxfId="7" priority="8">
       <formula>LEN(M2)&lt;13</formula>
     </cfRule>
@@ -10915,10 +10885,10 @@
   <conditionalFormatting sqref="M101:M104">
     <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M105:M115">
-    <cfRule type="duplicateValues" dxfId="3" priority="657"/>
+  <conditionalFormatting sqref="M105:M114">
+    <cfRule type="duplicateValues" dxfId="3" priority="667"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M116:M65095 M1">
+  <conditionalFormatting sqref="M115:M65094 M1">
     <cfRule type="duplicateValues" dxfId="2" priority="642" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11086,102 +11056,102 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B10"/>
       <c r="C10" s="31" t="s">
+        <v>566</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>567</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">

--- a/import-files/WC-CTN-O(1).xlsx
+++ b/import-files/WC-CTN-O(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Pictures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785F232C-5C2F-4A7D-87D9-FC2DF11BCD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCAC675-2707-47DC-8C2C-548BBBBB53D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Club Details" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Membership!$A$1:$T$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Membership!$A$1:$T$114</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="801">
   <si>
     <t>How To Complete/Update existing information.</t>
   </si>
@@ -1391,12 +1391,6 @@
     <t>6202235162084</t>
   </si>
   <si>
-    <t>DSA-120408</t>
-  </si>
-  <si>
-    <t>6506265181081</t>
-  </si>
-  <si>
     <t>DSA-121728</t>
   </si>
   <si>
@@ -1514,9 +1508,6 @@
     <t>Gavin</t>
   </si>
   <si>
-    <t>Joe</t>
-  </si>
-  <si>
     <t>DSA-180274</t>
   </si>
   <si>
@@ -1562,9 +1553,6 @@
     <t>DSA-123058</t>
   </si>
   <si>
-    <t>Talmarks</t>
-  </si>
-  <si>
     <t>Jade</t>
   </si>
   <si>
@@ -2033,9 +2021,6 @@
     <t>Titus</t>
   </si>
   <si>
-    <t>Eldridge</t>
-  </si>
-  <si>
     <t>Neville</t>
   </si>
   <si>
@@ -2375,9 +2360,6 @@
     <t>DSA-260117</t>
   </si>
   <si>
-    <t>Cheslin</t>
-  </si>
-  <si>
     <t>Cheezy</t>
   </si>
   <si>
@@ -2585,33 +2567,12 @@
     <t>Chesley</t>
   </si>
   <si>
-    <t>Micheal</t>
-  </si>
-  <si>
-    <t>Georgie</t>
-  </si>
-  <si>
     <t>Raymond</t>
   </si>
   <si>
     <t>V/D Westhuizen</t>
   </si>
   <si>
-    <t>DSA-100000</t>
-  </si>
-  <si>
-    <t>DSA-300000</t>
-  </si>
-  <si>
-    <t>DSA-400000</t>
-  </si>
-  <si>
-    <t>DSA-500000</t>
-  </si>
-  <si>
-    <t>DSA-600000</t>
-  </si>
-  <si>
     <t>Guardians</t>
   </si>
   <si>
@@ -2628,6 +2589,75 @@
   </si>
   <si>
     <t>4909035157088</t>
+  </si>
+  <si>
+    <t>DSA-220380</t>
+  </si>
+  <si>
+    <t>DSA-260508</t>
+  </si>
+  <si>
+    <t>DSA-260509</t>
+  </si>
+  <si>
+    <t>DSA-230265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgina </t>
+  </si>
+  <si>
+    <t>6404050131083</t>
+  </si>
+  <si>
+    <t>1964-04-05</t>
+  </si>
+  <si>
+    <t>23B Jasmine Street Bonteheuwel 7764</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>5705205196081</t>
+  </si>
+  <si>
+    <t>1957-05-20</t>
+  </si>
+  <si>
+    <t>6 Tottenham Close, London Village, Weltevreden Valley</t>
+  </si>
+  <si>
+    <t>0814055862</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>5503135006086</t>
+  </si>
+  <si>
+    <t>1955-03-13</t>
+  </si>
+  <si>
+    <t>32 Shepherd Way, Westridge, Mitchell's Plain</t>
+  </si>
+  <si>
+    <t>0679383734</t>
+  </si>
+  <si>
+    <t>7508195147082</t>
+  </si>
+  <si>
+    <t>1975-08-19</t>
+  </si>
+  <si>
+    <t>15 Bloubos Singel, Eastridge</t>
+  </si>
+  <si>
+    <t>0618527688</t>
+  </si>
+  <si>
+    <t>Cheslyn</t>
   </si>
 </sst>
 </file>
@@ -3080,12 +3110,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3100,6 +3124,12 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -3118,7 +3148,7 @@
     <cellStyle name="Normal 6" xfId="7" xr:uid="{787D59DA-ED81-4119-B772-4CD1818DC02D}"/>
     <cellStyle name="Normal 7" xfId="12" xr:uid="{93FD18A2-4F78-4C7B-91F3-95D146AE0B82}"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="18">
     <dxf>
       <font>
         <b/>
@@ -3192,13 +3222,11 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <color rgb="FFFF0000"/>
+        <color theme="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3209,6 +3237,28 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4147,7 +4197,7 @@
     <mergeCell ref="A22:B22"/>
   </mergeCells>
   <conditionalFormatting sqref="B16">
-    <cfRule type="containsText" dxfId="15" priority="1" stopIfTrue="1" operator="containsText" text="If a duplicate ID exist in the registration system, it will be RED with a light red background.">
+    <cfRule type="containsText" dxfId="17" priority="1" stopIfTrue="1" operator="containsText" text="If a duplicate ID exist in the registration system, it will be RED with a light red background.">
       <formula>NOT(ISERROR(SEARCH("If a duplicate ID exist in the registration system, it will be RED with a light red background.",B16)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4175,66 +4225,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
     </row>
     <row r="2" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>222</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
     </row>
     <row r="3" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
     </row>
     <row r="6" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
+      <c r="A6" s="45"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42" t="s">
+      <c r="B8" s="47"/>
+      <c r="C8" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="42"/>
+      <c r="D8" s="47"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
@@ -4327,20 +4377,20 @@
       <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42" t="s">
+      <c r="B18" s="47"/>
+      <c r="C18" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="42"/>
+      <c r="D18" s="47"/>
     </row>
     <row r="19" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
@@ -4445,20 +4495,20 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="43"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="42" t="s">
+      <c r="A28" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="42"/>
-      <c r="C28" s="42" t="s">
+      <c r="B28" s="47"/>
+      <c r="C28" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="42"/>
+      <c r="D28" s="47"/>
     </row>
     <row r="29" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
@@ -4570,12 +4620,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="A18:B18"/>
@@ -4584,6 +4628,12 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B26" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -4602,7 +4652,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:U115"/>
+  <dimension ref="A1:U124"/>
   <sheetFormatPr defaultColWidth="17.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" style="28" bestFit="1" customWidth="1"/>
@@ -4801,7 +4851,7 @@
     </row>
     <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B4" s="34" t="s">
         <v>59</v>
@@ -4831,22 +4881,22 @@
         <v>72</v>
       </c>
       <c r="K4" s="34" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="L4" s="34"/>
       <c r="M4" s="35" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="O4" s="34" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="P4" s="34"/>
       <c r="Q4" s="34"/>
       <c r="R4" s="35" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="S4" s="38"/>
       <c r="T4" s="38" t="s">
@@ -4855,7 +4905,7 @@
     </row>
     <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="B5" s="34" t="s">
         <v>59</v>
@@ -4885,11 +4935,11 @@
         <v>103</v>
       </c>
       <c r="K5" s="34" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="L5" s="34"/>
       <c r="M5" s="35" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="N5" s="36">
         <v>18144</v>
@@ -4905,7 +4955,7 @@
     </row>
     <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B6" s="34" t="s">
         <v>59</v>
@@ -4935,28 +4985,28 @@
         <v>71</v>
       </c>
       <c r="K6" s="35" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="L6" s="35" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="M6" s="35" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="N6" s="36">
         <v>34958</v>
       </c>
       <c r="O6" s="34" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="P6" s="35"/>
       <c r="Q6" s="35"/>
       <c r="R6" s="35" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="S6" s="35"/>
       <c r="T6" s="35" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -5069,7 +5119,7 @@
     </row>
     <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B9" s="34" t="s">
         <v>59</v>
@@ -5093,28 +5143,28 @@
         <v>63</v>
       </c>
       <c r="I9" s="35" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="J9" s="35" t="s">
         <v>72</v>
       </c>
       <c r="K9" s="35" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="L9" s="35"/>
       <c r="M9" s="35" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="N9" s="36" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="O9" s="34" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="P9" s="35"/>
       <c r="Q9" s="35"/>
       <c r="R9" s="35" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="S9" s="35"/>
       <c r="T9" s="38" t="s">
@@ -5123,7 +5173,7 @@
     </row>
     <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>59</v>
@@ -5147,28 +5197,28 @@
         <v>63</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="J10" s="34" t="s">
         <v>71</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="L10" s="34"/>
       <c r="M10" s="35" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="N10" s="36">
         <v>23651</v>
       </c>
       <c r="O10" s="34" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="P10" s="34"/>
       <c r="Q10" s="34"/>
       <c r="R10" s="35" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="S10" s="38"/>
       <c r="T10" s="38" t="s">
@@ -5222,7 +5272,7 @@
       <c r="P11" s="34"/>
       <c r="Q11" s="34"/>
       <c r="R11" s="34" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="S11" s="35"/>
       <c r="T11" s="38" t="s">
@@ -5231,7 +5281,7 @@
     </row>
     <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>59</v>
@@ -5255,33 +5305,33 @@
         <v>63</v>
       </c>
       <c r="I12" s="35" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="J12" s="35" t="s">
         <v>287</v>
       </c>
       <c r="K12" s="35" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="L12" s="35" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="M12" s="35" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="N12" s="36">
         <v>26677</v>
       </c>
       <c r="O12" s="34" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="P12" s="35"/>
       <c r="Q12" s="35"/>
       <c r="R12" s="35" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="S12" s="35" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="T12" s="38" t="s">
         <v>150</v>
@@ -5289,7 +5339,7 @@
     </row>
     <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>59</v>
@@ -5313,28 +5363,28 @@
         <v>63</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="J13" s="34" t="s">
         <v>287</v>
       </c>
       <c r="K13" s="34" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="L13" s="34"/>
       <c r="M13" s="35" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="N13" s="36" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="O13" s="34" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P13" s="34"/>
       <c r="Q13" s="34"/>
       <c r="R13" s="35" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="S13" s="39"/>
       <c r="T13" s="38" t="s">
@@ -5343,7 +5393,7 @@
     </row>
     <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>59</v>
@@ -5367,28 +5417,28 @@
         <v>63</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="J14" s="34" t="s">
         <v>103</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="35" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="N14" s="36" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="O14" s="34" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P14" s="34"/>
       <c r="Q14" s="34"/>
       <c r="R14" s="35" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="S14" s="39"/>
       <c r="T14" s="38" t="s">
@@ -5397,7 +5447,7 @@
     </row>
     <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>59</v>
@@ -5421,28 +5471,28 @@
         <v>63</v>
       </c>
       <c r="I15" s="34" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="J15" s="34" t="s">
         <v>71</v>
       </c>
       <c r="K15" s="34" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="35" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="O15" s="34" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P15" s="34"/>
       <c r="Q15" s="34"/>
       <c r="R15" s="35" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="S15" s="39"/>
       <c r="T15" s="38" t="s">
@@ -5451,7 +5501,7 @@
     </row>
     <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>59</v>
@@ -5475,28 +5525,28 @@
         <v>63</v>
       </c>
       <c r="I16" s="34" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="J16" s="34" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="K16" s="34" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="L16" s="34"/>
       <c r="M16" s="35" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="N16" s="36" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="O16" s="34" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="P16" s="34"/>
       <c r="Q16" s="34"/>
       <c r="R16" s="35" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="S16" s="39"/>
       <c r="T16" s="38" t="s">
@@ -5559,7 +5609,7 @@
     </row>
     <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
-        <v>378</v>
+        <v>441</v>
       </c>
       <c r="B18" s="34" t="s">
         <v>59</v>
@@ -5576,42 +5626,46 @@
       <c r="F18" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G18" s="34" t="s">
+      <c r="G18" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="H18" s="34" t="s">
+      <c r="H18" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="I18" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="J18" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="K18" s="34" t="s">
-        <v>419</v>
-      </c>
-      <c r="L18" s="34" t="s">
-        <v>419</v>
+      <c r="I18" s="35" t="s">
+        <v>436</v>
+      </c>
+      <c r="J18" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="K18" s="35" t="s">
+        <v>437</v>
+      </c>
+      <c r="L18" s="35" t="s">
+        <v>436</v>
       </c>
       <c r="M18" s="35" t="s">
-        <v>379</v>
+        <v>438</v>
       </c>
       <c r="N18" s="36">
-        <v>23919</v>
-      </c>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="39"/>
-      <c r="T18" s="38" t="s">
-        <v>786</v>
+        <v>28381</v>
+      </c>
+      <c r="O18" s="35" t="s">
+        <v>439</v>
+      </c>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="S18" s="37"/>
+      <c r="T18" s="37" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
-        <v>445</v>
+        <v>547</v>
       </c>
       <c r="B19" s="34" t="s">
         <v>59</v>
@@ -5628,46 +5682,42 @@
       <c r="F19" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G19" s="35" t="s">
+      <c r="G19" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="H19" s="35" t="s">
+      <c r="H19" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I19" s="35" t="s">
-        <v>440</v>
-      </c>
-      <c r="J19" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="K19" s="35" t="s">
-        <v>441</v>
-      </c>
-      <c r="L19" s="35" t="s">
-        <v>440</v>
-      </c>
+      <c r="I19" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="J19" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="K19" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="L19" s="34"/>
       <c r="M19" s="35" t="s">
-        <v>442</v>
+        <v>539</v>
       </c>
       <c r="N19" s="36">
-        <v>28381</v>
-      </c>
-      <c r="O19" s="35" t="s">
-        <v>443</v>
-      </c>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35" t="s">
-        <v>444</v>
-      </c>
-      <c r="S19" s="37"/>
-      <c r="T19" s="37" t="s">
-        <v>141</v>
+        <v>37912</v>
+      </c>
+      <c r="O19" s="34" t="s">
+        <v>538</v>
+      </c>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="39"/>
+      <c r="T19" s="38" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>551</v>
+        <v>289</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>59</v>
@@ -5694,32 +5744,36 @@
         <v>290</v>
       </c>
       <c r="J20" s="34" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="K20" s="34" t="s">
-        <v>541</v>
+        <v>291</v>
       </c>
       <c r="L20" s="34"/>
       <c r="M20" s="35" t="s">
-        <v>543</v>
+        <v>292</v>
       </c>
       <c r="N20" s="36">
-        <v>37912</v>
+        <v>23337</v>
       </c>
       <c r="O20" s="34" t="s">
-        <v>542</v>
+        <v>324</v>
       </c>
       <c r="P20" s="34"/>
       <c r="Q20" s="34"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="39"/>
+      <c r="R20" s="35" t="s">
+        <v>293</v>
+      </c>
+      <c r="S20" s="38" t="s">
+        <v>294</v>
+      </c>
       <c r="T20" s="38" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
-        <v>289</v>
+        <v>545</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>59</v>
@@ -5742,40 +5796,34 @@
       <c r="H21" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I21" s="34" t="s">
-        <v>290</v>
-      </c>
-      <c r="J21" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="K21" s="34" t="s">
-        <v>291</v>
-      </c>
-      <c r="L21" s="34"/>
+      <c r="I21" s="35" t="s">
+        <v>540</v>
+      </c>
+      <c r="J21" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="K21" s="35" t="s">
+        <v>541</v>
+      </c>
+      <c r="L21" s="35"/>
       <c r="M21" s="35" t="s">
-        <v>292</v>
+        <v>542</v>
       </c>
       <c r="N21" s="36">
-        <v>23337</v>
-      </c>
-      <c r="O21" s="34" t="s">
-        <v>324</v>
-      </c>
-      <c r="P21" s="34"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="S21" s="38" t="s">
-        <v>294</v>
-      </c>
+        <v>25927</v>
+      </c>
+      <c r="O21" s="34"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
       <c r="T21" s="38" t="s">
-        <v>150</v>
+        <v>561</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
-        <v>549</v>
+        <v>252</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>59</v>
@@ -5798,34 +5846,36 @@
       <c r="H22" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I22" s="35" t="s">
-        <v>544</v>
-      </c>
-      <c r="J22" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="K22" s="35" t="s">
-        <v>545</v>
-      </c>
-      <c r="L22" s="35"/>
+      <c r="I22" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="J22" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="K22" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="L22" s="34"/>
       <c r="M22" s="35" t="s">
-        <v>546</v>
+        <v>275</v>
       </c>
       <c r="N22" s="36">
-        <v>25927</v>
-      </c>
-      <c r="O22" s="34"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
+        <v>21575</v>
+      </c>
+      <c r="O22" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
       <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
+      <c r="S22" s="38"/>
       <c r="T22" s="38" t="s">
-        <v>565</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
-        <v>252</v>
+        <v>508</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>59</v>
@@ -5849,35 +5899,37 @@
         <v>63</v>
       </c>
       <c r="I23" s="34" t="s">
-        <v>99</v>
+        <v>509</v>
       </c>
       <c r="J23" s="34" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K23" s="34" t="s">
-        <v>100</v>
+        <v>510</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="35" t="s">
-        <v>275</v>
+        <v>511</v>
       </c>
       <c r="N23" s="36">
-        <v>21575</v>
+        <v>27616</v>
       </c>
       <c r="O23" s="34" t="s">
-        <v>171</v>
+        <v>512</v>
       </c>
       <c r="P23" s="34"/>
       <c r="Q23" s="34"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="38"/>
+      <c r="R23" s="35" t="s">
+        <v>513</v>
+      </c>
+      <c r="S23" s="39"/>
       <c r="T23" s="38" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="34" t="s">
-        <v>512</v>
+        <v>778</v>
       </c>
       <c r="B24" s="34" t="s">
         <v>59</v>
@@ -5889,49 +5941,47 @@
         <v>61</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F24" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H24" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I24" s="34" t="s">
-        <v>513</v>
+        <v>764</v>
       </c>
       <c r="J24" s="34" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K24" s="34" t="s">
-        <v>514</v>
+        <v>782</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="35" t="s">
-        <v>515</v>
-      </c>
-      <c r="N24" s="36">
-        <v>27616</v>
+        <v>783</v>
+      </c>
+      <c r="N24" s="36" t="s">
+        <v>784</v>
       </c>
       <c r="O24" s="34" t="s">
-        <v>516</v>
+        <v>785</v>
       </c>
       <c r="P24" s="34"/>
       <c r="Q24" s="34"/>
-      <c r="R24" s="35" t="s">
-        <v>517</v>
-      </c>
-      <c r="S24" s="39"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="38"/>
       <c r="T24" s="38" t="s">
-        <v>141</v>
+        <v>561</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="B25" s="34" t="s">
         <v>59</v>
@@ -5955,28 +6005,28 @@
         <v>63</v>
       </c>
       <c r="I25" s="34" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="J25" s="34" t="s">
         <v>72</v>
       </c>
       <c r="K25" s="34" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="L25" s="34"/>
       <c r="M25" s="35" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="N25" s="36" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="O25" s="34" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="P25" s="34"/>
       <c r="Q25" s="34"/>
       <c r="R25" s="35" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="S25" s="39"/>
       <c r="T25" s="38" t="s">
@@ -5985,7 +6035,7 @@
     </row>
     <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="B26" s="34" t="s">
         <v>59</v>
@@ -6009,28 +6059,28 @@
         <v>63</v>
       </c>
       <c r="I26" s="34" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="J26" s="34" t="s">
         <v>72</v>
       </c>
       <c r="K26" s="34" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="L26" s="34"/>
       <c r="M26" s="35" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="N26" s="36" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="O26" s="34" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="P26" s="34"/>
       <c r="Q26" s="34"/>
       <c r="R26" s="35" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="S26" s="39"/>
       <c r="T26" s="38" t="s">
@@ -6039,7 +6089,7 @@
     </row>
     <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B27" s="34" t="s">
         <v>59</v>
@@ -6075,18 +6125,18 @@
         <v>330</v>
       </c>
       <c r="M27" s="35" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="N27" s="36">
         <v>23057</v>
       </c>
       <c r="O27" s="35" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="35" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S27" s="37"/>
       <c r="T27" s="37" t="s">
@@ -6095,7 +6145,7 @@
     </row>
     <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="34" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B28" s="34" t="s">
         <v>59</v>
@@ -6119,34 +6169,34 @@
         <v>63</v>
       </c>
       <c r="I28" s="35" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="J28" s="35" t="s">
         <v>68</v>
       </c>
       <c r="K28" s="35" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="L28" s="35"/>
       <c r="M28" s="35" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="N28" s="36">
         <v>25256</v>
       </c>
       <c r="O28" s="35" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="35" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="S28" s="37" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="T28" s="37" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -6175,7 +6225,7 @@
         <v>63</v>
       </c>
       <c r="I29" s="35" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="J29" s="35" t="s">
         <v>73</v>
@@ -6184,25 +6234,25 @@
         <v>74</v>
       </c>
       <c r="L29" s="35" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="M29" s="35" t="s">
         <v>248</v>
       </c>
       <c r="N29" s="36" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="O29" s="34" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="P29" s="35"/>
       <c r="Q29" s="35"/>
       <c r="R29" s="35" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="S29" s="35"/>
       <c r="T29" s="38" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -6231,13 +6281,13 @@
         <v>63</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="J30" s="35" t="s">
         <v>103</v>
       </c>
       <c r="K30" s="35" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="L30" s="35"/>
       <c r="M30" s="35" t="s">
@@ -6263,7 +6313,7 @@
     </row>
     <row r="31" spans="1:20" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="35" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="B31" s="34" t="s">
         <v>59</v>
@@ -6287,28 +6337,28 @@
         <v>63</v>
       </c>
       <c r="I31" s="34" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="J31" s="34" t="s">
         <v>84</v>
       </c>
       <c r="K31" s="34" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="L31" s="34"/>
       <c r="M31" s="35" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="N31" s="36" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="O31" s="34" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="P31" s="34"/>
       <c r="Q31" s="34"/>
       <c r="R31" s="35" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="S31" s="39"/>
       <c r="T31" s="38" t="s">
@@ -6316,8 +6366,8 @@
       </c>
     </row>
     <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="34" t="s">
-        <v>425</v>
+      <c r="A32" s="35" t="s">
+        <v>747</v>
       </c>
       <c r="B32" s="34" t="s">
         <v>59</v>
@@ -6329,7 +6379,7 @@
         <v>61</v>
       </c>
       <c r="E32" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F32" s="35" t="s">
         <v>126</v>
@@ -6340,42 +6390,38 @@
       <c r="H32" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I32" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="J32" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="K32" s="35" t="s">
-        <v>409</v>
-      </c>
-      <c r="L32" s="35" t="s">
-        <v>409</v>
-      </c>
+      <c r="I32" s="34" t="s">
+        <v>707</v>
+      </c>
+      <c r="J32" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="K32" s="34" t="s">
+        <v>721</v>
+      </c>
+      <c r="L32" s="34"/>
       <c r="M32" s="35" t="s">
-        <v>410</v>
-      </c>
-      <c r="N32" s="36">
-        <v>30282</v>
+        <v>708</v>
+      </c>
+      <c r="N32" s="36" t="s">
+        <v>709</v>
       </c>
       <c r="O32" s="34" t="s">
-        <v>411</v>
-      </c>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
+        <v>710</v>
+      </c>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="34"/>
       <c r="R32" s="35" t="s">
-        <v>412</v>
-      </c>
-      <c r="S32" s="35" t="s">
-        <v>413</v>
-      </c>
+        <v>722</v>
+      </c>
+      <c r="S32" s="38"/>
       <c r="T32" s="38" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="34" t="s">
-        <v>254</v>
+      <c r="A33" s="35" t="s">
+        <v>779</v>
       </c>
       <c r="B33" s="34" t="s">
         <v>59</v>
@@ -6399,39 +6445,37 @@
         <v>63</v>
       </c>
       <c r="I33" s="35" t="s">
-        <v>127</v>
+        <v>763</v>
       </c>
       <c r="J33" s="35" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="K33" s="35" t="s">
-        <v>236</v>
+        <v>786</v>
       </c>
       <c r="L33" s="35"/>
       <c r="M33" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="N33" s="36">
-        <v>27970</v>
+        <v>787</v>
+      </c>
+      <c r="N33" s="36" t="s">
+        <v>788</v>
       </c>
       <c r="O33" s="34" t="s">
-        <v>201</v>
+        <v>789</v>
       </c>
       <c r="P33" s="35"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="S33" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="T33" s="38" t="s">
-        <v>204</v>
+        <v>790</v>
+      </c>
+      <c r="S33" s="35"/>
+      <c r="T33" s="35" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
-        <v>564</v>
+        <v>422</v>
       </c>
       <c r="B34" s="34" t="s">
         <v>59</v>
@@ -6443,7 +6487,7 @@
         <v>61</v>
       </c>
       <c r="E34" s="35" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F34" s="35" t="s">
         <v>126</v>
@@ -6455,37 +6499,41 @@
         <v>63</v>
       </c>
       <c r="I34" s="35" t="s">
-        <v>556</v>
+        <v>127</v>
       </c>
       <c r="J34" s="35" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="K34" s="35" t="s">
-        <v>557</v>
-      </c>
-      <c r="L34" s="35"/>
+        <v>407</v>
+      </c>
+      <c r="L34" s="35" t="s">
+        <v>407</v>
+      </c>
       <c r="M34" s="35" t="s">
-        <v>560</v>
-      </c>
-      <c r="N34" s="36" t="s">
-        <v>558</v>
+        <v>408</v>
+      </c>
+      <c r="N34" s="36">
+        <v>30282</v>
       </c>
       <c r="O34" s="34" t="s">
-        <v>559</v>
+        <v>409</v>
       </c>
       <c r="P34" s="35"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="35" t="s">
-        <v>620</v>
-      </c>
-      <c r="S34" s="35"/>
+        <v>410</v>
+      </c>
+      <c r="S34" s="35" t="s">
+        <v>411</v>
+      </c>
       <c r="T34" s="38" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="35" t="s">
-        <v>704</v>
+      <c r="A35" s="34" t="s">
+        <v>254</v>
       </c>
       <c r="B35" s="34" t="s">
         <v>59</v>
@@ -6509,37 +6557,39 @@
         <v>63</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>655</v>
+        <v>127</v>
       </c>
       <c r="J35" s="35" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K35" s="35" t="s">
-        <v>654</v>
+        <v>236</v>
       </c>
       <c r="L35" s="35"/>
       <c r="M35" s="35" t="s">
-        <v>646</v>
-      </c>
-      <c r="N35" s="36" t="s">
-        <v>650</v>
+        <v>200</v>
+      </c>
+      <c r="N35" s="36">
+        <v>27970</v>
       </c>
       <c r="O35" s="34" t="s">
-        <v>653</v>
+        <v>201</v>
       </c>
       <c r="P35" s="35"/>
       <c r="Q35" s="35"/>
       <c r="R35" s="35" t="s">
-        <v>656</v>
-      </c>
-      <c r="S35" s="35"/>
+        <v>202</v>
+      </c>
+      <c r="S35" s="35" t="s">
+        <v>203</v>
+      </c>
       <c r="T35" s="38" t="s">
-        <v>565</v>
+        <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
-        <v>631</v>
+        <v>560</v>
       </c>
       <c r="B36" s="34" t="s">
         <v>59</v>
@@ -6562,38 +6612,38 @@
       <c r="H36" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I36" s="34" t="s">
-        <v>495</v>
-      </c>
-      <c r="J36" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="K36" s="34" t="s">
-        <v>608</v>
-      </c>
-      <c r="L36" s="34"/>
+      <c r="I36" s="35" t="s">
+        <v>552</v>
+      </c>
+      <c r="J36" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="K36" s="35" t="s">
+        <v>553</v>
+      </c>
+      <c r="L36" s="35"/>
       <c r="M36" s="35" t="s">
-        <v>628</v>
-      </c>
-      <c r="N36" s="36">
-        <v>38935</v>
+        <v>556</v>
+      </c>
+      <c r="N36" s="36" t="s">
+        <v>554</v>
       </c>
       <c r="O36" s="34" t="s">
-        <v>609</v>
-      </c>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
+        <v>555</v>
+      </c>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35"/>
       <c r="R36" s="35" t="s">
-        <v>610</v>
-      </c>
-      <c r="S36" s="39"/>
+        <v>615</v>
+      </c>
+      <c r="S36" s="35"/>
       <c r="T36" s="38" t="s">
-        <v>785</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="34" t="s">
-        <v>662</v>
+      <c r="A37" s="35" t="s">
+        <v>699</v>
       </c>
       <c r="B37" s="34" t="s">
         <v>59</v>
@@ -6617,39 +6667,37 @@
         <v>63</v>
       </c>
       <c r="I37" s="35" t="s">
-        <v>495</v>
+        <v>650</v>
       </c>
       <c r="J37" s="35" t="s">
         <v>73</v>
       </c>
       <c r="K37" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="L37" s="35" t="s">
-        <v>663</v>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="L37" s="35"/>
       <c r="M37" s="35" t="s">
-        <v>664</v>
+        <v>641</v>
       </c>
       <c r="N37" s="36" t="s">
-        <v>673</v>
+        <v>645</v>
       </c>
       <c r="O37" s="34" t="s">
-        <v>609</v>
+        <v>648</v>
       </c>
       <c r="P37" s="35"/>
       <c r="Q37" s="35"/>
       <c r="R37" s="35" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="S37" s="35"/>
       <c r="T37" s="38" t="s">
-        <v>785</v>
+        <v>561</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="34" t="s">
-        <v>243</v>
+        <v>626</v>
       </c>
       <c r="B38" s="34" t="s">
         <v>59</v>
@@ -6673,37 +6721,37 @@
         <v>63</v>
       </c>
       <c r="I38" s="34" t="s">
-        <v>83</v>
+        <v>491</v>
       </c>
       <c r="J38" s="34" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="K38" s="34" t="s">
-        <v>85</v>
+        <v>603</v>
       </c>
       <c r="L38" s="34"/>
       <c r="M38" s="35" t="s">
-        <v>273</v>
+        <v>623</v>
       </c>
       <c r="N38" s="36">
-        <v>27347</v>
+        <v>38935</v>
       </c>
       <c r="O38" s="34" t="s">
-        <v>142</v>
+        <v>604</v>
       </c>
       <c r="P38" s="34"/>
       <c r="Q38" s="34"/>
       <c r="R38" s="35" t="s">
-        <v>143</v>
+        <v>605</v>
       </c>
       <c r="S38" s="39"/>
       <c r="T38" s="38" t="s">
-        <v>141</v>
+        <v>772</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="35" t="s">
-        <v>754</v>
+      <c r="A39" s="34" t="s">
+        <v>657</v>
       </c>
       <c r="B39" s="34" t="s">
         <v>59</v>
@@ -6726,40 +6774,40 @@
       <c r="H39" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I39" s="34" t="s">
-        <v>767</v>
-      </c>
-      <c r="J39" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="K39" s="34" t="s">
-        <v>706</v>
-      </c>
-      <c r="L39" s="34" t="s">
-        <v>707</v>
+      <c r="I39" s="35" t="s">
+        <v>491</v>
+      </c>
+      <c r="J39" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="K39" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="L39" s="35" t="s">
+        <v>658</v>
       </c>
       <c r="M39" s="35" t="s">
-        <v>708</v>
+        <v>659</v>
       </c>
       <c r="N39" s="36" t="s">
-        <v>709</v>
+        <v>668</v>
       </c>
       <c r="O39" s="34" t="s">
-        <v>710</v>
-      </c>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
+        <v>604</v>
+      </c>
+      <c r="P39" s="35"/>
+      <c r="Q39" s="35"/>
       <c r="R39" s="35" t="s">
-        <v>711</v>
-      </c>
-      <c r="S39" s="39"/>
+        <v>660</v>
+      </c>
+      <c r="S39" s="35"/>
       <c r="T39" s="38" t="s">
-        <v>787</v>
+        <v>772</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="34" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B40" s="34" t="s">
         <v>59</v>
@@ -6782,38 +6830,38 @@
       <c r="H40" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I40" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="J40" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="K40" s="35" t="s">
-        <v>772</v>
-      </c>
-      <c r="L40" s="35"/>
+      <c r="I40" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="J40" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="K40" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="L40" s="34"/>
       <c r="M40" s="35" t="s">
-        <v>217</v>
+        <v>273</v>
       </c>
       <c r="N40" s="36">
-        <v>22941</v>
+        <v>27347</v>
       </c>
       <c r="O40" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="P40" s="35"/>
-      <c r="Q40" s="35"/>
+        <v>142</v>
+      </c>
+      <c r="P40" s="34"/>
+      <c r="Q40" s="34"/>
       <c r="R40" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="S40" s="35"/>
+        <v>143</v>
+      </c>
+      <c r="S40" s="39"/>
       <c r="T40" s="38" t="s">
-        <v>204</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="34" t="s">
-        <v>597</v>
+      <c r="A41" s="35" t="s">
+        <v>748</v>
       </c>
       <c r="B41" s="34" t="s">
         <v>59</v>
@@ -6836,38 +6884,40 @@
       <c r="H41" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I41" s="35" t="s">
-        <v>598</v>
-      </c>
-      <c r="J41" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="K41" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="L41" s="35"/>
+      <c r="I41" s="34" t="s">
+        <v>761</v>
+      </c>
+      <c r="J41" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="K41" s="34" t="s">
+        <v>800</v>
+      </c>
+      <c r="L41" s="34" t="s">
+        <v>701</v>
+      </c>
       <c r="M41" s="35" t="s">
-        <v>599</v>
-      </c>
-      <c r="N41" s="36">
-        <v>30209</v>
+        <v>702</v>
+      </c>
+      <c r="N41" s="36" t="s">
+        <v>703</v>
       </c>
       <c r="O41" s="34" t="s">
-        <v>600</v>
-      </c>
-      <c r="P41" s="35"/>
-      <c r="Q41" s="35"/>
+        <v>704</v>
+      </c>
+      <c r="P41" s="34"/>
+      <c r="Q41" s="34"/>
       <c r="R41" s="35" t="s">
-        <v>601</v>
-      </c>
-      <c r="S41" s="35"/>
+        <v>705</v>
+      </c>
+      <c r="S41" s="39"/>
       <c r="T41" s="38" t="s">
-        <v>141</v>
+        <v>774</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="35" t="s">
-        <v>705</v>
+      <c r="A42" s="34" t="s">
+        <v>249</v>
       </c>
       <c r="B42" s="34" t="s">
         <v>59</v>
@@ -6891,37 +6941,37 @@
         <v>63</v>
       </c>
       <c r="I42" s="35" t="s">
-        <v>647</v>
+        <v>133</v>
       </c>
       <c r="J42" s="35" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K42" s="35" t="s">
-        <v>648</v>
+        <v>766</v>
       </c>
       <c r="L42" s="35"/>
       <c r="M42" s="35" t="s">
-        <v>649</v>
-      </c>
-      <c r="N42" s="36" t="s">
-        <v>651</v>
+        <v>217</v>
+      </c>
+      <c r="N42" s="36">
+        <v>22941</v>
       </c>
       <c r="O42" s="34" t="s">
-        <v>652</v>
+        <v>218</v>
       </c>
       <c r="P42" s="35"/>
       <c r="Q42" s="35"/>
       <c r="R42" s="35" t="s">
-        <v>657</v>
+        <v>219</v>
       </c>
       <c r="S42" s="35"/>
       <c r="T42" s="38" t="s">
-        <v>565</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="34" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
       <c r="B43" s="34" t="s">
         <v>59</v>
@@ -6933,51 +6983,49 @@
         <v>61</v>
       </c>
       <c r="E43" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F43" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G43" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="H43" s="35" t="s">
+      <c r="G43" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="H43" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I43" s="35" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="J43" s="35" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K43" s="35" t="s">
-        <v>577</v>
-      </c>
-      <c r="L43" s="35" t="s">
-        <v>578</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="L43" s="35"/>
       <c r="M43" s="35" t="s">
-        <v>579</v>
+        <v>594</v>
       </c>
       <c r="N43" s="36">
-        <v>23292</v>
-      </c>
-      <c r="O43" s="35" t="s">
-        <v>580</v>
+        <v>30209</v>
+      </c>
+      <c r="O43" s="34" t="s">
+        <v>595</v>
       </c>
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
       <c r="R43" s="35" t="s">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="S43" s="35"/>
-      <c r="T43" s="35" t="s">
-        <v>565</v>
+      <c r="T43" s="38" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="34" t="s">
-        <v>632</v>
+      <c r="A44" s="35" t="s">
+        <v>700</v>
       </c>
       <c r="B44" s="34" t="s">
         <v>59</v>
@@ -6989,54 +7037,49 @@
         <v>61</v>
       </c>
       <c r="E44" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F44" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G44" s="34" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="H44" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I44" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="J44" s="34" t="s">
+      <c r="I44" s="35" t="s">
+        <v>642</v>
+      </c>
+      <c r="J44" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="K44" s="34" t="s">
-        <v>587</v>
-      </c>
-      <c r="L44" s="34" t="s">
-        <v>588</v>
-      </c>
+      <c r="K44" s="35" t="s">
+        <v>643</v>
+      </c>
+      <c r="L44" s="35"/>
       <c r="M44" s="35" t="s">
-        <v>589</v>
-      </c>
-      <c r="N44" s="36">
-        <v>29846</v>
+        <v>644</v>
+      </c>
+      <c r="N44" s="36" t="s">
+        <v>646</v>
       </c>
       <c r="O44" s="34" t="s">
-        <v>572</v>
-      </c>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="34"/>
+        <v>647</v>
+      </c>
+      <c r="P44" s="35"/>
+      <c r="Q44" s="35"/>
       <c r="R44" s="35" t="s">
-        <v>566</v>
-      </c>
-      <c r="S44" s="39" t="s">
-        <v>590</v>
-      </c>
+        <v>652</v>
+      </c>
+      <c r="S44" s="35"/>
       <c r="T44" s="38" t="s">
-        <v>565</v>
-      </c>
-      <c r="U44" s="32"/>
+        <v>561</v>
+      </c>
     </row>
     <row r="45" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="34" t="s">
-        <v>285</v>
+        <v>571</v>
       </c>
       <c r="B45" s="34" t="s">
         <v>59</v>
@@ -7048,49 +7091,51 @@
         <v>61</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F45" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G45" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="H45" s="34" t="s">
+      <c r="G45" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="H45" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="I45" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="J45" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="K45" s="34" t="s">
-        <v>765</v>
-      </c>
-      <c r="L45" s="34"/>
+      <c r="I45" s="35" t="s">
+        <v>572</v>
+      </c>
+      <c r="J45" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="K45" s="35" t="s">
+        <v>573</v>
+      </c>
+      <c r="L45" s="35" t="s">
+        <v>574</v>
+      </c>
       <c r="M45" s="35" t="s">
-        <v>277</v>
+        <v>575</v>
       </c>
       <c r="N45" s="36">
-        <v>26758</v>
-      </c>
-      <c r="O45" s="34" t="s">
-        <v>278</v>
-      </c>
-      <c r="P45" s="34"/>
-      <c r="Q45" s="34"/>
+        <v>23292</v>
+      </c>
+      <c r="O45" s="35" t="s">
+        <v>576</v>
+      </c>
+      <c r="P45" s="35"/>
+      <c r="Q45" s="35"/>
       <c r="R45" s="35" t="s">
-        <v>279</v>
-      </c>
-      <c r="S45" s="39"/>
-      <c r="T45" s="38" t="s">
-        <v>180</v>
+        <v>577</v>
+      </c>
+      <c r="S45" s="35"/>
+      <c r="T45" s="35" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="34" t="s">
-        <v>464</v>
+        <v>627</v>
       </c>
       <c r="B46" s="34" t="s">
         <v>59</v>
@@ -7102,13 +7147,13 @@
         <v>61</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F46" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G46" s="34" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H46" s="34" t="s">
         <v>63</v>
@@ -7117,36 +7162,39 @@
         <v>328</v>
       </c>
       <c r="J46" s="34" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K46" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="L46" s="34"/>
+        <v>583</v>
+      </c>
+      <c r="L46" s="34" t="s">
+        <v>584</v>
+      </c>
       <c r="M46" s="35" t="s">
-        <v>465</v>
+        <v>585</v>
       </c>
       <c r="N46" s="36">
-        <v>31066</v>
+        <v>29846</v>
       </c>
       <c r="O46" s="34" t="s">
-        <v>466</v>
+        <v>568</v>
       </c>
       <c r="P46" s="34"/>
       <c r="Q46" s="34"/>
       <c r="R46" s="35" t="s">
-        <v>506</v>
+        <v>562</v>
       </c>
       <c r="S46" s="39" t="s">
-        <v>467</v>
+        <v>586</v>
       </c>
       <c r="T46" s="38" t="s">
-        <v>785</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="U46" s="32"/>
     </row>
     <row r="47" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="34" t="s">
-        <v>568</v>
+        <v>285</v>
       </c>
       <c r="B47" s="34" t="s">
         <v>59</v>
@@ -7173,38 +7221,34 @@
         <v>328</v>
       </c>
       <c r="J47" s="34" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="K47" s="34" t="s">
-        <v>569</v>
-      </c>
-      <c r="L47" s="34" t="s">
-        <v>570</v>
-      </c>
+        <v>759</v>
+      </c>
+      <c r="L47" s="34"/>
       <c r="M47" s="35" t="s">
-        <v>571</v>
+        <v>277</v>
       </c>
       <c r="N47" s="36">
-        <v>27169</v>
+        <v>26758</v>
       </c>
       <c r="O47" s="34" t="s">
-        <v>572</v>
+        <v>278</v>
       </c>
       <c r="P47" s="34"/>
       <c r="Q47" s="34"/>
       <c r="R47" s="35" t="s">
-        <v>573</v>
-      </c>
-      <c r="S47" s="39" t="s">
-        <v>574</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="S47" s="39"/>
       <c r="T47" s="38" t="s">
-        <v>565</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="34" t="s">
-        <v>387</v>
+        <v>460</v>
       </c>
       <c r="B48" s="34" t="s">
         <v>59</v>
@@ -7228,35 +7272,39 @@
         <v>63</v>
       </c>
       <c r="I48" s="34" t="s">
-        <v>388</v>
+        <v>328</v>
       </c>
       <c r="J48" s="34" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K48" s="34" t="s">
-        <v>389</v>
-      </c>
-      <c r="L48" s="34" t="s">
-        <v>389</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="L48" s="34"/>
       <c r="M48" s="35" t="s">
-        <v>390</v>
+        <v>461</v>
       </c>
       <c r="N48" s="36">
-        <v>25576</v>
-      </c>
-      <c r="O48" s="34"/>
+        <v>31066</v>
+      </c>
+      <c r="O48" s="34" t="s">
+        <v>462</v>
+      </c>
       <c r="P48" s="34"/>
       <c r="Q48" s="34"/>
-      <c r="R48" s="35"/>
-      <c r="S48" s="39"/>
+      <c r="R48" s="35" t="s">
+        <v>502</v>
+      </c>
+      <c r="S48" s="39" t="s">
+        <v>463</v>
+      </c>
       <c r="T48" s="38" t="s">
-        <v>150</v>
+        <v>772</v>
       </c>
     </row>
     <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="34" t="s">
-        <v>295</v>
+        <v>564</v>
       </c>
       <c r="B49" s="34" t="s">
         <v>59</v>
@@ -7280,39 +7328,41 @@
         <v>63</v>
       </c>
       <c r="I49" s="34" t="s">
-        <v>121</v>
+        <v>328</v>
       </c>
       <c r="J49" s="34" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="K49" s="34" t="s">
-        <v>764</v>
-      </c>
-      <c r="L49" s="34"/>
+        <v>565</v>
+      </c>
+      <c r="L49" s="34" t="s">
+        <v>566</v>
+      </c>
       <c r="M49" s="35" t="s">
-        <v>296</v>
+        <v>567</v>
       </c>
       <c r="N49" s="36">
-        <v>23532</v>
+        <v>27169</v>
       </c>
       <c r="O49" s="34" t="s">
-        <v>297</v>
+        <v>568</v>
       </c>
       <c r="P49" s="34"/>
       <c r="Q49" s="34"/>
       <c r="R49" s="35" t="s">
-        <v>298</v>
+        <v>569</v>
       </c>
       <c r="S49" s="39" t="s">
-        <v>299</v>
+        <v>570</v>
       </c>
       <c r="T49" s="38" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="34" t="s">
-        <v>633</v>
+        <v>385</v>
       </c>
       <c r="B50" s="34" t="s">
         <v>59</v>
@@ -7336,41 +7386,35 @@
         <v>63</v>
       </c>
       <c r="I50" s="34" t="s">
-        <v>121</v>
+        <v>386</v>
       </c>
       <c r="J50" s="34" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K50" s="34" t="s">
-        <v>102</v>
+        <v>387</v>
       </c>
       <c r="L50" s="34" t="s">
-        <v>582</v>
+        <v>387</v>
       </c>
       <c r="M50" s="35" t="s">
-        <v>583</v>
+        <v>388</v>
       </c>
       <c r="N50" s="36">
-        <v>24574</v>
-      </c>
-      <c r="O50" s="34" t="s">
-        <v>584</v>
-      </c>
+        <v>25576</v>
+      </c>
+      <c r="O50" s="34"/>
       <c r="P50" s="34"/>
       <c r="Q50" s="34"/>
-      <c r="R50" s="35" t="s">
-        <v>585</v>
-      </c>
-      <c r="S50" s="39" t="s">
-        <v>586</v>
-      </c>
+      <c r="R50" s="35"/>
+      <c r="S50" s="39"/>
       <c r="T50" s="38" t="s">
-        <v>565</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="34" t="s">
-        <v>692</v>
+        <v>295</v>
       </c>
       <c r="B51" s="34" t="s">
         <v>59</v>
@@ -7388,7 +7432,7 @@
         <v>126</v>
       </c>
       <c r="G51" s="34" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="H51" s="34" t="s">
         <v>63</v>
@@ -7397,36 +7441,36 @@
         <v>121</v>
       </c>
       <c r="J51" s="34" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K51" s="34" t="s">
-        <v>457</v>
-      </c>
-      <c r="L51" s="34" t="s">
-        <v>693</v>
-      </c>
+        <v>758</v>
+      </c>
+      <c r="L51" s="34"/>
       <c r="M51" s="35" t="s">
-        <v>694</v>
+        <v>296</v>
       </c>
       <c r="N51" s="36">
-        <v>20073</v>
+        <v>23532</v>
       </c>
       <c r="O51" s="34" t="s">
-        <v>695</v>
+        <v>297</v>
       </c>
       <c r="P51" s="34"/>
       <c r="Q51" s="34"/>
       <c r="R51" s="35" t="s">
-        <v>696</v>
-      </c>
-      <c r="S51" s="39"/>
+        <v>298</v>
+      </c>
+      <c r="S51" s="39" t="s">
+        <v>299</v>
+      </c>
       <c r="T51" s="38" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="34" t="s">
-        <v>552</v>
+        <v>628</v>
       </c>
       <c r="B52" s="34" t="s">
         <v>59</v>
@@ -7453,32 +7497,38 @@
         <v>121</v>
       </c>
       <c r="J52" s="34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K52" s="34" t="s">
-        <v>539</v>
-      </c>
-      <c r="L52" s="34"/>
+        <v>102</v>
+      </c>
+      <c r="L52" s="34" t="s">
+        <v>578</v>
+      </c>
       <c r="M52" s="35" t="s">
-        <v>540</v>
+        <v>579</v>
       </c>
       <c r="N52" s="36">
-        <v>40077</v>
+        <v>24574</v>
       </c>
       <c r="O52" s="34" t="s">
-        <v>332</v>
+        <v>580</v>
       </c>
       <c r="P52" s="34"/>
       <c r="Q52" s="34"/>
-      <c r="R52" s="35"/>
-      <c r="S52" s="39"/>
+      <c r="R52" s="35" t="s">
+        <v>581</v>
+      </c>
+      <c r="S52" s="39" t="s">
+        <v>582</v>
+      </c>
       <c r="T52" s="38" t="s">
-        <v>204</v>
+        <v>561</v>
       </c>
     </row>
     <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="34" t="s">
-        <v>244</v>
+        <v>687</v>
       </c>
       <c r="B53" s="34" t="s">
         <v>59</v>
@@ -7496,43 +7546,45 @@
         <v>126</v>
       </c>
       <c r="G53" s="34" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H53" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I53" s="34" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J53" s="34" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="K53" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="L53" s="34"/>
+        <v>453</v>
+      </c>
+      <c r="L53" s="34" t="s">
+        <v>688</v>
+      </c>
       <c r="M53" s="35" t="s">
-        <v>183</v>
+        <v>689</v>
       </c>
       <c r="N53" s="36">
-        <v>24906</v>
+        <v>20073</v>
       </c>
       <c r="O53" s="34" t="s">
-        <v>184</v>
+        <v>690</v>
       </c>
       <c r="P53" s="34"/>
       <c r="Q53" s="34"/>
       <c r="R53" s="35" t="s">
-        <v>185</v>
+        <v>691</v>
       </c>
       <c r="S53" s="39"/>
       <c r="T53" s="38" t="s">
-        <v>180</v>
+        <v>561</v>
       </c>
     </row>
     <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="34" t="s">
-        <v>468</v>
+        <v>548</v>
       </c>
       <c r="B54" s="34" t="s">
         <v>59</v>
@@ -7556,39 +7608,35 @@
         <v>63</v>
       </c>
       <c r="I54" s="34" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="J54" s="34" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K54" s="34" t="s">
-        <v>469</v>
+        <v>535</v>
       </c>
       <c r="L54" s="34"/>
       <c r="M54" s="35" t="s">
-        <v>470</v>
+        <v>536</v>
       </c>
       <c r="N54" s="36">
-        <v>23023</v>
+        <v>40077</v>
       </c>
       <c r="O54" s="34" t="s">
-        <v>471</v>
+        <v>332</v>
       </c>
       <c r="P54" s="34"/>
       <c r="Q54" s="34"/>
-      <c r="R54" s="35" t="s">
-        <v>623</v>
-      </c>
-      <c r="S54" s="39" t="s">
-        <v>472</v>
-      </c>
+      <c r="R54" s="35"/>
+      <c r="S54" s="39"/>
       <c r="T54" s="38" t="s">
-        <v>785</v>
+        <v>204</v>
       </c>
     </row>
     <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="34" t="s">
-        <v>349</v>
+        <v>244</v>
       </c>
       <c r="B55" s="34" t="s">
         <v>59</v>
@@ -7612,39 +7660,37 @@
         <v>63</v>
       </c>
       <c r="I55" s="34" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="J55" s="34" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="K55" s="34" t="s">
-        <v>340</v>
+        <v>116</v>
       </c>
       <c r="L55" s="34"/>
       <c r="M55" s="35" t="s">
-        <v>350</v>
+        <v>183</v>
       </c>
       <c r="N55" s="36">
-        <v>23467</v>
+        <v>24906</v>
       </c>
       <c r="O55" s="34" t="s">
-        <v>341</v>
+        <v>184</v>
       </c>
       <c r="P55" s="34"/>
       <c r="Q55" s="34"/>
       <c r="R55" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="S55" s="39" t="s">
-        <v>343</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="S55" s="39"/>
       <c r="T55" s="38" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="34" t="s">
-        <v>510</v>
+        <v>464</v>
       </c>
       <c r="B56" s="34" t="s">
         <v>59</v>
@@ -7668,39 +7714,39 @@
         <v>63</v>
       </c>
       <c r="I56" s="34" t="s">
-        <v>447</v>
+        <v>95</v>
       </c>
       <c r="J56" s="34" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K56" s="34" t="s">
-        <v>448</v>
-      </c>
-      <c r="L56" s="34" t="s">
-        <v>449</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="L56" s="34"/>
       <c r="M56" s="35" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="N56" s="36">
-        <v>25972</v>
+        <v>23023</v>
       </c>
       <c r="O56" s="34" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="P56" s="34"/>
       <c r="Q56" s="34"/>
       <c r="R56" s="35" t="s">
-        <v>613</v>
-      </c>
-      <c r="S56" s="39"/>
+        <v>618</v>
+      </c>
+      <c r="S56" s="39" t="s">
+        <v>468</v>
+      </c>
       <c r="T56" s="38" t="s">
-        <v>180</v>
+        <v>772</v>
       </c>
     </row>
     <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="34" t="s">
-        <v>255</v>
+        <v>349</v>
       </c>
       <c r="B57" s="34" t="s">
         <v>59</v>
@@ -7724,39 +7770,39 @@
         <v>63</v>
       </c>
       <c r="I57" s="34" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="J57" s="34" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K57" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="L57" s="34" t="s">
-        <v>433</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="L57" s="34"/>
       <c r="M57" s="35" t="s">
-        <v>288</v>
+        <v>350</v>
       </c>
       <c r="N57" s="36">
-        <v>27622</v>
+        <v>23467</v>
       </c>
       <c r="O57" s="34" t="s">
-        <v>205</v>
+        <v>341</v>
       </c>
       <c r="P57" s="34"/>
       <c r="Q57" s="34"/>
       <c r="R57" s="35" t="s">
-        <v>206</v>
-      </c>
-      <c r="S57" s="39"/>
+        <v>342</v>
+      </c>
+      <c r="S57" s="39" t="s">
+        <v>343</v>
+      </c>
       <c r="T57" s="38" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="34" t="s">
-        <v>375</v>
+        <v>506</v>
       </c>
       <c r="B58" s="34" t="s">
         <v>59</v>
@@ -7780,35 +7826,39 @@
         <v>63</v>
       </c>
       <c r="I58" s="34" t="s">
-        <v>110</v>
+        <v>443</v>
       </c>
       <c r="J58" s="34" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="K58" s="34" t="s">
-        <v>376</v>
+        <v>444</v>
       </c>
       <c r="L58" s="34" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="M58" s="35" t="s">
-        <v>377</v>
+        <v>446</v>
       </c>
       <c r="N58" s="36">
-        <v>22700</v>
-      </c>
-      <c r="O58" s="34"/>
+        <v>25972</v>
+      </c>
+      <c r="O58" s="34" t="s">
+        <v>447</v>
+      </c>
       <c r="P58" s="34"/>
       <c r="Q58" s="34"/>
-      <c r="R58" s="35"/>
+      <c r="R58" s="35" t="s">
+        <v>608</v>
+      </c>
       <c r="S58" s="39"/>
       <c r="T58" s="38" t="s">
-        <v>786</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="34" t="s">
-        <v>325</v>
+        <v>255</v>
       </c>
       <c r="B59" s="34" t="s">
         <v>59</v>
@@ -7832,39 +7882,39 @@
         <v>63</v>
       </c>
       <c r="I59" s="34" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="J59" s="34" t="s">
-        <v>774</v>
+        <v>76</v>
       </c>
       <c r="K59" s="34" t="s">
-        <v>763</v>
-      </c>
-      <c r="L59" s="34"/>
+        <v>128</v>
+      </c>
+      <c r="L59" s="34" t="s">
+        <v>430</v>
+      </c>
       <c r="M59" s="35" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="N59" s="36">
-        <v>30254</v>
+        <v>27622</v>
       </c>
       <c r="O59" s="34" t="s">
-        <v>307</v>
+        <v>205</v>
       </c>
       <c r="P59" s="34"/>
       <c r="Q59" s="34"/>
       <c r="R59" s="35" t="s">
-        <v>308</v>
-      </c>
-      <c r="S59" s="39" t="s">
-        <v>309</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="S59" s="39"/>
       <c r="T59" s="38" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="34" t="s">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="B60" s="34" t="s">
         <v>59</v>
@@ -7876,51 +7926,47 @@
         <v>61</v>
       </c>
       <c r="E60" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F60" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G60" s="34" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="H60" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I60" s="34" t="s">
-        <v>301</v>
+        <v>110</v>
       </c>
       <c r="J60" s="34" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K60" s="34" t="s">
-        <v>762</v>
-      </c>
-      <c r="L60" s="34"/>
+        <v>376</v>
+      </c>
+      <c r="L60" s="34" t="s">
+        <v>376</v>
+      </c>
       <c r="M60" s="35" t="s">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="N60" s="36">
-        <v>27776</v>
-      </c>
-      <c r="O60" s="34" t="s">
-        <v>303</v>
-      </c>
+        <v>22700</v>
+      </c>
+      <c r="O60" s="34"/>
       <c r="P60" s="34"/>
       <c r="Q60" s="34"/>
-      <c r="R60" s="35" t="s">
-        <v>304</v>
-      </c>
-      <c r="S60" s="39" t="s">
-        <v>305</v>
-      </c>
+      <c r="R60" s="35"/>
+      <c r="S60" s="39"/>
       <c r="T60" s="38" t="s">
-        <v>565</v>
+        <v>773</v>
       </c>
     </row>
     <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="34" t="s">
-        <v>426</v>
+        <v>325</v>
       </c>
       <c r="B61" s="34" t="s">
         <v>59</v>
@@ -7944,35 +7990,39 @@
         <v>63</v>
       </c>
       <c r="I61" s="34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J61" s="34" t="s">
-        <v>68</v>
+        <v>768</v>
       </c>
       <c r="K61" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="L61" s="34" t="s">
-        <v>69</v>
-      </c>
+        <v>757</v>
+      </c>
+      <c r="L61" s="34"/>
       <c r="M61" s="35" t="s">
-        <v>386</v>
+        <v>306</v>
       </c>
       <c r="N61" s="36">
-        <v>30538</v>
-      </c>
-      <c r="O61" s="34"/>
+        <v>30254</v>
+      </c>
+      <c r="O61" s="34" t="s">
+        <v>307</v>
+      </c>
       <c r="P61" s="34"/>
       <c r="Q61" s="34"/>
-      <c r="R61" s="35"/>
-      <c r="S61" s="39"/>
+      <c r="R61" s="35" t="s">
+        <v>308</v>
+      </c>
+      <c r="S61" s="39" t="s">
+        <v>309</v>
+      </c>
       <c r="T61" s="38" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="34" t="s">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="B62" s="34" t="s">
         <v>59</v>
@@ -7984,47 +8034,51 @@
         <v>61</v>
       </c>
       <c r="E62" s="35" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F62" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G62" s="34" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H62" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I62" s="34" t="s">
-        <v>381</v>
+        <v>301</v>
       </c>
       <c r="J62" s="34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K62" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="L62" s="34" t="s">
-        <v>92</v>
-      </c>
+        <v>756</v>
+      </c>
+      <c r="L62" s="34"/>
       <c r="M62" s="35" t="s">
-        <v>382</v>
+        <v>302</v>
       </c>
       <c r="N62" s="36">
-        <v>25896</v>
-      </c>
-      <c r="O62" s="34"/>
+        <v>27776</v>
+      </c>
+      <c r="O62" s="34" t="s">
+        <v>303</v>
+      </c>
       <c r="P62" s="34"/>
       <c r="Q62" s="34"/>
-      <c r="R62" s="35"/>
-      <c r="S62" s="39"/>
+      <c r="R62" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="S62" s="39" t="s">
+        <v>305</v>
+      </c>
       <c r="T62" s="38" t="s">
-        <v>786</v>
+        <v>561</v>
       </c>
     </row>
     <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="34" t="s">
-        <v>321</v>
+        <v>423</v>
       </c>
       <c r="B63" s="34" t="s">
         <v>59</v>
@@ -8048,29 +8102,27 @@
         <v>63</v>
       </c>
       <c r="I63" s="34" t="s">
-        <v>311</v>
+        <v>106</v>
       </c>
       <c r="J63" s="34" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K63" s="34" t="s">
-        <v>310</v>
-      </c>
-      <c r="L63" s="34"/>
+        <v>69</v>
+      </c>
+      <c r="L63" s="34" t="s">
+        <v>69</v>
+      </c>
       <c r="M63" s="35" t="s">
-        <v>318</v>
+        <v>384</v>
       </c>
       <c r="N63" s="36">
-        <v>25993</v>
-      </c>
-      <c r="O63" s="34" t="s">
-        <v>319</v>
-      </c>
+        <v>30538</v>
+      </c>
+      <c r="O63" s="34"/>
       <c r="P63" s="34"/>
       <c r="Q63" s="34"/>
-      <c r="R63" s="35" t="s">
-        <v>320</v>
-      </c>
+      <c r="R63" s="35"/>
       <c r="S63" s="39"/>
       <c r="T63" s="38" t="s">
         <v>180</v>
@@ -8078,7 +8130,7 @@
     </row>
     <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="34" t="s">
-        <v>256</v>
+        <v>378</v>
       </c>
       <c r="B64" s="34" t="s">
         <v>59</v>
@@ -8102,39 +8154,35 @@
         <v>63</v>
       </c>
       <c r="I64" s="34" t="s">
-        <v>88</v>
+        <v>379</v>
       </c>
       <c r="J64" s="34" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="K64" s="34" t="s">
-        <v>761</v>
-      </c>
-      <c r="L64" s="34"/>
+        <v>92</v>
+      </c>
+      <c r="L64" s="34" t="s">
+        <v>92</v>
+      </c>
       <c r="M64" s="35" t="s">
-        <v>151</v>
+        <v>380</v>
       </c>
       <c r="N64" s="36">
-        <v>25881</v>
-      </c>
-      <c r="O64" s="34" t="s">
-        <v>152</v>
-      </c>
+        <v>25896</v>
+      </c>
+      <c r="O64" s="34"/>
       <c r="P64" s="34"/>
       <c r="Q64" s="34"/>
-      <c r="R64" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="S64" s="39" t="s">
-        <v>154</v>
-      </c>
+      <c r="R64" s="35"/>
+      <c r="S64" s="39"/>
       <c r="T64" s="38" t="s">
-        <v>150</v>
+        <v>773</v>
       </c>
     </row>
     <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="34" t="s">
-        <v>393</v>
+        <v>321</v>
       </c>
       <c r="B65" s="34" t="s">
         <v>59</v>
@@ -8158,41 +8206,37 @@
         <v>63</v>
       </c>
       <c r="I65" s="34" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="J65" s="34" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K65" s="34" t="s">
-        <v>417</v>
-      </c>
-      <c r="L65" s="34" t="s">
-        <v>417</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="L65" s="34"/>
       <c r="M65" s="35" t="s">
-        <v>395</v>
+        <v>318</v>
       </c>
       <c r="N65" s="36">
-        <v>30157</v>
+        <v>25993</v>
       </c>
       <c r="O65" s="34" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="P65" s="34"/>
       <c r="Q65" s="34"/>
       <c r="R65" s="35" t="s">
-        <v>396</v>
-      </c>
-      <c r="S65" s="39" t="s">
-        <v>397</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="S65" s="39"/>
       <c r="T65" s="38" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="34" t="s">
-        <v>371</v>
+        <v>256</v>
       </c>
       <c r="B66" s="34" t="s">
         <v>59</v>
@@ -8216,31 +8260,31 @@
         <v>63</v>
       </c>
       <c r="I66" s="34" t="s">
-        <v>335</v>
+        <v>88</v>
       </c>
       <c r="J66" s="34" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="K66" s="34" t="s">
-        <v>301</v>
+        <v>755</v>
       </c>
       <c r="L66" s="34"/>
       <c r="M66" s="35" t="s">
-        <v>344</v>
+        <v>151</v>
       </c>
       <c r="N66" s="36">
-        <v>34772</v>
+        <v>25881</v>
       </c>
       <c r="O66" s="34" t="s">
-        <v>345</v>
+        <v>152</v>
       </c>
       <c r="P66" s="34"/>
       <c r="Q66" s="34"/>
       <c r="R66" s="35" t="s">
-        <v>346</v>
+        <v>153</v>
       </c>
       <c r="S66" s="39" t="s">
-        <v>347</v>
+        <v>154</v>
       </c>
       <c r="T66" s="38" t="s">
         <v>150</v>
@@ -8248,7 +8292,7 @@
     </row>
     <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="34" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="B67" s="34" t="s">
         <v>59</v>
@@ -8265,46 +8309,48 @@
       <c r="F67" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G67" s="35" t="s">
+      <c r="G67" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="H67" s="35" t="s">
+      <c r="H67" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I67" s="35" t="s">
+      <c r="I67" s="34" t="s">
         <v>335</v>
       </c>
-      <c r="J67" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="K67" s="35" t="s">
-        <v>760</v>
-      </c>
-      <c r="L67" s="35"/>
+      <c r="J67" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="K67" s="34" t="s">
+        <v>415</v>
+      </c>
+      <c r="L67" s="34" t="s">
+        <v>415</v>
+      </c>
       <c r="M67" s="35" t="s">
-        <v>336</v>
+        <v>393</v>
       </c>
       <c r="N67" s="36">
-        <v>23605</v>
-      </c>
-      <c r="O67" s="35" t="s">
+        <v>30157</v>
+      </c>
+      <c r="O67" s="34" t="s">
         <v>337</v>
       </c>
-      <c r="P67" s="35"/>
-      <c r="Q67" s="35"/>
+      <c r="P67" s="34"/>
+      <c r="Q67" s="34"/>
       <c r="R67" s="35" t="s">
-        <v>338</v>
-      </c>
-      <c r="S67" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="T67" s="37" t="s">
+        <v>394</v>
+      </c>
+      <c r="S67" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="T67" s="38" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="34" t="s">
-        <v>257</v>
+        <v>371</v>
       </c>
       <c r="B68" s="34" t="s">
         <v>59</v>
@@ -8316,43 +8362,43 @@
         <v>61</v>
       </c>
       <c r="E68" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F68" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G68" s="34" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="H68" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I68" s="34" t="s">
-        <v>89</v>
+        <v>335</v>
       </c>
       <c r="J68" s="34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K68" s="34" t="s">
-        <v>759</v>
+        <v>301</v>
       </c>
       <c r="L68" s="34"/>
       <c r="M68" s="35" t="s">
-        <v>155</v>
+        <v>344</v>
       </c>
       <c r="N68" s="36">
-        <v>22431</v>
+        <v>34772</v>
       </c>
       <c r="O68" s="34" t="s">
-        <v>156</v>
+        <v>345</v>
       </c>
       <c r="P68" s="34"/>
       <c r="Q68" s="34"/>
       <c r="R68" s="35" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="S68" s="39" t="s">
-        <v>157</v>
+        <v>347</v>
       </c>
       <c r="T68" s="38" t="s">
         <v>150</v>
@@ -8360,7 +8406,7 @@
     </row>
     <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="34" t="s">
-        <v>258</v>
+        <v>348</v>
       </c>
       <c r="B69" s="34" t="s">
         <v>59</v>
@@ -8377,44 +8423,46 @@
       <c r="F69" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="G69" s="34" t="s">
+      <c r="G69" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="H69" s="34" t="s">
+      <c r="H69" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I69" s="35" t="s">
-        <v>112</v>
+        <v>335</v>
       </c>
       <c r="J69" s="35" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K69" s="35" t="s">
-        <v>120</v>
+        <v>754</v>
       </c>
       <c r="L69" s="35"/>
       <c r="M69" s="35" t="s">
-        <v>192</v>
+        <v>336</v>
       </c>
       <c r="N69" s="36">
-        <v>23105</v>
-      </c>
-      <c r="O69" s="34" t="s">
-        <v>193</v>
+        <v>23605</v>
+      </c>
+      <c r="O69" s="35" t="s">
+        <v>337</v>
       </c>
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
       <c r="R69" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="S69" s="35"/>
-      <c r="T69" s="38" t="s">
-        <v>180</v>
+        <v>338</v>
+      </c>
+      <c r="S69" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="T69" s="37" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="34" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="B70" s="34" t="s">
         <v>59</v>
@@ -8437,38 +8485,40 @@
       <c r="H70" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I70" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="J70" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="K70" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="L70" s="35"/>
+      <c r="I70" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="J70" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="K70" s="34" t="s">
+        <v>753</v>
+      </c>
+      <c r="L70" s="34"/>
       <c r="M70" s="35" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="N70" s="36">
-        <v>36383</v>
+        <v>22431</v>
       </c>
       <c r="O70" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="P70" s="35"/>
-      <c r="Q70" s="35"/>
+        <v>156</v>
+      </c>
+      <c r="P70" s="34"/>
+      <c r="Q70" s="34"/>
       <c r="R70" s="35" t="s">
-        <v>612</v>
-      </c>
-      <c r="S70" s="35"/>
+        <v>284</v>
+      </c>
+      <c r="S70" s="39" t="s">
+        <v>157</v>
+      </c>
       <c r="T70" s="38" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="34" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B71" s="34" t="s">
         <v>59</v>
@@ -8495,25 +8545,25 @@
         <v>112</v>
       </c>
       <c r="J71" s="35" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K71" s="35" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="L71" s="35"/>
       <c r="M71" s="35" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="N71" s="36">
-        <v>33831</v>
+        <v>23105</v>
       </c>
       <c r="O71" s="34" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="P71" s="35"/>
       <c r="Q71" s="35"/>
       <c r="R71" s="35" t="s">
-        <v>614</v>
+        <v>194</v>
       </c>
       <c r="S71" s="35"/>
       <c r="T71" s="38" t="s">
@@ -8522,7 +8572,7 @@
     </row>
     <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="34" t="s">
-        <v>372</v>
+        <v>245</v>
       </c>
       <c r="B72" s="34" t="s">
         <v>59</v>
@@ -8534,13 +8584,13 @@
         <v>61</v>
       </c>
       <c r="E72" s="35" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F72" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G72" s="34" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H72" s="34" t="s">
         <v>63</v>
@@ -8549,34 +8599,34 @@
         <v>112</v>
       </c>
       <c r="J72" s="35" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="K72" s="35" t="s">
-        <v>331</v>
+        <v>111</v>
       </c>
       <c r="L72" s="35"/>
       <c r="M72" s="35" t="s">
-        <v>334</v>
+        <v>178</v>
       </c>
       <c r="N72" s="36">
-        <v>30287</v>
+        <v>36383</v>
       </c>
       <c r="O72" s="34" t="s">
-        <v>332</v>
+        <v>179</v>
       </c>
       <c r="P72" s="35"/>
       <c r="Q72" s="35"/>
       <c r="R72" s="35" t="s">
-        <v>333</v>
+        <v>607</v>
       </c>
       <c r="S72" s="35"/>
       <c r="T72" s="38" t="s">
-        <v>787</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B73" s="34" t="s">
         <v>59</v>
@@ -8603,25 +8653,25 @@
         <v>112</v>
       </c>
       <c r="J73" s="35" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K73" s="35" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="L73" s="35"/>
       <c r="M73" s="35" t="s">
-        <v>509</v>
+        <v>181</v>
       </c>
       <c r="N73" s="36">
-        <v>26138</v>
+        <v>33831</v>
       </c>
       <c r="O73" s="34" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="P73" s="35"/>
       <c r="Q73" s="35"/>
       <c r="R73" s="35" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="S73" s="35"/>
       <c r="T73" s="38" t="s">
@@ -8630,7 +8680,7 @@
     </row>
     <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="34" t="s">
-        <v>261</v>
+        <v>372</v>
       </c>
       <c r="B74" s="34" t="s">
         <v>59</v>
@@ -8657,34 +8707,34 @@
         <v>112</v>
       </c>
       <c r="J74" s="35" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="K74" s="35" t="s">
-        <v>118</v>
+        <v>331</v>
       </c>
       <c r="L74" s="35"/>
       <c r="M74" s="35" t="s">
-        <v>186</v>
+        <v>334</v>
       </c>
       <c r="N74" s="36">
-        <v>32984</v>
+        <v>30287</v>
       </c>
       <c r="O74" s="34" t="s">
-        <v>187</v>
+        <v>332</v>
       </c>
       <c r="P74" s="35"/>
       <c r="Q74" s="35"/>
       <c r="R74" s="35" t="s">
-        <v>188</v>
+        <v>333</v>
       </c>
       <c r="S74" s="35"/>
       <c r="T74" s="38" t="s">
-        <v>180</v>
+        <v>774</v>
       </c>
     </row>
     <row r="75" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="34" t="s">
-        <v>550</v>
+        <v>260</v>
       </c>
       <c r="B75" s="34" t="s">
         <v>59</v>
@@ -8708,39 +8758,37 @@
         <v>63</v>
       </c>
       <c r="I75" s="35" t="s">
-        <v>527</v>
+        <v>112</v>
       </c>
       <c r="J75" s="35" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="K75" s="35" t="s">
-        <v>528</v>
-      </c>
-      <c r="L75" s="35" t="s">
-        <v>529</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="L75" s="35"/>
       <c r="M75" s="35" t="s">
-        <v>530</v>
+        <v>505</v>
       </c>
       <c r="N75" s="36">
-        <v>23098</v>
+        <v>26138</v>
       </c>
       <c r="O75" s="34" t="s">
-        <v>531</v>
+        <v>195</v>
       </c>
       <c r="P75" s="35"/>
       <c r="Q75" s="35"/>
       <c r="R75" s="35" t="s">
-        <v>532</v>
+        <v>610</v>
       </c>
       <c r="S75" s="35"/>
       <c r="T75" s="38" t="s">
-        <v>785</v>
+        <v>180</v>
       </c>
     </row>
     <row r="76" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="34" t="s">
-        <v>432</v>
+        <v>261</v>
       </c>
       <c r="B76" s="34" t="s">
         <v>59</v>
@@ -8764,39 +8812,37 @@
         <v>63</v>
       </c>
       <c r="I76" s="35" t="s">
-        <v>329</v>
+        <v>112</v>
       </c>
       <c r="J76" s="35" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="K76" s="35" t="s">
-        <v>427</v>
+        <v>118</v>
       </c>
       <c r="L76" s="35"/>
       <c r="M76" s="35" t="s">
-        <v>428</v>
+        <v>186</v>
       </c>
       <c r="N76" s="36">
-        <v>25389</v>
+        <v>32984</v>
       </c>
       <c r="O76" s="34" t="s">
-        <v>429</v>
+        <v>187</v>
       </c>
       <c r="P76" s="35"/>
       <c r="Q76" s="35"/>
       <c r="R76" s="35" t="s">
-        <v>430</v>
-      </c>
-      <c r="S76" s="35" t="s">
-        <v>431</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="S76" s="35"/>
       <c r="T76" s="38" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
     </row>
     <row r="77" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="34" t="s">
-        <v>262</v>
+        <v>546</v>
       </c>
       <c r="B77" s="34" t="s">
         <v>59</v>
@@ -8820,37 +8866,39 @@
         <v>63</v>
       </c>
       <c r="I77" s="35" t="s">
-        <v>97</v>
+        <v>523</v>
       </c>
       <c r="J77" s="35" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="K77" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="L77" s="35"/>
+        <v>524</v>
+      </c>
+      <c r="L77" s="35" t="s">
+        <v>525</v>
+      </c>
       <c r="M77" s="35" t="s">
-        <v>168</v>
+        <v>526</v>
       </c>
       <c r="N77" s="36">
-        <v>29006</v>
+        <v>23098</v>
       </c>
       <c r="O77" s="34" t="s">
-        <v>169</v>
+        <v>527</v>
       </c>
       <c r="P77" s="35"/>
       <c r="Q77" s="35"/>
       <c r="R77" s="35" t="s">
-        <v>170</v>
+        <v>528</v>
       </c>
       <c r="S77" s="35"/>
       <c r="T77" s="38" t="s">
-        <v>787</v>
+        <v>772</v>
       </c>
     </row>
     <row r="78" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="34" t="s">
-        <v>263</v>
+        <v>429</v>
       </c>
       <c r="B78" s="34" t="s">
         <v>59</v>
@@ -8874,37 +8922,39 @@
         <v>63</v>
       </c>
       <c r="I78" s="35" t="s">
-        <v>131</v>
+        <v>329</v>
       </c>
       <c r="J78" s="35" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="K78" s="35" t="s">
-        <v>132</v>
+        <v>424</v>
       </c>
       <c r="L78" s="35"/>
       <c r="M78" s="35" t="s">
-        <v>214</v>
+        <v>425</v>
       </c>
       <c r="N78" s="36">
-        <v>21024</v>
+        <v>25389</v>
       </c>
       <c r="O78" s="34" t="s">
-        <v>215</v>
+        <v>426</v>
       </c>
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
       <c r="R78" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="S78" s="35"/>
+        <v>427</v>
+      </c>
+      <c r="S78" s="35" t="s">
+        <v>428</v>
+      </c>
       <c r="T78" s="38" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="34" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B79" s="34" t="s">
         <v>59</v>
@@ -8928,37 +8978,37 @@
         <v>63</v>
       </c>
       <c r="I79" s="35" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="J79" s="35" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="K79" s="35" t="s">
-        <v>376</v>
+        <v>98</v>
       </c>
       <c r="L79" s="35"/>
       <c r="M79" s="35" t="s">
-        <v>211</v>
+        <v>168</v>
       </c>
       <c r="N79" s="36">
-        <v>19757</v>
+        <v>29006</v>
       </c>
       <c r="O79" s="34" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
       <c r="R79" s="35" t="s">
-        <v>213</v>
+        <v>170</v>
       </c>
       <c r="S79" s="35"/>
       <c r="T79" s="38" t="s">
-        <v>204</v>
+        <v>774</v>
       </c>
     </row>
     <row r="80" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="34" t="s">
-        <v>374</v>
+        <v>263</v>
       </c>
       <c r="B80" s="34" t="s">
         <v>59</v>
@@ -8982,37 +9032,37 @@
         <v>63</v>
       </c>
       <c r="I80" s="35" t="s">
-        <v>361</v>
+        <v>131</v>
       </c>
       <c r="J80" s="35" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="K80" s="35" t="s">
-        <v>362</v>
+        <v>132</v>
       </c>
       <c r="L80" s="35"/>
       <c r="M80" s="35" t="s">
-        <v>368</v>
+        <v>214</v>
       </c>
       <c r="N80" s="36">
-        <v>30337</v>
+        <v>21024</v>
       </c>
       <c r="O80" s="34" t="s">
-        <v>363</v>
+        <v>215</v>
       </c>
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
       <c r="R80" s="35" t="s">
-        <v>364</v>
+        <v>216</v>
       </c>
       <c r="S80" s="35"/>
       <c r="T80" s="38" t="s">
-        <v>141</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="34" t="s">
-        <v>420</v>
+        <v>264</v>
       </c>
       <c r="B81" s="34" t="s">
         <v>59</v>
@@ -9036,35 +9086,37 @@
         <v>63</v>
       </c>
       <c r="I81" s="35" t="s">
-        <v>383</v>
+        <v>130</v>
       </c>
       <c r="J81" s="35" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="K81" s="35" t="s">
-        <v>384</v>
-      </c>
-      <c r="L81" s="35" t="s">
-        <v>384</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="L81" s="35"/>
       <c r="M81" s="35" t="s">
-        <v>385</v>
+        <v>211</v>
       </c>
       <c r="N81" s="36">
-        <v>29821</v>
-      </c>
-      <c r="O81" s="34"/>
+        <v>19757</v>
+      </c>
+      <c r="O81" s="34" t="s">
+        <v>212</v>
+      </c>
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
-      <c r="R81" s="35"/>
+      <c r="R81" s="35" t="s">
+        <v>213</v>
+      </c>
       <c r="S81" s="35"/>
       <c r="T81" s="38" t="s">
-        <v>786</v>
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="34" t="s">
-        <v>265</v>
+        <v>374</v>
       </c>
       <c r="B82" s="34" t="s">
         <v>59</v>
@@ -9088,39 +9140,37 @@
         <v>63</v>
       </c>
       <c r="I82" s="35" t="s">
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="J82" s="35" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K82" s="35" t="s">
-        <v>66</v>
+        <v>362</v>
       </c>
       <c r="L82" s="35"/>
       <c r="M82" s="35" t="s">
-        <v>134</v>
+        <v>368</v>
       </c>
       <c r="N82" s="36">
-        <v>27213</v>
+        <v>30337</v>
       </c>
       <c r="O82" s="34" t="s">
-        <v>135</v>
+        <v>363</v>
       </c>
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
       <c r="R82" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="S82" s="35" t="s">
-        <v>137</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="S82" s="35"/>
       <c r="T82" s="38" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="34" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B83" s="34" t="s">
         <v>59</v>
@@ -9144,37 +9194,35 @@
         <v>63</v>
       </c>
       <c r="I83" s="35" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="J83" s="35" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="K83" s="35" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="L83" s="35" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="M83" s="35" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="N83" s="36">
-        <v>24507</v>
+        <v>29821</v>
       </c>
       <c r="O83" s="34"/>
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
-      <c r="R83" s="35" t="s">
-        <v>616</v>
-      </c>
+      <c r="R83" s="35"/>
       <c r="S83" s="35"/>
       <c r="T83" s="38" t="s">
-        <v>141</v>
+        <v>773</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B84" s="34" t="s">
         <v>59</v>
@@ -9198,39 +9246,39 @@
         <v>63</v>
       </c>
       <c r="I84" s="35" t="s">
-        <v>129</v>
+        <v>64</v>
       </c>
       <c r="J84" s="35" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="K84" s="35" t="s">
-        <v>758</v>
+        <v>66</v>
       </c>
       <c r="L84" s="35"/>
       <c r="M84" s="35" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="N84" s="36">
-        <v>29328</v>
+        <v>27213</v>
       </c>
       <c r="O84" s="34" t="s">
-        <v>208</v>
+        <v>135</v>
       </c>
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
       <c r="R84" s="35" t="s">
-        <v>209</v>
+        <v>136</v>
       </c>
       <c r="S84" s="35" t="s">
-        <v>210</v>
+        <v>137</v>
       </c>
       <c r="T84" s="38" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="85" spans="1:21" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="34" t="s">
-        <v>645</v>
+        <v>418</v>
       </c>
       <c r="B85" s="34" t="s">
         <v>59</v>
@@ -9254,36 +9302,37 @@
         <v>63</v>
       </c>
       <c r="I85" s="35" t="s">
-        <v>129</v>
+        <v>389</v>
       </c>
       <c r="J85" s="35" t="s">
-        <v>642</v>
+        <v>72</v>
       </c>
       <c r="K85" s="35" t="s">
-        <v>643</v>
-      </c>
-      <c r="L85" s="35"/>
+        <v>419</v>
+      </c>
+      <c r="L85" s="35" t="s">
+        <v>390</v>
+      </c>
       <c r="M85" s="35" t="s">
-        <v>644</v>
+        <v>414</v>
       </c>
       <c r="N85" s="36">
-        <v>40905</v>
-      </c>
-      <c r="O85" s="34" t="s">
-        <v>208</v>
-      </c>
+        <v>24507</v>
+      </c>
+      <c r="O85" s="34"/>
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
-      <c r="R85" s="35"/>
+      <c r="R85" s="35" t="s">
+        <v>611</v>
+      </c>
       <c r="S85" s="35"/>
       <c r="T85" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="U85" s="27"/>
+        <v>141</v>
+      </c>
     </row>
     <row r="86" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="34" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B86" s="34" t="s">
         <v>59</v>
@@ -9307,39 +9356,39 @@
         <v>63</v>
       </c>
       <c r="I86" s="35" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="J86" s="35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K86" s="35" t="s">
-        <v>92</v>
+        <v>752</v>
       </c>
       <c r="L86" s="35"/>
       <c r="M86" s="35" t="s">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="N86" s="36">
-        <v>27907</v>
+        <v>29328</v>
       </c>
       <c r="O86" s="34" t="s">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
       <c r="R86" s="35" t="s">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="S86" s="35" t="s">
-        <v>162</v>
+        <v>210</v>
       </c>
       <c r="T86" s="38" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="87" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="34" t="s">
-        <v>548</v>
+        <v>640</v>
       </c>
       <c r="B87" s="34" t="s">
         <v>59</v>
@@ -9363,39 +9412,36 @@
         <v>63</v>
       </c>
       <c r="I87" s="35" t="s">
-        <v>518</v>
+        <v>129</v>
       </c>
       <c r="J87" s="35" t="s">
-        <v>117</v>
+        <v>637</v>
       </c>
       <c r="K87" s="35" t="s">
-        <v>519</v>
-      </c>
-      <c r="L87" s="35" t="s">
-        <v>520</v>
-      </c>
+        <v>638</v>
+      </c>
+      <c r="L87" s="35"/>
       <c r="M87" s="35" t="s">
-        <v>521</v>
-      </c>
-      <c r="N87" s="36" t="s">
-        <v>674</v>
+        <v>639</v>
+      </c>
+      <c r="N87" s="36">
+        <v>40905</v>
       </c>
       <c r="O87" s="34" t="s">
-        <v>522</v>
+        <v>208</v>
       </c>
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
-      <c r="R87" s="35" t="s">
-        <v>666</v>
-      </c>
+      <c r="R87" s="35"/>
       <c r="S87" s="35"/>
       <c r="T87" s="38" t="s">
-        <v>785</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="U87" s="27"/>
     </row>
     <row r="88" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="34" t="s">
-        <v>312</v>
+        <v>267</v>
       </c>
       <c r="B88" s="34" t="s">
         <v>59</v>
@@ -9407,49 +9453,51 @@
         <v>61</v>
       </c>
       <c r="E88" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F88" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G88" s="34" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="H88" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I88" s="35" t="s">
-        <v>313</v>
+        <v>91</v>
       </c>
       <c r="J88" s="35" t="s">
         <v>80</v>
       </c>
       <c r="K88" s="35" t="s">
-        <v>314</v>
+        <v>92</v>
       </c>
       <c r="L88" s="35"/>
       <c r="M88" s="35" t="s">
-        <v>315</v>
+        <v>159</v>
       </c>
       <c r="N88" s="36">
-        <v>23497</v>
+        <v>27907</v>
       </c>
       <c r="O88" s="34" t="s">
-        <v>316</v>
+        <v>160</v>
       </c>
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
       <c r="R88" s="35" t="s">
-        <v>317</v>
-      </c>
-      <c r="S88" s="35"/>
+        <v>161</v>
+      </c>
+      <c r="S88" s="35" t="s">
+        <v>162</v>
+      </c>
       <c r="T88" s="38" t="s">
-        <v>786</v>
+        <v>204</v>
       </c>
     </row>
     <row r="89" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="34" t="s">
-        <v>473</v>
+        <v>544</v>
       </c>
       <c r="B89" s="34" t="s">
         <v>59</v>
@@ -9473,39 +9521,39 @@
         <v>63</v>
       </c>
       <c r="I89" s="35" t="s">
-        <v>474</v>
+        <v>514</v>
       </c>
       <c r="J89" s="35" t="s">
-        <v>283</v>
+        <v>117</v>
       </c>
       <c r="K89" s="35" t="s">
-        <v>475</v>
+        <v>515</v>
       </c>
       <c r="L89" s="35" t="s">
-        <v>476</v>
+        <v>516</v>
       </c>
       <c r="M89" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="N89" s="36">
-        <v>24537</v>
+        <v>517</v>
+      </c>
+      <c r="N89" s="36" t="s">
+        <v>669</v>
       </c>
       <c r="O89" s="34" t="s">
-        <v>478</v>
+        <v>518</v>
       </c>
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
       <c r="R89" s="35" t="s">
-        <v>621</v>
+        <v>661</v>
       </c>
       <c r="S89" s="35"/>
       <c r="T89" s="38" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
     </row>
     <row r="90" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="35" t="s">
-        <v>755</v>
+      <c r="A90" s="34" t="s">
+        <v>312</v>
       </c>
       <c r="B90" s="34" t="s">
         <v>59</v>
@@ -9517,49 +9565,49 @@
         <v>61</v>
       </c>
       <c r="E90" s="35" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F90" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G90" s="34" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I90" s="34" t="s">
-        <v>712</v>
-      </c>
-      <c r="J90" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K90" s="34" t="s">
-        <v>732</v>
-      </c>
-      <c r="L90" s="34"/>
+      <c r="I90" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="J90" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="K90" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="L90" s="35"/>
       <c r="M90" s="35" t="s">
-        <v>733</v>
-      </c>
-      <c r="N90" s="36" t="s">
-        <v>734</v>
+        <v>315</v>
+      </c>
+      <c r="N90" s="36">
+        <v>23497</v>
       </c>
       <c r="O90" s="34" t="s">
-        <v>735</v>
-      </c>
-      <c r="P90" s="34"/>
-      <c r="Q90" s="34"/>
+        <v>316</v>
+      </c>
+      <c r="P90" s="35"/>
+      <c r="Q90" s="35"/>
       <c r="R90" s="35" t="s">
-        <v>736</v>
-      </c>
-      <c r="S90" s="39"/>
+        <v>317</v>
+      </c>
+      <c r="S90" s="35"/>
       <c r="T90" s="38" t="s">
-        <v>565</v>
+        <v>773</v>
       </c>
     </row>
     <row r="91" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="34" t="s">
-        <v>246</v>
+        <v>469</v>
       </c>
       <c r="B91" s="34" t="s">
         <v>59</v>
@@ -9583,37 +9631,39 @@
         <v>63</v>
       </c>
       <c r="I91" s="35" t="s">
-        <v>67</v>
+        <v>470</v>
       </c>
       <c r="J91" s="35" t="s">
-        <v>68</v>
+        <v>283</v>
       </c>
       <c r="K91" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="L91" s="35"/>
+        <v>471</v>
+      </c>
+      <c r="L91" s="35" t="s">
+        <v>472</v>
+      </c>
       <c r="M91" s="35" t="s">
-        <v>138</v>
+        <v>473</v>
       </c>
       <c r="N91" s="36">
-        <v>31298</v>
+        <v>24537</v>
       </c>
       <c r="O91" s="34" t="s">
-        <v>139</v>
+        <v>474</v>
       </c>
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
       <c r="R91" s="35" t="s">
-        <v>140</v>
+        <v>616</v>
       </c>
       <c r="S91" s="35"/>
       <c r="T91" s="38" t="s">
-        <v>141</v>
+        <v>772</v>
       </c>
     </row>
     <row r="92" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="34" t="s">
-        <v>268</v>
+      <c r="A92" s="35" t="s">
+        <v>749</v>
       </c>
       <c r="B92" s="34" t="s">
         <v>59</v>
@@ -9636,38 +9686,38 @@
       <c r="H92" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I92" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="J92" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="K92" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="L92" s="35"/>
+      <c r="I92" s="34" t="s">
+        <v>706</v>
+      </c>
+      <c r="J92" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="K92" s="34" t="s">
+        <v>726</v>
+      </c>
+      <c r="L92" s="34"/>
       <c r="M92" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="N92" s="36">
-        <v>28101</v>
+        <v>727</v>
+      </c>
+      <c r="N92" s="36" t="s">
+        <v>728</v>
       </c>
       <c r="O92" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="P92" s="35"/>
-      <c r="Q92" s="35"/>
+        <v>729</v>
+      </c>
+      <c r="P92" s="34"/>
+      <c r="Q92" s="34"/>
       <c r="R92" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="S92" s="35"/>
+        <v>730</v>
+      </c>
+      <c r="S92" s="39"/>
       <c r="T92" s="38" t="s">
-        <v>787</v>
+        <v>561</v>
       </c>
     </row>
     <row r="93" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="34" t="s">
-        <v>269</v>
+      <c r="A93" s="35" t="s">
+        <v>780</v>
       </c>
       <c r="B93" s="34" t="s">
         <v>59</v>
@@ -9679,47 +9729,49 @@
         <v>61</v>
       </c>
       <c r="E93" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F93" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G93" s="34" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="H93" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I93" s="35" t="s">
-        <v>90</v>
+        <v>762</v>
       </c>
       <c r="J93" s="35" t="s">
-        <v>79</v>
+        <v>791</v>
       </c>
       <c r="K93" s="35" t="s">
-        <v>323</v>
+        <v>769</v>
       </c>
       <c r="L93" s="35"/>
       <c r="M93" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="N93" s="36">
-        <v>30156</v>
-      </c>
-      <c r="O93" s="34"/>
+        <v>792</v>
+      </c>
+      <c r="N93" s="36" t="s">
+        <v>793</v>
+      </c>
+      <c r="O93" s="34" t="s">
+        <v>794</v>
+      </c>
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
       <c r="R93" s="35" t="s">
-        <v>158</v>
+        <v>795</v>
       </c>
       <c r="S93" s="35"/>
-      <c r="T93" s="38" t="s">
-        <v>787</v>
+      <c r="T93" s="35" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="34" t="s">
-        <v>635</v>
+        <v>246</v>
       </c>
       <c r="B94" s="34" t="s">
         <v>59</v>
@@ -9734,37 +9786,37 @@
         <v>62</v>
       </c>
       <c r="F94" s="35" t="s">
-        <v>636</v>
+        <v>126</v>
       </c>
       <c r="G94" s="34" t="s">
-        <v>669</v>
+        <v>221</v>
       </c>
       <c r="H94" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I94" s="35" t="s">
-        <v>637</v>
+        <v>67</v>
       </c>
       <c r="J94" s="35" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="K94" s="35" t="s">
-        <v>638</v>
+        <v>69</v>
       </c>
       <c r="L94" s="35"/>
       <c r="M94" s="35" t="s">
-        <v>639</v>
+        <v>138</v>
       </c>
       <c r="N94" s="36">
-        <v>33667</v>
+        <v>31298</v>
       </c>
       <c r="O94" s="34" t="s">
-        <v>640</v>
+        <v>139</v>
       </c>
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
       <c r="R94" s="35" t="s">
-        <v>641</v>
+        <v>140</v>
       </c>
       <c r="S94" s="35"/>
       <c r="T94" s="38" t="s">
@@ -9773,7 +9825,7 @@
     </row>
     <row r="95" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="34" t="s">
-        <v>553</v>
+        <v>268</v>
       </c>
       <c r="B95" s="34" t="s">
         <v>59</v>
@@ -9797,37 +9849,37 @@
         <v>63</v>
       </c>
       <c r="I95" s="35" t="s">
-        <v>533</v>
+        <v>101</v>
       </c>
       <c r="J95" s="35" t="s">
         <v>72</v>
       </c>
       <c r="K95" s="35" t="s">
-        <v>534</v>
+        <v>102</v>
       </c>
       <c r="L95" s="35"/>
       <c r="M95" s="35" t="s">
-        <v>535</v>
-      </c>
-      <c r="N95" s="36" t="s">
-        <v>536</v>
+        <v>172</v>
+      </c>
+      <c r="N95" s="36">
+        <v>28101</v>
       </c>
       <c r="O95" s="34" t="s">
-        <v>537</v>
+        <v>173</v>
       </c>
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
       <c r="R95" s="35" t="s">
-        <v>538</v>
+        <v>174</v>
       </c>
       <c r="S95" s="35"/>
       <c r="T95" s="38" t="s">
-        <v>204</v>
+        <v>774</v>
       </c>
     </row>
     <row r="96" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="34" t="s">
-        <v>479</v>
+        <v>269</v>
       </c>
       <c r="B96" s="34" t="s">
         <v>59</v>
@@ -9839,53 +9891,47 @@
         <v>61</v>
       </c>
       <c r="E96" s="35" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F96" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G96" s="34" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H96" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I96" s="35" t="s">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="J96" s="35" t="s">
-        <v>394</v>
+        <v>79</v>
       </c>
       <c r="K96" s="35" t="s">
-        <v>481</v>
-      </c>
-      <c r="L96" s="35" t="s">
-        <v>394</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="L96" s="35"/>
       <c r="M96" s="35" t="s">
-        <v>482</v>
+        <v>220</v>
       </c>
       <c r="N96" s="36">
-        <v>34298</v>
-      </c>
-      <c r="O96" s="34" t="s">
-        <v>483</v>
-      </c>
+        <v>30156</v>
+      </c>
+      <c r="O96" s="34"/>
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
       <c r="R96" s="35" t="s">
-        <v>484</v>
-      </c>
-      <c r="S96" s="35" t="s">
-        <v>485</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="S96" s="35"/>
       <c r="T96" s="38" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
     </row>
     <row r="97" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="34" t="s">
-        <v>486</v>
+        <v>630</v>
       </c>
       <c r="B97" s="34" t="s">
         <v>59</v>
@@ -9900,48 +9946,46 @@
         <v>62</v>
       </c>
       <c r="F97" s="35" t="s">
-        <v>126</v>
+        <v>631</v>
       </c>
       <c r="G97" s="34" t="s">
-        <v>221</v>
+        <v>664</v>
       </c>
       <c r="H97" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I97" s="35" t="s">
-        <v>480</v>
+        <v>632</v>
       </c>
       <c r="J97" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K97" s="35" t="s">
-        <v>487</v>
+        <v>633</v>
       </c>
       <c r="L97" s="35"/>
       <c r="M97" s="35" t="s">
-        <v>488</v>
+        <v>634</v>
       </c>
       <c r="N97" s="36">
-        <v>29452</v>
+        <v>33667</v>
       </c>
       <c r="O97" s="34" t="s">
-        <v>489</v>
+        <v>635</v>
       </c>
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
       <c r="R97" s="35" t="s">
-        <v>618</v>
-      </c>
-      <c r="S97" s="35" t="s">
-        <v>490</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="S97" s="35"/>
       <c r="T97" s="38" t="s">
-        <v>785</v>
+        <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="34" t="s">
-        <v>356</v>
+        <v>549</v>
       </c>
       <c r="B98" s="34" t="s">
         <v>59</v>
@@ -9956,48 +10000,46 @@
         <v>62</v>
       </c>
       <c r="F98" s="35" t="s">
-        <v>636</v>
+        <v>126</v>
       </c>
       <c r="G98" s="34" t="s">
-        <v>669</v>
+        <v>221</v>
       </c>
       <c r="H98" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I98" s="35" t="s">
-        <v>357</v>
+        <v>529</v>
       </c>
       <c r="J98" s="35" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K98" s="35" t="s">
-        <v>358</v>
-      </c>
-      <c r="L98" s="35" t="s">
-        <v>667</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="L98" s="35"/>
       <c r="M98" s="35" t="s">
-        <v>359</v>
+        <v>531</v>
       </c>
       <c r="N98" s="36" t="s">
-        <v>675</v>
+        <v>532</v>
       </c>
       <c r="O98" s="34" t="s">
-        <v>360</v>
+        <v>533</v>
       </c>
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
       <c r="R98" s="35" t="s">
-        <v>611</v>
+        <v>534</v>
       </c>
       <c r="S98" s="35"/>
       <c r="T98" s="38" t="s">
-        <v>785</v>
+        <v>204</v>
       </c>
     </row>
     <row r="99" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="34" t="s">
-        <v>697</v>
+        <v>475</v>
       </c>
       <c r="B99" s="34" t="s">
         <v>59</v>
@@ -10021,37 +10063,41 @@
         <v>63</v>
       </c>
       <c r="I99" s="35" t="s">
-        <v>698</v>
+        <v>476</v>
       </c>
       <c r="J99" s="35" t="s">
-        <v>71</v>
+        <v>392</v>
       </c>
       <c r="K99" s="35" t="s">
-        <v>699</v>
-      </c>
-      <c r="L99" s="35"/>
+        <v>477</v>
+      </c>
+      <c r="L99" s="35" t="s">
+        <v>392</v>
+      </c>
       <c r="M99" s="35" t="s">
-        <v>700</v>
+        <v>478</v>
       </c>
       <c r="N99" s="36">
-        <v>32200</v>
+        <v>34298</v>
       </c>
       <c r="O99" s="34" t="s">
-        <v>701</v>
+        <v>479</v>
       </c>
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
       <c r="R99" s="35" t="s">
-        <v>702</v>
-      </c>
-      <c r="S99" s="35"/>
+        <v>480</v>
+      </c>
+      <c r="S99" s="35" t="s">
+        <v>481</v>
+      </c>
       <c r="T99" s="38" t="s">
-        <v>204</v>
+        <v>772</v>
       </c>
     </row>
     <row r="100" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="34" t="s">
-        <v>286</v>
+        <v>482</v>
       </c>
       <c r="B100" s="34" t="s">
         <v>59</v>
@@ -10075,37 +10121,39 @@
         <v>63</v>
       </c>
       <c r="I100" s="35" t="s">
-        <v>757</v>
+        <v>476</v>
       </c>
       <c r="J100" s="35" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="K100" s="35" t="s">
-        <v>756</v>
+        <v>483</v>
       </c>
       <c r="L100" s="35"/>
       <c r="M100" s="35" t="s">
-        <v>280</v>
+        <v>484</v>
       </c>
       <c r="N100" s="36">
-        <v>28570</v>
+        <v>29452</v>
       </c>
       <c r="O100" s="34" t="s">
-        <v>281</v>
+        <v>485</v>
       </c>
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
       <c r="R100" s="35" t="s">
-        <v>282</v>
-      </c>
-      <c r="S100" s="35"/>
+        <v>613</v>
+      </c>
+      <c r="S100" s="35" t="s">
+        <v>486</v>
+      </c>
       <c r="T100" s="38" t="s">
-        <v>180</v>
+        <v>772</v>
       </c>
     </row>
     <row r="101" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="34" t="s">
-        <v>434</v>
+        <v>781</v>
       </c>
       <c r="B101" s="34" t="s">
         <v>59</v>
@@ -10128,38 +10176,38 @@
       <c r="H101" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I101" s="35" t="s">
-        <v>435</v>
-      </c>
-      <c r="J101" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="K101" s="35" t="s">
-        <v>436</v>
-      </c>
-      <c r="L101" s="35"/>
+      <c r="I101" s="34" t="s">
+        <v>765</v>
+      </c>
+      <c r="J101" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="K101" s="34" t="s">
+        <v>770</v>
+      </c>
+      <c r="L101" s="34"/>
       <c r="M101" s="35" t="s">
-        <v>437</v>
-      </c>
-      <c r="N101" s="36">
-        <v>33544</v>
+        <v>796</v>
+      </c>
+      <c r="N101" s="36" t="s">
+        <v>797</v>
       </c>
       <c r="O101" s="34" t="s">
-        <v>438</v>
-      </c>
-      <c r="P101" s="35"/>
-      <c r="Q101" s="35"/>
+        <v>798</v>
+      </c>
+      <c r="P101" s="34"/>
+      <c r="Q101" s="34"/>
       <c r="R101" s="35" t="s">
-        <v>439</v>
-      </c>
-      <c r="S101" s="35"/>
+        <v>799</v>
+      </c>
+      <c r="S101" s="38"/>
       <c r="T101" s="38" t="s">
-        <v>141</v>
+        <v>774</v>
       </c>
     </row>
     <row r="102" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="34" t="s">
-        <v>398</v>
+        <v>356</v>
       </c>
       <c r="B102" s="34" t="s">
         <v>59</v>
@@ -10174,50 +10222,48 @@
         <v>62</v>
       </c>
       <c r="F102" s="35" t="s">
-        <v>126</v>
+        <v>631</v>
       </c>
       <c r="G102" s="34" t="s">
-        <v>221</v>
+        <v>664</v>
       </c>
       <c r="H102" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I102" s="35" t="s">
-        <v>96</v>
+        <v>357</v>
       </c>
       <c r="J102" s="35" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="K102" s="35" t="s">
-        <v>418</v>
+        <v>358</v>
       </c>
       <c r="L102" s="35" t="s">
-        <v>418</v>
+        <v>662</v>
       </c>
       <c r="M102" s="35" t="s">
-        <v>399</v>
-      </c>
-      <c r="N102" s="36">
-        <v>25204</v>
+        <v>359</v>
+      </c>
+      <c r="N102" s="36" t="s">
+        <v>670</v>
       </c>
       <c r="O102" s="34" t="s">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
       <c r="R102" s="35" t="s">
-        <v>401</v>
-      </c>
-      <c r="S102" s="35" t="s">
-        <v>402</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="S102" s="35"/>
       <c r="T102" s="38" t="s">
-        <v>150</v>
+        <v>772</v>
       </c>
     </row>
     <row r="103" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="34" t="s">
-        <v>270</v>
+        <v>692</v>
       </c>
       <c r="B103" s="34" t="s">
         <v>59</v>
@@ -10241,35 +10287,37 @@
         <v>63</v>
       </c>
       <c r="I103" s="35" t="s">
-        <v>96</v>
+        <v>693</v>
       </c>
       <c r="J103" s="35" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="K103" s="35" t="s">
-        <v>78</v>
+        <v>694</v>
       </c>
       <c r="L103" s="35"/>
       <c r="M103" s="35" t="s">
-        <v>276</v>
+        <v>695</v>
       </c>
       <c r="N103" s="36">
-        <v>26134</v>
+        <v>32200</v>
       </c>
       <c r="O103" s="34" t="s">
-        <v>166</v>
+        <v>696</v>
       </c>
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
-      <c r="R103" s="35"/>
+      <c r="R103" s="35" t="s">
+        <v>697</v>
+      </c>
       <c r="S103" s="35"/>
       <c r="T103" s="38" t="s">
-        <v>787</v>
+        <v>204</v>
       </c>
     </row>
     <row r="104" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="34" t="s">
-        <v>634</v>
+        <v>286</v>
       </c>
       <c r="B104" s="34" t="s">
         <v>59</v>
@@ -10287,45 +10335,43 @@
         <v>126</v>
       </c>
       <c r="G104" s="34" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="H104" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I104" s="35" t="s">
-        <v>591</v>
+        <v>751</v>
       </c>
       <c r="J104" s="35" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="K104" s="35" t="s">
-        <v>592</v>
-      </c>
-      <c r="L104" s="35" t="s">
-        <v>593</v>
-      </c>
+        <v>750</v>
+      </c>
+      <c r="L104" s="35"/>
       <c r="M104" s="35" t="s">
-        <v>594</v>
+        <v>280</v>
       </c>
       <c r="N104" s="36">
-        <v>31906</v>
+        <v>28570</v>
       </c>
       <c r="O104" s="34" t="s">
-        <v>595</v>
+        <v>281</v>
       </c>
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
       <c r="R104" s="35" t="s">
-        <v>596</v>
+        <v>282</v>
       </c>
       <c r="S104" s="35"/>
       <c r="T104" s="38" t="s">
-        <v>787</v>
+        <v>180</v>
       </c>
     </row>
     <row r="105" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="34" t="s">
-        <v>668</v>
+        <v>431</v>
       </c>
       <c r="B105" s="34" t="s">
         <v>59</v>
@@ -10340,37 +10386,37 @@
         <v>62</v>
       </c>
       <c r="F105" s="35" t="s">
-        <v>636</v>
+        <v>126</v>
       </c>
       <c r="G105" s="34" t="s">
-        <v>669</v>
+        <v>221</v>
       </c>
       <c r="H105" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I105" s="35" t="s">
-        <v>779</v>
+        <v>751</v>
       </c>
       <c r="J105" s="35" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K105" s="35" t="s">
-        <v>647</v>
+        <v>432</v>
       </c>
       <c r="L105" s="35"/>
       <c r="M105" s="35" t="s">
-        <v>677</v>
-      </c>
-      <c r="N105" s="36" t="s">
-        <v>678</v>
+        <v>433</v>
+      </c>
+      <c r="N105" s="36">
+        <v>33544</v>
       </c>
       <c r="O105" s="34" t="s">
-        <v>670</v>
+        <v>434</v>
       </c>
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
       <c r="R105" s="35" t="s">
-        <v>676</v>
+        <v>435</v>
       </c>
       <c r="S105" s="35"/>
       <c r="T105" s="38" t="s">
@@ -10379,7 +10425,7 @@
     </row>
     <row r="106" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="34" t="s">
-        <v>271</v>
+        <v>396</v>
       </c>
       <c r="B106" s="34" t="s">
         <v>59</v>
@@ -10391,49 +10437,53 @@
         <v>61</v>
       </c>
       <c r="E106" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F106" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G106" s="34" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="H106" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I106" s="35" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J106" s="35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K106" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="L106" s="35"/>
+        <v>416</v>
+      </c>
+      <c r="L106" s="35" t="s">
+        <v>416</v>
+      </c>
       <c r="M106" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="N106" s="36" t="s">
-        <v>671</v>
+        <v>397</v>
+      </c>
+      <c r="N106" s="36">
+        <v>25204</v>
       </c>
       <c r="O106" s="34" t="s">
-        <v>176</v>
+        <v>398</v>
       </c>
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
       <c r="R106" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="S106" s="35"/>
+        <v>399</v>
+      </c>
+      <c r="S106" s="35" t="s">
+        <v>400</v>
+      </c>
       <c r="T106" s="38" t="s">
-        <v>786</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="34" t="s">
-        <v>703</v>
+        <v>270</v>
       </c>
       <c r="B107" s="34" t="s">
         <v>59</v>
@@ -10457,39 +10507,35 @@
         <v>63</v>
       </c>
       <c r="I107" s="35" t="s">
-        <v>684</v>
+        <v>96</v>
       </c>
       <c r="J107" s="35" t="s">
-        <v>642</v>
+        <v>77</v>
       </c>
       <c r="K107" s="35" t="s">
-        <v>685</v>
-      </c>
-      <c r="L107" s="35" t="s">
-        <v>686</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="L107" s="35"/>
       <c r="M107" s="35" t="s">
-        <v>689</v>
-      </c>
-      <c r="N107" s="36" t="s">
-        <v>691</v>
+        <v>276</v>
+      </c>
+      <c r="N107" s="36">
+        <v>26134</v>
       </c>
       <c r="O107" s="34" t="s">
-        <v>687</v>
+        <v>166</v>
       </c>
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
-      <c r="R107" s="35" t="s">
-        <v>688</v>
-      </c>
+      <c r="R107" s="35"/>
       <c r="S107" s="35"/>
       <c r="T107" s="38" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
     </row>
     <row r="108" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="34" t="s">
-        <v>491</v>
+        <v>629</v>
       </c>
       <c r="B108" s="34" t="s">
         <v>59</v>
@@ -10507,45 +10553,43 @@
         <v>126</v>
       </c>
       <c r="G108" s="34" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H108" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I108" s="35" t="s">
-        <v>124</v>
+        <v>587</v>
       </c>
       <c r="J108" s="35" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="K108" s="35" t="s">
-        <v>330</v>
+        <v>588</v>
       </c>
       <c r="L108" s="35"/>
       <c r="M108" s="35" t="s">
-        <v>492</v>
+        <v>589</v>
       </c>
       <c r="N108" s="36">
-        <v>26766</v>
+        <v>31906</v>
       </c>
       <c r="O108" s="34" t="s">
-        <v>493</v>
+        <v>590</v>
       </c>
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
       <c r="R108" s="35" t="s">
-        <v>619</v>
-      </c>
-      <c r="S108" s="35" t="s">
-        <v>494</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="S108" s="35"/>
       <c r="T108" s="38" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
     </row>
     <row r="109" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="34" t="s">
-        <v>272</v>
+        <v>663</v>
       </c>
       <c r="B109" s="34" t="s">
         <v>59</v>
@@ -10560,46 +10604,46 @@
         <v>62</v>
       </c>
       <c r="F109" s="35" t="s">
-        <v>126</v>
+        <v>631</v>
       </c>
       <c r="G109" s="34" t="s">
-        <v>221</v>
+        <v>664</v>
       </c>
       <c r="H109" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I109" s="35" t="s">
-        <v>124</v>
+        <v>771</v>
       </c>
       <c r="J109" s="35" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="K109" s="35" t="s">
-        <v>125</v>
+        <v>642</v>
       </c>
       <c r="L109" s="35"/>
       <c r="M109" s="35" t="s">
-        <v>198</v>
-      </c>
-      <c r="N109" s="36">
-        <v>24263</v>
+        <v>672</v>
+      </c>
+      <c r="N109" s="36" t="s">
+        <v>673</v>
       </c>
       <c r="O109" s="34" t="s">
-        <v>199</v>
+        <v>665</v>
       </c>
       <c r="P109" s="35"/>
       <c r="Q109" s="35"/>
       <c r="R109" s="35" t="s">
-        <v>617</v>
+        <v>671</v>
       </c>
       <c r="S109" s="35"/>
       <c r="T109" s="38" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
     </row>
     <row r="110" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="34" t="s">
-        <v>780</v>
+        <v>271</v>
       </c>
       <c r="B110" s="34" t="s">
         <v>59</v>
@@ -10611,41 +10655,49 @@
         <v>61</v>
       </c>
       <c r="E110" s="35" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F110" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G110" s="34" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="H110" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I110" s="35" t="s">
-        <v>768</v>
+        <v>105</v>
       </c>
       <c r="J110" s="35" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K110" s="35" t="s">
-        <v>775</v>
+        <v>108</v>
       </c>
       <c r="L110" s="35"/>
-      <c r="M110" s="35"/>
-      <c r="N110" s="36"/>
-      <c r="O110" s="34"/>
+      <c r="M110" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="N110" s="36" t="s">
+        <v>666</v>
+      </c>
+      <c r="O110" s="34" t="s">
+        <v>176</v>
+      </c>
       <c r="P110" s="35"/>
       <c r="Q110" s="35"/>
-      <c r="R110" s="35"/>
+      <c r="R110" s="35" t="s">
+        <v>177</v>
+      </c>
       <c r="S110" s="35"/>
       <c r="T110" s="38" t="s">
-        <v>180</v>
+        <v>773</v>
       </c>
     </row>
     <row r="111" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="34" t="s">
-        <v>781</v>
+        <v>698</v>
       </c>
       <c r="B111" s="34" t="s">
         <v>59</v>
@@ -10669,29 +10721,39 @@
         <v>63</v>
       </c>
       <c r="I111" s="35" t="s">
-        <v>713</v>
+        <v>679</v>
       </c>
       <c r="J111" s="35" t="s">
-        <v>84</v>
+        <v>637</v>
       </c>
       <c r="K111" s="35" t="s">
-        <v>727</v>
-      </c>
-      <c r="L111" s="35"/>
-      <c r="M111" s="35"/>
-      <c r="N111" s="36"/>
-      <c r="O111" s="34"/>
+        <v>680</v>
+      </c>
+      <c r="L111" s="35" t="s">
+        <v>681</v>
+      </c>
+      <c r="M111" s="35" t="s">
+        <v>684</v>
+      </c>
+      <c r="N111" s="36" t="s">
+        <v>686</v>
+      </c>
+      <c r="O111" s="34" t="s">
+        <v>682</v>
+      </c>
       <c r="P111" s="35"/>
       <c r="Q111" s="35"/>
-      <c r="R111" s="35"/>
+      <c r="R111" s="35" t="s">
+        <v>683</v>
+      </c>
       <c r="S111" s="35"/>
       <c r="T111" s="38" t="s">
-        <v>180</v>
+        <v>772</v>
       </c>
     </row>
     <row r="112" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="34" t="s">
-        <v>782</v>
+        <v>487</v>
       </c>
       <c r="B112" s="34" t="s">
         <v>59</v>
@@ -10715,29 +10777,39 @@
         <v>63</v>
       </c>
       <c r="I112" s="35" t="s">
-        <v>769</v>
+        <v>124</v>
       </c>
       <c r="J112" s="35" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="K112" s="35" t="s">
-        <v>776</v>
+        <v>330</v>
       </c>
       <c r="L112" s="35"/>
-      <c r="M112" s="35"/>
-      <c r="N112" s="36"/>
-      <c r="O112" s="34"/>
+      <c r="M112" s="35" t="s">
+        <v>488</v>
+      </c>
+      <c r="N112" s="36">
+        <v>26766</v>
+      </c>
+      <c r="O112" s="34" t="s">
+        <v>489</v>
+      </c>
       <c r="P112" s="35"/>
       <c r="Q112" s="35"/>
-      <c r="R112" s="35"/>
-      <c r="S112" s="35"/>
+      <c r="R112" s="35" t="s">
+        <v>614</v>
+      </c>
+      <c r="S112" s="35" t="s">
+        <v>490</v>
+      </c>
       <c r="T112" s="38" t="s">
-        <v>180</v>
+        <v>772</v>
       </c>
     </row>
     <row r="113" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="34" t="s">
-        <v>783</v>
+        <v>272</v>
       </c>
       <c r="B113" s="34" t="s">
         <v>59</v>
@@ -10749,147 +10821,130 @@
         <v>61</v>
       </c>
       <c r="E113" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F113" s="35" t="s">
         <v>126</v>
       </c>
       <c r="G113" s="34" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="H113" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I113" s="35" t="s">
-        <v>770</v>
+        <v>124</v>
       </c>
       <c r="J113" s="35" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="K113" s="35" t="s">
-        <v>777</v>
+        <v>125</v>
       </c>
       <c r="L113" s="35"/>
-      <c r="M113" s="35"/>
-      <c r="N113" s="36"/>
-      <c r="O113" s="34"/>
+      <c r="M113" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="N113" s="36">
+        <v>24263</v>
+      </c>
+      <c r="O113" s="34" t="s">
+        <v>199</v>
+      </c>
       <c r="P113" s="35"/>
       <c r="Q113" s="35"/>
-      <c r="R113" s="35"/>
+      <c r="R113" s="35" t="s">
+        <v>612</v>
+      </c>
       <c r="S113" s="35"/>
       <c r="T113" s="38" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="114" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="34" t="s">
-        <v>784</v>
-      </c>
-      <c r="B114" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C114" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D114" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="E114" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="F114" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G114" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="H114" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="I114" s="35" t="s">
-        <v>771</v>
-      </c>
-      <c r="J114" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="K114" s="35" t="s">
-        <v>778</v>
-      </c>
-      <c r="L114" s="35"/>
-      <c r="M114" s="35"/>
-      <c r="N114" s="36"/>
-      <c r="O114" s="34"/>
-      <c r="P114" s="35"/>
-      <c r="Q114" s="35"/>
-      <c r="R114" s="35"/>
-      <c r="S114" s="35"/>
       <c r="T114" s="38" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="115" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="T115" s="38" t="s">
-        <v>787</v>
-      </c>
+        <v>774</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I120" s="34"/>
+    </row>
+    <row r="121" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I121" s="35"/>
+    </row>
+    <row r="122" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I122" s="35"/>
+    </row>
+    <row r="123" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I123" s="35"/>
+    </row>
+    <row r="124" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I124" s="34"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" sort="0"/>
-  <autoFilter ref="A1:T115" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:T114" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U113">
     <sortCondition ref="I2:I17000"/>
     <sortCondition ref="K2:K17000"/>
   </sortState>
   <phoneticPr fontId="31" type="noConversion"/>
-  <conditionalFormatting sqref="A115:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="14" priority="585"/>
+  <conditionalFormatting sqref="A114 A1 A120:A1048576">
+    <cfRule type="duplicateValues" dxfId="16" priority="590"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H97 H105:H114">
-    <cfRule type="containsText" dxfId="13" priority="16" operator="containsText" text="Inactive - ADS">
+  <conditionalFormatting sqref="H2:H101 H109:H113">
+    <cfRule type="containsText" dxfId="15" priority="21" operator="containsText" text="Inactive - ADS">
       <formula>NOT(ISERROR(SEARCH("Inactive - ADS",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H98">
-    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="Inactive-ADS">
-      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H98)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H99:H100">
-    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="Inactive - ADS">
-      <formula>NOT(ISERROR(SEARCH("Inactive - ADS",H99)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H101:H104">
-    <cfRule type="containsText" dxfId="10" priority="7" operator="containsText" text="Inactive-ADS">
+  <conditionalFormatting sqref="H101:H102">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Inactive-ADS">
       <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H101)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1 M115:M65094">
-    <cfRule type="expression" dxfId="9" priority="582" stopIfTrue="1">
+  <conditionalFormatting sqref="H103:H104">
+    <cfRule type="containsText" dxfId="13" priority="15" operator="containsText" text="Inactive - ADS">
+      <formula>NOT(ISERROR(SEARCH("Inactive - ADS",H103)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H105:H108">
+    <cfRule type="containsText" dxfId="12" priority="12" operator="containsText" text="Inactive-ADS">
+      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H105)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1 M114 M120:M65093">
+    <cfRule type="expression" dxfId="11" priority="587" stopIfTrue="1">
       <formula>LEN(M1)&lt;&gt;13</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M97">
-    <cfRule type="duplicateValues" dxfId="8" priority="661"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M114">
-    <cfRule type="expression" dxfId="7" priority="8">
+  <conditionalFormatting sqref="M2:M113">
+    <cfRule type="expression" dxfId="10" priority="13">
       <formula>LEN(M2)&lt;13</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M98">
-    <cfRule type="duplicateValues" dxfId="6" priority="15"/>
+  <conditionalFormatting sqref="M34:M92 M94:M100 M2:M23 M25:M31">
+    <cfRule type="duplicateValues" dxfId="9" priority="676"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M99:M100">
-    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
+  <conditionalFormatting sqref="M93 M32:M33 M24">
+    <cfRule type="duplicateValues" dxfId="8" priority="712"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M101:M104">
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+  <conditionalFormatting sqref="M101">
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M105:M114">
-    <cfRule type="duplicateValues" dxfId="3" priority="667"/>
+  <conditionalFormatting sqref="M102">
+    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M115:M65094 M1">
-    <cfRule type="duplicateValues" dxfId="2" priority="642" stopIfTrue="1"/>
+  <conditionalFormatting sqref="M103:M104">
+    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M105:M108">
+    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M109:M113">
+    <cfRule type="duplicateValues" dxfId="3" priority="716"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M114 M1 M120:M65093">
+    <cfRule type="duplicateValues" dxfId="2" priority="647" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -11059,21 +11114,21 @@
         <v>141</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C3" s="31" t="s">
         <v>317</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -11084,7 +11139,7 @@
         <v>148</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -11092,21 +11147,21 @@
         <v>167</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -11114,10 +11169,10 @@
         <v>180</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -11128,30 +11183,30 @@
         <v>202</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B10"/>
       <c r="C10" s="31" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">

--- a/import-files/WC-CTN-O(1).xlsx
+++ b/import-files/WC-CTN-O(1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Pictures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Videos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCAC675-2707-47DC-8C2C-548BBBBB53D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AD5DE8-211E-4A1B-A7C9-7D59B623FD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Club Details" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Membership!$A$1:$T$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Membership!$A$1:$T$107</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="826">
   <si>
     <t>How To Complete/Update existing information.</t>
   </si>
@@ -466,9 +466,15 @@
     <t>Brent</t>
   </si>
   <si>
+    <t>Willoughby</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
+    <t>Carl</t>
+  </si>
+  <si>
     <t>S</t>
   </si>
   <si>
@@ -520,12 +526,21 @@
     <t>Magmoed</t>
   </si>
   <si>
+    <t>MG</t>
+  </si>
+  <si>
     <t>Maart</t>
   </si>
   <si>
+    <t>NG</t>
+  </si>
+  <si>
     <t>Martin</t>
   </si>
   <si>
+    <t>DA</t>
+  </si>
+  <si>
     <t>Sawyer</t>
   </si>
   <si>
@@ -640,15 +655,24 @@
     <t>Dowman</t>
   </si>
   <si>
+    <t>GW</t>
+  </si>
+  <si>
     <t>Hilton</t>
   </si>
   <si>
     <t>Pieterse</t>
   </si>
   <si>
+    <t>RW</t>
+  </si>
+  <si>
     <t>Olivier</t>
   </si>
   <si>
+    <t>RM</t>
+  </si>
+  <si>
     <t>Oliphant</t>
   </si>
   <si>
@@ -658,6 +682,9 @@
     <t>Hendricks</t>
   </si>
   <si>
+    <t>JC</t>
+  </si>
+  <si>
     <t>7407035203082</t>
   </si>
   <si>
@@ -670,6 +697,9 @@
     <t>earl@pnp.co.za</t>
   </si>
   <si>
+    <t>Best of Order</t>
+  </si>
+  <si>
     <t>8509085191080</t>
   </si>
   <si>
@@ -682,6 +712,15 @@
     <t>Best Of Order</t>
   </si>
   <si>
+    <t>8008315040084</t>
+  </si>
+  <si>
+    <t>23 Vlamboom Street, Ferness Estate, Ottery</t>
+  </si>
+  <si>
+    <t>0826047025</t>
+  </si>
+  <si>
     <t>43 Chatham Road, Heathfield</t>
   </si>
   <si>
@@ -1075,6 +1114,9 @@
     <t>DSA-210555</t>
   </si>
   <si>
+    <t>DSA-210556</t>
+  </si>
+  <si>
     <t>7411145109080</t>
   </si>
   <si>
@@ -1144,6 +1186,9 @@
     <t>DSA-180194</t>
   </si>
   <si>
+    <t>AJ</t>
+  </si>
+  <si>
     <t>6406045181081</t>
   </si>
   <si>
@@ -1162,6 +1207,9 @@
     <t>Joshua</t>
   </si>
   <si>
+    <t>LC</t>
+  </si>
+  <si>
     <t>7601170140089</t>
   </si>
   <si>
@@ -1172,6 +1220,9 @@
   </si>
   <si>
     <t>leeann.joshua@gmail.com</t>
+  </si>
+  <si>
+    <t>L J</t>
   </si>
   <si>
     <t>8210305089085</t>
@@ -1265,6 +1316,9 @@
     <t>Maneveldt</t>
   </si>
   <si>
+    <t>KJ</t>
+  </si>
+  <si>
     <t>6408165227082</t>
   </si>
   <si>
@@ -1448,6 +1502,9 @@
     <t>DSA-180184</t>
   </si>
   <si>
+    <t>GG</t>
+  </si>
+  <si>
     <t>6901015271086</t>
   </si>
   <si>
@@ -1616,6 +1673,12 @@
     <t>9305075343081</t>
   </si>
   <si>
+    <t>MALE</t>
+  </si>
+  <si>
+    <t>COLOURED</t>
+  </si>
+  <si>
     <t>Glen</t>
   </si>
   <si>
@@ -2252,6 +2315,9 @@
     <t>WM</t>
   </si>
   <si>
+    <t>EH</t>
+  </si>
+  <si>
     <t>53 Strelitzia Street Vredenburg</t>
   </si>
   <si>
@@ -2270,6 +2336,9 @@
     <t>1954-11-14</t>
   </si>
   <si>
+    <t>WHITE</t>
+  </si>
+  <si>
     <t>0752679976</t>
   </si>
   <si>
@@ -2360,6 +2429,9 @@
     <t>DSA-260117</t>
   </si>
   <si>
+    <t>CL</t>
+  </si>
+  <si>
     <t>Cheezy</t>
   </si>
   <si>
@@ -2507,157 +2579,160 @@
     <t>DSA-260223</t>
   </si>
   <si>
+    <t>Doolings</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>6 Tottenham Close, London Village, Weltevreden Valley</t>
+  </si>
+  <si>
+    <t>0814055862</t>
+  </si>
+  <si>
+    <t>5705205196081</t>
+  </si>
+  <si>
+    <t>1957-05-20</t>
+  </si>
+  <si>
+    <t>Roberts</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>Chesley</t>
+  </si>
+  <si>
+    <t>32 Shepherd Way, Westridge, Mitchell's Plain</t>
+  </si>
+  <si>
+    <t>5503135006086</t>
+  </si>
+  <si>
+    <t>1955-03-13</t>
+  </si>
+  <si>
+    <t>0679383734</t>
+  </si>
+  <si>
+    <t>Damonse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgina </t>
+  </si>
+  <si>
+    <t>6404050131083</t>
+  </si>
+  <si>
+    <t>1964-04-05</t>
+  </si>
+  <si>
+    <t>23B Jasmine Street Bonteheuwel 7764</t>
+  </si>
+  <si>
+    <t>DSA-230265</t>
+  </si>
+  <si>
+    <t>Solomon</t>
+  </si>
+  <si>
+    <t>Raymond</t>
+  </si>
+  <si>
+    <t>7508195147082</t>
+  </si>
+  <si>
+    <t>15 Bloubos Singel, Eastridge</t>
+  </si>
+  <si>
+    <t>0618527688</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Fernando</t>
+  </si>
+  <si>
+    <t>8704235093084</t>
+  </si>
+  <si>
+    <t>1975-08-19</t>
+  </si>
+  <si>
+    <t>1987-04-23</t>
+  </si>
+  <si>
+    <t>8 Cedar Avenue, Rocklands</t>
+  </si>
+  <si>
+    <t>'0784931174</t>
+  </si>
+  <si>
+    <t>DSA-220380</t>
+  </si>
+  <si>
+    <t>DSA-190274</t>
+  </si>
+  <si>
+    <t>DSA-260508</t>
+  </si>
+  <si>
+    <t>DSA-260509</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Jerome</t>
+  </si>
+  <si>
+    <t>Cheslyn</t>
+  </si>
+  <si>
+    <t>Ebrahiem</t>
+  </si>
+  <si>
+    <t>Ashley</t>
+  </si>
+  <si>
+    <t>Llewellen</t>
+  </si>
+  <si>
+    <t>Lee-Ann</t>
+  </si>
+  <si>
+    <t>Nigel</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Desiree</t>
+  </si>
+  <si>
+    <t>Ryan</t>
+  </si>
+  <si>
     <t>Eugene</t>
   </si>
   <si>
+    <t>Hartnick</t>
+  </si>
+  <si>
+    <t>De Long</t>
+  </si>
+  <si>
     <t>Talmarkes</t>
   </si>
   <si>
-    <t>Ryan</t>
-  </si>
-  <si>
-    <t>Desiree</t>
-  </si>
-  <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>Nigel</t>
-  </si>
-  <si>
-    <t>Lee-Ann</t>
-  </si>
-  <si>
-    <t>Llewellen</t>
-  </si>
-  <si>
-    <t>Ashley</t>
-  </si>
-  <si>
-    <t>Ebrahiem</t>
-  </si>
-  <si>
-    <t>Mark</t>
-  </si>
-  <si>
-    <t>Hartnick</t>
-  </si>
-  <si>
-    <t>Roberts</t>
-  </si>
-  <si>
-    <t>Dooling</t>
-  </si>
-  <si>
-    <t>Damonse</t>
-  </si>
-  <si>
-    <t>Solomon</t>
-  </si>
-  <si>
-    <t>Jerome</t>
-  </si>
-  <si>
-    <t>De Long</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L </t>
-  </si>
-  <si>
-    <t>Chesley</t>
-  </si>
-  <si>
-    <t>Raymond</t>
+    <t>NE</t>
   </si>
   <si>
     <t>V/D Westhuizen</t>
-  </si>
-  <si>
-    <t>Guardians</t>
-  </si>
-  <si>
-    <t>Brisdel</t>
-  </si>
-  <si>
-    <t>East Side</t>
-  </si>
-  <si>
-    <t>DSA-180519</t>
-  </si>
-  <si>
-    <t>Melvin</t>
-  </si>
-  <si>
-    <t>4909035157088</t>
-  </si>
-  <si>
-    <t>DSA-220380</t>
-  </si>
-  <si>
-    <t>DSA-260508</t>
-  </si>
-  <si>
-    <t>DSA-260509</t>
-  </si>
-  <si>
-    <t>DSA-230265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Georgina </t>
-  </si>
-  <si>
-    <t>6404050131083</t>
-  </si>
-  <si>
-    <t>1964-04-05</t>
-  </si>
-  <si>
-    <t>23B Jasmine Street Bonteheuwel 7764</t>
-  </si>
-  <si>
-    <t>Michael</t>
-  </si>
-  <si>
-    <t>5705205196081</t>
-  </si>
-  <si>
-    <t>1957-05-20</t>
-  </si>
-  <si>
-    <t>6 Tottenham Close, London Village, Weltevreden Valley</t>
-  </si>
-  <si>
-    <t>0814055862</t>
-  </si>
-  <si>
-    <t>CG</t>
-  </si>
-  <si>
-    <t>5503135006086</t>
-  </si>
-  <si>
-    <t>1955-03-13</t>
-  </si>
-  <si>
-    <t>32 Shepherd Way, Westridge, Mitchell's Plain</t>
-  </si>
-  <si>
-    <t>0679383734</t>
-  </si>
-  <si>
-    <t>7508195147082</t>
-  </si>
-  <si>
-    <t>1975-08-19</t>
-  </si>
-  <si>
-    <t>15 Bloubos Singel, Eastridge</t>
-  </si>
-  <si>
-    <t>0618527688</t>
-  </si>
-  <si>
-    <t>Cheslyn</t>
   </si>
 </sst>
 </file>
@@ -2669,7 +2744,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2886,6 +2961,13 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2954,7 +3036,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="14">
+  <cellStyleXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
@@ -2972,6 +3054,9 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3110,6 +3195,12 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3125,16 +3216,11 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="14">
+  <cellStyles count="17">
     <cellStyle name="Comma 2" xfId="8" xr:uid="{34B69B07-4B63-4829-81F8-97E864EAE812}"/>
     <cellStyle name="Comma 3" xfId="13" xr:uid="{6CD0E041-AA9C-4A03-AFA7-EF6407F81488}"/>
+    <cellStyle name="Comma 3 2" xfId="16" xr:uid="{D2CC3490-499A-4F14-94D9-FF29398A1FD3}"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Hyperlink 4" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3147,8 +3233,10 @@
     <cellStyle name="Normal 5" xfId="9" xr:uid="{28D89999-3ABD-402B-8681-F83C97C492A6}"/>
     <cellStyle name="Normal 6" xfId="7" xr:uid="{787D59DA-ED81-4119-B772-4CD1818DC02D}"/>
     <cellStyle name="Normal 7" xfId="12" xr:uid="{93FD18A2-4F78-4C7B-91F3-95D146AE0B82}"/>
+    <cellStyle name="Normal 7 2" xfId="15" xr:uid="{EE5848B8-56C8-45F1-A517-B885E1AF4D16}"/>
+    <cellStyle name="Normal 8" xfId="14" xr:uid="{4EABBA24-76A8-4352-B39A-B5112A27DA65}"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
     <dxf>
       <font>
         <b/>
@@ -3170,6 +3258,16 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i/>
         <color rgb="FFFF0000"/>
@@ -3177,16 +3275,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3268,6 +3356,16 @@
         <i/>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4197,7 +4295,7 @@
     <mergeCell ref="A22:B22"/>
   </mergeCells>
   <conditionalFormatting sqref="B16">
-    <cfRule type="containsText" dxfId="17" priority="1" stopIfTrue="1" operator="containsText" text="If a duplicate ID exist in the registration system, it will be RED with a light red background.">
+    <cfRule type="containsText" dxfId="18" priority="1" stopIfTrue="1" operator="containsText" text="If a duplicate ID exist in the registration system, it will be RED with a light red background.">
       <formula>NOT(ISERROR(SEARCH("If a duplicate ID exist in the registration system, it will be RED with a light red background.",B16)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4225,73 +4323,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
     </row>
     <row r="2" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>222</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
+      <c r="A2" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
     </row>
     <row r="3" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
     </row>
     <row r="6" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47" t="s">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="47"/>
+      <c r="D8" s="42"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>49</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>49</v>
@@ -4303,7 +4401,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>27</v>
@@ -4315,7 +4413,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>28</v>
@@ -4327,7 +4425,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>17</v>
@@ -4359,7 +4457,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>18</v>
@@ -4377,33 +4475,33 @@
       <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="48"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47" t="s">
+      <c r="B18" s="42"/>
+      <c r="C18" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="47"/>
+      <c r="D18" s="42"/>
     </row>
     <row r="19" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>49</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4411,13 +4509,13 @@
         <v>27</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>27</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4425,13 +4523,13 @@
         <v>28</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4439,7 +4537,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>17</v>
@@ -4471,13 +4569,13 @@
         <v>18</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4485,43 +4583,43 @@
         <v>29</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="47" t="s">
+      <c r="A28" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47" t="s">
+      <c r="B28" s="42"/>
+      <c r="C28" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="47"/>
+      <c r="D28" s="42"/>
     </row>
     <row r="29" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>49</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>49</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4529,13 +4627,13 @@
         <v>27</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>27</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4543,13 +4641,13 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4561,7 +4659,7 @@
         <v>17</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4589,13 +4687,13 @@
         <v>18</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4603,13 +4701,13 @@
         <v>29</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4620,6 +4718,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="A18:B18"/>
@@ -4628,12 +4732,6 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B26" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -4652,7 +4750,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:U124"/>
+  <dimension ref="A1:U113"/>
   <sheetFormatPr defaultColWidth="17.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" style="28" bestFit="1" customWidth="1"/>
@@ -4681,7 +4779,7 @@
   <sheetData>
     <row r="1" spans="1:20" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>33</v>
@@ -4720,7 +4818,7 @@
         <v>14</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="O1" s="10" t="s">
         <v>15</v>
@@ -4743,7 +4841,7 @@
     </row>
     <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="B2" s="34" t="s">
         <v>59</v>
@@ -4758,46 +4856,46 @@
         <v>62</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H2" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="J2" s="35" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="K2" s="35" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L2" s="35"/>
       <c r="M2" s="35" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="N2" s="36">
         <v>18768</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
       <c r="R2" s="35" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="S2" s="37"/>
       <c r="T2" s="37" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="B3" s="34" t="s">
         <v>59</v>
@@ -4812,46 +4910,46 @@
         <v>62</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H3" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="J3" s="34" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K3" s="34" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="L3" s="34"/>
       <c r="M3" s="35" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="N3" s="36">
         <v>21633</v>
       </c>
       <c r="O3" s="34" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="P3" s="34"/>
       <c r="Q3" s="34"/>
       <c r="R3" s="35" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="S3" s="38"/>
       <c r="T3" s="38" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="B4" s="34" t="s">
         <v>59</v>
@@ -4863,49 +4961,49 @@
         <v>61</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H4" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I4" s="34" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="J4" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K4" s="34" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="L4" s="34"/>
       <c r="M4" s="35" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="O4" s="34" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="P4" s="34"/>
       <c r="Q4" s="34"/>
       <c r="R4" s="35" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="S4" s="38"/>
       <c r="T4" s="38" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>775</v>
+        <v>564</v>
       </c>
       <c r="B5" s="34" t="s">
         <v>59</v>
@@ -4917,45 +5015,51 @@
         <v>61</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H5" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I5" s="34" t="s">
-        <v>351</v>
-      </c>
-      <c r="J5" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="K5" s="34" t="s">
-        <v>776</v>
-      </c>
-      <c r="L5" s="34"/>
+      <c r="I5" s="35" t="s">
+        <v>369</v>
+      </c>
+      <c r="J5" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="K5" s="35" t="s">
+        <v>540</v>
+      </c>
+      <c r="L5" s="35" t="s">
+        <v>541</v>
+      </c>
       <c r="M5" s="35" t="s">
-        <v>777</v>
+        <v>542</v>
       </c>
       <c r="N5" s="36">
-        <v>18144</v>
-      </c>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38" t="s">
-        <v>150</v>
+        <v>34958</v>
+      </c>
+      <c r="O5" s="34" t="s">
+        <v>543</v>
+      </c>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35" t="s">
+        <v>642</v>
+      </c>
+      <c r="S5" s="35"/>
+      <c r="T5" s="35" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="B6" s="34" t="s">
         <v>59</v>
@@ -4970,48 +5074,46 @@
         <v>62</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H6" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="35" t="s">
-        <v>351</v>
-      </c>
-      <c r="J6" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="K6" s="35" t="s">
-        <v>519</v>
-      </c>
-      <c r="L6" s="35" t="s">
-        <v>520</v>
-      </c>
+      <c r="I6" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="L6" s="34"/>
       <c r="M6" s="35" t="s">
-        <v>521</v>
+        <v>177</v>
       </c>
       <c r="N6" s="36">
-        <v>34958</v>
+        <v>20787</v>
       </c>
       <c r="O6" s="34" t="s">
-        <v>522</v>
-      </c>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
+        <v>176</v>
+      </c>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="34"/>
       <c r="R6" s="35" t="s">
-        <v>621</v>
-      </c>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35" t="s">
-        <v>772</v>
+        <v>178</v>
+      </c>
+      <c r="S6" s="38"/>
+      <c r="T6" s="38" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>59</v>
@@ -5026,46 +5128,44 @@
         <v>62</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H7" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="J7" s="34" t="s">
-        <v>72</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="J7" s="34"/>
       <c r="K7" s="34" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L7" s="34"/>
       <c r="M7" s="35" t="s">
-        <v>164</v>
+        <v>288</v>
       </c>
       <c r="N7" s="36">
-        <v>20787</v>
+        <v>30024</v>
       </c>
       <c r="O7" s="34" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="P7" s="34"/>
       <c r="Q7" s="34"/>
       <c r="R7" s="35" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="S7" s="38"/>
       <c r="T7" s="38" t="s">
-        <v>204</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
-        <v>250</v>
+        <v>697</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>59</v>
@@ -5080,46 +5180,46 @@
         <v>62</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H8" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="J8" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="K8" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="L8" s="34"/>
+      <c r="I8" s="35" t="s">
+        <v>619</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" s="35" t="s">
+        <v>698</v>
+      </c>
+      <c r="L8" s="35"/>
       <c r="M8" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="N8" s="36">
-        <v>30024</v>
+        <v>699</v>
+      </c>
+      <c r="N8" s="36" t="s">
+        <v>708</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
+        <v>700</v>
+      </c>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
       <c r="R8" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="S8" s="38"/>
+        <v>701</v>
+      </c>
+      <c r="S8" s="35"/>
       <c r="T8" s="38" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
-        <v>674</v>
+        <v>618</v>
       </c>
       <c r="B9" s="34" t="s">
         <v>59</v>
@@ -5134,46 +5234,46 @@
         <v>62</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H9" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="35" t="s">
-        <v>598</v>
-      </c>
-      <c r="J9" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" s="35" t="s">
-        <v>675</v>
-      </c>
-      <c r="L9" s="35"/>
+      <c r="I9" s="34" t="s">
+        <v>619</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>620</v>
+      </c>
+      <c r="L9" s="34"/>
       <c r="M9" s="35" t="s">
-        <v>676</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>685</v>
+        <v>621</v>
+      </c>
+      <c r="N9" s="36">
+        <v>23651</v>
       </c>
       <c r="O9" s="34" t="s">
-        <v>677</v>
-      </c>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
+        <v>622</v>
+      </c>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="34"/>
       <c r="R9" s="35" t="s">
-        <v>678</v>
-      </c>
-      <c r="S9" s="35"/>
+        <v>623</v>
+      </c>
+      <c r="S9" s="38"/>
       <c r="T9" s="38" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>597</v>
+        <v>255</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>59</v>
@@ -5188,46 +5288,46 @@
         <v>62</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H10" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>598</v>
+        <v>127</v>
       </c>
       <c r="J10" s="34" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>599</v>
+        <v>128</v>
       </c>
       <c r="L10" s="34"/>
       <c r="M10" s="35" t="s">
-        <v>600</v>
+        <v>209</v>
       </c>
       <c r="N10" s="36">
-        <v>23651</v>
+        <v>24982</v>
       </c>
       <c r="O10" s="34" t="s">
-        <v>601</v>
+        <v>210</v>
       </c>
       <c r="P10" s="34"/>
       <c r="Q10" s="34"/>
-      <c r="R10" s="35" t="s">
-        <v>602</v>
-      </c>
-      <c r="S10" s="38"/>
+      <c r="R10" s="34" t="s">
+        <v>643</v>
+      </c>
+      <c r="S10" s="35"/>
       <c r="T10" s="38" t="s">
-        <v>141</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>242</v>
+        <v>439</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>59</v>
@@ -5242,46 +5342,50 @@
         <v>62</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H11" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="J11" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="K11" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="L11" s="34"/>
+      <c r="I11" s="35" t="s">
+        <v>420</v>
+      </c>
+      <c r="J11" s="35" t="s">
+        <v>301</v>
+      </c>
+      <c r="K11" s="35" t="s">
+        <v>421</v>
+      </c>
+      <c r="L11" s="35" t="s">
+        <v>421</v>
+      </c>
       <c r="M11" s="35" t="s">
-        <v>196</v>
+        <v>422</v>
       </c>
       <c r="N11" s="36">
-        <v>24982</v>
+        <v>26677</v>
       </c>
       <c r="O11" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34" t="s">
-        <v>622</v>
-      </c>
-      <c r="S11" s="35"/>
+        <v>423</v>
+      </c>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35" t="s">
+        <v>424</v>
+      </c>
+      <c r="S11" s="35" t="s">
+        <v>425</v>
+      </c>
       <c r="T11" s="38" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
-        <v>420</v>
+      <c r="A12" s="35" t="s">
+        <v>769</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>59</v>
@@ -5296,50 +5400,46 @@
         <v>62</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H12" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="35" t="s">
-        <v>401</v>
-      </c>
-      <c r="J12" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="K12" s="35" t="s">
-        <v>402</v>
-      </c>
-      <c r="L12" s="35" t="s">
-        <v>402</v>
-      </c>
+      <c r="I12" s="34" t="s">
+        <v>467</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="K12" s="34" t="s">
+        <v>763</v>
+      </c>
+      <c r="L12" s="34"/>
       <c r="M12" s="35" t="s">
-        <v>403</v>
-      </c>
-      <c r="N12" s="36">
-        <v>26677</v>
+        <v>764</v>
+      </c>
+      <c r="N12" s="36" t="s">
+        <v>765</v>
       </c>
       <c r="O12" s="34" t="s">
-        <v>404</v>
-      </c>
-      <c r="P12" s="35"/>
-      <c r="Q12" s="35"/>
+        <v>470</v>
+      </c>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
       <c r="R12" s="35" t="s">
-        <v>405</v>
-      </c>
-      <c r="S12" s="35" t="s">
-        <v>406</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="S12" s="39"/>
       <c r="T12" s="38" t="s">
-        <v>150</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
-        <v>745</v>
+        <v>770</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>59</v>
@@ -5354,46 +5454,46 @@
         <v>62</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H13" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="J13" s="34" t="s">
-        <v>287</v>
+        <v>108</v>
       </c>
       <c r="K13" s="34" t="s">
-        <v>739</v>
+        <v>759</v>
       </c>
       <c r="L13" s="34"/>
       <c r="M13" s="35" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="N13" s="36" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="O13" s="34" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="P13" s="34"/>
       <c r="Q13" s="34"/>
       <c r="R13" s="35" t="s">
-        <v>743</v>
+        <v>766</v>
       </c>
       <c r="S13" s="39"/>
       <c r="T13" s="38" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
-        <v>746</v>
+      <c r="A14" s="34" t="s">
+        <v>768</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>59</v>
@@ -5408,46 +5508,46 @@
         <v>62</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H14" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="J14" s="34" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="35" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="N14" s="36" t="s">
-        <v>737</v>
+        <v>757</v>
       </c>
       <c r="O14" s="34" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="P14" s="34"/>
       <c r="Q14" s="34"/>
       <c r="R14" s="35" t="s">
-        <v>742</v>
+        <v>758</v>
       </c>
       <c r="S14" s="39"/>
       <c r="T14" s="38" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
-        <v>744</v>
+        <v>528</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>59</v>
@@ -5462,46 +5562,46 @@
         <v>62</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I15" s="34" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="J15" s="34" t="s">
-        <v>71</v>
+        <v>468</v>
       </c>
       <c r="K15" s="34" t="s">
-        <v>738</v>
+        <v>469</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="35" t="s">
-        <v>732</v>
+        <v>471</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>733</v>
+        <v>755</v>
       </c>
       <c r="O15" s="34" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="P15" s="34"/>
       <c r="Q15" s="34"/>
       <c r="R15" s="35" t="s">
-        <v>734</v>
+        <v>749</v>
       </c>
       <c r="S15" s="39"/>
       <c r="T15" s="38" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
-        <v>507</v>
+        <v>264</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>59</v>
@@ -5516,46 +5616,46 @@
         <v>62</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H16" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I16" s="34" t="s">
-        <v>448</v>
+        <v>114</v>
       </c>
       <c r="J16" s="34" t="s">
-        <v>449</v>
+        <v>75</v>
       </c>
       <c r="K16" s="34" t="s">
-        <v>450</v>
+        <v>124</v>
       </c>
       <c r="L16" s="34"/>
       <c r="M16" s="35" t="s">
-        <v>452</v>
-      </c>
-      <c r="N16" s="36" t="s">
-        <v>731</v>
+        <v>202</v>
+      </c>
+      <c r="N16" s="36">
+        <v>23212</v>
       </c>
       <c r="O16" s="34" t="s">
-        <v>451</v>
+        <v>203</v>
       </c>
       <c r="P16" s="34"/>
       <c r="Q16" s="34"/>
       <c r="R16" s="35" t="s">
-        <v>725</v>
+        <v>204</v>
       </c>
       <c r="S16" s="39"/>
       <c r="T16" s="38" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
-        <v>251</v>
+        <v>460</v>
       </c>
       <c r="B17" s="34" t="s">
         <v>59</v>
@@ -5570,46 +5670,48 @@
         <v>62</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="H17" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="H17" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="I17" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="J17" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="K17" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="L17" s="34"/>
+      <c r="I17" s="35" t="s">
+        <v>455</v>
+      </c>
+      <c r="J17" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="K17" s="35" t="s">
+        <v>456</v>
+      </c>
+      <c r="L17" s="35" t="s">
+        <v>455</v>
+      </c>
       <c r="M17" s="35" t="s">
-        <v>189</v>
+        <v>457</v>
       </c>
       <c r="N17" s="36">
-        <v>23212</v>
-      </c>
-      <c r="O17" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
+        <v>28381</v>
+      </c>
+      <c r="O17" s="35" t="s">
+        <v>458</v>
+      </c>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
       <c r="R17" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="S17" s="39"/>
-      <c r="T17" s="38" t="s">
-        <v>180</v>
+        <v>459</v>
+      </c>
+      <c r="S17" s="37"/>
+      <c r="T17" s="37" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
-        <v>441</v>
+        <v>568</v>
       </c>
       <c r="B18" s="34" t="s">
         <v>59</v>
@@ -5624,48 +5726,44 @@
         <v>62</v>
       </c>
       <c r="F18" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G18" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="H18" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="H18" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I18" s="35" t="s">
-        <v>436</v>
-      </c>
-      <c r="J18" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="K18" s="35" t="s">
-        <v>437</v>
-      </c>
-      <c r="L18" s="35" t="s">
-        <v>436</v>
-      </c>
+      <c r="I18" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="J18" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" s="34" t="s">
+        <v>558</v>
+      </c>
+      <c r="L18" s="34"/>
       <c r="M18" s="35" t="s">
-        <v>438</v>
+        <v>560</v>
       </c>
       <c r="N18" s="36">
-        <v>28381</v>
-      </c>
-      <c r="O18" s="35" t="s">
-        <v>439</v>
-      </c>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35" t="s">
-        <v>440</v>
-      </c>
-      <c r="S18" s="37"/>
-      <c r="T18" s="37" t="s">
-        <v>141</v>
+        <v>37912</v>
+      </c>
+      <c r="O18" s="34" t="s">
+        <v>559</v>
+      </c>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="39"/>
+      <c r="T18" s="38" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
-        <v>547</v>
+        <v>303</v>
       </c>
       <c r="B19" s="34" t="s">
         <v>59</v>
@@ -5680,44 +5778,48 @@
         <v>62</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H19" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I19" s="34" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="J19" s="34" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="K19" s="34" t="s">
-        <v>537</v>
+        <v>305</v>
       </c>
       <c r="L19" s="34"/>
       <c r="M19" s="35" t="s">
-        <v>539</v>
+        <v>306</v>
       </c>
       <c r="N19" s="36">
-        <v>37912</v>
+        <v>23337</v>
       </c>
       <c r="O19" s="34" t="s">
-        <v>538</v>
+        <v>341</v>
       </c>
       <c r="P19" s="34"/>
       <c r="Q19" s="34"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="39"/>
+      <c r="R19" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="S19" s="38" t="s">
+        <v>308</v>
+      </c>
       <c r="T19" s="38" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>289</v>
+        <v>566</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>59</v>
@@ -5732,48 +5834,42 @@
         <v>62</v>
       </c>
       <c r="F20" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H20" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I20" s="34" t="s">
-        <v>290</v>
-      </c>
-      <c r="J20" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="K20" s="34" t="s">
-        <v>291</v>
-      </c>
-      <c r="L20" s="34"/>
+      <c r="I20" s="35" t="s">
+        <v>561</v>
+      </c>
+      <c r="J20" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20" s="35" t="s">
+        <v>562</v>
+      </c>
+      <c r="L20" s="35"/>
       <c r="M20" s="35" t="s">
-        <v>292</v>
+        <v>563</v>
       </c>
       <c r="N20" s="36">
-        <v>23337</v>
-      </c>
-      <c r="O20" s="34" t="s">
-        <v>324</v>
-      </c>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="35" t="s">
-        <v>293</v>
-      </c>
-      <c r="S20" s="38" t="s">
-        <v>294</v>
-      </c>
+        <v>25927</v>
+      </c>
+      <c r="O20" s="34"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
       <c r="T20" s="38" t="s">
-        <v>150</v>
+        <v>582</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
-        <v>545</v>
+        <v>265</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>59</v>
@@ -5788,42 +5884,44 @@
         <v>62</v>
       </c>
       <c r="F21" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H21" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I21" s="35" t="s">
-        <v>540</v>
-      </c>
-      <c r="J21" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="K21" s="35" t="s">
-        <v>541</v>
-      </c>
-      <c r="L21" s="35"/>
+      <c r="I21" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="J21" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="K21" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="L21" s="34"/>
       <c r="M21" s="35" t="s">
-        <v>542</v>
+        <v>289</v>
       </c>
       <c r="N21" s="36">
-        <v>25927</v>
-      </c>
-      <c r="O21" s="34"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
+        <v>21575</v>
+      </c>
+      <c r="O21" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
       <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
+      <c r="S21" s="38"/>
       <c r="T21" s="38" t="s">
-        <v>561</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
-        <v>252</v>
+        <v>529</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>59</v>
@@ -5838,44 +5936,46 @@
         <v>62</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H22" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I22" s="34" t="s">
-        <v>99</v>
+        <v>530</v>
       </c>
       <c r="J22" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K22" s="34" t="s">
-        <v>100</v>
+        <v>531</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="35" t="s">
-        <v>275</v>
+        <v>532</v>
       </c>
       <c r="N22" s="36">
-        <v>21575</v>
+        <v>27616</v>
       </c>
       <c r="O22" s="34" t="s">
-        <v>171</v>
+        <v>533</v>
       </c>
       <c r="P22" s="34"/>
       <c r="Q22" s="34"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="38"/>
+      <c r="R22" s="35" t="s">
+        <v>534</v>
+      </c>
+      <c r="S22" s="39"/>
       <c r="T22" s="38" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
-        <v>508</v>
+        <v>805</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>59</v>
@@ -5887,49 +5987,47 @@
         <v>61</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F23" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="H23" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I23" s="34" t="s">
-        <v>509</v>
+        <v>787</v>
       </c>
       <c r="J23" s="34" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K23" s="34" t="s">
-        <v>510</v>
+        <v>788</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="35" t="s">
-        <v>511</v>
-      </c>
-      <c r="N23" s="36">
-        <v>27616</v>
+        <v>789</v>
+      </c>
+      <c r="N23" s="36" t="s">
+        <v>790</v>
       </c>
       <c r="O23" s="34" t="s">
-        <v>512</v>
+        <v>791</v>
       </c>
       <c r="P23" s="34"/>
       <c r="Q23" s="34"/>
-      <c r="R23" s="35" t="s">
-        <v>513</v>
-      </c>
-      <c r="S23" s="39"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="38"/>
       <c r="T23" s="38" t="s">
-        <v>141</v>
+        <v>582</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="34" t="s">
-        <v>778</v>
+        <v>735</v>
       </c>
       <c r="B24" s="34" t="s">
         <v>59</v>
@@ -5941,47 +6039,49 @@
         <v>61</v>
       </c>
       <c r="E24" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F24" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H24" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I24" s="34" t="s">
-        <v>764</v>
+        <v>737</v>
       </c>
       <c r="J24" s="34" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K24" s="34" t="s">
-        <v>782</v>
+        <v>738</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="35" t="s">
-        <v>783</v>
+        <v>740</v>
       </c>
       <c r="N24" s="36" t="s">
-        <v>784</v>
+        <v>742</v>
       </c>
       <c r="O24" s="34" t="s">
-        <v>785</v>
+        <v>744</v>
       </c>
       <c r="P24" s="34"/>
       <c r="Q24" s="34"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="38"/>
+      <c r="R24" s="35" t="s">
+        <v>748</v>
+      </c>
+      <c r="S24" s="39"/>
       <c r="T24" s="38" t="s">
-        <v>561</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>711</v>
+        <v>736</v>
       </c>
       <c r="B25" s="34" t="s">
         <v>59</v>
@@ -5993,49 +6093,49 @@
         <v>61</v>
       </c>
       <c r="E25" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F25" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H25" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I25" s="34" t="s">
-        <v>713</v>
+        <v>737</v>
       </c>
       <c r="J25" s="34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K25" s="34" t="s">
-        <v>714</v>
+        <v>739</v>
       </c>
       <c r="L25" s="34"/>
       <c r="M25" s="35" t="s">
-        <v>716</v>
+        <v>741</v>
       </c>
       <c r="N25" s="36" t="s">
-        <v>718</v>
+        <v>743</v>
       </c>
       <c r="O25" s="34" t="s">
-        <v>720</v>
+        <v>744</v>
       </c>
       <c r="P25" s="34"/>
       <c r="Q25" s="34"/>
       <c r="R25" s="35" t="s">
-        <v>724</v>
+        <v>747</v>
       </c>
       <c r="S25" s="39"/>
       <c r="T25" s="38" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
-        <v>712</v>
+        <v>440</v>
       </c>
       <c r="B26" s="34" t="s">
         <v>59</v>
@@ -6047,49 +6147,51 @@
         <v>61</v>
       </c>
       <c r="E26" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F26" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="H26" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="H26" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="I26" s="34" t="s">
-        <v>713</v>
-      </c>
-      <c r="J26" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="K26" s="34" t="s">
-        <v>715</v>
-      </c>
-      <c r="L26" s="34"/>
+      <c r="I26" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="J26" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="K26" s="35" t="s">
+        <v>347</v>
+      </c>
+      <c r="L26" s="35" t="s">
+        <v>347</v>
+      </c>
       <c r="M26" s="35" t="s">
-        <v>717</v>
-      </c>
-      <c r="N26" s="36" t="s">
-        <v>719</v>
-      </c>
-      <c r="O26" s="34" t="s">
-        <v>720</v>
-      </c>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="34"/>
+        <v>431</v>
+      </c>
+      <c r="N26" s="36">
+        <v>23057</v>
+      </c>
+      <c r="O26" s="35" t="s">
+        <v>432</v>
+      </c>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
       <c r="R26" s="35" t="s">
-        <v>723</v>
-      </c>
-      <c r="S26" s="39"/>
-      <c r="T26" s="38" t="s">
-        <v>180</v>
+        <v>638</v>
+      </c>
+      <c r="S26" s="37"/>
+      <c r="T26" s="37" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
-        <v>421</v>
+        <v>475</v>
       </c>
       <c r="B27" s="34" t="s">
         <v>59</v>
@@ -6101,51 +6203,51 @@
         <v>61</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F27" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G27" s="35" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H27" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I27" s="35" t="s">
-        <v>94</v>
+        <v>476</v>
       </c>
       <c r="J27" s="35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K27" s="35" t="s">
-        <v>330</v>
-      </c>
-      <c r="L27" s="35" t="s">
-        <v>330</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="L27" s="35"/>
       <c r="M27" s="35" t="s">
-        <v>412</v>
+        <v>478</v>
       </c>
       <c r="N27" s="36">
-        <v>23057</v>
+        <v>25256</v>
       </c>
       <c r="O27" s="35" t="s">
-        <v>413</v>
+        <v>479</v>
       </c>
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="35" t="s">
-        <v>617</v>
-      </c>
-      <c r="S27" s="37"/>
+        <v>640</v>
+      </c>
+      <c r="S27" s="37" t="s">
+        <v>480</v>
+      </c>
       <c r="T27" s="37" t="s">
-        <v>141</v>
+        <v>513</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="34" t="s">
-        <v>454</v>
+        <v>260</v>
       </c>
       <c r="B28" s="34" t="s">
         <v>59</v>
@@ -6157,51 +6259,51 @@
         <v>61</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F28" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G28" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="H28" s="35" t="s">
+        <v>473</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="H28" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I28" s="35" t="s">
-        <v>455</v>
+        <v>674</v>
       </c>
       <c r="J28" s="35" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K28" s="35" t="s">
-        <v>456</v>
-      </c>
-      <c r="L28" s="35"/>
+        <v>76</v>
+      </c>
+      <c r="L28" s="35" t="s">
+        <v>675</v>
+      </c>
       <c r="M28" s="35" t="s">
-        <v>457</v>
-      </c>
-      <c r="N28" s="36">
-        <v>25256</v>
-      </c>
-      <c r="O28" s="35" t="s">
-        <v>458</v>
+        <v>261</v>
+      </c>
+      <c r="N28" s="36" t="s">
+        <v>689</v>
+      </c>
+      <c r="O28" s="34" t="s">
+        <v>676</v>
       </c>
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="35" t="s">
-        <v>619</v>
-      </c>
-      <c r="S28" s="37" t="s">
-        <v>459</v>
-      </c>
-      <c r="T28" s="37" t="s">
-        <v>772</v>
+        <v>677</v>
+      </c>
+      <c r="S28" s="35"/>
+      <c r="T28" s="38" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="34" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="B29" s="34" t="s">
         <v>59</v>
@@ -6216,48 +6318,48 @@
         <v>62</v>
       </c>
       <c r="F29" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="H29" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="G29" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="H29" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I29" s="35" t="s">
-        <v>653</v>
+        <v>822</v>
       </c>
       <c r="J29" s="35" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K29" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="L29" s="35" t="s">
-        <v>654</v>
-      </c>
+        <v>809</v>
+      </c>
+      <c r="L29" s="35"/>
       <c r="M29" s="35" t="s">
-        <v>248</v>
-      </c>
-      <c r="N29" s="36" t="s">
-        <v>667</v>
-      </c>
-      <c r="O29" s="34" t="s">
-        <v>655</v>
+        <v>159</v>
+      </c>
+      <c r="N29" s="36">
+        <v>22633</v>
+      </c>
+      <c r="O29" s="35" t="s">
+        <v>160</v>
       </c>
       <c r="P29" s="35"/>
       <c r="Q29" s="35"/>
       <c r="R29" s="35" t="s">
-        <v>656</v>
-      </c>
-      <c r="S29" s="35"/>
-      <c r="T29" s="38" t="s">
-        <v>772</v>
+        <v>161</v>
+      </c>
+      <c r="S29" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="T29" s="35" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="34" t="s">
-        <v>253</v>
+      <c r="A30" s="35" t="s">
+        <v>807</v>
       </c>
       <c r="B30" s="34" t="s">
         <v>59</v>
@@ -6272,48 +6374,46 @@
         <v>62</v>
       </c>
       <c r="F30" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G30" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="H30" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="H30" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="J30" s="35" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K30" s="35" t="s">
-        <v>760</v>
+        <v>775</v>
       </c>
       <c r="L30" s="35"/>
       <c r="M30" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="N30" s="36">
-        <v>22633</v>
-      </c>
-      <c r="O30" s="35" t="s">
-        <v>147</v>
+        <v>778</v>
+      </c>
+      <c r="N30" s="36" t="s">
+        <v>779</v>
+      </c>
+      <c r="O30" s="34" t="s">
+        <v>776</v>
       </c>
       <c r="P30" s="35"/>
       <c r="Q30" s="35"/>
       <c r="R30" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="S30" s="35" t="s">
-        <v>149</v>
-      </c>
+        <v>777</v>
+      </c>
+      <c r="S30" s="35"/>
       <c r="T30" s="35" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="35" t="s">
-        <v>747</v>
+        <v>771</v>
       </c>
       <c r="B31" s="34" t="s">
         <v>59</v>
@@ -6328,46 +6428,46 @@
         <v>62</v>
       </c>
       <c r="F31" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H31" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I31" s="34" t="s">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="J31" s="34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K31" s="34" t="s">
-        <v>721</v>
+        <v>745</v>
       </c>
       <c r="L31" s="34"/>
       <c r="M31" s="35" t="s">
-        <v>708</v>
+        <v>732</v>
       </c>
       <c r="N31" s="36" t="s">
-        <v>709</v>
+        <v>733</v>
       </c>
       <c r="O31" s="34" t="s">
-        <v>710</v>
+        <v>734</v>
       </c>
       <c r="P31" s="34"/>
       <c r="Q31" s="34"/>
       <c r="R31" s="35" t="s">
-        <v>722</v>
-      </c>
-      <c r="S31" s="39"/>
+        <v>746</v>
+      </c>
+      <c r="S31" s="38"/>
       <c r="T31" s="38" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="35" t="s">
-        <v>747</v>
+      <c r="A32" s="34" t="s">
+        <v>441</v>
       </c>
       <c r="B32" s="34" t="s">
         <v>59</v>
@@ -6379,49 +6479,53 @@
         <v>61</v>
       </c>
       <c r="E32" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F32" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I32" s="34" t="s">
-        <v>707</v>
-      </c>
-      <c r="J32" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K32" s="34" t="s">
-        <v>721</v>
-      </c>
-      <c r="L32" s="34"/>
+      <c r="I32" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="J32" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="K32" s="35" t="s">
+        <v>426</v>
+      </c>
+      <c r="L32" s="35" t="s">
+        <v>426</v>
+      </c>
       <c r="M32" s="35" t="s">
-        <v>708</v>
-      </c>
-      <c r="N32" s="36" t="s">
-        <v>709</v>
+        <v>427</v>
+      </c>
+      <c r="N32" s="36">
+        <v>30282</v>
       </c>
       <c r="O32" s="34" t="s">
-        <v>710</v>
-      </c>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="34"/>
+        <v>428</v>
+      </c>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
       <c r="R32" s="35" t="s">
-        <v>722</v>
-      </c>
-      <c r="S32" s="38"/>
+        <v>429</v>
+      </c>
+      <c r="S32" s="35" t="s">
+        <v>430</v>
+      </c>
       <c r="T32" s="38" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="35" t="s">
-        <v>779</v>
+      <c r="A33" s="34" t="s">
+        <v>267</v>
       </c>
       <c r="B33" s="34" t="s">
         <v>59</v>
@@ -6436,46 +6540,48 @@
         <v>62</v>
       </c>
       <c r="F33" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H33" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I33" s="35" t="s">
-        <v>763</v>
+        <v>132</v>
       </c>
       <c r="J33" s="35" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="K33" s="35" t="s">
-        <v>786</v>
+        <v>249</v>
       </c>
       <c r="L33" s="35"/>
       <c r="M33" s="35" t="s">
-        <v>787</v>
-      </c>
-      <c r="N33" s="36" t="s">
-        <v>788</v>
+        <v>213</v>
+      </c>
+      <c r="N33" s="36">
+        <v>27970</v>
       </c>
       <c r="O33" s="34" t="s">
-        <v>789</v>
+        <v>214</v>
       </c>
       <c r="P33" s="35"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="35" t="s">
-        <v>790</v>
-      </c>
-      <c r="S33" s="35"/>
-      <c r="T33" s="35" t="s">
-        <v>180</v>
+        <v>215</v>
+      </c>
+      <c r="S33" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="T33" s="38" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
-        <v>422</v>
+        <v>581</v>
       </c>
       <c r="B34" s="34" t="s">
         <v>59</v>
@@ -6487,53 +6593,49 @@
         <v>61</v>
       </c>
       <c r="E34" s="35" t="s">
-        <v>75</v>
+        <v>472</v>
       </c>
       <c r="F34" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H34" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I34" s="35" t="s">
-        <v>127</v>
+        <v>573</v>
       </c>
       <c r="J34" s="35" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="K34" s="35" t="s">
-        <v>407</v>
-      </c>
-      <c r="L34" s="35" t="s">
-        <v>407</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="L34" s="35"/>
       <c r="M34" s="35" t="s">
-        <v>408</v>
-      </c>
-      <c r="N34" s="36">
-        <v>30282</v>
+        <v>577</v>
+      </c>
+      <c r="N34" s="36" t="s">
+        <v>575</v>
       </c>
       <c r="O34" s="34" t="s">
-        <v>409</v>
+        <v>576</v>
       </c>
       <c r="P34" s="35"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="35" t="s">
-        <v>410</v>
-      </c>
-      <c r="S34" s="35" t="s">
-        <v>411</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="S34" s="35"/>
       <c r="T34" s="38" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="34" t="s">
-        <v>254</v>
+      <c r="A35" s="35" t="s">
+        <v>722</v>
       </c>
       <c r="B35" s="34" t="s">
         <v>59</v>
@@ -6548,48 +6650,46 @@
         <v>62</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>127</v>
+        <v>671</v>
       </c>
       <c r="J35" s="35" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="K35" s="35" t="s">
-        <v>236</v>
+        <v>670</v>
       </c>
       <c r="L35" s="35"/>
       <c r="M35" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="N35" s="36">
-        <v>27970</v>
+        <v>662</v>
+      </c>
+      <c r="N35" s="36" t="s">
+        <v>666</v>
       </c>
       <c r="O35" s="34" t="s">
-        <v>201</v>
+        <v>669</v>
       </c>
       <c r="P35" s="35"/>
       <c r="Q35" s="35"/>
       <c r="R35" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="S35" s="35" t="s">
-        <v>203</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="S35" s="35"/>
       <c r="T35" s="38" t="s">
-        <v>204</v>
+        <v>582</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
-        <v>560</v>
+        <v>647</v>
       </c>
       <c r="B36" s="34" t="s">
         <v>59</v>
@@ -6601,49 +6701,49 @@
         <v>61</v>
       </c>
       <c r="E36" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F36" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H36" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I36" s="35" t="s">
-        <v>552</v>
-      </c>
-      <c r="J36" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="K36" s="35" t="s">
-        <v>553</v>
-      </c>
-      <c r="L36" s="35"/>
+      <c r="I36" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="J36" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="K36" s="34" t="s">
+        <v>624</v>
+      </c>
+      <c r="L36" s="34"/>
       <c r="M36" s="35" t="s">
-        <v>556</v>
-      </c>
-      <c r="N36" s="36" t="s">
-        <v>554</v>
+        <v>644</v>
+      </c>
+      <c r="N36" s="36">
+        <v>38935</v>
       </c>
       <c r="O36" s="34" t="s">
-        <v>555</v>
-      </c>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="35"/>
+        <v>625</v>
+      </c>
+      <c r="P36" s="34"/>
+      <c r="Q36" s="34"/>
       <c r="R36" s="35" t="s">
-        <v>615</v>
-      </c>
-      <c r="S36" s="35"/>
+        <v>626</v>
+      </c>
+      <c r="S36" s="39"/>
       <c r="T36" s="38" t="s">
-        <v>204</v>
+        <v>513</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="35" t="s">
-        <v>699</v>
+      <c r="A37" s="34" t="s">
+        <v>678</v>
       </c>
       <c r="B37" s="34" t="s">
         <v>59</v>
@@ -6655,49 +6755,51 @@
         <v>61</v>
       </c>
       <c r="E37" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F37" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G37" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H37" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I37" s="35" t="s">
-        <v>650</v>
+        <v>512</v>
       </c>
       <c r="J37" s="35" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K37" s="35" t="s">
-        <v>649</v>
-      </c>
-      <c r="L37" s="35"/>
+        <v>76</v>
+      </c>
+      <c r="L37" s="35" t="s">
+        <v>679</v>
+      </c>
       <c r="M37" s="35" t="s">
-        <v>641</v>
+        <v>680</v>
       </c>
       <c r="N37" s="36" t="s">
-        <v>645</v>
+        <v>690</v>
       </c>
       <c r="O37" s="34" t="s">
-        <v>648</v>
+        <v>625</v>
       </c>
       <c r="P37" s="35"/>
       <c r="Q37" s="35"/>
       <c r="R37" s="35" t="s">
-        <v>651</v>
+        <v>681</v>
       </c>
       <c r="S37" s="35"/>
       <c r="T37" s="38" t="s">
-        <v>561</v>
+        <v>513</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="34" t="s">
-        <v>626</v>
+        <v>256</v>
       </c>
       <c r="B38" s="34" t="s">
         <v>59</v>
@@ -6712,46 +6814,46 @@
         <v>62</v>
       </c>
       <c r="F38" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H38" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I38" s="34" t="s">
-        <v>491</v>
+        <v>85</v>
       </c>
       <c r="J38" s="34" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K38" s="34" t="s">
-        <v>603</v>
+        <v>87</v>
       </c>
       <c r="L38" s="34"/>
       <c r="M38" s="35" t="s">
-        <v>623</v>
+        <v>287</v>
       </c>
       <c r="N38" s="36">
-        <v>38935</v>
+        <v>27347</v>
       </c>
       <c r="O38" s="34" t="s">
-        <v>604</v>
+        <v>155</v>
       </c>
       <c r="P38" s="34"/>
       <c r="Q38" s="34"/>
       <c r="R38" s="35" t="s">
-        <v>605</v>
+        <v>156</v>
       </c>
       <c r="S38" s="39"/>
       <c r="T38" s="38" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="35" t="s">
         <v>772</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="34" t="s">
-        <v>657</v>
       </c>
       <c r="B39" s="34" t="s">
         <v>59</v>
@@ -6763,51 +6865,51 @@
         <v>61</v>
       </c>
       <c r="E39" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G39" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H39" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I39" s="35" t="s">
-        <v>491</v>
-      </c>
-      <c r="J39" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="K39" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="L39" s="35" t="s">
-        <v>658</v>
+      <c r="I39" s="34" t="s">
+        <v>821</v>
+      </c>
+      <c r="J39" s="34" t="s">
+        <v>724</v>
+      </c>
+      <c r="K39" s="34" t="s">
+        <v>811</v>
+      </c>
+      <c r="L39" s="34" t="s">
+        <v>725</v>
       </c>
       <c r="M39" s="35" t="s">
-        <v>659</v>
+        <v>726</v>
       </c>
       <c r="N39" s="36" t="s">
-        <v>668</v>
+        <v>727</v>
       </c>
       <c r="O39" s="34" t="s">
-        <v>604</v>
-      </c>
-      <c r="P39" s="35"/>
-      <c r="Q39" s="35"/>
+        <v>728</v>
+      </c>
+      <c r="P39" s="34"/>
+      <c r="Q39" s="34"/>
       <c r="R39" s="35" t="s">
-        <v>660</v>
-      </c>
-      <c r="S39" s="35"/>
+        <v>729</v>
+      </c>
+      <c r="S39" s="39"/>
       <c r="T39" s="38" t="s">
-        <v>772</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="34" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="B40" s="34" t="s">
         <v>59</v>
@@ -6822,46 +6924,46 @@
         <v>62</v>
       </c>
       <c r="F40" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H40" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I40" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="J40" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K40" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="L40" s="34"/>
+      <c r="I40" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="J40" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="K40" s="35" t="s">
+        <v>810</v>
+      </c>
+      <c r="L40" s="35"/>
       <c r="M40" s="35" t="s">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="N40" s="36">
-        <v>27347</v>
+        <v>22941</v>
       </c>
       <c r="O40" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="P40" s="34"/>
-      <c r="Q40" s="34"/>
+        <v>231</v>
+      </c>
+      <c r="P40" s="35"/>
+      <c r="Q40" s="35"/>
       <c r="R40" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="S40" s="39"/>
+        <v>232</v>
+      </c>
+      <c r="S40" s="35"/>
       <c r="T40" s="38" t="s">
-        <v>141</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="35" t="s">
-        <v>748</v>
+      <c r="A41" s="34" t="s">
+        <v>613</v>
       </c>
       <c r="B41" s="34" t="s">
         <v>59</v>
@@ -6876,48 +6978,46 @@
         <v>62</v>
       </c>
       <c r="F41" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I41" s="34" t="s">
-        <v>761</v>
-      </c>
-      <c r="J41" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="K41" s="34" t="s">
-        <v>800</v>
-      </c>
-      <c r="L41" s="34" t="s">
-        <v>701</v>
-      </c>
+      <c r="I41" s="35" t="s">
+        <v>614</v>
+      </c>
+      <c r="J41" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K41" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="L41" s="35"/>
       <c r="M41" s="35" t="s">
-        <v>702</v>
-      </c>
-      <c r="N41" s="36" t="s">
-        <v>703</v>
+        <v>615</v>
+      </c>
+      <c r="N41" s="36">
+        <v>30209</v>
       </c>
       <c r="O41" s="34" t="s">
-        <v>704</v>
-      </c>
-      <c r="P41" s="34"/>
-      <c r="Q41" s="34"/>
+        <v>616</v>
+      </c>
+      <c r="P41" s="35"/>
+      <c r="Q41" s="35"/>
       <c r="R41" s="35" t="s">
-        <v>705</v>
-      </c>
-      <c r="S41" s="39"/>
+        <v>617</v>
+      </c>
+      <c r="S41" s="35"/>
       <c r="T41" s="38" t="s">
-        <v>774</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="34" t="s">
-        <v>249</v>
+      <c r="A42" s="35" t="s">
+        <v>723</v>
       </c>
       <c r="B42" s="34" t="s">
         <v>59</v>
@@ -6932,41 +7032,41 @@
         <v>62</v>
       </c>
       <c r="F42" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G42" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H42" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I42" s="35" t="s">
-        <v>133</v>
+        <v>663</v>
       </c>
       <c r="J42" s="35" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K42" s="35" t="s">
-        <v>766</v>
+        <v>664</v>
       </c>
       <c r="L42" s="35"/>
       <c r="M42" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="N42" s="36">
-        <v>22941</v>
+        <v>665</v>
+      </c>
+      <c r="N42" s="36" t="s">
+        <v>667</v>
       </c>
       <c r="O42" s="34" t="s">
-        <v>218</v>
+        <v>668</v>
       </c>
       <c r="P42" s="35"/>
       <c r="Q42" s="35"/>
       <c r="R42" s="35" t="s">
-        <v>219</v>
+        <v>673</v>
       </c>
       <c r="S42" s="35"/>
       <c r="T42" s="38" t="s">
-        <v>204</v>
+        <v>582</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
@@ -6983,49 +7083,51 @@
         <v>61</v>
       </c>
       <c r="E43" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F43" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G43" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="H43" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="G43" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="H43" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I43" s="35" t="s">
         <v>593</v>
       </c>
       <c r="J43" s="35" t="s">
-        <v>84</v>
+        <v>310</v>
       </c>
       <c r="K43" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="L43" s="35"/>
+        <v>594</v>
+      </c>
+      <c r="L43" s="35" t="s">
+        <v>595</v>
+      </c>
       <c r="M43" s="35" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N43" s="36">
-        <v>30209</v>
-      </c>
-      <c r="O43" s="34" t="s">
-        <v>595</v>
+        <v>23292</v>
+      </c>
+      <c r="O43" s="35" t="s">
+        <v>597</v>
       </c>
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
       <c r="R43" s="35" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="S43" s="35"/>
-      <c r="T43" s="38" t="s">
-        <v>141</v>
+      <c r="T43" s="35" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="35" t="s">
-        <v>700</v>
+      <c r="A44" s="34" t="s">
+        <v>648</v>
       </c>
       <c r="B44" s="34" t="s">
         <v>59</v>
@@ -7037,49 +7139,54 @@
         <v>61</v>
       </c>
       <c r="E44" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F44" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G44" s="34" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="H44" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I44" s="35" t="s">
-        <v>642</v>
-      </c>
-      <c r="J44" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="K44" s="35" t="s">
-        <v>643</v>
-      </c>
-      <c r="L44" s="35"/>
+      <c r="I44" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="J44" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K44" s="34" t="s">
+        <v>604</v>
+      </c>
+      <c r="L44" s="34" t="s">
+        <v>605</v>
+      </c>
       <c r="M44" s="35" t="s">
-        <v>644</v>
-      </c>
-      <c r="N44" s="36" t="s">
-        <v>646</v>
+        <v>606</v>
+      </c>
+      <c r="N44" s="36">
+        <v>29846</v>
       </c>
       <c r="O44" s="34" t="s">
-        <v>647</v>
-      </c>
-      <c r="P44" s="35"/>
-      <c r="Q44" s="35"/>
+        <v>589</v>
+      </c>
+      <c r="P44" s="34"/>
+      <c r="Q44" s="34"/>
       <c r="R44" s="35" t="s">
-        <v>652</v>
-      </c>
-      <c r="S44" s="35"/>
+        <v>583</v>
+      </c>
+      <c r="S44" s="39" t="s">
+        <v>607</v>
+      </c>
       <c r="T44" s="38" t="s">
-        <v>561</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="U44" s="32"/>
     </row>
     <row r="45" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="34" t="s">
-        <v>571</v>
+        <v>299</v>
       </c>
       <c r="B45" s="34" t="s">
         <v>59</v>
@@ -7091,51 +7198,49 @@
         <v>61</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F45" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G45" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="H45" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="G45" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="H45" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I45" s="35" t="s">
-        <v>572</v>
-      </c>
-      <c r="J45" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="K45" s="35" t="s">
-        <v>573</v>
-      </c>
-      <c r="L45" s="35" t="s">
-        <v>574</v>
-      </c>
+      <c r="I45" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="J45" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="K45" s="34" t="s">
+        <v>812</v>
+      </c>
+      <c r="L45" s="34"/>
       <c r="M45" s="35" t="s">
-        <v>575</v>
+        <v>291</v>
       </c>
       <c r="N45" s="36">
-        <v>23292</v>
-      </c>
-      <c r="O45" s="35" t="s">
-        <v>576</v>
-      </c>
-      <c r="P45" s="35"/>
-      <c r="Q45" s="35"/>
+        <v>26758</v>
+      </c>
+      <c r="O45" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="P45" s="34"/>
+      <c r="Q45" s="34"/>
       <c r="R45" s="35" t="s">
-        <v>577</v>
-      </c>
-      <c r="S45" s="35"/>
-      <c r="T45" s="35" t="s">
-        <v>561</v>
+        <v>293</v>
+      </c>
+      <c r="S45" s="39"/>
+      <c r="T45" s="38" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="34" t="s">
-        <v>627</v>
+        <v>481</v>
       </c>
       <c r="B46" s="34" t="s">
         <v>59</v>
@@ -7147,54 +7252,51 @@
         <v>61</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>75</v>
+        <v>472</v>
       </c>
       <c r="F46" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G46" s="34" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H46" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I46" s="34" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="J46" s="34" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="K46" s="34" t="s">
-        <v>583</v>
-      </c>
-      <c r="L46" s="34" t="s">
-        <v>584</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="L46" s="34"/>
       <c r="M46" s="35" t="s">
-        <v>585</v>
+        <v>482</v>
       </c>
       <c r="N46" s="36">
-        <v>29846</v>
+        <v>31066</v>
       </c>
       <c r="O46" s="34" t="s">
-        <v>568</v>
+        <v>483</v>
       </c>
       <c r="P46" s="34"/>
       <c r="Q46" s="34"/>
       <c r="R46" s="35" t="s">
-        <v>562</v>
+        <v>523</v>
       </c>
       <c r="S46" s="39" t="s">
-        <v>586</v>
+        <v>484</v>
       </c>
       <c r="T46" s="38" t="s">
-        <v>561</v>
-      </c>
-      <c r="U46" s="32"/>
+        <v>513</v>
+      </c>
     </row>
     <row r="47" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="34" t="s">
-        <v>285</v>
+        <v>585</v>
       </c>
       <c r="B47" s="34" t="s">
         <v>59</v>
@@ -7209,46 +7311,50 @@
         <v>62</v>
       </c>
       <c r="F47" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G47" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I47" s="34" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="J47" s="34" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="K47" s="34" t="s">
-        <v>759</v>
-      </c>
-      <c r="L47" s="34"/>
+        <v>586</v>
+      </c>
+      <c r="L47" s="34" t="s">
+        <v>587</v>
+      </c>
       <c r="M47" s="35" t="s">
-        <v>277</v>
+        <v>588</v>
       </c>
       <c r="N47" s="36">
-        <v>26758</v>
+        <v>27169</v>
       </c>
       <c r="O47" s="34" t="s">
-        <v>278</v>
+        <v>589</v>
       </c>
       <c r="P47" s="34"/>
       <c r="Q47" s="34"/>
       <c r="R47" s="35" t="s">
-        <v>279</v>
-      </c>
-      <c r="S47" s="39"/>
+        <v>590</v>
+      </c>
+      <c r="S47" s="39" t="s">
+        <v>591</v>
+      </c>
       <c r="T47" s="38" t="s">
-        <v>180</v>
+        <v>582</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="34" t="s">
-        <v>460</v>
+        <v>403</v>
       </c>
       <c r="B48" s="34" t="s">
         <v>59</v>
@@ -7263,48 +7369,44 @@
         <v>62</v>
       </c>
       <c r="F48" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G48" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H48" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I48" s="34" t="s">
-        <v>328</v>
+        <v>404</v>
       </c>
       <c r="J48" s="34" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K48" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="L48" s="34"/>
+        <v>405</v>
+      </c>
+      <c r="L48" s="34" t="s">
+        <v>405</v>
+      </c>
       <c r="M48" s="35" t="s">
-        <v>461</v>
+        <v>406</v>
       </c>
       <c r="N48" s="36">
-        <v>31066</v>
-      </c>
-      <c r="O48" s="34" t="s">
-        <v>462</v>
-      </c>
+        <v>25576</v>
+      </c>
+      <c r="O48" s="34"/>
       <c r="P48" s="34"/>
       <c r="Q48" s="34"/>
-      <c r="R48" s="35" t="s">
-        <v>502</v>
-      </c>
-      <c r="S48" s="39" t="s">
-        <v>463</v>
-      </c>
+      <c r="R48" s="35"/>
+      <c r="S48" s="39"/>
       <c r="T48" s="38" t="s">
-        <v>772</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="34" t="s">
-        <v>564</v>
+        <v>309</v>
       </c>
       <c r="B49" s="34" t="s">
         <v>59</v>
@@ -7319,50 +7421,48 @@
         <v>62</v>
       </c>
       <c r="F49" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G49" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H49" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I49" s="34" t="s">
-        <v>328</v>
+        <v>126</v>
       </c>
       <c r="J49" s="34" t="s">
-        <v>107</v>
+        <v>310</v>
       </c>
       <c r="K49" s="34" t="s">
-        <v>565</v>
-      </c>
-      <c r="L49" s="34" t="s">
-        <v>566</v>
-      </c>
+        <v>813</v>
+      </c>
+      <c r="L49" s="34"/>
       <c r="M49" s="35" t="s">
-        <v>567</v>
+        <v>311</v>
       </c>
       <c r="N49" s="36">
-        <v>27169</v>
+        <v>23532</v>
       </c>
       <c r="O49" s="34" t="s">
-        <v>568</v>
+        <v>312</v>
       </c>
       <c r="P49" s="34"/>
       <c r="Q49" s="34"/>
       <c r="R49" s="35" t="s">
-        <v>569</v>
+        <v>313</v>
       </c>
       <c r="S49" s="39" t="s">
-        <v>570</v>
+        <v>314</v>
       </c>
       <c r="T49" s="38" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="34" t="s">
-        <v>385</v>
+        <v>649</v>
       </c>
       <c r="B50" s="34" t="s">
         <v>59</v>
@@ -7377,44 +7477,50 @@
         <v>62</v>
       </c>
       <c r="F50" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G50" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H50" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I50" s="34" t="s">
-        <v>386</v>
+        <v>126</v>
       </c>
       <c r="J50" s="34" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="K50" s="34" t="s">
-        <v>387</v>
+        <v>107</v>
       </c>
       <c r="L50" s="34" t="s">
-        <v>387</v>
+        <v>599</v>
       </c>
       <c r="M50" s="35" t="s">
-        <v>388</v>
+        <v>600</v>
       </c>
       <c r="N50" s="36">
-        <v>25576</v>
-      </c>
-      <c r="O50" s="34"/>
+        <v>24574</v>
+      </c>
+      <c r="O50" s="34" t="s">
+        <v>601</v>
+      </c>
       <c r="P50" s="34"/>
       <c r="Q50" s="34"/>
-      <c r="R50" s="35"/>
-      <c r="S50" s="39"/>
+      <c r="R50" s="35" t="s">
+        <v>602</v>
+      </c>
+      <c r="S50" s="39" t="s">
+        <v>603</v>
+      </c>
       <c r="T50" s="38" t="s">
-        <v>150</v>
+        <v>582</v>
       </c>
     </row>
     <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="34" t="s">
-        <v>295</v>
+        <v>710</v>
       </c>
       <c r="B51" s="34" t="s">
         <v>59</v>
@@ -7429,48 +7535,48 @@
         <v>62</v>
       </c>
       <c r="F51" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G51" s="34" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="H51" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I51" s="34" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J51" s="34" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K51" s="34" t="s">
-        <v>758</v>
-      </c>
-      <c r="L51" s="34"/>
+        <v>474</v>
+      </c>
+      <c r="L51" s="34" t="s">
+        <v>711</v>
+      </c>
       <c r="M51" s="35" t="s">
-        <v>296</v>
+        <v>712</v>
       </c>
       <c r="N51" s="36">
-        <v>23532</v>
+        <v>20073</v>
       </c>
       <c r="O51" s="34" t="s">
-        <v>297</v>
+        <v>713</v>
       </c>
       <c r="P51" s="34"/>
       <c r="Q51" s="34"/>
       <c r="R51" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="S51" s="39" t="s">
-        <v>299</v>
-      </c>
+        <v>714</v>
+      </c>
+      <c r="S51" s="39"/>
       <c r="T51" s="38" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
     </row>
     <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="34" t="s">
-        <v>628</v>
+        <v>569</v>
       </c>
       <c r="B52" s="34" t="s">
         <v>59</v>
@@ -7485,50 +7591,44 @@
         <v>62</v>
       </c>
       <c r="F52" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G52" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H52" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I52" s="34" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J52" s="34" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K52" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="L52" s="34" t="s">
-        <v>578</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="L52" s="34"/>
       <c r="M52" s="35" t="s">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="N52" s="36">
-        <v>24574</v>
+        <v>40077</v>
       </c>
       <c r="O52" s="34" t="s">
-        <v>580</v>
+        <v>349</v>
       </c>
       <c r="P52" s="34"/>
       <c r="Q52" s="34"/>
-      <c r="R52" s="35" t="s">
-        <v>581</v>
-      </c>
-      <c r="S52" s="39" t="s">
-        <v>582</v>
-      </c>
+      <c r="R52" s="35"/>
+      <c r="S52" s="39"/>
       <c r="T52" s="38" t="s">
-        <v>561</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="34" t="s">
-        <v>687</v>
+        <v>257</v>
       </c>
       <c r="B53" s="34" t="s">
         <v>59</v>
@@ -7543,48 +7643,46 @@
         <v>62</v>
       </c>
       <c r="F53" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G53" s="34" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H53" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I53" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="J53" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="K53" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="J53" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K53" s="34" t="s">
-        <v>453</v>
-      </c>
-      <c r="L53" s="34" t="s">
-        <v>688</v>
-      </c>
+      <c r="L53" s="34"/>
       <c r="M53" s="35" t="s">
-        <v>689</v>
+        <v>196</v>
       </c>
       <c r="N53" s="36">
-        <v>20073</v>
+        <v>24906</v>
       </c>
       <c r="O53" s="34" t="s">
-        <v>690</v>
+        <v>197</v>
       </c>
       <c r="P53" s="34"/>
       <c r="Q53" s="34"/>
       <c r="R53" s="35" t="s">
-        <v>691</v>
+        <v>198</v>
       </c>
       <c r="S53" s="39"/>
       <c r="T53" s="38" t="s">
-        <v>561</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="34" t="s">
-        <v>548</v>
+        <v>485</v>
       </c>
       <c r="B54" s="34" t="s">
         <v>59</v>
@@ -7596,47 +7694,51 @@
         <v>61</v>
       </c>
       <c r="E54" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F54" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G54" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H54" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I54" s="34" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="J54" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K54" s="34" t="s">
-        <v>535</v>
+        <v>486</v>
       </c>
       <c r="L54" s="34"/>
       <c r="M54" s="35" t="s">
-        <v>536</v>
+        <v>487</v>
       </c>
       <c r="N54" s="36">
-        <v>40077</v>
+        <v>23023</v>
       </c>
       <c r="O54" s="34" t="s">
-        <v>332</v>
+        <v>488</v>
       </c>
       <c r="P54" s="34"/>
       <c r="Q54" s="34"/>
-      <c r="R54" s="35"/>
-      <c r="S54" s="39"/>
+      <c r="R54" s="35" t="s">
+        <v>639</v>
+      </c>
+      <c r="S54" s="39" t="s">
+        <v>489</v>
+      </c>
       <c r="T54" s="38" t="s">
-        <v>204</v>
+        <v>513</v>
       </c>
     </row>
     <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="34" t="s">
-        <v>244</v>
+        <v>367</v>
       </c>
       <c r="B55" s="34" t="s">
         <v>59</v>
@@ -7651,46 +7753,48 @@
         <v>62</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G55" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I55" s="34" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="J55" s="34" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="K55" s="34" t="s">
-        <v>116</v>
+        <v>358</v>
       </c>
       <c r="L55" s="34"/>
       <c r="M55" s="35" t="s">
-        <v>183</v>
+        <v>368</v>
       </c>
       <c r="N55" s="36">
-        <v>24906</v>
+        <v>23467</v>
       </c>
       <c r="O55" s="34" t="s">
-        <v>184</v>
+        <v>359</v>
       </c>
       <c r="P55" s="34"/>
       <c r="Q55" s="34"/>
       <c r="R55" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="S55" s="39"/>
+        <v>360</v>
+      </c>
+      <c r="S55" s="39" t="s">
+        <v>361</v>
+      </c>
       <c r="T55" s="38" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="34" t="s">
-        <v>464</v>
+        <v>527</v>
       </c>
       <c r="B56" s="34" t="s">
         <v>59</v>
@@ -7705,48 +7809,48 @@
         <v>62</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G56" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H56" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I56" s="34" t="s">
-        <v>95</v>
+        <v>462</v>
       </c>
       <c r="J56" s="34" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="K56" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="L56" s="34" t="s">
+        <v>464</v>
+      </c>
+      <c r="M56" s="35" t="s">
         <v>465</v>
       </c>
-      <c r="L56" s="34"/>
-      <c r="M56" s="35" t="s">
+      <c r="N56" s="36">
+        <v>25972</v>
+      </c>
+      <c r="O56" s="34" t="s">
         <v>466</v>
-      </c>
-      <c r="N56" s="36">
-        <v>23023</v>
-      </c>
-      <c r="O56" s="34" t="s">
-        <v>467</v>
       </c>
       <c r="P56" s="34"/>
       <c r="Q56" s="34"/>
       <c r="R56" s="35" t="s">
-        <v>618</v>
-      </c>
-      <c r="S56" s="39" t="s">
-        <v>468</v>
-      </c>
+        <v>629</v>
+      </c>
+      <c r="S56" s="39"/>
       <c r="T56" s="38" t="s">
-        <v>772</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="34" t="s">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="B57" s="34" t="s">
         <v>59</v>
@@ -7761,48 +7865,48 @@
         <v>62</v>
       </c>
       <c r="F57" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G57" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H57" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I57" s="34" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="J57" s="34" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K57" s="34" t="s">
-        <v>340</v>
-      </c>
-      <c r="L57" s="34"/>
+        <v>134</v>
+      </c>
+      <c r="L57" s="34" t="s">
+        <v>449</v>
+      </c>
       <c r="M57" s="35" t="s">
-        <v>350</v>
+        <v>302</v>
       </c>
       <c r="N57" s="36">
-        <v>23467</v>
+        <v>27622</v>
       </c>
       <c r="O57" s="34" t="s">
-        <v>341</v>
+        <v>218</v>
       </c>
       <c r="P57" s="34"/>
       <c r="Q57" s="34"/>
       <c r="R57" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="S57" s="39" t="s">
-        <v>343</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="S57" s="39"/>
       <c r="T57" s="38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="34" t="s">
-        <v>506</v>
+        <v>393</v>
       </c>
       <c r="B58" s="34" t="s">
         <v>59</v>
@@ -7817,48 +7921,44 @@
         <v>62</v>
       </c>
       <c r="F58" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G58" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H58" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I58" s="34" t="s">
-        <v>443</v>
+        <v>115</v>
       </c>
       <c r="J58" s="34" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="K58" s="34" t="s">
-        <v>444</v>
+        <v>394</v>
       </c>
       <c r="L58" s="34" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="M58" s="35" t="s">
-        <v>446</v>
+        <v>395</v>
       </c>
       <c r="N58" s="36">
-        <v>25972</v>
-      </c>
-      <c r="O58" s="34" t="s">
-        <v>447</v>
-      </c>
+        <v>22700</v>
+      </c>
+      <c r="O58" s="34"/>
       <c r="P58" s="34"/>
       <c r="Q58" s="34"/>
-      <c r="R58" s="35" t="s">
-        <v>608</v>
-      </c>
+      <c r="R58" s="35"/>
       <c r="S58" s="39"/>
       <c r="T58" s="38" t="s">
-        <v>180</v>
+        <v>461</v>
       </c>
     </row>
     <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="34" t="s">
-        <v>255</v>
+        <v>342</v>
       </c>
       <c r="B59" s="34" t="s">
         <v>59</v>
@@ -7873,48 +7973,48 @@
         <v>62</v>
       </c>
       <c r="F59" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G59" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H59" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I59" s="34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J59" s="34" t="s">
-        <v>76</v>
+        <v>322</v>
       </c>
       <c r="K59" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="L59" s="34" t="s">
-        <v>430</v>
-      </c>
+        <v>814</v>
+      </c>
+      <c r="L59" s="34"/>
       <c r="M59" s="35" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="N59" s="36">
-        <v>27622</v>
+        <v>30254</v>
       </c>
       <c r="O59" s="34" t="s">
-        <v>205</v>
+        <v>324</v>
       </c>
       <c r="P59" s="34"/>
       <c r="Q59" s="34"/>
       <c r="R59" s="35" t="s">
-        <v>206</v>
-      </c>
-      <c r="S59" s="39"/>
+        <v>325</v>
+      </c>
+      <c r="S59" s="39" t="s">
+        <v>326</v>
+      </c>
       <c r="T59" s="38" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="34" t="s">
-        <v>375</v>
+        <v>315</v>
       </c>
       <c r="B60" s="34" t="s">
         <v>59</v>
@@ -7926,47 +8026,51 @@
         <v>61</v>
       </c>
       <c r="E60" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F60" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G60" s="34" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="H60" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I60" s="34" t="s">
-        <v>110</v>
+        <v>316</v>
       </c>
       <c r="J60" s="34" t="s">
-        <v>81</v>
+        <v>317</v>
       </c>
       <c r="K60" s="34" t="s">
-        <v>376</v>
-      </c>
-      <c r="L60" s="34" t="s">
-        <v>376</v>
-      </c>
+        <v>815</v>
+      </c>
+      <c r="L60" s="34"/>
       <c r="M60" s="35" t="s">
-        <v>377</v>
+        <v>318</v>
       </c>
       <c r="N60" s="36">
-        <v>22700</v>
-      </c>
-      <c r="O60" s="34"/>
+        <v>27776</v>
+      </c>
+      <c r="O60" s="34" t="s">
+        <v>319</v>
+      </c>
       <c r="P60" s="34"/>
       <c r="Q60" s="34"/>
-      <c r="R60" s="35"/>
-      <c r="S60" s="39"/>
+      <c r="R60" s="35" t="s">
+        <v>320</v>
+      </c>
+      <c r="S60" s="39" t="s">
+        <v>321</v>
+      </c>
       <c r="T60" s="38" t="s">
-        <v>773</v>
+        <v>582</v>
       </c>
     </row>
     <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="34" t="s">
-        <v>325</v>
+        <v>442</v>
       </c>
       <c r="B61" s="34" t="s">
         <v>59</v>
@@ -7981,48 +8085,44 @@
         <v>62</v>
       </c>
       <c r="F61" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G61" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H61" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I61" s="34" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="J61" s="34" t="s">
-        <v>768</v>
+        <v>68</v>
       </c>
       <c r="K61" s="34" t="s">
-        <v>757</v>
-      </c>
-      <c r="L61" s="34"/>
+        <v>69</v>
+      </c>
+      <c r="L61" s="34" t="s">
+        <v>69</v>
+      </c>
       <c r="M61" s="35" t="s">
-        <v>306</v>
+        <v>402</v>
       </c>
       <c r="N61" s="36">
-        <v>30254</v>
-      </c>
-      <c r="O61" s="34" t="s">
-        <v>307</v>
-      </c>
+        <v>30538</v>
+      </c>
+      <c r="O61" s="34"/>
       <c r="P61" s="34"/>
       <c r="Q61" s="34"/>
-      <c r="R61" s="35" t="s">
-        <v>308</v>
-      </c>
-      <c r="S61" s="39" t="s">
-        <v>309</v>
-      </c>
+      <c r="R61" s="35"/>
+      <c r="S61" s="39"/>
       <c r="T61" s="38" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="34" t="s">
-        <v>300</v>
+        <v>396</v>
       </c>
       <c r="B62" s="34" t="s">
         <v>59</v>
@@ -8034,51 +8134,47 @@
         <v>61</v>
       </c>
       <c r="E62" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F62" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G62" s="34" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H62" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I62" s="34" t="s">
-        <v>301</v>
+        <v>397</v>
       </c>
       <c r="J62" s="34" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K62" s="34" t="s">
-        <v>756</v>
-      </c>
-      <c r="L62" s="34"/>
+        <v>97</v>
+      </c>
+      <c r="L62" s="34" t="s">
+        <v>97</v>
+      </c>
       <c r="M62" s="35" t="s">
-        <v>302</v>
+        <v>398</v>
       </c>
       <c r="N62" s="36">
-        <v>27776</v>
-      </c>
-      <c r="O62" s="34" t="s">
-        <v>303</v>
-      </c>
+        <v>25896</v>
+      </c>
+      <c r="O62" s="34"/>
       <c r="P62" s="34"/>
       <c r="Q62" s="34"/>
-      <c r="R62" s="35" t="s">
-        <v>304</v>
-      </c>
-      <c r="S62" s="39" t="s">
-        <v>305</v>
-      </c>
+      <c r="R62" s="35"/>
+      <c r="S62" s="39"/>
       <c r="T62" s="38" t="s">
-        <v>561</v>
+        <v>461</v>
       </c>
     </row>
     <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="34" t="s">
-        <v>423</v>
+        <v>338</v>
       </c>
       <c r="B63" s="34" t="s">
         <v>59</v>
@@ -8093,44 +8189,46 @@
         <v>62</v>
       </c>
       <c r="F63" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G63" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H63" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I63" s="34" t="s">
-        <v>106</v>
+        <v>328</v>
       </c>
       <c r="J63" s="34" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K63" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="L63" s="34" t="s">
-        <v>69</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="L63" s="34"/>
       <c r="M63" s="35" t="s">
-        <v>384</v>
+        <v>335</v>
       </c>
       <c r="N63" s="36">
-        <v>30538</v>
-      </c>
-      <c r="O63" s="34"/>
+        <v>25993</v>
+      </c>
+      <c r="O63" s="34" t="s">
+        <v>336</v>
+      </c>
       <c r="P63" s="34"/>
       <c r="Q63" s="34"/>
-      <c r="R63" s="35"/>
+      <c r="R63" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="S63" s="39"/>
       <c r="T63" s="38" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="34" t="s">
-        <v>378</v>
+        <v>269</v>
       </c>
       <c r="B64" s="34" t="s">
         <v>59</v>
@@ -8145,44 +8243,48 @@
         <v>62</v>
       </c>
       <c r="F64" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G64" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H64" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I64" s="34" t="s">
-        <v>379</v>
+        <v>91</v>
       </c>
       <c r="J64" s="34" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K64" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="L64" s="34" t="s">
-        <v>92</v>
-      </c>
+        <v>816</v>
+      </c>
+      <c r="L64" s="34"/>
       <c r="M64" s="35" t="s">
-        <v>380</v>
+        <v>164</v>
       </c>
       <c r="N64" s="36">
-        <v>25896</v>
-      </c>
-      <c r="O64" s="34"/>
+        <v>25881</v>
+      </c>
+      <c r="O64" s="34" t="s">
+        <v>165</v>
+      </c>
       <c r="P64" s="34"/>
       <c r="Q64" s="34"/>
-      <c r="R64" s="35"/>
-      <c r="S64" s="39"/>
+      <c r="R64" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="S64" s="39" t="s">
+        <v>167</v>
+      </c>
       <c r="T64" s="38" t="s">
-        <v>773</v>
+        <v>163</v>
       </c>
     </row>
     <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="34" t="s">
-        <v>321</v>
+        <v>409</v>
       </c>
       <c r="B65" s="34" t="s">
         <v>59</v>
@@ -8197,46 +8299,50 @@
         <v>62</v>
       </c>
       <c r="F65" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G65" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H65" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I65" s="34" t="s">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="J65" s="34" t="s">
-        <v>65</v>
+        <v>410</v>
       </c>
       <c r="K65" s="34" t="s">
-        <v>310</v>
-      </c>
-      <c r="L65" s="34"/>
+        <v>434</v>
+      </c>
+      <c r="L65" s="34" t="s">
+        <v>434</v>
+      </c>
       <c r="M65" s="35" t="s">
-        <v>318</v>
+        <v>411</v>
       </c>
       <c r="N65" s="36">
-        <v>25993</v>
+        <v>30157</v>
       </c>
       <c r="O65" s="34" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="P65" s="34"/>
       <c r="Q65" s="34"/>
       <c r="R65" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="S65" s="39"/>
+        <v>412</v>
+      </c>
+      <c r="S65" s="39" t="s">
+        <v>413</v>
+      </c>
       <c r="T65" s="38" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="34" t="s">
-        <v>256</v>
+        <v>389</v>
       </c>
       <c r="B66" s="34" t="s">
         <v>59</v>
@@ -8251,48 +8357,48 @@
         <v>62</v>
       </c>
       <c r="F66" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G66" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H66" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I66" s="34" t="s">
-        <v>88</v>
+        <v>352</v>
       </c>
       <c r="J66" s="34" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="K66" s="34" t="s">
-        <v>755</v>
+        <v>316</v>
       </c>
       <c r="L66" s="34"/>
       <c r="M66" s="35" t="s">
-        <v>151</v>
+        <v>362</v>
       </c>
       <c r="N66" s="36">
-        <v>25881</v>
+        <v>34772</v>
       </c>
       <c r="O66" s="34" t="s">
-        <v>152</v>
+        <v>363</v>
       </c>
       <c r="P66" s="34"/>
       <c r="Q66" s="34"/>
       <c r="R66" s="35" t="s">
-        <v>153</v>
+        <v>364</v>
       </c>
       <c r="S66" s="39" t="s">
-        <v>154</v>
+        <v>365</v>
       </c>
       <c r="T66" s="38" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="34" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="B67" s="34" t="s">
         <v>59</v>
@@ -8307,50 +8413,48 @@
         <v>62</v>
       </c>
       <c r="F67" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G67" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="H67" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="G67" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="H67" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="I67" s="34" t="s">
-        <v>335</v>
-      </c>
-      <c r="J67" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="K67" s="34" t="s">
-        <v>415</v>
-      </c>
-      <c r="L67" s="34" t="s">
-        <v>415</v>
-      </c>
+      <c r="I67" s="35" t="s">
+        <v>352</v>
+      </c>
+      <c r="J67" s="35" t="s">
+        <v>353</v>
+      </c>
+      <c r="K67" s="35" t="s">
+        <v>817</v>
+      </c>
+      <c r="L67" s="35"/>
       <c r="M67" s="35" t="s">
-        <v>393</v>
+        <v>354</v>
       </c>
       <c r="N67" s="36">
-        <v>30157</v>
-      </c>
-      <c r="O67" s="34" t="s">
-        <v>337</v>
-      </c>
-      <c r="P67" s="34"/>
-      <c r="Q67" s="34"/>
+        <v>23605</v>
+      </c>
+      <c r="O67" s="35" t="s">
+        <v>355</v>
+      </c>
+      <c r="P67" s="35"/>
+      <c r="Q67" s="35"/>
       <c r="R67" s="35" t="s">
-        <v>394</v>
-      </c>
-      <c r="S67" s="39" t="s">
-        <v>395</v>
-      </c>
-      <c r="T67" s="38" t="s">
-        <v>150</v>
+        <v>356</v>
+      </c>
+      <c r="S67" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="T67" s="37" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="34" t="s">
-        <v>371</v>
+        <v>270</v>
       </c>
       <c r="B68" s="34" t="s">
         <v>59</v>
@@ -8362,51 +8466,51 @@
         <v>61</v>
       </c>
       <c r="E68" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F68" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G68" s="34" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="H68" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I68" s="34" t="s">
-        <v>335</v>
+        <v>93</v>
       </c>
       <c r="J68" s="34" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="K68" s="34" t="s">
-        <v>301</v>
+        <v>818</v>
       </c>
       <c r="L68" s="34"/>
       <c r="M68" s="35" t="s">
-        <v>344</v>
+        <v>168</v>
       </c>
       <c r="N68" s="36">
-        <v>34772</v>
+        <v>22431</v>
       </c>
       <c r="O68" s="34" t="s">
-        <v>345</v>
+        <v>169</v>
       </c>
       <c r="P68" s="34"/>
       <c r="Q68" s="34"/>
       <c r="R68" s="35" t="s">
-        <v>346</v>
+        <v>298</v>
       </c>
       <c r="S68" s="39" t="s">
-        <v>347</v>
+        <v>170</v>
       </c>
       <c r="T68" s="38" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="34" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="B69" s="34" t="s">
         <v>59</v>
@@ -8421,48 +8525,46 @@
         <v>62</v>
       </c>
       <c r="F69" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G69" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="H69" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="G69" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="H69" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I69" s="35" t="s">
-        <v>335</v>
+        <v>117</v>
       </c>
       <c r="J69" s="35" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K69" s="35" t="s">
-        <v>754</v>
+        <v>125</v>
       </c>
       <c r="L69" s="35"/>
       <c r="M69" s="35" t="s">
-        <v>336</v>
+        <v>205</v>
       </c>
       <c r="N69" s="36">
-        <v>23605</v>
-      </c>
-      <c r="O69" s="35" t="s">
-        <v>337</v>
+        <v>23105</v>
+      </c>
+      <c r="O69" s="34" t="s">
+        <v>206</v>
       </c>
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
       <c r="R69" s="35" t="s">
-        <v>338</v>
-      </c>
-      <c r="S69" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="T69" s="37" t="s">
-        <v>150</v>
+        <v>207</v>
+      </c>
+      <c r="S69" s="35"/>
+      <c r="T69" s="38" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="34" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B70" s="34" t="s">
         <v>59</v>
@@ -8474,51 +8576,49 @@
         <v>61</v>
       </c>
       <c r="E70" s="35" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F70" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G70" s="34" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="H70" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I70" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="J70" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="K70" s="34" t="s">
-        <v>753</v>
-      </c>
-      <c r="L70" s="34"/>
+      <c r="I70" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="J70" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="K70" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="L70" s="35"/>
       <c r="M70" s="35" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="N70" s="36">
-        <v>22431</v>
+        <v>36383</v>
       </c>
       <c r="O70" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="P70" s="34"/>
-      <c r="Q70" s="34"/>
+        <v>192</v>
+      </c>
+      <c r="P70" s="35"/>
+      <c r="Q70" s="35"/>
       <c r="R70" s="35" t="s">
-        <v>284</v>
-      </c>
-      <c r="S70" s="39" t="s">
-        <v>157</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="S70" s="35"/>
       <c r="T70" s="38" t="s">
-        <v>150</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="34" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B71" s="34" t="s">
         <v>59</v>
@@ -8533,46 +8633,46 @@
         <v>62</v>
       </c>
       <c r="F71" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G71" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H71" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I71" s="35" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J71" s="35" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K71" s="35" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L71" s="35"/>
       <c r="M71" s="35" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N71" s="36">
-        <v>23105</v>
+        <v>33831</v>
       </c>
       <c r="O71" s="34" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P71" s="35"/>
       <c r="Q71" s="35"/>
       <c r="R71" s="35" t="s">
-        <v>194</v>
+        <v>630</v>
       </c>
       <c r="S71" s="35"/>
       <c r="T71" s="38" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="34" t="s">
-        <v>245</v>
+        <v>390</v>
       </c>
       <c r="B72" s="34" t="s">
         <v>59</v>
@@ -8584,40 +8684,40 @@
         <v>61</v>
       </c>
       <c r="E72" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F72" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G72" s="34" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H72" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I72" s="35" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J72" s="35" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K72" s="35" t="s">
-        <v>111</v>
+        <v>348</v>
       </c>
       <c r="L72" s="35"/>
       <c r="M72" s="35" t="s">
-        <v>178</v>
+        <v>351</v>
       </c>
       <c r="N72" s="36">
-        <v>36383</v>
+        <v>30287</v>
       </c>
       <c r="O72" s="34" t="s">
-        <v>179</v>
+        <v>349</v>
       </c>
       <c r="P72" s="35"/>
       <c r="Q72" s="35"/>
       <c r="R72" s="35" t="s">
-        <v>607</v>
+        <v>350</v>
       </c>
       <c r="S72" s="35"/>
       <c r="T72" s="38" t="s">
@@ -8626,7 +8726,7 @@
     </row>
     <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="34" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="B73" s="34" t="s">
         <v>59</v>
@@ -8641,46 +8741,46 @@
         <v>62</v>
       </c>
       <c r="F73" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G73" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H73" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I73" s="35" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J73" s="35" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="K73" s="35" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="L73" s="35"/>
       <c r="M73" s="35" t="s">
-        <v>181</v>
+        <v>526</v>
       </c>
       <c r="N73" s="36">
-        <v>33831</v>
+        <v>26138</v>
       </c>
       <c r="O73" s="34" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="P73" s="35"/>
       <c r="Q73" s="35"/>
       <c r="R73" s="35" t="s">
-        <v>609</v>
+        <v>631</v>
       </c>
       <c r="S73" s="35"/>
       <c r="T73" s="38" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="34" t="s">
-        <v>372</v>
+        <v>274</v>
       </c>
       <c r="B74" s="34" t="s">
         <v>59</v>
@@ -8695,46 +8795,46 @@
         <v>62</v>
       </c>
       <c r="F74" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G74" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H74" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I74" s="35" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J74" s="35" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="K74" s="35" t="s">
-        <v>331</v>
+        <v>123</v>
       </c>
       <c r="L74" s="35"/>
       <c r="M74" s="35" t="s">
-        <v>334</v>
+        <v>199</v>
       </c>
       <c r="N74" s="36">
-        <v>30287</v>
+        <v>32984</v>
       </c>
       <c r="O74" s="34" t="s">
-        <v>332</v>
+        <v>200</v>
       </c>
       <c r="P74" s="35"/>
       <c r="Q74" s="35"/>
       <c r="R74" s="35" t="s">
-        <v>333</v>
+        <v>201</v>
       </c>
       <c r="S74" s="35"/>
       <c r="T74" s="38" t="s">
-        <v>774</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="34" t="s">
-        <v>260</v>
+        <v>567</v>
       </c>
       <c r="B75" s="34" t="s">
         <v>59</v>
@@ -8746,49 +8846,51 @@
         <v>61</v>
       </c>
       <c r="E75" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F75" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G75" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H75" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I75" s="35" t="s">
-        <v>112</v>
+        <v>544</v>
       </c>
       <c r="J75" s="35" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="K75" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="L75" s="35"/>
+        <v>545</v>
+      </c>
+      <c r="L75" s="35" t="s">
+        <v>546</v>
+      </c>
       <c r="M75" s="35" t="s">
-        <v>505</v>
+        <v>547</v>
       </c>
       <c r="N75" s="36">
-        <v>26138</v>
+        <v>23098</v>
       </c>
       <c r="O75" s="34" t="s">
-        <v>195</v>
+        <v>548</v>
       </c>
       <c r="P75" s="35"/>
       <c r="Q75" s="35"/>
       <c r="R75" s="35" t="s">
-        <v>610</v>
+        <v>549</v>
       </c>
       <c r="S75" s="35"/>
       <c r="T75" s="38" t="s">
-        <v>180</v>
+        <v>513</v>
       </c>
     </row>
     <row r="76" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="34" t="s">
-        <v>261</v>
+        <v>448</v>
       </c>
       <c r="B76" s="34" t="s">
         <v>59</v>
@@ -8803,46 +8905,48 @@
         <v>62</v>
       </c>
       <c r="F76" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G76" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H76" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I76" s="35" t="s">
-        <v>112</v>
+        <v>346</v>
       </c>
       <c r="J76" s="35" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="K76" s="35" t="s">
-        <v>118</v>
+        <v>443</v>
       </c>
       <c r="L76" s="35"/>
       <c r="M76" s="35" t="s">
-        <v>186</v>
+        <v>444</v>
       </c>
       <c r="N76" s="36">
-        <v>32984</v>
+        <v>25389</v>
       </c>
       <c r="O76" s="34" t="s">
-        <v>187</v>
+        <v>445</v>
       </c>
       <c r="P76" s="35"/>
       <c r="Q76" s="35"/>
       <c r="R76" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="S76" s="35"/>
+        <v>446</v>
+      </c>
+      <c r="S76" s="35" t="s">
+        <v>447</v>
+      </c>
       <c r="T76" s="38" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
     </row>
     <row r="77" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="34" t="s">
-        <v>546</v>
+        <v>275</v>
       </c>
       <c r="B77" s="34" t="s">
         <v>59</v>
@@ -8857,48 +8961,46 @@
         <v>62</v>
       </c>
       <c r="F77" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G77" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H77" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I77" s="35" t="s">
-        <v>523</v>
+        <v>102</v>
       </c>
       <c r="J77" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="K77" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="K77" s="35" t="s">
-        <v>524</v>
-      </c>
-      <c r="L77" s="35" t="s">
-        <v>525</v>
-      </c>
+      <c r="L77" s="35"/>
       <c r="M77" s="35" t="s">
-        <v>526</v>
+        <v>181</v>
       </c>
       <c r="N77" s="36">
-        <v>23098</v>
+        <v>29006</v>
       </c>
       <c r="O77" s="34" t="s">
-        <v>527</v>
+        <v>182</v>
       </c>
       <c r="P77" s="35"/>
       <c r="Q77" s="35"/>
       <c r="R77" s="35" t="s">
-        <v>528</v>
+        <v>183</v>
       </c>
       <c r="S77" s="35"/>
       <c r="T77" s="38" t="s">
-        <v>772</v>
+        <v>180</v>
       </c>
     </row>
     <row r="78" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="34" t="s">
-        <v>429</v>
+        <v>276</v>
       </c>
       <c r="B78" s="34" t="s">
         <v>59</v>
@@ -8913,48 +9015,46 @@
         <v>62</v>
       </c>
       <c r="F78" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G78" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H78" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I78" s="35" t="s">
-        <v>329</v>
+        <v>139</v>
       </c>
       <c r="J78" s="35" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="K78" s="35" t="s">
-        <v>424</v>
+        <v>140</v>
       </c>
       <c r="L78" s="35"/>
       <c r="M78" s="35" t="s">
-        <v>425</v>
+        <v>227</v>
       </c>
       <c r="N78" s="36">
-        <v>25389</v>
+        <v>21024</v>
       </c>
       <c r="O78" s="34" t="s">
-        <v>426</v>
+        <v>228</v>
       </c>
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
       <c r="R78" s="35" t="s">
-        <v>427</v>
-      </c>
-      <c r="S78" s="35" t="s">
-        <v>428</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="S78" s="35"/>
       <c r="T78" s="38" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="34" t="s">
-        <v>262</v>
+        <v>806</v>
       </c>
       <c r="B79" s="34" t="s">
         <v>59</v>
@@ -8969,46 +9069,46 @@
         <v>62</v>
       </c>
       <c r="F79" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G79" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I79" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="J79" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="K79" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="L79" s="35"/>
+      <c r="I79" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="J79" s="34" t="s">
+        <v>798</v>
+      </c>
+      <c r="K79" s="34" t="s">
+        <v>799</v>
+      </c>
+      <c r="L79" s="34"/>
       <c r="M79" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="N79" s="36">
-        <v>29006</v>
+        <v>800</v>
+      </c>
+      <c r="N79" s="36" t="s">
+        <v>802</v>
       </c>
       <c r="O79" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="P79" s="35"/>
-      <c r="Q79" s="35"/>
+        <v>803</v>
+      </c>
+      <c r="P79" s="34"/>
+      <c r="Q79" s="34"/>
       <c r="R79" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="S79" s="35"/>
+        <v>804</v>
+      </c>
+      <c r="S79" s="38"/>
       <c r="T79" s="38" t="s">
-        <v>774</v>
+        <v>217</v>
       </c>
     </row>
     <row r="80" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="34" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B80" s="34" t="s">
         <v>59</v>
@@ -9023,46 +9123,46 @@
         <v>62</v>
       </c>
       <c r="F80" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G80" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H80" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I80" s="35" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J80" s="35" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="K80" s="35" t="s">
-        <v>132</v>
+        <v>394</v>
       </c>
       <c r="L80" s="35"/>
       <c r="M80" s="35" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="N80" s="36">
-        <v>21024</v>
+        <v>19757</v>
       </c>
       <c r="O80" s="34" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
       <c r="R80" s="35" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="S80" s="35"/>
       <c r="T80" s="38" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="34" t="s">
-        <v>264</v>
+        <v>392</v>
       </c>
       <c r="B81" s="34" t="s">
         <v>59</v>
@@ -9077,46 +9177,46 @@
         <v>62</v>
       </c>
       <c r="F81" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G81" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H81" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I81" s="35" t="s">
-        <v>130</v>
+        <v>379</v>
       </c>
       <c r="J81" s="35" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K81" s="35" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L81" s="35"/>
       <c r="M81" s="35" t="s">
-        <v>211</v>
+        <v>386</v>
       </c>
       <c r="N81" s="36">
-        <v>19757</v>
+        <v>30337</v>
       </c>
       <c r="O81" s="34" t="s">
-        <v>212</v>
+        <v>381</v>
       </c>
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
       <c r="R81" s="35" t="s">
-        <v>213</v>
+        <v>382</v>
       </c>
       <c r="S81" s="35"/>
       <c r="T81" s="38" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="34" t="s">
-        <v>374</v>
+        <v>436</v>
       </c>
       <c r="B82" s="34" t="s">
         <v>59</v>
@@ -9131,46 +9231,45 @@
         <v>62</v>
       </c>
       <c r="F82" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G82" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H82" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I82" s="35" t="s">
-        <v>361</v>
+        <v>399</v>
       </c>
       <c r="J82" s="35" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K82" s="35" t="s">
-        <v>362</v>
-      </c>
-      <c r="L82" s="35"/>
+        <v>400</v>
+      </c>
+      <c r="L82" s="35" t="s">
+        <v>400</v>
+      </c>
       <c r="M82" s="35" t="s">
-        <v>368</v>
+        <v>401</v>
       </c>
       <c r="N82" s="36">
-        <v>30337</v>
-      </c>
-      <c r="O82" s="34" t="s">
-        <v>363</v>
-      </c>
+        <v>29821</v>
+      </c>
+      <c r="O82" s="34"/>
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
-      <c r="R82" s="35" t="s">
-        <v>364</v>
-      </c>
+      <c r="R82" s="35"/>
       <c r="S82" s="35"/>
       <c r="T82" s="38" t="s">
-        <v>141</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="U82" s="27"/>
     </row>
     <row r="83" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="34" t="s">
-        <v>417</v>
+        <v>278</v>
       </c>
       <c r="B83" s="34" t="s">
         <v>59</v>
@@ -9185,44 +9284,48 @@
         <v>62</v>
       </c>
       <c r="F83" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G83" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H83" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I83" s="35" t="s">
-        <v>381</v>
+        <v>64</v>
       </c>
       <c r="J83" s="35" t="s">
         <v>65</v>
       </c>
       <c r="K83" s="35" t="s">
-        <v>382</v>
-      </c>
-      <c r="L83" s="35" t="s">
-        <v>382</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="L83" s="35"/>
       <c r="M83" s="35" t="s">
-        <v>383</v>
+        <v>143</v>
       </c>
       <c r="N83" s="36">
-        <v>29821</v>
-      </c>
-      <c r="O83" s="34"/>
+        <v>27213</v>
+      </c>
+      <c r="O83" s="34" t="s">
+        <v>144</v>
+      </c>
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
-      <c r="R83" s="35"/>
-      <c r="S83" s="35"/>
+      <c r="R83" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="S83" s="35" t="s">
+        <v>146</v>
+      </c>
       <c r="T83" s="38" t="s">
-        <v>773</v>
+        <v>147</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="34" t="s">
-        <v>265</v>
+        <v>437</v>
       </c>
       <c r="B84" s="34" t="s">
         <v>59</v>
@@ -9237,48 +9340,46 @@
         <v>62</v>
       </c>
       <c r="F84" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G84" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H84" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I84" s="35" t="s">
-        <v>64</v>
+        <v>407</v>
       </c>
       <c r="J84" s="35" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="K84" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="L84" s="35"/>
+        <v>438</v>
+      </c>
+      <c r="L84" s="35" t="s">
+        <v>408</v>
+      </c>
       <c r="M84" s="35" t="s">
-        <v>134</v>
+        <v>433</v>
       </c>
       <c r="N84" s="36">
-        <v>27213</v>
-      </c>
-      <c r="O84" s="34" t="s">
-        <v>135</v>
-      </c>
+        <v>24507</v>
+      </c>
+      <c r="O84" s="34"/>
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
       <c r="R84" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="S84" s="35" t="s">
-        <v>137</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="S84" s="35"/>
       <c r="T84" s="38" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="85" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="34" t="s">
-        <v>418</v>
+        <v>279</v>
       </c>
       <c r="B85" s="34" t="s">
         <v>59</v>
@@ -9293,46 +9394,48 @@
         <v>62</v>
       </c>
       <c r="F85" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G85" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H85" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I85" s="35" t="s">
-        <v>389</v>
+        <v>135</v>
       </c>
       <c r="J85" s="35" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="K85" s="35" t="s">
-        <v>419</v>
-      </c>
-      <c r="L85" s="35" t="s">
-        <v>390</v>
-      </c>
+        <v>819</v>
+      </c>
+      <c r="L85" s="35"/>
       <c r="M85" s="35" t="s">
-        <v>414</v>
+        <v>220</v>
       </c>
       <c r="N85" s="36">
-        <v>24507</v>
-      </c>
-      <c r="O85" s="34"/>
+        <v>29328</v>
+      </c>
+      <c r="O85" s="34" t="s">
+        <v>221</v>
+      </c>
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
       <c r="R85" s="35" t="s">
-        <v>611</v>
-      </c>
-      <c r="S85" s="35"/>
+        <v>222</v>
+      </c>
+      <c r="S85" s="35" t="s">
+        <v>223</v>
+      </c>
       <c r="T85" s="38" t="s">
-        <v>141</v>
+        <v>217</v>
       </c>
     </row>
     <row r="86" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="34" t="s">
-        <v>266</v>
+        <v>661</v>
       </c>
       <c r="B86" s="34" t="s">
         <v>59</v>
@@ -9347,48 +9450,44 @@
         <v>62</v>
       </c>
       <c r="F86" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G86" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H86" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I86" s="35" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J86" s="35" t="s">
-        <v>81</v>
+        <v>658</v>
       </c>
       <c r="K86" s="35" t="s">
-        <v>752</v>
+        <v>659</v>
       </c>
       <c r="L86" s="35"/>
       <c r="M86" s="35" t="s">
-        <v>207</v>
+        <v>660</v>
       </c>
       <c r="N86" s="36">
-        <v>29328</v>
+        <v>40905</v>
       </c>
       <c r="O86" s="34" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
-      <c r="R86" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="S86" s="35" t="s">
-        <v>210</v>
-      </c>
+      <c r="R86" s="35"/>
+      <c r="S86" s="35"/>
       <c r="T86" s="38" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="87" spans="1:21" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="34" t="s">
-        <v>640</v>
+        <v>280</v>
       </c>
       <c r="B87" s="34" t="s">
         <v>59</v>
@@ -9403,45 +9502,48 @@
         <v>62</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G87" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I87" s="35" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="J87" s="35" t="s">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="K87" s="35" t="s">
-        <v>638</v>
+        <v>97</v>
       </c>
       <c r="L87" s="35"/>
       <c r="M87" s="35" t="s">
-        <v>639</v>
+        <v>172</v>
       </c>
       <c r="N87" s="36">
-        <v>40905</v>
+        <v>27907</v>
       </c>
       <c r="O87" s="34" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
-      <c r="R87" s="35"/>
-      <c r="S87" s="35"/>
+      <c r="R87" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="S87" s="35" t="s">
+        <v>175</v>
+      </c>
       <c r="T87" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="U87" s="27"/>
+        <v>217</v>
+      </c>
     </row>
     <row r="88" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="34" t="s">
-        <v>267</v>
+        <v>565</v>
       </c>
       <c r="B88" s="34" t="s">
         <v>59</v>
@@ -9453,51 +9555,51 @@
         <v>61</v>
       </c>
       <c r="E88" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F88" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G88" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H88" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I88" s="35" t="s">
-        <v>91</v>
+        <v>535</v>
       </c>
       <c r="J88" s="35" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="K88" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="L88" s="35"/>
+        <v>536</v>
+      </c>
+      <c r="L88" s="35" t="s">
+        <v>537</v>
+      </c>
       <c r="M88" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="N88" s="36">
-        <v>27907</v>
+        <v>538</v>
+      </c>
+      <c r="N88" s="36" t="s">
+        <v>691</v>
       </c>
       <c r="O88" s="34" t="s">
-        <v>160</v>
+        <v>539</v>
       </c>
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
       <c r="R88" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="S88" s="35" t="s">
-        <v>162</v>
-      </c>
+        <v>682</v>
+      </c>
+      <c r="S88" s="35"/>
       <c r="T88" s="38" t="s">
-        <v>204</v>
+        <v>513</v>
       </c>
     </row>
     <row r="89" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="34" t="s">
-        <v>544</v>
+        <v>329</v>
       </c>
       <c r="B89" s="34" t="s">
         <v>59</v>
@@ -9509,51 +9611,49 @@
         <v>61</v>
       </c>
       <c r="E89" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F89" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G89" s="34" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="H89" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I89" s="35" t="s">
-        <v>514</v>
+        <v>330</v>
       </c>
       <c r="J89" s="35" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="K89" s="35" t="s">
-        <v>515</v>
-      </c>
-      <c r="L89" s="35" t="s">
-        <v>516</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="L89" s="35"/>
       <c r="M89" s="35" t="s">
-        <v>517</v>
-      </c>
-      <c r="N89" s="36" t="s">
-        <v>669</v>
+        <v>332</v>
+      </c>
+      <c r="N89" s="36">
+        <v>23497</v>
       </c>
       <c r="O89" s="34" t="s">
-        <v>518</v>
+        <v>333</v>
       </c>
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
       <c r="R89" s="35" t="s">
-        <v>661</v>
+        <v>334</v>
       </c>
       <c r="S89" s="35"/>
       <c r="T89" s="38" t="s">
-        <v>772</v>
+        <v>461</v>
       </c>
     </row>
     <row r="90" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="34" t="s">
-        <v>312</v>
+        <v>490</v>
       </c>
       <c r="B90" s="34" t="s">
         <v>59</v>
@@ -9565,49 +9665,51 @@
         <v>61</v>
       </c>
       <c r="E90" s="35" t="s">
-        <v>75</v>
+        <v>472</v>
       </c>
       <c r="F90" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G90" s="34" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I90" s="35" t="s">
-        <v>313</v>
+        <v>491</v>
       </c>
       <c r="J90" s="35" t="s">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="K90" s="35" t="s">
-        <v>314</v>
-      </c>
-      <c r="L90" s="35"/>
+        <v>492</v>
+      </c>
+      <c r="L90" s="35" t="s">
+        <v>493</v>
+      </c>
       <c r="M90" s="35" t="s">
-        <v>315</v>
+        <v>494</v>
       </c>
       <c r="N90" s="36">
-        <v>23497</v>
+        <v>24537</v>
       </c>
       <c r="O90" s="34" t="s">
-        <v>316</v>
+        <v>495</v>
       </c>
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
       <c r="R90" s="35" t="s">
-        <v>317</v>
+        <v>637</v>
       </c>
       <c r="S90" s="35"/>
       <c r="T90" s="38" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A91" s="35" t="s">
         <v>773</v>
-      </c>
-    </row>
-    <row r="91" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="34" t="s">
-        <v>469</v>
       </c>
       <c r="B91" s="34" t="s">
         <v>59</v>
@@ -9619,51 +9721,49 @@
         <v>61</v>
       </c>
       <c r="E91" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F91" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G91" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H91" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I91" s="35" t="s">
-        <v>470</v>
-      </c>
-      <c r="J91" s="35" t="s">
-        <v>283</v>
-      </c>
-      <c r="K91" s="35" t="s">
-        <v>471</v>
-      </c>
-      <c r="L91" s="35" t="s">
-        <v>472</v>
-      </c>
+      <c r="I91" s="34" t="s">
+        <v>730</v>
+      </c>
+      <c r="J91" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="K91" s="34" t="s">
+        <v>750</v>
+      </c>
+      <c r="L91" s="34"/>
       <c r="M91" s="35" t="s">
-        <v>473</v>
-      </c>
-      <c r="N91" s="36">
-        <v>24537</v>
+        <v>751</v>
+      </c>
+      <c r="N91" s="36" t="s">
+        <v>752</v>
       </c>
       <c r="O91" s="34" t="s">
-        <v>474</v>
-      </c>
-      <c r="P91" s="35"/>
-      <c r="Q91" s="35"/>
+        <v>753</v>
+      </c>
+      <c r="P91" s="34"/>
+      <c r="Q91" s="34"/>
       <c r="R91" s="35" t="s">
-        <v>616</v>
-      </c>
-      <c r="S91" s="35"/>
+        <v>754</v>
+      </c>
+      <c r="S91" s="39"/>
       <c r="T91" s="38" t="s">
-        <v>772</v>
+        <v>582</v>
       </c>
     </row>
     <row r="92" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="35" t="s">
-        <v>749</v>
+        <v>808</v>
       </c>
       <c r="B92" s="34" t="s">
         <v>59</v>
@@ -9678,46 +9778,46 @@
         <v>62</v>
       </c>
       <c r="F92" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G92" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H92" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I92" s="34" t="s">
-        <v>706</v>
-      </c>
-      <c r="J92" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="K92" s="34" t="s">
-        <v>726</v>
-      </c>
-      <c r="L92" s="34"/>
+      <c r="I92" s="35" t="s">
+        <v>780</v>
+      </c>
+      <c r="J92" s="35" t="s">
+        <v>781</v>
+      </c>
+      <c r="K92" s="35" t="s">
+        <v>782</v>
+      </c>
+      <c r="L92" s="35"/>
       <c r="M92" s="35" t="s">
-        <v>727</v>
+        <v>784</v>
       </c>
       <c r="N92" s="36" t="s">
-        <v>728</v>
+        <v>785</v>
       </c>
       <c r="O92" s="34" t="s">
-        <v>729</v>
-      </c>
-      <c r="P92" s="34"/>
-      <c r="Q92" s="34"/>
+        <v>783</v>
+      </c>
+      <c r="P92" s="35"/>
+      <c r="Q92" s="35"/>
       <c r="R92" s="35" t="s">
-        <v>730</v>
-      </c>
-      <c r="S92" s="39"/>
-      <c r="T92" s="38" t="s">
-        <v>561</v>
+        <v>786</v>
+      </c>
+      <c r="S92" s="35"/>
+      <c r="T92" s="35" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="35" t="s">
-        <v>780</v>
+      <c r="A93" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="B93" s="34" t="s">
         <v>59</v>
@@ -9732,46 +9832,46 @@
         <v>62</v>
       </c>
       <c r="F93" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G93" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H93" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I93" s="35" t="s">
-        <v>762</v>
+        <v>67</v>
       </c>
       <c r="J93" s="35" t="s">
-        <v>791</v>
+        <v>68</v>
       </c>
       <c r="K93" s="35" t="s">
-        <v>769</v>
+        <v>69</v>
       </c>
       <c r="L93" s="35"/>
       <c r="M93" s="35" t="s">
-        <v>792</v>
-      </c>
-      <c r="N93" s="36" t="s">
-        <v>793</v>
+        <v>148</v>
+      </c>
+      <c r="N93" s="36">
+        <v>31298</v>
       </c>
       <c r="O93" s="34" t="s">
-        <v>794</v>
+        <v>149</v>
       </c>
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
       <c r="R93" s="35" t="s">
-        <v>795</v>
+        <v>150</v>
       </c>
       <c r="S93" s="35"/>
-      <c r="T93" s="35" t="s">
-        <v>180</v>
+      <c r="T93" s="38" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="94" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="34" t="s">
-        <v>246</v>
+        <v>281</v>
       </c>
       <c r="B94" s="34" t="s">
         <v>59</v>
@@ -9786,46 +9886,46 @@
         <v>62</v>
       </c>
       <c r="F94" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G94" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H94" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I94" s="35" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="J94" s="35" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K94" s="35" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="L94" s="35"/>
       <c r="M94" s="35" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="N94" s="36">
-        <v>31298</v>
+        <v>28101</v>
       </c>
       <c r="O94" s="34" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
       <c r="R94" s="35" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="S94" s="35"/>
       <c r="T94" s="38" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="34" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B95" s="34" t="s">
         <v>59</v>
@@ -9837,49 +9937,47 @@
         <v>61</v>
       </c>
       <c r="E95" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F95" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G95" s="34" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="H95" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I95" s="35" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J95" s="35" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="K95" s="35" t="s">
-        <v>102</v>
+        <v>340</v>
       </c>
       <c r="L95" s="35"/>
       <c r="M95" s="35" t="s">
-        <v>172</v>
+        <v>233</v>
       </c>
       <c r="N95" s="36">
-        <v>28101</v>
-      </c>
-      <c r="O95" s="34" t="s">
-        <v>173</v>
-      </c>
+        <v>30156</v>
+      </c>
+      <c r="O95" s="34"/>
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
       <c r="R95" s="35" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="S95" s="35"/>
       <c r="T95" s="38" t="s">
-        <v>774</v>
+        <v>180</v>
       </c>
     </row>
     <row r="96" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="34" t="s">
-        <v>269</v>
+        <v>651</v>
       </c>
       <c r="B96" s="34" t="s">
         <v>59</v>
@@ -9891,47 +9989,49 @@
         <v>61</v>
       </c>
       <c r="E96" s="35" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F96" s="35" t="s">
-        <v>126</v>
+        <v>652</v>
       </c>
       <c r="G96" s="34" t="s">
-        <v>240</v>
+        <v>685</v>
       </c>
       <c r="H96" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I96" s="35" t="s">
-        <v>90</v>
+        <v>653</v>
       </c>
       <c r="J96" s="35" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K96" s="35" t="s">
-        <v>323</v>
+        <v>654</v>
       </c>
       <c r="L96" s="35"/>
       <c r="M96" s="35" t="s">
-        <v>220</v>
+        <v>655</v>
       </c>
       <c r="N96" s="36">
-        <v>30156</v>
-      </c>
-      <c r="O96" s="34"/>
+        <v>33667</v>
+      </c>
+      <c r="O96" s="34" t="s">
+        <v>656</v>
+      </c>
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
       <c r="R96" s="35" t="s">
-        <v>158</v>
+        <v>657</v>
       </c>
       <c r="S96" s="35"/>
       <c r="T96" s="38" t="s">
-        <v>774</v>
+        <v>151</v>
       </c>
     </row>
     <row r="97" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="34" t="s">
-        <v>630</v>
+        <v>570</v>
       </c>
       <c r="B97" s="34" t="s">
         <v>59</v>
@@ -9943,49 +10043,49 @@
         <v>61</v>
       </c>
       <c r="E97" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F97" s="35" t="s">
-        <v>631</v>
+        <v>473</v>
       </c>
       <c r="G97" s="34" t="s">
-        <v>664</v>
+        <v>234</v>
       </c>
       <c r="H97" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I97" s="35" t="s">
-        <v>632</v>
+        <v>550</v>
       </c>
       <c r="J97" s="35" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K97" s="35" t="s">
-        <v>633</v>
+        <v>551</v>
       </c>
       <c r="L97" s="35"/>
       <c r="M97" s="35" t="s">
-        <v>634</v>
-      </c>
-      <c r="N97" s="36">
-        <v>33667</v>
+        <v>552</v>
+      </c>
+      <c r="N97" s="36" t="s">
+        <v>553</v>
       </c>
       <c r="O97" s="34" t="s">
-        <v>635</v>
+        <v>554</v>
       </c>
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
       <c r="R97" s="35" t="s">
-        <v>636</v>
+        <v>555</v>
       </c>
       <c r="S97" s="35"/>
       <c r="T97" s="38" t="s">
-        <v>141</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="34" t="s">
-        <v>549</v>
+        <v>496</v>
       </c>
       <c r="B98" s="34" t="s">
         <v>59</v>
@@ -9997,49 +10097,53 @@
         <v>61</v>
       </c>
       <c r="E98" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F98" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G98" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H98" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I98" s="35" t="s">
-        <v>529</v>
+        <v>497</v>
       </c>
       <c r="J98" s="35" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K98" s="35" t="s">
-        <v>530</v>
-      </c>
-      <c r="L98" s="35"/>
+        <v>498</v>
+      </c>
+      <c r="L98" s="35" t="s">
+        <v>410</v>
+      </c>
       <c r="M98" s="35" t="s">
-        <v>531</v>
-      </c>
-      <c r="N98" s="36" t="s">
-        <v>532</v>
+        <v>499</v>
+      </c>
+      <c r="N98" s="36">
+        <v>34298</v>
       </c>
       <c r="O98" s="34" t="s">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
       <c r="R98" s="35" t="s">
-        <v>534</v>
-      </c>
-      <c r="S98" s="35"/>
+        <v>501</v>
+      </c>
+      <c r="S98" s="35" t="s">
+        <v>502</v>
+      </c>
       <c r="T98" s="38" t="s">
-        <v>204</v>
+        <v>513</v>
       </c>
     </row>
     <row r="99" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="34" t="s">
-        <v>475</v>
+        <v>503</v>
       </c>
       <c r="B99" s="34" t="s">
         <v>59</v>
@@ -10051,53 +10155,51 @@
         <v>61</v>
       </c>
       <c r="E99" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F99" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G99" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H99" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I99" s="35" t="s">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="J99" s="35" t="s">
-        <v>392</v>
+        <v>84</v>
       </c>
       <c r="K99" s="35" t="s">
-        <v>477</v>
-      </c>
-      <c r="L99" s="35" t="s">
-        <v>392</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="L99" s="35"/>
       <c r="M99" s="35" t="s">
-        <v>478</v>
+        <v>505</v>
       </c>
       <c r="N99" s="36">
-        <v>34298</v>
+        <v>29452</v>
       </c>
       <c r="O99" s="34" t="s">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="P99" s="35"/>
       <c r="Q99" s="35"/>
       <c r="R99" s="35" t="s">
-        <v>480</v>
+        <v>634</v>
       </c>
       <c r="S99" s="35" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="T99" s="38" t="s">
-        <v>772</v>
+        <v>513</v>
       </c>
     </row>
     <row r="100" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="34" t="s">
-        <v>482</v>
+        <v>792</v>
       </c>
       <c r="B100" s="34" t="s">
         <v>59</v>
@@ -10112,48 +10214,46 @@
         <v>62</v>
       </c>
       <c r="F100" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G100" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H100" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I100" s="35" t="s">
-        <v>476</v>
-      </c>
-      <c r="J100" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="K100" s="35" t="s">
-        <v>483</v>
-      </c>
-      <c r="L100" s="35"/>
+      <c r="I100" s="34" t="s">
+        <v>793</v>
+      </c>
+      <c r="J100" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K100" s="34" t="s">
+        <v>794</v>
+      </c>
+      <c r="L100" s="34"/>
       <c r="M100" s="35" t="s">
-        <v>484</v>
-      </c>
-      <c r="N100" s="36">
-        <v>29452</v>
+        <v>795</v>
+      </c>
+      <c r="N100" s="36" t="s">
+        <v>801</v>
       </c>
       <c r="O100" s="34" t="s">
-        <v>485</v>
-      </c>
-      <c r="P100" s="35"/>
-      <c r="Q100" s="35"/>
+        <v>796</v>
+      </c>
+      <c r="P100" s="34"/>
+      <c r="Q100" s="34"/>
       <c r="R100" s="35" t="s">
-        <v>613</v>
-      </c>
-      <c r="S100" s="35" t="s">
-        <v>486</v>
-      </c>
+        <v>797</v>
+      </c>
+      <c r="S100" s="38"/>
       <c r="T100" s="38" t="s">
-        <v>772</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="34" t="s">
-        <v>781</v>
+        <v>374</v>
       </c>
       <c r="B101" s="34" t="s">
         <v>59</v>
@@ -10168,46 +10268,48 @@
         <v>62</v>
       </c>
       <c r="F101" s="35" t="s">
-        <v>126</v>
+        <v>693</v>
       </c>
       <c r="G101" s="34" t="s">
-        <v>221</v>
+        <v>685</v>
       </c>
       <c r="H101" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I101" s="34" t="s">
-        <v>765</v>
-      </c>
-      <c r="J101" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="K101" s="34" t="s">
-        <v>770</v>
-      </c>
-      <c r="L101" s="34"/>
+      <c r="I101" s="35" t="s">
+        <v>375</v>
+      </c>
+      <c r="J101" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="K101" s="35" t="s">
+        <v>376</v>
+      </c>
+      <c r="L101" s="35" t="s">
+        <v>683</v>
+      </c>
       <c r="M101" s="35" t="s">
-        <v>796</v>
+        <v>377</v>
       </c>
       <c r="N101" s="36" t="s">
-        <v>797</v>
+        <v>692</v>
       </c>
       <c r="O101" s="34" t="s">
-        <v>798</v>
-      </c>
-      <c r="P101" s="34"/>
-      <c r="Q101" s="34"/>
+        <v>378</v>
+      </c>
+      <c r="P101" s="35"/>
+      <c r="Q101" s="35"/>
       <c r="R101" s="35" t="s">
-        <v>799</v>
-      </c>
-      <c r="S101" s="38"/>
+        <v>627</v>
+      </c>
+      <c r="S101" s="35"/>
       <c r="T101" s="38" t="s">
-        <v>774</v>
+        <v>513</v>
       </c>
     </row>
     <row r="102" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="34" t="s">
-        <v>356</v>
+        <v>715</v>
       </c>
       <c r="B102" s="34" t="s">
         <v>59</v>
@@ -10222,48 +10324,46 @@
         <v>62</v>
       </c>
       <c r="F102" s="35" t="s">
-        <v>631</v>
+        <v>131</v>
       </c>
       <c r="G102" s="34" t="s">
-        <v>664</v>
+        <v>234</v>
       </c>
       <c r="H102" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I102" s="35" t="s">
-        <v>357</v>
+        <v>716</v>
       </c>
       <c r="J102" s="35" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K102" s="35" t="s">
-        <v>358</v>
-      </c>
-      <c r="L102" s="35" t="s">
-        <v>662</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="L102" s="35"/>
       <c r="M102" s="35" t="s">
-        <v>359</v>
-      </c>
-      <c r="N102" s="36" t="s">
-        <v>670</v>
+        <v>718</v>
+      </c>
+      <c r="N102" s="36">
+        <v>32200</v>
       </c>
       <c r="O102" s="34" t="s">
-        <v>360</v>
+        <v>719</v>
       </c>
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
       <c r="R102" s="35" t="s">
-        <v>606</v>
+        <v>720</v>
       </c>
       <c r="S102" s="35"/>
       <c r="T102" s="38" t="s">
-        <v>772</v>
+        <v>217</v>
       </c>
     </row>
     <row r="103" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="34" t="s">
-        <v>692</v>
+        <v>300</v>
       </c>
       <c r="B103" s="34" t="s">
         <v>59</v>
@@ -10278,46 +10378,46 @@
         <v>62</v>
       </c>
       <c r="F103" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G103" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H103" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I103" s="35" t="s">
-        <v>693</v>
+        <v>823</v>
       </c>
       <c r="J103" s="35" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K103" s="35" t="s">
-        <v>694</v>
+        <v>820</v>
       </c>
       <c r="L103" s="35"/>
       <c r="M103" s="35" t="s">
-        <v>695</v>
+        <v>294</v>
       </c>
       <c r="N103" s="36">
-        <v>32200</v>
+        <v>28570</v>
       </c>
       <c r="O103" s="34" t="s">
-        <v>696</v>
+        <v>295</v>
       </c>
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
       <c r="R103" s="35" t="s">
-        <v>697</v>
+        <v>296</v>
       </c>
       <c r="S103" s="35"/>
       <c r="T103" s="38" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="104" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="34" t="s">
-        <v>286</v>
+        <v>450</v>
       </c>
       <c r="B104" s="34" t="s">
         <v>59</v>
@@ -10332,46 +10432,46 @@
         <v>62</v>
       </c>
       <c r="F104" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G104" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H104" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I104" s="35" t="s">
-        <v>751</v>
+        <v>823</v>
       </c>
       <c r="J104" s="35" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K104" s="35" t="s">
-        <v>750</v>
+        <v>451</v>
       </c>
       <c r="L104" s="35"/>
       <c r="M104" s="35" t="s">
-        <v>280</v>
+        <v>452</v>
       </c>
       <c r="N104" s="36">
-        <v>28570</v>
+        <v>33544</v>
       </c>
       <c r="O104" s="34" t="s">
-        <v>281</v>
+        <v>453</v>
       </c>
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
       <c r="R104" s="35" t="s">
-        <v>282</v>
+        <v>454</v>
       </c>
       <c r="S104" s="35"/>
       <c r="T104" s="38" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="34" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="B105" s="34" t="s">
         <v>59</v>
@@ -10386,46 +10486,50 @@
         <v>62</v>
       </c>
       <c r="F105" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G105" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H105" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I105" s="35" t="s">
-        <v>751</v>
+        <v>101</v>
       </c>
       <c r="J105" s="35" t="s">
-        <v>73</v>
+        <v>415</v>
       </c>
       <c r="K105" s="35" t="s">
-        <v>432</v>
-      </c>
-      <c r="L105" s="35"/>
+        <v>435</v>
+      </c>
+      <c r="L105" s="35" t="s">
+        <v>435</v>
+      </c>
       <c r="M105" s="35" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="N105" s="36">
-        <v>33544</v>
+        <v>25204</v>
       </c>
       <c r="O105" s="34" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
       <c r="R105" s="35" t="s">
-        <v>435</v>
-      </c>
-      <c r="S105" s="35"/>
+        <v>418</v>
+      </c>
+      <c r="S105" s="35" t="s">
+        <v>419</v>
+      </c>
       <c r="T105" s="38" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
     </row>
     <row r="106" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="34" t="s">
-        <v>396</v>
+        <v>283</v>
       </c>
       <c r="B106" s="34" t="s">
         <v>59</v>
@@ -10440,50 +10544,44 @@
         <v>62</v>
       </c>
       <c r="F106" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G106" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H106" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I106" s="35" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J106" s="35" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="K106" s="35" t="s">
-        <v>416</v>
-      </c>
-      <c r="L106" s="35" t="s">
-        <v>416</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="L106" s="35"/>
       <c r="M106" s="35" t="s">
-        <v>397</v>
+        <v>290</v>
       </c>
       <c r="N106" s="36">
-        <v>25204</v>
+        <v>26134</v>
       </c>
       <c r="O106" s="34" t="s">
-        <v>398</v>
+        <v>179</v>
       </c>
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
-      <c r="R106" s="35" t="s">
-        <v>399</v>
-      </c>
-      <c r="S106" s="35" t="s">
-        <v>400</v>
-      </c>
+      <c r="R106" s="35"/>
+      <c r="S106" s="35"/>
       <c r="T106" s="38" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
     </row>
     <row r="107" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="34" t="s">
-        <v>270</v>
+        <v>650</v>
       </c>
       <c r="B107" s="34" t="s">
         <v>59</v>
@@ -10498,44 +10596,48 @@
         <v>62</v>
       </c>
       <c r="F107" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G107" s="34" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="H107" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I107" s="35" t="s">
-        <v>96</v>
+        <v>608</v>
       </c>
       <c r="J107" s="35" t="s">
-        <v>77</v>
+        <v>824</v>
       </c>
       <c r="K107" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="L107" s="35"/>
+        <v>609</v>
+      </c>
+      <c r="L107" s="35" t="s">
+        <v>609</v>
+      </c>
       <c r="M107" s="35" t="s">
-        <v>276</v>
+        <v>610</v>
       </c>
       <c r="N107" s="36">
-        <v>26134</v>
+        <v>31906</v>
       </c>
       <c r="O107" s="34" t="s">
-        <v>166</v>
+        <v>611</v>
       </c>
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
-      <c r="R107" s="35"/>
+      <c r="R107" s="35" t="s">
+        <v>612</v>
+      </c>
       <c r="S107" s="35"/>
       <c r="T107" s="38" t="s">
-        <v>774</v>
+        <v>180</v>
       </c>
     </row>
     <row r="108" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="34" t="s">
-        <v>629</v>
+        <v>684</v>
       </c>
       <c r="B108" s="34" t="s">
         <v>59</v>
@@ -10547,49 +10649,49 @@
         <v>61</v>
       </c>
       <c r="E108" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F108" s="35" t="s">
-        <v>126</v>
+        <v>693</v>
       </c>
       <c r="G108" s="34" t="s">
-        <v>240</v>
+        <v>685</v>
       </c>
       <c r="H108" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I108" s="35" t="s">
-        <v>587</v>
+        <v>825</v>
       </c>
       <c r="J108" s="35" t="s">
-        <v>107</v>
+        <v>686</v>
       </c>
       <c r="K108" s="35" t="s">
-        <v>588</v>
+        <v>663</v>
       </c>
       <c r="L108" s="35"/>
       <c r="M108" s="35" t="s">
-        <v>589</v>
-      </c>
-      <c r="N108" s="36">
-        <v>31906</v>
+        <v>695</v>
+      </c>
+      <c r="N108" s="36" t="s">
+        <v>696</v>
       </c>
       <c r="O108" s="34" t="s">
-        <v>590</v>
+        <v>687</v>
       </c>
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
       <c r="R108" s="35" t="s">
-        <v>591</v>
+        <v>694</v>
       </c>
       <c r="S108" s="35"/>
       <c r="T108" s="38" t="s">
-        <v>774</v>
+        <v>151</v>
       </c>
     </row>
     <row r="109" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="34" t="s">
-        <v>663</v>
+        <v>284</v>
       </c>
       <c r="B109" s="34" t="s">
         <v>59</v>
@@ -10601,49 +10703,49 @@
         <v>61</v>
       </c>
       <c r="E109" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F109" s="35" t="s">
-        <v>631</v>
+        <v>473</v>
       </c>
       <c r="G109" s="34" t="s">
-        <v>664</v>
+        <v>253</v>
       </c>
       <c r="H109" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I109" s="35" t="s">
-        <v>771</v>
+        <v>110</v>
       </c>
       <c r="J109" s="35" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="K109" s="35" t="s">
-        <v>642</v>
+        <v>113</v>
       </c>
       <c r="L109" s="35"/>
       <c r="M109" s="35" t="s">
-        <v>672</v>
+        <v>188</v>
       </c>
       <c r="N109" s="36" t="s">
-        <v>673</v>
+        <v>688</v>
       </c>
       <c r="O109" s="34" t="s">
-        <v>665</v>
+        <v>189</v>
       </c>
       <c r="P109" s="35"/>
       <c r="Q109" s="35"/>
       <c r="R109" s="35" t="s">
-        <v>671</v>
+        <v>190</v>
       </c>
       <c r="S109" s="35"/>
       <c r="T109" s="38" t="s">
-        <v>141</v>
+        <v>461</v>
       </c>
     </row>
     <row r="110" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="34" t="s">
-        <v>271</v>
+        <v>721</v>
       </c>
       <c r="B110" s="34" t="s">
         <v>59</v>
@@ -10655,49 +10757,51 @@
         <v>61</v>
       </c>
       <c r="E110" s="35" t="s">
-        <v>75</v>
+        <v>472</v>
       </c>
       <c r="F110" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G110" s="34" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H110" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I110" s="35" t="s">
-        <v>105</v>
+        <v>702</v>
       </c>
       <c r="J110" s="35" t="s">
-        <v>82</v>
+        <v>658</v>
       </c>
       <c r="K110" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="L110" s="35"/>
+        <v>703</v>
+      </c>
+      <c r="L110" s="35" t="s">
+        <v>704</v>
+      </c>
       <c r="M110" s="35" t="s">
-        <v>175</v>
+        <v>707</v>
       </c>
       <c r="N110" s="36" t="s">
-        <v>666</v>
+        <v>709</v>
       </c>
       <c r="O110" s="34" t="s">
-        <v>176</v>
+        <v>705</v>
       </c>
       <c r="P110" s="35"/>
       <c r="Q110" s="35"/>
       <c r="R110" s="35" t="s">
-        <v>177</v>
+        <v>706</v>
       </c>
       <c r="S110" s="35"/>
       <c r="T110" s="38" t="s">
-        <v>773</v>
+        <v>513</v>
       </c>
     </row>
     <row r="111" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="34" t="s">
-        <v>698</v>
+        <v>508</v>
       </c>
       <c r="B111" s="34" t="s">
         <v>59</v>
@@ -10709,51 +10813,51 @@
         <v>61</v>
       </c>
       <c r="E111" s="35" t="s">
-        <v>62</v>
+        <v>472</v>
       </c>
       <c r="F111" s="35" t="s">
-        <v>126</v>
+        <v>473</v>
       </c>
       <c r="G111" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I111" s="35" t="s">
-        <v>679</v>
+        <v>129</v>
       </c>
       <c r="J111" s="35" t="s">
-        <v>637</v>
+        <v>71</v>
       </c>
       <c r="K111" s="35" t="s">
-        <v>680</v>
-      </c>
-      <c r="L111" s="35" t="s">
-        <v>681</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="L111" s="35"/>
       <c r="M111" s="35" t="s">
-        <v>684</v>
-      </c>
-      <c r="N111" s="36" t="s">
-        <v>686</v>
+        <v>509</v>
+      </c>
+      <c r="N111" s="36">
+        <v>26766</v>
       </c>
       <c r="O111" s="34" t="s">
-        <v>682</v>
+        <v>510</v>
       </c>
       <c r="P111" s="35"/>
       <c r="Q111" s="35"/>
       <c r="R111" s="35" t="s">
-        <v>683</v>
-      </c>
-      <c r="S111" s="35"/>
+        <v>635</v>
+      </c>
+      <c r="S111" s="35" t="s">
+        <v>511</v>
+      </c>
       <c r="T111" s="38" t="s">
-        <v>772</v>
+        <v>513</v>
       </c>
     </row>
     <row r="112" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="34" t="s">
-        <v>487</v>
+        <v>285</v>
       </c>
       <c r="B112" s="34" t="s">
         <v>59</v>
@@ -10768,48 +10872,46 @@
         <v>62</v>
       </c>
       <c r="F112" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G112" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H112" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I112" s="35" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J112" s="35" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="K112" s="35" t="s">
-        <v>330</v>
+        <v>130</v>
       </c>
       <c r="L112" s="35"/>
       <c r="M112" s="35" t="s">
-        <v>488</v>
+        <v>211</v>
       </c>
       <c r="N112" s="36">
-        <v>26766</v>
+        <v>24263</v>
       </c>
       <c r="O112" s="34" t="s">
-        <v>489</v>
+        <v>212</v>
       </c>
       <c r="P112" s="35"/>
       <c r="Q112" s="35"/>
       <c r="R112" s="35" t="s">
-        <v>614</v>
-      </c>
-      <c r="S112" s="35" t="s">
-        <v>490</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="S112" s="35"/>
       <c r="T112" s="38" t="s">
-        <v>772</v>
+        <v>193</v>
       </c>
     </row>
     <row r="113" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="34" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B113" s="34" t="s">
         <v>59</v>
@@ -10824,127 +10926,112 @@
         <v>62</v>
       </c>
       <c r="F113" s="35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G113" s="34" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="H113" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I113" s="35" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="J113" s="35" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="K113" s="35" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="L113" s="35"/>
       <c r="M113" s="35" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="N113" s="36">
-        <v>24263</v>
+        <v>29464</v>
       </c>
       <c r="O113" s="34" t="s">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="P113" s="35"/>
       <c r="Q113" s="35"/>
       <c r="R113" s="35" t="s">
-        <v>612</v>
+        <v>154</v>
       </c>
       <c r="S113" s="35"/>
       <c r="T113" s="38" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="114" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="T114" s="38" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="120" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I120" s="34"/>
-    </row>
-    <row r="121" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I121" s="35"/>
-    </row>
-    <row r="122" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I122" s="35"/>
-    </row>
-    <row r="123" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I123" s="35"/>
-    </row>
-    <row r="124" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I124" s="34"/>
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" sort="0"/>
-  <autoFilter ref="A1:T114" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U113">
-    <sortCondition ref="I2:I17000"/>
-    <sortCondition ref="K2:K17000"/>
+  <autoFilter ref="A1:T107" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U116">
+    <sortCondition ref="I2:I16999"/>
+    <sortCondition ref="K2:K16999"/>
   </sortState>
-  <phoneticPr fontId="31" type="noConversion"/>
-  <conditionalFormatting sqref="A114 A1 A120:A1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="590"/>
+  <phoneticPr fontId="32" type="noConversion"/>
+  <conditionalFormatting sqref="A114:A1048576 A1">
+    <cfRule type="duplicateValues" dxfId="17" priority="591"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H101 H109:H113">
-    <cfRule type="containsText" dxfId="15" priority="21" operator="containsText" text="Inactive - ADS">
+  <conditionalFormatting sqref="H102:H107 H2:H94">
+    <cfRule type="containsText" dxfId="16" priority="22" operator="containsText" text="Inactive - ADS">
       <formula>NOT(ISERROR(SEARCH("Inactive - ADS",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H101:H102">
-    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="Inactive-ADS">
-      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H101)))</formula>
+  <conditionalFormatting sqref="H95">
+    <cfRule type="containsText" dxfId="15" priority="19" operator="containsText" text="Inactive-ADS">
+      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H95)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H103:H104">
-    <cfRule type="containsText" dxfId="13" priority="15" operator="containsText" text="Inactive - ADS">
-      <formula>NOT(ISERROR(SEARCH("Inactive - ADS",H103)))</formula>
+  <conditionalFormatting sqref="H96:H97">
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="Inactive - ADS">
+      <formula>NOT(ISERROR(SEARCH("Inactive - ADS",H96)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H105:H108">
-    <cfRule type="containsText" dxfId="12" priority="12" operator="containsText" text="Inactive-ADS">
-      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H105)))</formula>
+  <conditionalFormatting sqref="H98:H101">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="Inactive-ADS">
+      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H98)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1 M114 M120:M65093">
-    <cfRule type="expression" dxfId="11" priority="587" stopIfTrue="1">
+  <conditionalFormatting sqref="H108:H113">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="Inactive-ADS">
+      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H108)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1 M114:M65094">
+    <cfRule type="expression" dxfId="11" priority="588" stopIfTrue="1">
       <formula>LEN(M1)&lt;&gt;13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M113">
-    <cfRule type="expression" dxfId="10" priority="13">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>LEN(M2)&lt;13</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M34:M92 M94:M100 M2:M23 M25:M31">
-    <cfRule type="duplicateValues" dxfId="9" priority="676"/>
+  <conditionalFormatting sqref="M95">
+    <cfRule type="duplicateValues" dxfId="9" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M93 M32:M33 M24">
-    <cfRule type="duplicateValues" dxfId="8" priority="712"/>
+  <conditionalFormatting sqref="M96:M97">
+    <cfRule type="duplicateValues" dxfId="8" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M101">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+  <conditionalFormatting sqref="M98:M101">
+    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M102">
-    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
+  <conditionalFormatting sqref="M102:M107">
+    <cfRule type="duplicateValues" dxfId="6" priority="652"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M103:M104">
-    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
+  <conditionalFormatting sqref="M108:M111">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M105:M108">
-    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
+  <conditionalFormatting sqref="M112:M113">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M109:M113">
-    <cfRule type="duplicateValues" dxfId="3" priority="716"/>
+  <conditionalFormatting sqref="M114:M65094 M1">
+    <cfRule type="duplicateValues" dxfId="3" priority="648" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M114 M1 M120:M65093">
-    <cfRule type="duplicateValues" dxfId="2" priority="647" stopIfTrue="1"/>
+  <conditionalFormatting sqref="M2:M94">
+    <cfRule type="duplicateValues" dxfId="2" priority="666"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -11111,102 +11198,102 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>625</v>
+        <v>646</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>624</v>
+        <v>645</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="B10"/>
       <c r="C10" s="31" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">

--- a/import-files/WC-CTN-O(1).xlsx
+++ b/import-files/WC-CTN-O(1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Videos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Music\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52AD5DE8-211E-4A1B-A7C9-7D59B623FD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D94D959-49AD-48A4-8B00-85804EC20A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Club Details" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Membership!$A$1:$T$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Membership!$A$1:$T$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="819">
   <si>
     <t>How To Complete/Update existing information.</t>
   </si>
@@ -1643,21 +1643,6 @@
     <t>Brisdel Dart Club</t>
   </si>
   <si>
-    <t>Jassiem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ebrahim </t>
-  </si>
-  <si>
-    <t>Ebrahim Jassiem</t>
-  </si>
-  <si>
-    <t>7102085593082</t>
-  </si>
-  <si>
-    <t>3 Rustenburg Close Portlands mitchells Plain</t>
-  </si>
-  <si>
     <t>Boyce</t>
   </si>
   <si>
@@ -1838,9 +1823,6 @@
     <t>7107245061086</t>
   </si>
   <si>
-    <t>DSA-210316</t>
-  </si>
-  <si>
     <t>DSA-240278</t>
   </si>
   <si>
@@ -2142,9 +2124,6 @@
   </si>
   <si>
     <t>0603239006</t>
-  </si>
-  <si>
-    <t>0682989550</t>
   </si>
   <si>
     <t>0678974512</t>
@@ -3195,12 +3174,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3215,6 +3188,12 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="17">
@@ -3239,6 +3218,16 @@
   <dxfs count="19">
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i/>
         <color rgb="FFFF0000"/>
@@ -3255,16 +3244,6 @@
         <i/>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4323,66 +4302,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
     </row>
     <row r="2" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="43" t="s">
         <v>235</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
     </row>
     <row r="3" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
     </row>
     <row r="6" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
+      <c r="A6" s="45"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42" t="s">
+      <c r="B8" s="47"/>
+      <c r="C8" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="42"/>
+      <c r="D8" s="47"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
@@ -4475,20 +4454,20 @@
       <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42" t="s">
+      <c r="B18" s="47"/>
+      <c r="C18" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="42"/>
+      <c r="D18" s="47"/>
     </row>
     <row r="19" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
@@ -4593,20 +4572,20 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="43"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="42" t="s">
+      <c r="A28" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="42"/>
-      <c r="C28" s="42" t="s">
+      <c r="B28" s="47"/>
+      <c r="C28" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="42"/>
+      <c r="D28" s="47"/>
     </row>
     <row r="29" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
@@ -4718,12 +4697,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="A18:B18"/>
@@ -4732,6 +4705,12 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B26" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -4750,7 +4729,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:U113"/>
+  <dimension ref="A1:U112"/>
   <sheetFormatPr defaultColWidth="17.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" style="28" bestFit="1" customWidth="1"/>
@@ -4949,7 +4928,7 @@
     </row>
     <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="B4" s="34" t="s">
         <v>59</v>
@@ -4961,10 +4940,10 @@
         <v>61</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G4" s="34" t="s">
         <v>234</v>
@@ -4979,22 +4958,22 @@
         <v>74</v>
       </c>
       <c r="K4" s="34" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="L4" s="34"/>
       <c r="M4" s="35" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="O4" s="34" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="P4" s="34"/>
       <c r="Q4" s="34"/>
       <c r="R4" s="35" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="S4" s="38"/>
       <c r="T4" s="38" t="s">
@@ -5003,7 +4982,7 @@
     </row>
     <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="B5" s="34" t="s">
         <v>59</v>
@@ -5015,10 +4994,10 @@
         <v>61</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G5" s="34" t="s">
         <v>234</v>
@@ -5033,28 +5012,28 @@
         <v>73</v>
       </c>
       <c r="K5" s="35" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="L5" s="35" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="M5" s="35" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="N5" s="36">
         <v>34958</v>
       </c>
       <c r="O5" s="34" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="P5" s="35"/>
       <c r="Q5" s="35"/>
       <c r="R5" s="35" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="S5" s="35"/>
       <c r="T5" s="35" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -5165,7 +5144,7 @@
     </row>
     <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>59</v>
@@ -5189,28 +5168,28 @@
         <v>63</v>
       </c>
       <c r="I8" s="35" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="J8" s="35" t="s">
         <v>74</v>
       </c>
       <c r="K8" s="35" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="L8" s="35"/>
       <c r="M8" s="35" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="N8" s="36" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="P8" s="35"/>
       <c r="Q8" s="35"/>
       <c r="R8" s="35" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="S8" s="35"/>
       <c r="T8" s="38" t="s">
@@ -5219,7 +5198,7 @@
     </row>
     <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="B9" s="34" t="s">
         <v>59</v>
@@ -5243,28 +5222,28 @@
         <v>63</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="J9" s="34" t="s">
         <v>73</v>
       </c>
       <c r="K9" s="34" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="L9" s="34"/>
       <c r="M9" s="35" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="N9" s="36">
         <v>23651</v>
       </c>
       <c r="O9" s="34" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="P9" s="34"/>
       <c r="Q9" s="34"/>
       <c r="R9" s="35" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="S9" s="38"/>
       <c r="T9" s="38" t="s">
@@ -5318,7 +5297,7 @@
       <c r="P10" s="34"/>
       <c r="Q10" s="34"/>
       <c r="R10" s="34" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="S10" s="35"/>
       <c r="T10" s="38" t="s">
@@ -5385,7 +5364,7 @@
     </row>
     <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>59</v>
@@ -5409,28 +5388,28 @@
         <v>63</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="J12" s="34" t="s">
         <v>301</v>
       </c>
       <c r="K12" s="34" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="L12" s="34"/>
       <c r="M12" s="35" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="N12" s="36" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="O12" s="34" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="P12" s="34"/>
       <c r="Q12" s="34"/>
       <c r="R12" s="35" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="S12" s="39"/>
       <c r="T12" s="38" t="s">
@@ -5439,7 +5418,7 @@
     </row>
     <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>59</v>
@@ -5463,28 +5442,28 @@
         <v>63</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="J13" s="34" t="s">
         <v>108</v>
       </c>
       <c r="K13" s="34" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="L13" s="34"/>
       <c r="M13" s="35" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="N13" s="36" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="O13" s="34" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="P13" s="34"/>
       <c r="Q13" s="34"/>
       <c r="R13" s="35" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="S13" s="39"/>
       <c r="T13" s="38" t="s">
@@ -5493,7 +5472,7 @@
     </row>
     <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>59</v>
@@ -5517,28 +5496,28 @@
         <v>63</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="J14" s="34" t="s">
         <v>73</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="35" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="N14" s="36" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="O14" s="34" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="P14" s="34"/>
       <c r="Q14" s="34"/>
       <c r="R14" s="35" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="S14" s="39"/>
       <c r="T14" s="38" t="s">
@@ -5547,7 +5526,7 @@
     </row>
     <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>59</v>
@@ -5571,28 +5550,28 @@
         <v>63</v>
       </c>
       <c r="I15" s="34" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="J15" s="34" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="K15" s="34" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="35" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="O15" s="34" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="P15" s="34"/>
       <c r="Q15" s="34"/>
       <c r="R15" s="35" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="S15" s="39"/>
       <c r="T15" s="38" t="s">
@@ -5711,7 +5690,7 @@
     </row>
     <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B18" s="34" t="s">
         <v>59</v>
@@ -5741,17 +5720,17 @@
         <v>108</v>
       </c>
       <c r="K18" s="34" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="L18" s="34"/>
       <c r="M18" s="35" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="N18" s="36">
         <v>37912</v>
       </c>
       <c r="O18" s="34" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="P18" s="34"/>
       <c r="Q18" s="34"/>
@@ -5819,7 +5798,7 @@
     </row>
     <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>59</v>
@@ -5843,17 +5822,17 @@
         <v>63</v>
       </c>
       <c r="I20" s="35" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="J20" s="35" t="s">
         <v>75</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="L20" s="35"/>
       <c r="M20" s="35" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="N20" s="36">
         <v>25927</v>
@@ -5864,7 +5843,7 @@
       <c r="R20" s="35"/>
       <c r="S20" s="35"/>
       <c r="T20" s="38" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -5921,7 +5900,7 @@
     </row>
     <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>59</v>
@@ -5945,28 +5924,28 @@
         <v>63</v>
       </c>
       <c r="I22" s="34" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="J22" s="34" t="s">
         <v>83</v>
       </c>
       <c r="K22" s="34" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="35" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="N22" s="36">
         <v>27616</v>
       </c>
       <c r="O22" s="34" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="P22" s="34"/>
       <c r="Q22" s="34"/>
       <c r="R22" s="35" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="S22" s="39"/>
       <c r="T22" s="38" t="s">
@@ -5975,7 +5954,7 @@
     </row>
     <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>59</v>
@@ -5999,35 +5978,35 @@
         <v>63</v>
       </c>
       <c r="I23" s="34" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="J23" s="34" t="s">
         <v>86</v>
       </c>
       <c r="K23" s="34" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="35" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="N23" s="36" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="O23" s="34" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="P23" s="34"/>
       <c r="Q23" s="34"/>
       <c r="R23" s="35"/>
       <c r="S23" s="38"/>
       <c r="T23" s="38" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="34" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B24" s="34" t="s">
         <v>59</v>
@@ -6051,28 +6030,28 @@
         <v>63</v>
       </c>
       <c r="I24" s="34" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="J24" s="34" t="s">
         <v>74</v>
       </c>
       <c r="K24" s="34" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="35" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="N24" s="36" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="O24" s="34" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="P24" s="34"/>
       <c r="Q24" s="34"/>
       <c r="R24" s="35" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="S24" s="39"/>
       <c r="T24" s="38" t="s">
@@ -6081,7 +6060,7 @@
     </row>
     <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="B25" s="34" t="s">
         <v>59</v>
@@ -6105,28 +6084,28 @@
         <v>63</v>
       </c>
       <c r="I25" s="34" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="J25" s="34" t="s">
         <v>74</v>
       </c>
       <c r="K25" s="34" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="L25" s="34"/>
       <c r="M25" s="35" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="N25" s="36" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="O25" s="34" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="P25" s="34"/>
       <c r="Q25" s="34"/>
       <c r="R25" s="35" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="S25" s="39"/>
       <c r="T25" s="38" t="s">
@@ -6182,7 +6161,7 @@
       <c r="P26" s="35"/>
       <c r="Q26" s="35"/>
       <c r="R26" s="35" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="S26" s="37"/>
       <c r="T26" s="37" t="s">
@@ -6191,7 +6170,7 @@
     </row>
     <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B27" s="34" t="s">
         <v>59</v>
@@ -6203,10 +6182,10 @@
         <v>61</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F27" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G27" s="35" t="s">
         <v>234</v>
@@ -6215,34 +6194,34 @@
         <v>63</v>
       </c>
       <c r="I27" s="35" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="J27" s="35" t="s">
         <v>68</v>
       </c>
       <c r="K27" s="35" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="L27" s="35"/>
       <c r="M27" s="35" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="N27" s="36">
         <v>25256</v>
       </c>
       <c r="O27" s="35" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="35" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="S27" s="37" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="T27" s="37" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -6259,10 +6238,10 @@
         <v>61</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F28" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G28" s="34" t="s">
         <v>234</v>
@@ -6271,7 +6250,7 @@
         <v>63</v>
       </c>
       <c r="I28" s="35" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="J28" s="35" t="s">
         <v>75</v>
@@ -6280,25 +6259,25 @@
         <v>76</v>
       </c>
       <c r="L28" s="35" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="M28" s="35" t="s">
         <v>261</v>
       </c>
       <c r="N28" s="36" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="O28" s="34" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="35" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="S28" s="35"/>
       <c r="T28" s="38" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -6327,13 +6306,13 @@
         <v>63</v>
       </c>
       <c r="I29" s="35" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="J29" s="35" t="s">
         <v>90</v>
       </c>
       <c r="K29" s="35" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="L29" s="35"/>
       <c r="M29" s="35" t="s">
@@ -6359,7 +6338,7 @@
     </row>
     <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="35" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="B30" s="34" t="s">
         <v>59</v>
@@ -6383,28 +6362,28 @@
         <v>63</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="J30" s="35" t="s">
         <v>108</v>
       </c>
       <c r="K30" s="35" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="L30" s="35"/>
       <c r="M30" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N30" s="36" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="O30" s="34" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="P30" s="35"/>
       <c r="Q30" s="35"/>
       <c r="R30" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="S30" s="35"/>
       <c r="T30" s="35" t="s">
@@ -6413,7 +6392,7 @@
     </row>
     <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="35" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="B31" s="34" t="s">
         <v>59</v>
@@ -6437,28 +6416,28 @@
         <v>63</v>
       </c>
       <c r="I31" s="34" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="J31" s="34" t="s">
         <v>86</v>
       </c>
       <c r="K31" s="34" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="L31" s="34"/>
       <c r="M31" s="35" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="N31" s="36" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="O31" s="34" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="P31" s="34"/>
       <c r="Q31" s="34"/>
       <c r="R31" s="35" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="S31" s="38"/>
       <c r="T31" s="38" t="s">
@@ -6581,7 +6560,7 @@
     </row>
     <row r="34" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B34" s="34" t="s">
         <v>59</v>
@@ -6593,10 +6572,10 @@
         <v>61</v>
       </c>
       <c r="E34" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F34" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G34" s="34" t="s">
         <v>234</v>
@@ -6605,28 +6584,28 @@
         <v>63</v>
       </c>
       <c r="I34" s="35" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="J34" s="35" t="s">
         <v>108</v>
       </c>
       <c r="K34" s="35" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="L34" s="35"/>
       <c r="M34" s="35" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="N34" s="36" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="O34" s="34" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="P34" s="35"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="35" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="S34" s="35"/>
       <c r="T34" s="38" t="s">
@@ -6635,7 +6614,7 @@
     </row>
     <row r="35" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="35" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="B35" s="34" t="s">
         <v>59</v>
@@ -6650,7 +6629,7 @@
         <v>62</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G35" s="34" t="s">
         <v>234</v>
@@ -6659,37 +6638,37 @@
         <v>63</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="J35" s="35" t="s">
         <v>75</v>
       </c>
       <c r="K35" s="35" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="L35" s="35"/>
       <c r="M35" s="35" t="s">
+        <v>655</v>
+      </c>
+      <c r="N35" s="36" t="s">
+        <v>659</v>
+      </c>
+      <c r="O35" s="34" t="s">
         <v>662</v>
-      </c>
-      <c r="N35" s="36" t="s">
-        <v>666</v>
-      </c>
-      <c r="O35" s="34" t="s">
-        <v>669</v>
       </c>
       <c r="P35" s="35"/>
       <c r="Q35" s="35"/>
       <c r="R35" s="35" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="S35" s="35"/>
       <c r="T35" s="38" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="B36" s="34" t="s">
         <v>59</v>
@@ -6701,10 +6680,10 @@
         <v>61</v>
       </c>
       <c r="E36" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F36" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G36" s="34" t="s">
         <v>234</v>
@@ -6713,37 +6692,37 @@
         <v>63</v>
       </c>
       <c r="I36" s="34" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="J36" s="34" t="s">
         <v>75</v>
       </c>
       <c r="K36" s="34" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="L36" s="34"/>
       <c r="M36" s="35" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="N36" s="36">
         <v>38935</v>
       </c>
       <c r="O36" s="34" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="P36" s="34"/>
       <c r="Q36" s="34"/>
       <c r="R36" s="35" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="S36" s="39"/>
       <c r="T36" s="38" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="B37" s="34" t="s">
         <v>59</v>
@@ -6755,10 +6734,10 @@
         <v>61</v>
       </c>
       <c r="E37" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F37" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G37" s="34" t="s">
         <v>234</v>
@@ -6767,7 +6746,7 @@
         <v>63</v>
       </c>
       <c r="I37" s="35" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="J37" s="35" t="s">
         <v>75</v>
@@ -6776,25 +6755,25 @@
         <v>76</v>
       </c>
       <c r="L37" s="35" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="M37" s="35" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="N37" s="36" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="O37" s="34" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="P37" s="35"/>
       <c r="Q37" s="35"/>
       <c r="R37" s="35" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="S37" s="35"/>
       <c r="T37" s="38" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
@@ -6853,7 +6832,7 @@
     </row>
     <row r="39" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="35" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="B39" s="34" t="s">
         <v>59</v>
@@ -6865,10 +6844,10 @@
         <v>61</v>
       </c>
       <c r="E39" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G39" s="34" t="s">
         <v>234</v>
@@ -6877,30 +6856,30 @@
         <v>63</v>
       </c>
       <c r="I39" s="34" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="J39" s="34" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="K39" s="34" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="L39" s="34" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="M39" s="35" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="N39" s="36" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="O39" s="34" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="P39" s="34"/>
       <c r="Q39" s="34"/>
       <c r="R39" s="35" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="S39" s="39"/>
       <c r="T39" s="38" t="s">
@@ -6939,7 +6918,7 @@
         <v>142</v>
       </c>
       <c r="K40" s="35" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="L40" s="35"/>
       <c r="M40" s="35" t="s">
@@ -6963,7 +6942,7 @@
     </row>
     <row r="41" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="34" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B41" s="34" t="s">
         <v>59</v>
@@ -6987,7 +6966,7 @@
         <v>63</v>
       </c>
       <c r="I41" s="35" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="J41" s="35" t="s">
         <v>86</v>
@@ -6997,18 +6976,18 @@
       </c>
       <c r="L41" s="35"/>
       <c r="M41" s="35" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="N41" s="36">
         <v>30209</v>
       </c>
       <c r="O41" s="34" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="P41" s="35"/>
       <c r="Q41" s="35"/>
       <c r="R41" s="35" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="S41" s="35"/>
       <c r="T41" s="38" t="s">
@@ -7017,7 +6996,7 @@
     </row>
     <row r="42" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="35" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="B42" s="34" t="s">
         <v>59</v>
@@ -7032,7 +7011,7 @@
         <v>62</v>
       </c>
       <c r="F42" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G42" s="34" t="s">
         <v>234</v>
@@ -7041,37 +7020,37 @@
         <v>63</v>
       </c>
       <c r="I42" s="35" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="J42" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K42" s="35" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="L42" s="35"/>
       <c r="M42" s="35" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="N42" s="36" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="O42" s="34" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="P42" s="35"/>
       <c r="Q42" s="35"/>
       <c r="R42" s="35" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="S42" s="35"/>
       <c r="T42" s="38" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="34" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="B43" s="34" t="s">
         <v>59</v>
@@ -7095,39 +7074,39 @@
         <v>63</v>
       </c>
       <c r="I43" s="35" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="J43" s="35" t="s">
         <v>310</v>
       </c>
       <c r="K43" s="35" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="L43" s="35" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="M43" s="35" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="N43" s="36">
         <v>23292</v>
       </c>
       <c r="O43" s="35" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
       <c r="R43" s="35" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="S43" s="35"/>
       <c r="T43" s="35" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="34" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="B44" s="34" t="s">
         <v>59</v>
@@ -7157,30 +7136,30 @@
         <v>82</v>
       </c>
       <c r="K44" s="34" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="L44" s="34" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="M44" s="35" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="N44" s="36">
         <v>29846</v>
       </c>
       <c r="O44" s="34" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="P44" s="34"/>
       <c r="Q44" s="34"/>
       <c r="R44" s="35" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="S44" s="39" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="T44" s="38" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="U44" s="32"/>
     </row>
@@ -7216,7 +7195,7 @@
         <v>65</v>
       </c>
       <c r="K45" s="34" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="L45" s="34"/>
       <c r="M45" s="35" t="s">
@@ -7240,7 +7219,7 @@
     </row>
     <row r="46" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="34" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="B46" s="34" t="s">
         <v>59</v>
@@ -7252,10 +7231,10 @@
         <v>61</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F46" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G46" s="34" t="s">
         <v>234</v>
@@ -7274,29 +7253,29 @@
       </c>
       <c r="L46" s="34"/>
       <c r="M46" s="35" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N46" s="36">
         <v>31066</v>
       </c>
       <c r="O46" s="34" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="P46" s="34"/>
       <c r="Q46" s="34"/>
       <c r="R46" s="35" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="S46" s="39" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="T46" s="38" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="34" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B47" s="34" t="s">
         <v>59</v>
@@ -7326,30 +7305,30 @@
         <v>112</v>
       </c>
       <c r="K47" s="34" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="L47" s="34" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="M47" s="35" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="N47" s="36">
         <v>27169</v>
       </c>
       <c r="O47" s="34" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="P47" s="34"/>
       <c r="Q47" s="34"/>
       <c r="R47" s="35" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="S47" s="39" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="T47" s="38" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
@@ -7436,7 +7415,7 @@
         <v>310</v>
       </c>
       <c r="K49" s="34" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="L49" s="34"/>
       <c r="M49" s="35" t="s">
@@ -7457,12 +7436,12 @@
         <v>314</v>
       </c>
       <c r="T49" s="38" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="34" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="B50" s="34" t="s">
         <v>59</v>
@@ -7495,32 +7474,32 @@
         <v>107</v>
       </c>
       <c r="L50" s="34" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="M50" s="35" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="N50" s="36">
         <v>24574</v>
       </c>
       <c r="O50" s="34" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="P50" s="34"/>
       <c r="Q50" s="34"/>
       <c r="R50" s="35" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="S50" s="39" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="T50" s="38" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="34" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="B51" s="34" t="s">
         <v>59</v>
@@ -7550,33 +7529,33 @@
         <v>86</v>
       </c>
       <c r="K51" s="34" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="L51" s="34" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="M51" s="35" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="N51" s="36">
         <v>20073</v>
       </c>
       <c r="O51" s="34" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="P51" s="34"/>
       <c r="Q51" s="34"/>
       <c r="R51" s="35" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="S51" s="39"/>
       <c r="T51" s="38" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="34" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="B52" s="34" t="s">
         <v>59</v>
@@ -7606,11 +7585,11 @@
         <v>75</v>
       </c>
       <c r="K52" s="34" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="L52" s="34"/>
       <c r="M52" s="35" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="N52" s="36">
         <v>40077</v>
@@ -7682,7 +7661,7 @@
     </row>
     <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="34" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B54" s="34" t="s">
         <v>59</v>
@@ -7694,10 +7673,10 @@
         <v>61</v>
       </c>
       <c r="E54" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F54" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G54" s="34" t="s">
         <v>234</v>
@@ -7712,28 +7691,28 @@
         <v>71</v>
       </c>
       <c r="K54" s="34" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="L54" s="34"/>
       <c r="M54" s="35" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="N54" s="36">
         <v>23023</v>
       </c>
       <c r="O54" s="34" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="P54" s="34"/>
       <c r="Q54" s="34"/>
       <c r="R54" s="35" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="S54" s="39" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="T54" s="38" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -7794,7 +7773,7 @@
     </row>
     <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="34" t="s">
-        <v>527</v>
+        <v>268</v>
       </c>
       <c r="B56" s="34" t="s">
         <v>59</v>
@@ -7818,39 +7797,39 @@
         <v>63</v>
       </c>
       <c r="I56" s="34" t="s">
-        <v>462</v>
+        <v>115</v>
       </c>
       <c r="J56" s="34" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="K56" s="34" t="s">
-        <v>463</v>
+        <v>134</v>
       </c>
       <c r="L56" s="34" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="M56" s="35" t="s">
-        <v>465</v>
+        <v>302</v>
       </c>
       <c r="N56" s="36">
-        <v>25972</v>
+        <v>27622</v>
       </c>
       <c r="O56" s="34" t="s">
-        <v>466</v>
+        <v>218</v>
       </c>
       <c r="P56" s="34"/>
       <c r="Q56" s="34"/>
       <c r="R56" s="35" t="s">
-        <v>629</v>
+        <v>219</v>
       </c>
       <c r="S56" s="39"/>
       <c r="T56" s="38" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="34" t="s">
-        <v>268</v>
+        <v>393</v>
       </c>
       <c r="B57" s="34" t="s">
         <v>59</v>
@@ -7877,36 +7856,32 @@
         <v>115</v>
       </c>
       <c r="J57" s="34" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K57" s="34" t="s">
-        <v>134</v>
+        <v>394</v>
       </c>
       <c r="L57" s="34" t="s">
-        <v>449</v>
+        <v>394</v>
       </c>
       <c r="M57" s="35" t="s">
-        <v>302</v>
+        <v>395</v>
       </c>
       <c r="N57" s="36">
-        <v>27622</v>
-      </c>
-      <c r="O57" s="34" t="s">
-        <v>218</v>
-      </c>
+        <v>22700</v>
+      </c>
+      <c r="O57" s="34"/>
       <c r="P57" s="34"/>
       <c r="Q57" s="34"/>
-      <c r="R57" s="35" t="s">
-        <v>219</v>
-      </c>
+      <c r="R57" s="35"/>
       <c r="S57" s="39"/>
       <c r="T57" s="38" t="s">
-        <v>151</v>
+        <v>461</v>
       </c>
     </row>
     <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="34" t="s">
-        <v>393</v>
+        <v>342</v>
       </c>
       <c r="B58" s="34" t="s">
         <v>59</v>
@@ -7930,35 +7905,39 @@
         <v>63</v>
       </c>
       <c r="I58" s="34" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="J58" s="34" t="s">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="K58" s="34" t="s">
-        <v>394</v>
-      </c>
-      <c r="L58" s="34" t="s">
-        <v>394</v>
-      </c>
+        <v>807</v>
+      </c>
+      <c r="L58" s="34"/>
       <c r="M58" s="35" t="s">
-        <v>395</v>
+        <v>323</v>
       </c>
       <c r="N58" s="36">
-        <v>22700</v>
-      </c>
-      <c r="O58" s="34"/>
+        <v>30254</v>
+      </c>
+      <c r="O58" s="34" t="s">
+        <v>324</v>
+      </c>
       <c r="P58" s="34"/>
       <c r="Q58" s="34"/>
-      <c r="R58" s="35"/>
-      <c r="S58" s="39"/>
+      <c r="R58" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="S58" s="39" t="s">
+        <v>326</v>
+      </c>
       <c r="T58" s="38" t="s">
-        <v>461</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="34" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="B59" s="34" t="s">
         <v>59</v>
@@ -7970,51 +7949,51 @@
         <v>61</v>
       </c>
       <c r="E59" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F59" s="35" t="s">
         <v>131</v>
       </c>
       <c r="G59" s="34" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="H59" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I59" s="34" t="s">
-        <v>109</v>
+        <v>316</v>
       </c>
       <c r="J59" s="34" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="K59" s="34" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="L59" s="34"/>
       <c r="M59" s="35" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="N59" s="36">
-        <v>30254</v>
+        <v>27776</v>
       </c>
       <c r="O59" s="34" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="P59" s="34"/>
       <c r="Q59" s="34"/>
       <c r="R59" s="35" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="S59" s="39" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="T59" s="38" t="s">
-        <v>163</v>
+        <v>576</v>
       </c>
     </row>
     <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="34" t="s">
-        <v>315</v>
+        <v>442</v>
       </c>
       <c r="B60" s="34" t="s">
         <v>59</v>
@@ -8026,51 +8005,47 @@
         <v>61</v>
       </c>
       <c r="E60" s="35" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F60" s="35" t="s">
         <v>131</v>
       </c>
       <c r="G60" s="34" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="H60" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I60" s="34" t="s">
-        <v>316</v>
+        <v>111</v>
       </c>
       <c r="J60" s="34" t="s">
-        <v>317</v>
+        <v>68</v>
       </c>
       <c r="K60" s="34" t="s">
-        <v>815</v>
-      </c>
-      <c r="L60" s="34"/>
+        <v>69</v>
+      </c>
+      <c r="L60" s="34" t="s">
+        <v>69</v>
+      </c>
       <c r="M60" s="35" t="s">
-        <v>318</v>
+        <v>402</v>
       </c>
       <c r="N60" s="36">
-        <v>27776</v>
-      </c>
-      <c r="O60" s="34" t="s">
-        <v>319</v>
-      </c>
+        <v>30538</v>
+      </c>
+      <c r="O60" s="34"/>
       <c r="P60" s="34"/>
       <c r="Q60" s="34"/>
-      <c r="R60" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="S60" s="39" t="s">
-        <v>321</v>
-      </c>
+      <c r="R60" s="35"/>
+      <c r="S60" s="39"/>
       <c r="T60" s="38" t="s">
-        <v>582</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="34" t="s">
-        <v>442</v>
+        <v>396</v>
       </c>
       <c r="B61" s="34" t="s">
         <v>59</v>
@@ -8094,22 +8069,22 @@
         <v>63</v>
       </c>
       <c r="I61" s="34" t="s">
-        <v>111</v>
+        <v>397</v>
       </c>
       <c r="J61" s="34" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="K61" s="34" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="L61" s="34" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="M61" s="35" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="N61" s="36">
-        <v>30538</v>
+        <v>25896</v>
       </c>
       <c r="O61" s="34"/>
       <c r="P61" s="34"/>
@@ -8117,12 +8092,12 @@
       <c r="R61" s="35"/>
       <c r="S61" s="39"/>
       <c r="T61" s="38" t="s">
-        <v>193</v>
+        <v>461</v>
       </c>
     </row>
     <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="34" t="s">
-        <v>396</v>
+        <v>338</v>
       </c>
       <c r="B62" s="34" t="s">
         <v>59</v>
@@ -8146,35 +8121,37 @@
         <v>63</v>
       </c>
       <c r="I62" s="34" t="s">
-        <v>397</v>
+        <v>328</v>
       </c>
       <c r="J62" s="34" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="K62" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="L62" s="34" t="s">
-        <v>97</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="L62" s="34"/>
       <c r="M62" s="35" t="s">
-        <v>398</v>
+        <v>335</v>
       </c>
       <c r="N62" s="36">
-        <v>25896</v>
-      </c>
-      <c r="O62" s="34"/>
+        <v>25993</v>
+      </c>
+      <c r="O62" s="34" t="s">
+        <v>336</v>
+      </c>
       <c r="P62" s="34"/>
       <c r="Q62" s="34"/>
-      <c r="R62" s="35"/>
+      <c r="R62" s="35" t="s">
+        <v>337</v>
+      </c>
       <c r="S62" s="39"/>
       <c r="T62" s="38" t="s">
-        <v>461</v>
+        <v>193</v>
       </c>
     </row>
     <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="34" t="s">
-        <v>338</v>
+        <v>269</v>
       </c>
       <c r="B63" s="34" t="s">
         <v>59</v>
@@ -8198,37 +8175,39 @@
         <v>63</v>
       </c>
       <c r="I63" s="34" t="s">
-        <v>328</v>
+        <v>91</v>
       </c>
       <c r="J63" s="34" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="K63" s="34" t="s">
-        <v>327</v>
+        <v>809</v>
       </c>
       <c r="L63" s="34"/>
       <c r="M63" s="35" t="s">
-        <v>335</v>
+        <v>164</v>
       </c>
       <c r="N63" s="36">
-        <v>25993</v>
+        <v>25881</v>
       </c>
       <c r="O63" s="34" t="s">
-        <v>336</v>
+        <v>165</v>
       </c>
       <c r="P63" s="34"/>
       <c r="Q63" s="34"/>
       <c r="R63" s="35" t="s">
-        <v>337</v>
-      </c>
-      <c r="S63" s="39"/>
+        <v>166</v>
+      </c>
+      <c r="S63" s="39" t="s">
+        <v>167</v>
+      </c>
       <c r="T63" s="38" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
     </row>
     <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="34" t="s">
-        <v>269</v>
+        <v>409</v>
       </c>
       <c r="B64" s="34" t="s">
         <v>59</v>
@@ -8252,31 +8231,33 @@
         <v>63</v>
       </c>
       <c r="I64" s="34" t="s">
-        <v>91</v>
+        <v>352</v>
       </c>
       <c r="J64" s="34" t="s">
-        <v>92</v>
+        <v>410</v>
       </c>
       <c r="K64" s="34" t="s">
-        <v>816</v>
-      </c>
-      <c r="L64" s="34"/>
+        <v>434</v>
+      </c>
+      <c r="L64" s="34" t="s">
+        <v>434</v>
+      </c>
       <c r="M64" s="35" t="s">
-        <v>164</v>
+        <v>411</v>
       </c>
       <c r="N64" s="36">
-        <v>25881</v>
+        <v>30157</v>
       </c>
       <c r="O64" s="34" t="s">
-        <v>165</v>
+        <v>355</v>
       </c>
       <c r="P64" s="34"/>
       <c r="Q64" s="34"/>
       <c r="R64" s="35" t="s">
-        <v>166</v>
+        <v>412</v>
       </c>
       <c r="S64" s="39" t="s">
-        <v>167</v>
+        <v>413</v>
       </c>
       <c r="T64" s="38" t="s">
         <v>163</v>
@@ -8284,7 +8265,7 @@
     </row>
     <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="34" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="B65" s="34" t="s">
         <v>59</v>
@@ -8311,30 +8292,28 @@
         <v>352</v>
       </c>
       <c r="J65" s="34" t="s">
-        <v>410</v>
+        <v>75</v>
       </c>
       <c r="K65" s="34" t="s">
-        <v>434</v>
-      </c>
-      <c r="L65" s="34" t="s">
-        <v>434</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="L65" s="34"/>
       <c r="M65" s="35" t="s">
-        <v>411</v>
+        <v>362</v>
       </c>
       <c r="N65" s="36">
-        <v>30157</v>
+        <v>34772</v>
       </c>
       <c r="O65" s="34" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="P65" s="34"/>
       <c r="Q65" s="34"/>
       <c r="R65" s="35" t="s">
-        <v>412</v>
+        <v>364</v>
       </c>
       <c r="S65" s="39" t="s">
-        <v>413</v>
+        <v>365</v>
       </c>
       <c r="T65" s="38" t="s">
         <v>163</v>
@@ -8342,7 +8321,7 @@
     </row>
     <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="34" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="B66" s="34" t="s">
         <v>59</v>
@@ -8359,46 +8338,46 @@
       <c r="F66" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="G66" s="34" t="s">
+      <c r="G66" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="H66" s="34" t="s">
+      <c r="H66" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="I66" s="34" t="s">
+      <c r="I66" s="35" t="s">
         <v>352</v>
       </c>
-      <c r="J66" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="K66" s="34" t="s">
-        <v>316</v>
-      </c>
-      <c r="L66" s="34"/>
+      <c r="J66" s="35" t="s">
+        <v>353</v>
+      </c>
+      <c r="K66" s="35" t="s">
+        <v>810</v>
+      </c>
+      <c r="L66" s="35"/>
       <c r="M66" s="35" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="N66" s="36">
-        <v>34772</v>
-      </c>
-      <c r="O66" s="34" t="s">
-        <v>363</v>
-      </c>
-      <c r="P66" s="34"/>
-      <c r="Q66" s="34"/>
+        <v>23605</v>
+      </c>
+      <c r="O66" s="35" t="s">
+        <v>355</v>
+      </c>
+      <c r="P66" s="35"/>
+      <c r="Q66" s="35"/>
       <c r="R66" s="35" t="s">
-        <v>364</v>
-      </c>
-      <c r="S66" s="39" t="s">
-        <v>365</v>
-      </c>
-      <c r="T66" s="38" t="s">
+        <v>356</v>
+      </c>
+      <c r="S66" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="T66" s="37" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="34" t="s">
-        <v>366</v>
+        <v>270</v>
       </c>
       <c r="B67" s="34" t="s">
         <v>59</v>
@@ -8410,51 +8389,51 @@
         <v>61</v>
       </c>
       <c r="E67" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F67" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="G67" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="H67" s="35" t="s">
+      <c r="G67" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="H67" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I67" s="35" t="s">
-        <v>352</v>
-      </c>
-      <c r="J67" s="35" t="s">
-        <v>353</v>
-      </c>
-      <c r="K67" s="35" t="s">
-        <v>817</v>
-      </c>
-      <c r="L67" s="35"/>
+      <c r="I67" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="J67" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="K67" s="34" t="s">
+        <v>811</v>
+      </c>
+      <c r="L67" s="34"/>
       <c r="M67" s="35" t="s">
-        <v>354</v>
+        <v>168</v>
       </c>
       <c r="N67" s="36">
-        <v>23605</v>
-      </c>
-      <c r="O67" s="35" t="s">
-        <v>355</v>
-      </c>
-      <c r="P67" s="35"/>
-      <c r="Q67" s="35"/>
+        <v>22431</v>
+      </c>
+      <c r="O67" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="P67" s="34"/>
+      <c r="Q67" s="34"/>
       <c r="R67" s="35" t="s">
-        <v>356</v>
-      </c>
-      <c r="S67" s="37" t="s">
-        <v>357</v>
-      </c>
-      <c r="T67" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="S67" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="T67" s="38" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="34" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B68" s="34" t="s">
         <v>59</v>
@@ -8466,51 +8445,49 @@
         <v>61</v>
       </c>
       <c r="E68" s="35" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F68" s="35" t="s">
         <v>131</v>
       </c>
       <c r="G68" s="34" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="H68" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I68" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="J68" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="K68" s="34" t="s">
-        <v>818</v>
-      </c>
-      <c r="L68" s="34"/>
+      <c r="I68" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="J68" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="K68" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="L68" s="35"/>
       <c r="M68" s="35" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="N68" s="36">
-        <v>22431</v>
+        <v>23105</v>
       </c>
       <c r="O68" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="P68" s="34"/>
-      <c r="Q68" s="34"/>
+        <v>206</v>
+      </c>
+      <c r="P68" s="35"/>
+      <c r="Q68" s="35"/>
       <c r="R68" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="S68" s="39" t="s">
-        <v>170</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="S68" s="35"/>
       <c r="T68" s="38" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="34" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="B69" s="34" t="s">
         <v>59</v>
@@ -8522,13 +8499,13 @@
         <v>61</v>
       </c>
       <c r="E69" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F69" s="35" t="s">
         <v>131</v>
       </c>
       <c r="G69" s="34" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="H69" s="34" t="s">
         <v>63</v>
@@ -8537,25 +8514,25 @@
         <v>117</v>
       </c>
       <c r="J69" s="35" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="K69" s="35" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="L69" s="35"/>
       <c r="M69" s="35" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="N69" s="36">
-        <v>23105</v>
+        <v>36383</v>
       </c>
       <c r="O69" s="34" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
       <c r="R69" s="35" t="s">
-        <v>207</v>
+        <v>622</v>
       </c>
       <c r="S69" s="35"/>
       <c r="T69" s="38" t="s">
@@ -8564,7 +8541,7 @@
     </row>
     <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="34" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B70" s="34" t="s">
         <v>59</v>
@@ -8576,13 +8553,13 @@
         <v>61</v>
       </c>
       <c r="E70" s="35" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F70" s="35" t="s">
         <v>131</v>
       </c>
       <c r="G70" s="34" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="H70" s="34" t="s">
         <v>63</v>
@@ -8591,25 +8568,25 @@
         <v>117</v>
       </c>
       <c r="J70" s="35" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="K70" s="35" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L70" s="35"/>
       <c r="M70" s="35" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="N70" s="36">
-        <v>36383</v>
+        <v>33831</v>
       </c>
       <c r="O70" s="34" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="P70" s="35"/>
       <c r="Q70" s="35"/>
       <c r="R70" s="35" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="S70" s="35"/>
       <c r="T70" s="38" t="s">
@@ -8618,7 +8595,7 @@
     </row>
     <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="34" t="s">
-        <v>272</v>
+        <v>390</v>
       </c>
       <c r="B71" s="34" t="s">
         <v>59</v>
@@ -8648,31 +8625,31 @@
         <v>86</v>
       </c>
       <c r="K71" s="35" t="s">
-        <v>118</v>
+        <v>348</v>
       </c>
       <c r="L71" s="35"/>
       <c r="M71" s="35" t="s">
-        <v>194</v>
+        <v>351</v>
       </c>
       <c r="N71" s="36">
-        <v>33831</v>
+        <v>30287</v>
       </c>
       <c r="O71" s="34" t="s">
-        <v>195</v>
+        <v>349</v>
       </c>
       <c r="P71" s="35"/>
       <c r="Q71" s="35"/>
       <c r="R71" s="35" t="s">
-        <v>630</v>
+        <v>350</v>
       </c>
       <c r="S71" s="35"/>
       <c r="T71" s="38" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="34" t="s">
-        <v>390</v>
+        <v>273</v>
       </c>
       <c r="B72" s="34" t="s">
         <v>59</v>
@@ -8699,34 +8676,34 @@
         <v>117</v>
       </c>
       <c r="J72" s="35" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="K72" s="35" t="s">
-        <v>348</v>
+        <v>80</v>
       </c>
       <c r="L72" s="35"/>
       <c r="M72" s="35" t="s">
-        <v>351</v>
+        <v>521</v>
       </c>
       <c r="N72" s="36">
-        <v>30287</v>
+        <v>26138</v>
       </c>
       <c r="O72" s="34" t="s">
-        <v>349</v>
+        <v>208</v>
       </c>
       <c r="P72" s="35"/>
       <c r="Q72" s="35"/>
       <c r="R72" s="35" t="s">
-        <v>350</v>
+        <v>624</v>
       </c>
       <c r="S72" s="35"/>
       <c r="T72" s="38" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="34" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B73" s="34" t="s">
         <v>59</v>
@@ -8753,25 +8730,25 @@
         <v>117</v>
       </c>
       <c r="J73" s="35" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="K73" s="35" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="L73" s="35"/>
       <c r="M73" s="35" t="s">
-        <v>526</v>
+        <v>199</v>
       </c>
       <c r="N73" s="36">
-        <v>26138</v>
+        <v>32984</v>
       </c>
       <c r="O73" s="34" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="P73" s="35"/>
       <c r="Q73" s="35"/>
       <c r="R73" s="35" t="s">
-        <v>631</v>
+        <v>201</v>
       </c>
       <c r="S73" s="35"/>
       <c r="T73" s="38" t="s">
@@ -8780,7 +8757,7 @@
     </row>
     <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="34" t="s">
-        <v>274</v>
+        <v>561</v>
       </c>
       <c r="B74" s="34" t="s">
         <v>59</v>
@@ -8792,10 +8769,10 @@
         <v>61</v>
       </c>
       <c r="E74" s="35" t="s">
-        <v>62</v>
+        <v>467</v>
       </c>
       <c r="F74" s="35" t="s">
-        <v>131</v>
+        <v>468</v>
       </c>
       <c r="G74" s="34" t="s">
         <v>234</v>
@@ -8804,37 +8781,39 @@
         <v>63</v>
       </c>
       <c r="I74" s="35" t="s">
-        <v>117</v>
+        <v>538</v>
       </c>
       <c r="J74" s="35" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="K74" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="L74" s="35"/>
+        <v>539</v>
+      </c>
+      <c r="L74" s="35" t="s">
+        <v>540</v>
+      </c>
       <c r="M74" s="35" t="s">
-        <v>199</v>
+        <v>541</v>
       </c>
       <c r="N74" s="36">
-        <v>32984</v>
+        <v>23098</v>
       </c>
       <c r="O74" s="34" t="s">
-        <v>200</v>
+        <v>542</v>
       </c>
       <c r="P74" s="35"/>
       <c r="Q74" s="35"/>
       <c r="R74" s="35" t="s">
-        <v>201</v>
+        <v>543</v>
       </c>
       <c r="S74" s="35"/>
       <c r="T74" s="38" t="s">
-        <v>193</v>
+        <v>508</v>
       </c>
     </row>
     <row r="75" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="34" t="s">
-        <v>567</v>
+        <v>448</v>
       </c>
       <c r="B75" s="34" t="s">
         <v>59</v>
@@ -8846,10 +8825,10 @@
         <v>61</v>
       </c>
       <c r="E75" s="35" t="s">
-        <v>472</v>
+        <v>62</v>
       </c>
       <c r="F75" s="35" t="s">
-        <v>473</v>
+        <v>131</v>
       </c>
       <c r="G75" s="34" t="s">
         <v>234</v>
@@ -8858,39 +8837,39 @@
         <v>63</v>
       </c>
       <c r="I75" s="35" t="s">
-        <v>544</v>
+        <v>346</v>
       </c>
       <c r="J75" s="35" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="K75" s="35" t="s">
-        <v>545</v>
-      </c>
-      <c r="L75" s="35" t="s">
-        <v>546</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="L75" s="35"/>
       <c r="M75" s="35" t="s">
-        <v>547</v>
+        <v>444</v>
       </c>
       <c r="N75" s="36">
-        <v>23098</v>
+        <v>25389</v>
       </c>
       <c r="O75" s="34" t="s">
-        <v>548</v>
+        <v>445</v>
       </c>
       <c r="P75" s="35"/>
       <c r="Q75" s="35"/>
       <c r="R75" s="35" t="s">
-        <v>549</v>
-      </c>
-      <c r="S75" s="35"/>
+        <v>446</v>
+      </c>
+      <c r="S75" s="35" t="s">
+        <v>447</v>
+      </c>
       <c r="T75" s="38" t="s">
-        <v>513</v>
+        <v>217</v>
       </c>
     </row>
     <row r="76" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="34" t="s">
-        <v>448</v>
+        <v>275</v>
       </c>
       <c r="B76" s="34" t="s">
         <v>59</v>
@@ -8914,39 +8893,37 @@
         <v>63</v>
       </c>
       <c r="I76" s="35" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="J76" s="35" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K76" s="35" t="s">
-        <v>443</v>
+        <v>103</v>
       </c>
       <c r="L76" s="35"/>
       <c r="M76" s="35" t="s">
-        <v>444</v>
+        <v>181</v>
       </c>
       <c r="N76" s="36">
-        <v>25389</v>
+        <v>29006</v>
       </c>
       <c r="O76" s="34" t="s">
-        <v>445</v>
+        <v>182</v>
       </c>
       <c r="P76" s="35"/>
       <c r="Q76" s="35"/>
       <c r="R76" s="35" t="s">
-        <v>446</v>
-      </c>
-      <c r="S76" s="35" t="s">
-        <v>447</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="S76" s="35"/>
       <c r="T76" s="38" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
     </row>
     <row r="77" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="34" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B77" s="34" t="s">
         <v>59</v>
@@ -8970,37 +8947,37 @@
         <v>63</v>
       </c>
       <c r="I77" s="35" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="J77" s="35" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="K77" s="35" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="L77" s="35"/>
       <c r="M77" s="35" t="s">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="N77" s="36">
-        <v>29006</v>
+        <v>21024</v>
       </c>
       <c r="O77" s="34" t="s">
-        <v>182</v>
+        <v>228</v>
       </c>
       <c r="P77" s="35"/>
       <c r="Q77" s="35"/>
       <c r="R77" s="35" t="s">
-        <v>183</v>
+        <v>229</v>
       </c>
       <c r="S77" s="35"/>
       <c r="T77" s="38" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
     </row>
     <row r="78" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="34" t="s">
-        <v>276</v>
+        <v>799</v>
       </c>
       <c r="B78" s="34" t="s">
         <v>59</v>
@@ -9023,38 +9000,38 @@
       <c r="H78" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I78" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="J78" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="K78" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="L78" s="35"/>
+      <c r="I78" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="J78" s="34" t="s">
+        <v>791</v>
+      </c>
+      <c r="K78" s="34" t="s">
+        <v>792</v>
+      </c>
+      <c r="L78" s="34"/>
       <c r="M78" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="N78" s="36">
-        <v>21024</v>
+        <v>793</v>
+      </c>
+      <c r="N78" s="36" t="s">
+        <v>795</v>
       </c>
       <c r="O78" s="34" t="s">
-        <v>228</v>
-      </c>
-      <c r="P78" s="35"/>
-      <c r="Q78" s="35"/>
+        <v>796</v>
+      </c>
+      <c r="P78" s="34"/>
+      <c r="Q78" s="34"/>
       <c r="R78" s="35" t="s">
-        <v>229</v>
-      </c>
-      <c r="S78" s="35"/>
+        <v>797</v>
+      </c>
+      <c r="S78" s="38"/>
       <c r="T78" s="38" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="79" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="34" t="s">
-        <v>806</v>
+        <v>277</v>
       </c>
       <c r="B79" s="34" t="s">
         <v>59</v>
@@ -9077,38 +9054,38 @@
       <c r="H79" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I79" s="34" t="s">
+      <c r="I79" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="J79" s="34" t="s">
-        <v>798</v>
-      </c>
-      <c r="K79" s="34" t="s">
-        <v>799</v>
-      </c>
-      <c r="L79" s="34"/>
+      <c r="J79" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="K79" s="35" t="s">
+        <v>394</v>
+      </c>
+      <c r="L79" s="35"/>
       <c r="M79" s="35" t="s">
-        <v>800</v>
-      </c>
-      <c r="N79" s="36" t="s">
-        <v>802</v>
+        <v>224</v>
+      </c>
+      <c r="N79" s="36">
+        <v>19757</v>
       </c>
       <c r="O79" s="34" t="s">
-        <v>803</v>
-      </c>
-      <c r="P79" s="34"/>
-      <c r="Q79" s="34"/>
+        <v>225</v>
+      </c>
+      <c r="P79" s="35"/>
+      <c r="Q79" s="35"/>
       <c r="R79" s="35" t="s">
-        <v>804</v>
-      </c>
-      <c r="S79" s="38"/>
+        <v>226</v>
+      </c>
+      <c r="S79" s="35"/>
       <c r="T79" s="38" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="80" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="34" t="s">
-        <v>277</v>
+        <v>392</v>
       </c>
       <c r="B80" s="34" t="s">
         <v>59</v>
@@ -9132,37 +9109,37 @@
         <v>63</v>
       </c>
       <c r="I80" s="35" t="s">
-        <v>137</v>
+        <v>379</v>
       </c>
       <c r="J80" s="35" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="K80" s="35" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="L80" s="35"/>
       <c r="M80" s="35" t="s">
-        <v>224</v>
+        <v>386</v>
       </c>
       <c r="N80" s="36">
-        <v>19757</v>
+        <v>30337</v>
       </c>
       <c r="O80" s="34" t="s">
-        <v>225</v>
+        <v>381</v>
       </c>
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
       <c r="R80" s="35" t="s">
-        <v>226</v>
+        <v>382</v>
       </c>
       <c r="S80" s="35"/>
       <c r="T80" s="38" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="34" t="s">
-        <v>392</v>
+        <v>436</v>
       </c>
       <c r="B81" s="34" t="s">
         <v>59</v>
@@ -9186,37 +9163,36 @@
         <v>63</v>
       </c>
       <c r="I81" s="35" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="J81" s="35" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="K81" s="35" t="s">
-        <v>380</v>
-      </c>
-      <c r="L81" s="35"/>
+        <v>400</v>
+      </c>
+      <c r="L81" s="35" t="s">
+        <v>400</v>
+      </c>
       <c r="M81" s="35" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="N81" s="36">
-        <v>30337</v>
-      </c>
-      <c r="O81" s="34" t="s">
-        <v>381</v>
-      </c>
+        <v>29821</v>
+      </c>
+      <c r="O81" s="34"/>
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
-      <c r="R81" s="35" t="s">
-        <v>382</v>
-      </c>
+      <c r="R81" s="35"/>
       <c r="S81" s="35"/>
       <c r="T81" s="38" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+      <c r="U81" s="27"/>
+    </row>
+    <row r="82" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="34" t="s">
-        <v>436</v>
+        <v>278</v>
       </c>
       <c r="B82" s="34" t="s">
         <v>59</v>
@@ -9240,36 +9216,39 @@
         <v>63</v>
       </c>
       <c r="I82" s="35" t="s">
-        <v>399</v>
+        <v>64</v>
       </c>
       <c r="J82" s="35" t="s">
         <v>65</v>
       </c>
       <c r="K82" s="35" t="s">
-        <v>400</v>
-      </c>
-      <c r="L82" s="35" t="s">
-        <v>400</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="L82" s="35"/>
       <c r="M82" s="35" t="s">
-        <v>401</v>
+        <v>143</v>
       </c>
       <c r="N82" s="36">
-        <v>29821</v>
-      </c>
-      <c r="O82" s="34"/>
+        <v>27213</v>
+      </c>
+      <c r="O82" s="34" t="s">
+        <v>144</v>
+      </c>
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
-      <c r="R82" s="35"/>
-      <c r="S82" s="35"/>
+      <c r="R82" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="S82" s="35" t="s">
+        <v>146</v>
+      </c>
       <c r="T82" s="38" t="s">
-        <v>461</v>
-      </c>
-      <c r="U82" s="27"/>
+        <v>147</v>
+      </c>
     </row>
     <row r="83" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="34" t="s">
-        <v>278</v>
+        <v>437</v>
       </c>
       <c r="B83" s="34" t="s">
         <v>59</v>
@@ -9293,39 +9272,37 @@
         <v>63</v>
       </c>
       <c r="I83" s="35" t="s">
-        <v>64</v>
+        <v>407</v>
       </c>
       <c r="J83" s="35" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="K83" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="L83" s="35"/>
+        <v>438</v>
+      </c>
+      <c r="L83" s="35" t="s">
+        <v>408</v>
+      </c>
       <c r="M83" s="35" t="s">
-        <v>143</v>
+        <v>433</v>
       </c>
       <c r="N83" s="36">
-        <v>27213</v>
-      </c>
-      <c r="O83" s="34" t="s">
-        <v>144</v>
-      </c>
+        <v>24507</v>
+      </c>
+      <c r="O83" s="34"/>
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
       <c r="R83" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="S83" s="35" t="s">
-        <v>146</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="S83" s="35"/>
       <c r="T83" s="38" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="34" t="s">
-        <v>437</v>
+        <v>279</v>
       </c>
       <c r="B84" s="34" t="s">
         <v>59</v>
@@ -9349,37 +9326,39 @@
         <v>63</v>
       </c>
       <c r="I84" s="35" t="s">
-        <v>407</v>
+        <v>135</v>
       </c>
       <c r="J84" s="35" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="K84" s="35" t="s">
-        <v>438</v>
-      </c>
-      <c r="L84" s="35" t="s">
-        <v>408</v>
-      </c>
+        <v>812</v>
+      </c>
+      <c r="L84" s="35"/>
       <c r="M84" s="35" t="s">
-        <v>433</v>
+        <v>220</v>
       </c>
       <c r="N84" s="36">
-        <v>24507</v>
-      </c>
-      <c r="O84" s="34"/>
+        <v>29328</v>
+      </c>
+      <c r="O84" s="34" t="s">
+        <v>221</v>
+      </c>
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
       <c r="R84" s="35" t="s">
-        <v>632</v>
-      </c>
-      <c r="S84" s="35"/>
+        <v>222</v>
+      </c>
+      <c r="S84" s="35" t="s">
+        <v>223</v>
+      </c>
       <c r="T84" s="38" t="s">
-        <v>151</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="34" t="s">
-        <v>279</v>
+        <v>654</v>
       </c>
       <c r="B85" s="34" t="s">
         <v>59</v>
@@ -9406,36 +9385,32 @@
         <v>135</v>
       </c>
       <c r="J85" s="35" t="s">
-        <v>136</v>
+        <v>651</v>
       </c>
       <c r="K85" s="35" t="s">
-        <v>819</v>
+        <v>652</v>
       </c>
       <c r="L85" s="35"/>
       <c r="M85" s="35" t="s">
-        <v>220</v>
+        <v>653</v>
       </c>
       <c r="N85" s="36">
-        <v>29328</v>
+        <v>40905</v>
       </c>
       <c r="O85" s="34" t="s">
         <v>221</v>
       </c>
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
-      <c r="R85" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="S85" s="35" t="s">
-        <v>223</v>
-      </c>
+      <c r="R85" s="35"/>
+      <c r="S85" s="35"/>
       <c r="T85" s="38" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="86" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="34" t="s">
-        <v>661</v>
+        <v>280</v>
       </c>
       <c r="B86" s="34" t="s">
         <v>59</v>
@@ -9459,35 +9434,39 @@
         <v>63</v>
       </c>
       <c r="I86" s="35" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="J86" s="35" t="s">
-        <v>658</v>
+        <v>82</v>
       </c>
       <c r="K86" s="35" t="s">
-        <v>659</v>
+        <v>97</v>
       </c>
       <c r="L86" s="35"/>
       <c r="M86" s="35" t="s">
-        <v>660</v>
+        <v>172</v>
       </c>
       <c r="N86" s="36">
-        <v>40905</v>
+        <v>27907</v>
       </c>
       <c r="O86" s="34" t="s">
-        <v>221</v>
+        <v>173</v>
       </c>
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
-      <c r="R86" s="35"/>
-      <c r="S86" s="35"/>
+      <c r="R86" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="S86" s="35" t="s">
+        <v>175</v>
+      </c>
       <c r="T86" s="38" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="87" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="34" t="s">
-        <v>280</v>
+        <v>559</v>
       </c>
       <c r="B87" s="34" t="s">
         <v>59</v>
@@ -9499,10 +9478,10 @@
         <v>61</v>
       </c>
       <c r="E87" s="35" t="s">
-        <v>62</v>
+        <v>467</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>131</v>
+        <v>468</v>
       </c>
       <c r="G87" s="34" t="s">
         <v>234</v>
@@ -9511,39 +9490,39 @@
         <v>63</v>
       </c>
       <c r="I87" s="35" t="s">
-        <v>96</v>
+        <v>529</v>
       </c>
       <c r="J87" s="35" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="K87" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="L87" s="35"/>
+        <v>530</v>
+      </c>
+      <c r="L87" s="35" t="s">
+        <v>531</v>
+      </c>
       <c r="M87" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="N87" s="36">
-        <v>27907</v>
+        <v>532</v>
+      </c>
+      <c r="N87" s="36" t="s">
+        <v>684</v>
       </c>
       <c r="O87" s="34" t="s">
-        <v>173</v>
+        <v>533</v>
       </c>
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
       <c r="R87" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="S87" s="35" t="s">
-        <v>175</v>
-      </c>
+        <v>675</v>
+      </c>
+      <c r="S87" s="35"/>
       <c r="T87" s="38" t="s">
-        <v>217</v>
+        <v>508</v>
       </c>
     </row>
     <row r="88" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="34" t="s">
-        <v>565</v>
+        <v>329</v>
       </c>
       <c r="B88" s="34" t="s">
         <v>59</v>
@@ -9555,51 +9534,49 @@
         <v>61</v>
       </c>
       <c r="E88" s="35" t="s">
-        <v>472</v>
+        <v>77</v>
       </c>
       <c r="F88" s="35" t="s">
-        <v>473</v>
+        <v>131</v>
       </c>
       <c r="G88" s="34" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="H88" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I88" s="35" t="s">
-        <v>535</v>
+        <v>330</v>
       </c>
       <c r="J88" s="35" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="K88" s="35" t="s">
-        <v>536</v>
-      </c>
-      <c r="L88" s="35" t="s">
-        <v>537</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="L88" s="35"/>
       <c r="M88" s="35" t="s">
-        <v>538</v>
-      </c>
-      <c r="N88" s="36" t="s">
-        <v>691</v>
+        <v>332</v>
+      </c>
+      <c r="N88" s="36">
+        <v>23497</v>
       </c>
       <c r="O88" s="34" t="s">
-        <v>539</v>
+        <v>333</v>
       </c>
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
       <c r="R88" s="35" t="s">
-        <v>682</v>
+        <v>334</v>
       </c>
       <c r="S88" s="35"/>
       <c r="T88" s="38" t="s">
-        <v>513</v>
+        <v>461</v>
       </c>
     </row>
     <row r="89" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="34" t="s">
-        <v>329</v>
+        <v>485</v>
       </c>
       <c r="B89" s="34" t="s">
         <v>59</v>
@@ -9611,49 +9588,51 @@
         <v>61</v>
       </c>
       <c r="E89" s="35" t="s">
-        <v>77</v>
+        <v>467</v>
       </c>
       <c r="F89" s="35" t="s">
-        <v>131</v>
+        <v>468</v>
       </c>
       <c r="G89" s="34" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="H89" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I89" s="35" t="s">
-        <v>330</v>
+        <v>486</v>
       </c>
       <c r="J89" s="35" t="s">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="K89" s="35" t="s">
-        <v>331</v>
-      </c>
-      <c r="L89" s="35"/>
+        <v>487</v>
+      </c>
+      <c r="L89" s="35" t="s">
+        <v>488</v>
+      </c>
       <c r="M89" s="35" t="s">
-        <v>332</v>
+        <v>489</v>
       </c>
       <c r="N89" s="36">
-        <v>23497</v>
+        <v>24537</v>
       </c>
       <c r="O89" s="34" t="s">
-        <v>333</v>
+        <v>490</v>
       </c>
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
       <c r="R89" s="35" t="s">
-        <v>334</v>
+        <v>630</v>
       </c>
       <c r="S89" s="35"/>
       <c r="T89" s="38" t="s">
-        <v>461</v>
+        <v>508</v>
       </c>
     </row>
     <row r="90" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="34" t="s">
-        <v>490</v>
+      <c r="A90" s="35" t="s">
+        <v>766</v>
       </c>
       <c r="B90" s="34" t="s">
         <v>59</v>
@@ -9665,10 +9644,10 @@
         <v>61</v>
       </c>
       <c r="E90" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F90" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G90" s="34" t="s">
         <v>234</v>
@@ -9676,40 +9655,38 @@
       <c r="H90" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I90" s="35" t="s">
-        <v>491</v>
-      </c>
-      <c r="J90" s="35" t="s">
-        <v>297</v>
-      </c>
-      <c r="K90" s="35" t="s">
-        <v>492</v>
-      </c>
-      <c r="L90" s="35" t="s">
-        <v>493</v>
-      </c>
+      <c r="I90" s="34" t="s">
+        <v>723</v>
+      </c>
+      <c r="J90" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="K90" s="34" t="s">
+        <v>743</v>
+      </c>
+      <c r="L90" s="34"/>
       <c r="M90" s="35" t="s">
-        <v>494</v>
-      </c>
-      <c r="N90" s="36">
-        <v>24537</v>
+        <v>744</v>
+      </c>
+      <c r="N90" s="36" t="s">
+        <v>745</v>
       </c>
       <c r="O90" s="34" t="s">
-        <v>495</v>
-      </c>
-      <c r="P90" s="35"/>
-      <c r="Q90" s="35"/>
+        <v>746</v>
+      </c>
+      <c r="P90" s="34"/>
+      <c r="Q90" s="34"/>
       <c r="R90" s="35" t="s">
-        <v>637</v>
-      </c>
-      <c r="S90" s="35"/>
+        <v>747</v>
+      </c>
+      <c r="S90" s="39"/>
       <c r="T90" s="38" t="s">
-        <v>513</v>
+        <v>576</v>
       </c>
     </row>
     <row r="91" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="35" t="s">
-        <v>773</v>
+        <v>801</v>
       </c>
       <c r="B91" s="34" t="s">
         <v>59</v>
@@ -9721,10 +9698,10 @@
         <v>61</v>
       </c>
       <c r="E91" s="35" t="s">
-        <v>472</v>
+        <v>62</v>
       </c>
       <c r="F91" s="35" t="s">
-        <v>473</v>
+        <v>131</v>
       </c>
       <c r="G91" s="34" t="s">
         <v>234</v>
@@ -9732,38 +9709,38 @@
       <c r="H91" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I91" s="34" t="s">
-        <v>730</v>
-      </c>
-      <c r="J91" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="K91" s="34" t="s">
-        <v>750</v>
-      </c>
-      <c r="L91" s="34"/>
+      <c r="I91" s="35" t="s">
+        <v>773</v>
+      </c>
+      <c r="J91" s="35" t="s">
+        <v>774</v>
+      </c>
+      <c r="K91" s="35" t="s">
+        <v>775</v>
+      </c>
+      <c r="L91" s="35"/>
       <c r="M91" s="35" t="s">
-        <v>751</v>
+        <v>777</v>
       </c>
       <c r="N91" s="36" t="s">
-        <v>752</v>
+        <v>778</v>
       </c>
       <c r="O91" s="34" t="s">
-        <v>753</v>
-      </c>
-      <c r="P91" s="34"/>
-      <c r="Q91" s="34"/>
+        <v>776</v>
+      </c>
+      <c r="P91" s="35"/>
+      <c r="Q91" s="35"/>
       <c r="R91" s="35" t="s">
-        <v>754</v>
-      </c>
-      <c r="S91" s="39"/>
-      <c r="T91" s="38" t="s">
-        <v>582</v>
+        <v>779</v>
+      </c>
+      <c r="S91" s="35"/>
+      <c r="T91" s="35" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="35" t="s">
-        <v>808</v>
+      <c r="A92" s="34" t="s">
+        <v>259</v>
       </c>
       <c r="B92" s="34" t="s">
         <v>59</v>
@@ -9787,37 +9764,37 @@
         <v>63</v>
       </c>
       <c r="I92" s="35" t="s">
-        <v>780</v>
+        <v>67</v>
       </c>
       <c r="J92" s="35" t="s">
-        <v>781</v>
+        <v>68</v>
       </c>
       <c r="K92" s="35" t="s">
-        <v>782</v>
+        <v>69</v>
       </c>
       <c r="L92" s="35"/>
       <c r="M92" s="35" t="s">
-        <v>784</v>
-      </c>
-      <c r="N92" s="36" t="s">
-        <v>785</v>
+        <v>148</v>
+      </c>
+      <c r="N92" s="36">
+        <v>31298</v>
       </c>
       <c r="O92" s="34" t="s">
-        <v>783</v>
+        <v>149</v>
       </c>
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
       <c r="R92" s="35" t="s">
-        <v>786</v>
+        <v>150</v>
       </c>
       <c r="S92" s="35"/>
-      <c r="T92" s="35" t="s">
-        <v>193</v>
+      <c r="T92" s="38" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="34" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="B93" s="34" t="s">
         <v>59</v>
@@ -9841,37 +9818,37 @@
         <v>63</v>
       </c>
       <c r="I93" s="35" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="J93" s="35" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K93" s="35" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="L93" s="35"/>
       <c r="M93" s="35" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="N93" s="36">
-        <v>31298</v>
+        <v>28101</v>
       </c>
       <c r="O93" s="34" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
       <c r="R93" s="35" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="S93" s="35"/>
       <c r="T93" s="38" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="34" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B94" s="34" t="s">
         <v>59</v>
@@ -9883,40 +9860,38 @@
         <v>61</v>
       </c>
       <c r="E94" s="35" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F94" s="35" t="s">
         <v>131</v>
       </c>
       <c r="G94" s="34" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="H94" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I94" s="35" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="J94" s="35" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="K94" s="35" t="s">
-        <v>107</v>
+        <v>340</v>
       </c>
       <c r="L94" s="35"/>
       <c r="M94" s="35" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="N94" s="36">
-        <v>28101</v>
-      </c>
-      <c r="O94" s="34" t="s">
-        <v>186</v>
-      </c>
+        <v>30156</v>
+      </c>
+      <c r="O94" s="34"/>
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
       <c r="R94" s="35" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="S94" s="35"/>
       <c r="T94" s="38" t="s">
@@ -9925,7 +9900,7 @@
     </row>
     <row r="95" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="34" t="s">
-        <v>282</v>
+        <v>644</v>
       </c>
       <c r="B95" s="34" t="s">
         <v>59</v>
@@ -9937,47 +9912,49 @@
         <v>61</v>
       </c>
       <c r="E95" s="35" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F95" s="35" t="s">
-        <v>131</v>
+        <v>645</v>
       </c>
       <c r="G95" s="34" t="s">
-        <v>253</v>
+        <v>678</v>
       </c>
       <c r="H95" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I95" s="35" t="s">
-        <v>95</v>
+        <v>646</v>
       </c>
       <c r="J95" s="35" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K95" s="35" t="s">
-        <v>340</v>
+        <v>647</v>
       </c>
       <c r="L95" s="35"/>
       <c r="M95" s="35" t="s">
-        <v>233</v>
+        <v>648</v>
       </c>
       <c r="N95" s="36">
-        <v>30156</v>
-      </c>
-      <c r="O95" s="34"/>
+        <v>33667</v>
+      </c>
+      <c r="O95" s="34" t="s">
+        <v>649</v>
+      </c>
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
       <c r="R95" s="35" t="s">
-        <v>171</v>
+        <v>650</v>
       </c>
       <c r="S95" s="35"/>
       <c r="T95" s="38" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
     </row>
     <row r="96" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="34" t="s">
-        <v>651</v>
+        <v>564</v>
       </c>
       <c r="B96" s="34" t="s">
         <v>59</v>
@@ -9989,49 +9966,49 @@
         <v>61</v>
       </c>
       <c r="E96" s="35" t="s">
-        <v>62</v>
+        <v>467</v>
       </c>
       <c r="F96" s="35" t="s">
-        <v>652</v>
+        <v>468</v>
       </c>
       <c r="G96" s="34" t="s">
-        <v>685</v>
+        <v>234</v>
       </c>
       <c r="H96" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I96" s="35" t="s">
-        <v>653</v>
+        <v>544</v>
       </c>
       <c r="J96" s="35" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K96" s="35" t="s">
-        <v>654</v>
+        <v>545</v>
       </c>
       <c r="L96" s="35"/>
       <c r="M96" s="35" t="s">
-        <v>655</v>
-      </c>
-      <c r="N96" s="36">
-        <v>33667</v>
+        <v>546</v>
+      </c>
+      <c r="N96" s="36" t="s">
+        <v>547</v>
       </c>
       <c r="O96" s="34" t="s">
-        <v>656</v>
+        <v>548</v>
       </c>
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
       <c r="R96" s="35" t="s">
-        <v>657</v>
+        <v>549</v>
       </c>
       <c r="S96" s="35"/>
       <c r="T96" s="38" t="s">
-        <v>151</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="34" t="s">
-        <v>570</v>
+        <v>491</v>
       </c>
       <c r="B97" s="34" t="s">
         <v>59</v>
@@ -10043,10 +10020,10 @@
         <v>61</v>
       </c>
       <c r="E97" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F97" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G97" s="34" t="s">
         <v>234</v>
@@ -10055,37 +10032,41 @@
         <v>63</v>
       </c>
       <c r="I97" s="35" t="s">
-        <v>550</v>
+        <v>492</v>
       </c>
       <c r="J97" s="35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K97" s="35" t="s">
-        <v>551</v>
-      </c>
-      <c r="L97" s="35"/>
+        <v>493</v>
+      </c>
+      <c r="L97" s="35" t="s">
+        <v>410</v>
+      </c>
       <c r="M97" s="35" t="s">
-        <v>552</v>
-      </c>
-      <c r="N97" s="36" t="s">
-        <v>553</v>
+        <v>494</v>
+      </c>
+      <c r="N97" s="36">
+        <v>34298</v>
       </c>
       <c r="O97" s="34" t="s">
-        <v>554</v>
+        <v>495</v>
       </c>
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
       <c r="R97" s="35" t="s">
-        <v>555</v>
-      </c>
-      <c r="S97" s="35"/>
+        <v>496</v>
+      </c>
+      <c r="S97" s="35" t="s">
+        <v>497</v>
+      </c>
       <c r="T97" s="38" t="s">
-        <v>217</v>
+        <v>508</v>
       </c>
     </row>
     <row r="98" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="34" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B98" s="34" t="s">
         <v>59</v>
@@ -10097,10 +10078,10 @@
         <v>61</v>
       </c>
       <c r="E98" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F98" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G98" s="34" t="s">
         <v>234</v>
@@ -10109,41 +10090,39 @@
         <v>63</v>
       </c>
       <c r="I98" s="35" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="J98" s="35" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="K98" s="35" t="s">
-        <v>498</v>
-      </c>
-      <c r="L98" s="35" t="s">
-        <v>410</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="L98" s="35"/>
       <c r="M98" s="35" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N98" s="36">
-        <v>34298</v>
+        <v>29452</v>
       </c>
       <c r="O98" s="34" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
       <c r="R98" s="35" t="s">
-        <v>501</v>
+        <v>627</v>
       </c>
       <c r="S98" s="35" t="s">
         <v>502</v>
       </c>
       <c r="T98" s="38" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="99" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="34" t="s">
-        <v>503</v>
+        <v>785</v>
       </c>
       <c r="B99" s="34" t="s">
         <v>59</v>
@@ -10155,10 +10134,10 @@
         <v>61</v>
       </c>
       <c r="E99" s="35" t="s">
-        <v>472</v>
+        <v>62</v>
       </c>
       <c r="F99" s="35" t="s">
-        <v>473</v>
+        <v>131</v>
       </c>
       <c r="G99" s="34" t="s">
         <v>234</v>
@@ -10166,40 +10145,38 @@
       <c r="H99" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I99" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="J99" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="K99" s="35" t="s">
-        <v>504</v>
-      </c>
-      <c r="L99" s="35"/>
+      <c r="I99" s="34" t="s">
+        <v>786</v>
+      </c>
+      <c r="J99" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="K99" s="34" t="s">
+        <v>787</v>
+      </c>
+      <c r="L99" s="34"/>
       <c r="M99" s="35" t="s">
-        <v>505</v>
-      </c>
-      <c r="N99" s="36">
-        <v>29452</v>
+        <v>788</v>
+      </c>
+      <c r="N99" s="36" t="s">
+        <v>794</v>
       </c>
       <c r="O99" s="34" t="s">
-        <v>506</v>
-      </c>
-      <c r="P99" s="35"/>
-      <c r="Q99" s="35"/>
+        <v>789</v>
+      </c>
+      <c r="P99" s="34"/>
+      <c r="Q99" s="34"/>
       <c r="R99" s="35" t="s">
-        <v>634</v>
-      </c>
-      <c r="S99" s="35" t="s">
-        <v>507</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="S99" s="38"/>
       <c r="T99" s="38" t="s">
-        <v>513</v>
+        <v>180</v>
       </c>
     </row>
     <row r="100" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="34" t="s">
-        <v>792</v>
+        <v>374</v>
       </c>
       <c r="B100" s="34" t="s">
         <v>59</v>
@@ -10214,46 +10191,48 @@
         <v>62</v>
       </c>
       <c r="F100" s="35" t="s">
-        <v>131</v>
+        <v>686</v>
       </c>
       <c r="G100" s="34" t="s">
-        <v>234</v>
+        <v>678</v>
       </c>
       <c r="H100" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="I100" s="34" t="s">
-        <v>793</v>
-      </c>
-      <c r="J100" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="K100" s="34" t="s">
-        <v>794</v>
-      </c>
-      <c r="L100" s="34"/>
+      <c r="I100" s="35" t="s">
+        <v>375</v>
+      </c>
+      <c r="J100" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="K100" s="35" t="s">
+        <v>376</v>
+      </c>
+      <c r="L100" s="35" t="s">
+        <v>676</v>
+      </c>
       <c r="M100" s="35" t="s">
-        <v>795</v>
+        <v>377</v>
       </c>
       <c r="N100" s="36" t="s">
-        <v>801</v>
+        <v>685</v>
       </c>
       <c r="O100" s="34" t="s">
-        <v>796</v>
-      </c>
-      <c r="P100" s="34"/>
-      <c r="Q100" s="34"/>
+        <v>378</v>
+      </c>
+      <c r="P100" s="35"/>
+      <c r="Q100" s="35"/>
       <c r="R100" s="35" t="s">
-        <v>797</v>
-      </c>
-      <c r="S100" s="38"/>
+        <v>621</v>
+      </c>
+      <c r="S100" s="35"/>
       <c r="T100" s="38" t="s">
-        <v>180</v>
+        <v>508</v>
       </c>
     </row>
     <row r="101" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="34" t="s">
-        <v>374</v>
+        <v>708</v>
       </c>
       <c r="B101" s="34" t="s">
         <v>59</v>
@@ -10268,48 +10247,46 @@
         <v>62</v>
       </c>
       <c r="F101" s="35" t="s">
-        <v>693</v>
+        <v>131</v>
       </c>
       <c r="G101" s="34" t="s">
-        <v>685</v>
+        <v>234</v>
       </c>
       <c r="H101" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I101" s="35" t="s">
-        <v>375</v>
+        <v>709</v>
       </c>
       <c r="J101" s="35" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K101" s="35" t="s">
-        <v>376</v>
-      </c>
-      <c r="L101" s="35" t="s">
-        <v>683</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="L101" s="35"/>
       <c r="M101" s="35" t="s">
-        <v>377</v>
-      </c>
-      <c r="N101" s="36" t="s">
-        <v>692</v>
+        <v>711</v>
+      </c>
+      <c r="N101" s="36">
+        <v>32200</v>
       </c>
       <c r="O101" s="34" t="s">
-        <v>378</v>
+        <v>712</v>
       </c>
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
       <c r="R101" s="35" t="s">
-        <v>627</v>
+        <v>713</v>
       </c>
       <c r="S101" s="35"/>
       <c r="T101" s="38" t="s">
-        <v>513</v>
+        <v>217</v>
       </c>
     </row>
     <row r="102" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="34" t="s">
-        <v>715</v>
+        <v>300</v>
       </c>
       <c r="B102" s="34" t="s">
         <v>59</v>
@@ -10333,37 +10310,37 @@
         <v>63</v>
       </c>
       <c r="I102" s="35" t="s">
-        <v>716</v>
+        <v>816</v>
       </c>
       <c r="J102" s="35" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K102" s="35" t="s">
-        <v>717</v>
+        <v>813</v>
       </c>
       <c r="L102" s="35"/>
       <c r="M102" s="35" t="s">
-        <v>718</v>
+        <v>294</v>
       </c>
       <c r="N102" s="36">
-        <v>32200</v>
+        <v>28570</v>
       </c>
       <c r="O102" s="34" t="s">
-        <v>719</v>
+        <v>295</v>
       </c>
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
       <c r="R102" s="35" t="s">
-        <v>720</v>
+        <v>296</v>
       </c>
       <c r="S102" s="35"/>
       <c r="T102" s="38" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="34" t="s">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="B103" s="34" t="s">
         <v>59</v>
@@ -10387,37 +10364,37 @@
         <v>63</v>
       </c>
       <c r="I103" s="35" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="J103" s="35" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K103" s="35" t="s">
-        <v>820</v>
+        <v>451</v>
       </c>
       <c r="L103" s="35"/>
       <c r="M103" s="35" t="s">
-        <v>294</v>
+        <v>452</v>
       </c>
       <c r="N103" s="36">
-        <v>28570</v>
+        <v>33544</v>
       </c>
       <c r="O103" s="34" t="s">
-        <v>295</v>
+        <v>453</v>
       </c>
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
       <c r="R103" s="35" t="s">
-        <v>296</v>
+        <v>454</v>
       </c>
       <c r="S103" s="35"/>
       <c r="T103" s="38" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
     </row>
     <row r="104" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="34" t="s">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="B104" s="34" t="s">
         <v>59</v>
@@ -10441,37 +10418,41 @@
         <v>63</v>
       </c>
       <c r="I104" s="35" t="s">
-        <v>823</v>
+        <v>101</v>
       </c>
       <c r="J104" s="35" t="s">
-        <v>75</v>
+        <v>415</v>
       </c>
       <c r="K104" s="35" t="s">
-        <v>451</v>
-      </c>
-      <c r="L104" s="35"/>
+        <v>435</v>
+      </c>
+      <c r="L104" s="35" t="s">
+        <v>435</v>
+      </c>
       <c r="M104" s="35" t="s">
-        <v>452</v>
+        <v>416</v>
       </c>
       <c r="N104" s="36">
-        <v>33544</v>
+        <v>25204</v>
       </c>
       <c r="O104" s="34" t="s">
-        <v>453</v>
+        <v>417</v>
       </c>
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
       <c r="R104" s="35" t="s">
-        <v>454</v>
-      </c>
-      <c r="S104" s="35"/>
+        <v>418</v>
+      </c>
+      <c r="S104" s="35" t="s">
+        <v>419</v>
+      </c>
       <c r="T104" s="38" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="105" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="34" t="s">
-        <v>414</v>
+        <v>283</v>
       </c>
       <c r="B105" s="34" t="s">
         <v>59</v>
@@ -10498,38 +10479,32 @@
         <v>101</v>
       </c>
       <c r="J105" s="35" t="s">
-        <v>415</v>
+        <v>79</v>
       </c>
       <c r="K105" s="35" t="s">
-        <v>435</v>
-      </c>
-      <c r="L105" s="35" t="s">
-        <v>435</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="L105" s="35"/>
       <c r="M105" s="35" t="s">
-        <v>416</v>
+        <v>290</v>
       </c>
       <c r="N105" s="36">
-        <v>25204</v>
+        <v>26134</v>
       </c>
       <c r="O105" s="34" t="s">
-        <v>417</v>
+        <v>179</v>
       </c>
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
-      <c r="R105" s="35" t="s">
-        <v>418</v>
-      </c>
-      <c r="S105" s="35" t="s">
-        <v>419</v>
-      </c>
+      <c r="R105" s="35"/>
+      <c r="S105" s="35"/>
       <c r="T105" s="38" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="106" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="34" t="s">
-        <v>283</v>
+        <v>643</v>
       </c>
       <c r="B106" s="34" t="s">
         <v>59</v>
@@ -10547,33 +10522,37 @@
         <v>131</v>
       </c>
       <c r="G106" s="34" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="H106" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I106" s="35" t="s">
-        <v>101</v>
+        <v>602</v>
       </c>
       <c r="J106" s="35" t="s">
-        <v>79</v>
+        <v>817</v>
       </c>
       <c r="K106" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="L106" s="35"/>
+        <v>603</v>
+      </c>
+      <c r="L106" s="35" t="s">
+        <v>603</v>
+      </c>
       <c r="M106" s="35" t="s">
-        <v>290</v>
+        <v>604</v>
       </c>
       <c r="N106" s="36">
-        <v>26134</v>
+        <v>31906</v>
       </c>
       <c r="O106" s="34" t="s">
-        <v>179</v>
+        <v>605</v>
       </c>
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
-      <c r="R106" s="35"/>
+      <c r="R106" s="35" t="s">
+        <v>606</v>
+      </c>
       <c r="S106" s="35"/>
       <c r="T106" s="38" t="s">
         <v>180</v>
@@ -10581,7 +10560,7 @@
     </row>
     <row r="107" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="34" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="B107" s="34" t="s">
         <v>59</v>
@@ -10593,51 +10572,49 @@
         <v>61</v>
       </c>
       <c r="E107" s="35" t="s">
-        <v>62</v>
+        <v>467</v>
       </c>
       <c r="F107" s="35" t="s">
-        <v>131</v>
+        <v>686</v>
       </c>
       <c r="G107" s="34" t="s">
-        <v>253</v>
+        <v>678</v>
       </c>
       <c r="H107" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I107" s="35" t="s">
-        <v>608</v>
+        <v>818</v>
       </c>
       <c r="J107" s="35" t="s">
-        <v>824</v>
+        <v>679</v>
       </c>
       <c r="K107" s="35" t="s">
-        <v>609</v>
-      </c>
-      <c r="L107" s="35" t="s">
-        <v>609</v>
-      </c>
+        <v>656</v>
+      </c>
+      <c r="L107" s="35"/>
       <c r="M107" s="35" t="s">
-        <v>610</v>
-      </c>
-      <c r="N107" s="36">
-        <v>31906</v>
+        <v>688</v>
+      </c>
+      <c r="N107" s="36" t="s">
+        <v>689</v>
       </c>
       <c r="O107" s="34" t="s">
-        <v>611</v>
+        <v>680</v>
       </c>
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
       <c r="R107" s="35" t="s">
-        <v>612</v>
+        <v>687</v>
       </c>
       <c r="S107" s="35"/>
       <c r="T107" s="38" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="34" t="s">
-        <v>684</v>
+        <v>284</v>
       </c>
       <c r="B108" s="34" t="s">
         <v>59</v>
@@ -10649,49 +10626,49 @@
         <v>61</v>
       </c>
       <c r="E108" s="35" t="s">
-        <v>472</v>
+        <v>77</v>
       </c>
       <c r="F108" s="35" t="s">
-        <v>693</v>
+        <v>468</v>
       </c>
       <c r="G108" s="34" t="s">
-        <v>685</v>
+        <v>253</v>
       </c>
       <c r="H108" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I108" s="35" t="s">
-        <v>825</v>
+        <v>110</v>
       </c>
       <c r="J108" s="35" t="s">
-        <v>686</v>
+        <v>84</v>
       </c>
       <c r="K108" s="35" t="s">
-        <v>663</v>
+        <v>113</v>
       </c>
       <c r="L108" s="35"/>
       <c r="M108" s="35" t="s">
-        <v>695</v>
+        <v>188</v>
       </c>
       <c r="N108" s="36" t="s">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="O108" s="34" t="s">
-        <v>687</v>
+        <v>189</v>
       </c>
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
       <c r="R108" s="35" t="s">
-        <v>694</v>
+        <v>190</v>
       </c>
       <c r="S108" s="35"/>
       <c r="T108" s="38" t="s">
-        <v>151</v>
+        <v>461</v>
       </c>
     </row>
     <row r="109" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="34" t="s">
-        <v>284</v>
+        <v>714</v>
       </c>
       <c r="B109" s="34" t="s">
         <v>59</v>
@@ -10703,49 +10680,51 @@
         <v>61</v>
       </c>
       <c r="E109" s="35" t="s">
-        <v>77</v>
+        <v>467</v>
       </c>
       <c r="F109" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G109" s="34" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="H109" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I109" s="35" t="s">
-        <v>110</v>
+        <v>695</v>
       </c>
       <c r="J109" s="35" t="s">
-        <v>84</v>
+        <v>651</v>
       </c>
       <c r="K109" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="L109" s="35"/>
+        <v>696</v>
+      </c>
+      <c r="L109" s="35" t="s">
+        <v>697</v>
+      </c>
       <c r="M109" s="35" t="s">
-        <v>188</v>
+        <v>700</v>
       </c>
       <c r="N109" s="36" t="s">
-        <v>688</v>
+        <v>702</v>
       </c>
       <c r="O109" s="34" t="s">
-        <v>189</v>
+        <v>698</v>
       </c>
       <c r="P109" s="35"/>
       <c r="Q109" s="35"/>
       <c r="R109" s="35" t="s">
-        <v>190</v>
+        <v>699</v>
       </c>
       <c r="S109" s="35"/>
       <c r="T109" s="38" t="s">
-        <v>461</v>
+        <v>508</v>
       </c>
     </row>
     <row r="110" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="34" t="s">
-        <v>721</v>
+        <v>503</v>
       </c>
       <c r="B110" s="34" t="s">
         <v>59</v>
@@ -10757,10 +10736,10 @@
         <v>61</v>
       </c>
       <c r="E110" s="35" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F110" s="35" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G110" s="34" t="s">
         <v>234</v>
@@ -10769,39 +10748,39 @@
         <v>63</v>
       </c>
       <c r="I110" s="35" t="s">
-        <v>702</v>
+        <v>129</v>
       </c>
       <c r="J110" s="35" t="s">
-        <v>658</v>
+        <v>71</v>
       </c>
       <c r="K110" s="35" t="s">
-        <v>703</v>
-      </c>
-      <c r="L110" s="35" t="s">
-        <v>704</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="L110" s="35"/>
       <c r="M110" s="35" t="s">
-        <v>707</v>
-      </c>
-      <c r="N110" s="36" t="s">
-        <v>709</v>
+        <v>504</v>
+      </c>
+      <c r="N110" s="36">
+        <v>26766</v>
       </c>
       <c r="O110" s="34" t="s">
-        <v>705</v>
+        <v>505</v>
       </c>
       <c r="P110" s="35"/>
       <c r="Q110" s="35"/>
       <c r="R110" s="35" t="s">
-        <v>706</v>
-      </c>
-      <c r="S110" s="35"/>
+        <v>628</v>
+      </c>
+      <c r="S110" s="35" t="s">
+        <v>506</v>
+      </c>
       <c r="T110" s="38" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="111" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="34" t="s">
-        <v>508</v>
+        <v>285</v>
       </c>
       <c r="B111" s="34" t="s">
         <v>59</v>
@@ -10813,10 +10792,10 @@
         <v>61</v>
       </c>
       <c r="E111" s="35" t="s">
-        <v>472</v>
+        <v>62</v>
       </c>
       <c r="F111" s="35" t="s">
-        <v>473</v>
+        <v>131</v>
       </c>
       <c r="G111" s="34" t="s">
         <v>234</v>
@@ -10828,36 +10807,34 @@
         <v>129</v>
       </c>
       <c r="J111" s="35" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="K111" s="35" t="s">
-        <v>347</v>
+        <v>130</v>
       </c>
       <c r="L111" s="35"/>
       <c r="M111" s="35" t="s">
-        <v>509</v>
+        <v>211</v>
       </c>
       <c r="N111" s="36">
-        <v>26766</v>
+        <v>24263</v>
       </c>
       <c r="O111" s="34" t="s">
-        <v>510</v>
+        <v>212</v>
       </c>
       <c r="P111" s="35"/>
       <c r="Q111" s="35"/>
       <c r="R111" s="35" t="s">
-        <v>635</v>
-      </c>
-      <c r="S111" s="35" t="s">
-        <v>511</v>
-      </c>
+        <v>626</v>
+      </c>
+      <c r="S111" s="35"/>
       <c r="T111" s="38" t="s">
-        <v>513</v>
+        <v>193</v>
       </c>
     </row>
     <row r="112" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="34" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B112" s="34" t="s">
         <v>59</v>
@@ -10881,157 +10858,103 @@
         <v>63</v>
       </c>
       <c r="I112" s="35" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="J112" s="35" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="K112" s="35" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="L112" s="35"/>
       <c r="M112" s="35" t="s">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="N112" s="36">
-        <v>24263</v>
+        <v>29464</v>
       </c>
       <c r="O112" s="34" t="s">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="P112" s="35"/>
       <c r="Q112" s="35"/>
       <c r="R112" s="35" t="s">
-        <v>633</v>
+        <v>154</v>
       </c>
       <c r="S112" s="35"/>
       <c r="T112" s="38" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="113" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="34" t="s">
-        <v>286</v>
-      </c>
-      <c r="B113" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C113" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D113" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="E113" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="F113" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="G113" s="34" t="s">
-        <v>234</v>
-      </c>
-      <c r="H113" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="I113" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="J113" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="K113" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="L113" s="35"/>
-      <c r="M113" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="N113" s="36">
-        <v>29464</v>
-      </c>
-      <c r="O113" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="P113" s="35"/>
-      <c r="Q113" s="35"/>
-      <c r="R113" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="S113" s="35"/>
-      <c r="T113" s="38" t="s">
         <v>151</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" sort="0"/>
-  <autoFilter ref="A1:T107" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U116">
-    <sortCondition ref="I2:I16999"/>
-    <sortCondition ref="K2:K16999"/>
+  <autoFilter ref="A1:T106" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U115">
+    <sortCondition ref="I2:I16998"/>
+    <sortCondition ref="K2:K16998"/>
   </sortState>
   <phoneticPr fontId="32" type="noConversion"/>
-  <conditionalFormatting sqref="A114:A1048576 A1">
+  <conditionalFormatting sqref="A113:A1048576 A1">
     <cfRule type="duplicateValues" dxfId="17" priority="591"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H102:H107 H2:H94">
+  <conditionalFormatting sqref="H101:H106 H2:H93">
     <cfRule type="containsText" dxfId="16" priority="22" operator="containsText" text="Inactive - ADS">
       <formula>NOT(ISERROR(SEARCH("Inactive - ADS",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H95">
+  <conditionalFormatting sqref="H94">
     <cfRule type="containsText" dxfId="15" priority="19" operator="containsText" text="Inactive-ADS">
-      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H95)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H94)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H96:H97">
+  <conditionalFormatting sqref="H95:H96">
     <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="Inactive - ADS">
-      <formula>NOT(ISERROR(SEARCH("Inactive - ADS",H96)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Inactive - ADS",H95)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H98:H101">
+  <conditionalFormatting sqref="H97:H100">
     <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="Inactive-ADS">
-      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H98)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H97)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H108:H113">
+  <conditionalFormatting sqref="H107:H112">
     <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="Inactive-ADS">
-      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H108)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Inactive-ADS",H107)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M1 M114:M65094">
+  <conditionalFormatting sqref="M1 M113:M65093">
     <cfRule type="expression" dxfId="11" priority="588" stopIfTrue="1">
       <formula>LEN(M1)&lt;&gt;13</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M113">
+  <conditionalFormatting sqref="M2:M112">
     <cfRule type="expression" dxfId="10" priority="2">
       <formula>LEN(M2)&lt;13</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M95">
+  <conditionalFormatting sqref="M94">
     <cfRule type="duplicateValues" dxfId="9" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M96:M97">
+  <conditionalFormatting sqref="M95:M96">
     <cfRule type="duplicateValues" dxfId="8" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M98:M101">
+  <conditionalFormatting sqref="M97:M100">
     <cfRule type="duplicateValues" dxfId="7" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M102:M107">
+  <conditionalFormatting sqref="M101:M106">
     <cfRule type="duplicateValues" dxfId="6" priority="652"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M108:M111">
+  <conditionalFormatting sqref="M107:M110">
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M112:M113">
+  <conditionalFormatting sqref="M111:M112">
     <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M114:M65094 M1">
+  <conditionalFormatting sqref="M113:M65093 M1">
     <cfRule type="duplicateValues" dxfId="3" priority="648" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M94">
-    <cfRule type="duplicateValues" dxfId="2" priority="666"/>
+  <conditionalFormatting sqref="M2:M93">
+    <cfRule type="duplicateValues" dxfId="0" priority="670"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -11155,12 +11078,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="M1 M18:M65486">
-    <cfRule type="expression" dxfId="1" priority="560" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="560" stopIfTrue="1">
       <formula>LEN(M1)&lt;&gt;13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:M65486 M1">
-    <cfRule type="duplicateValues" dxfId="0" priority="559" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="559" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11201,10 +11124,10 @@
         <v>151</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -11215,7 +11138,7 @@
         <v>334</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -11226,7 +11149,7 @@
         <v>161</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -11234,21 +11157,21 @@
         <v>180</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -11256,10 +11179,10 @@
         <v>193</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -11270,30 +11193,30 @@
         <v>215</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="B10"/>
       <c r="C10" s="31" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">

--- a/import-files/WC-CTN-O(1).xlsx
+++ b/import-files/WC-CTN-O(1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Music\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Pictures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D94D959-49AD-48A4-8B00-85804EC20A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F22106F-7DB2-4B25-A26C-C78CBA05E0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Club Details" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Membership!$A$1:$T$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Membership!$A$1:$T$112</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="817">
   <si>
     <t>How To Complete/Update existing information.</t>
   </si>
@@ -688,9 +688,6 @@
     <t>7407035203082</t>
   </si>
   <si>
-    <t>16 Amandal Close West ridge</t>
-  </si>
-  <si>
     <t>0739132118</t>
   </si>
   <si>
@@ -736,9 +733,6 @@
     <t>6112185224083</t>
   </si>
   <si>
-    <t>3 Eagle Road Gleemoor</t>
-  </si>
-  <si>
     <t>0822160229</t>
   </si>
   <si>
@@ -751,9 +745,6 @@
     <t>7011095183089</t>
   </si>
   <si>
-    <t>68 Bloem Street Goodwood</t>
-  </si>
-  <si>
     <t>0833903133</t>
   </si>
   <si>
@@ -763,9 +754,6 @@
     <t>6105300055085</t>
   </si>
   <si>
-    <t>2 Durr Road Greenhaven</t>
-  </si>
-  <si>
     <t>desmartin007@gmail.com</t>
   </si>
   <si>
@@ -784,18 +772,12 @@
     <t>andrepoole360@gmail.com</t>
   </si>
   <si>
-    <t>Voorbrug Delft</t>
-  </si>
-  <si>
     <t>5611285233085</t>
   </si>
   <si>
     <t>0721697912</t>
   </si>
   <si>
-    <t>24 Blinkbaar Stree, Eastridge</t>
-  </si>
-  <si>
     <t>Eastside</t>
   </si>
   <si>
@@ -823,9 +805,6 @@
     <t>6709280117086</t>
   </si>
   <si>
-    <t>51 Siversands Road Westridge</t>
-  </si>
-  <si>
     <t>0846994478</t>
   </si>
   <si>
@@ -874,9 +853,6 @@
     <t>6304045244084</t>
   </si>
   <si>
-    <t>7 Chelsea Road London Village</t>
-  </si>
-  <si>
     <t>0741310506</t>
   </si>
   <si>
@@ -892,15 +868,9 @@
     <t>6606055069080</t>
   </si>
   <si>
-    <t>28 Primrose Street, Newfields village</t>
-  </si>
-  <si>
     <t>7607295205087</t>
   </si>
   <si>
-    <t>30 Marsh Cresent Highlands Village M/Plain</t>
-  </si>
-  <si>
     <t>0724504573</t>
   </si>
   <si>
@@ -931,18 +901,12 @@
     <t>5402025154082</t>
   </si>
   <si>
-    <t>51 Viscount Road, Rocklands, M/Plain</t>
-  </si>
-  <si>
     <t>0767531399</t>
   </si>
   <si>
     <t>5707235186082</t>
   </si>
   <si>
-    <t>68 Mitchel Avenue, Woodlands,M/Plain</t>
-  </si>
-  <si>
     <t>0840481615</t>
   </si>
   <si>
@@ -1132,18 +1096,12 @@
     <t>7304045280087</t>
   </si>
   <si>
-    <t>38 LANSPORT ROAD HANOVER PARK</t>
-  </si>
-  <si>
     <t>0817191168</t>
   </si>
   <si>
     <t>7803215213083</t>
   </si>
   <si>
-    <t>36 MISSOURI CRESCENT PORTLANDS</t>
-  </si>
-  <si>
     <t>0798377916</t>
   </si>
   <si>
@@ -1192,9 +1150,6 @@
     <t>6406045181081</t>
   </si>
   <si>
-    <t>29 Milano Crescent San Remo</t>
-  </si>
-  <si>
     <t>0616341337</t>
   </si>
   <si>
@@ -1213,9 +1168,6 @@
     <t>7601170140089</t>
   </si>
   <si>
-    <t>3 Culloden Close Strandfontein</t>
-  </si>
-  <si>
     <t>0833847139</t>
   </si>
   <si>
@@ -1228,9 +1180,6 @@
     <t>8210305089085</t>
   </si>
   <si>
-    <t>11 Moses Kottler New Woodlands</t>
-  </si>
-  <si>
     <t>0837853018</t>
   </si>
   <si>
@@ -1262,9 +1211,6 @@
   </si>
   <si>
     <t>7103015606085</t>
-  </si>
-  <si>
-    <t>8 Glider Street, Beacon Valley, M/Plain</t>
   </si>
   <si>
     <t>0650329760</t>
@@ -1346,9 +1292,6 @@
     <t>9503145277087</t>
   </si>
   <si>
-    <t>29 Clyde Street Bayview</t>
-  </si>
-  <si>
     <t>0659326547</t>
   </si>
   <si>
@@ -1508,9 +1451,6 @@
     <t>6901015271086</t>
   </si>
   <si>
-    <t>158 Downberg Road Hanover Park</t>
-  </si>
-  <si>
     <t>0849005505</t>
   </si>
   <si>
@@ -1526,9 +1466,6 @@
     <t>7301135153083</t>
   </si>
   <si>
-    <t>149 Harvester Way Westridge</t>
-  </si>
-  <si>
     <t>0714106664</t>
   </si>
   <si>
@@ -1541,9 +1478,6 @@
     <t>8211270093086</t>
   </si>
   <si>
-    <t>30 Marsh Cresent, Weltevreden Village M/Plain</t>
-  </si>
-  <si>
     <t>0824559800</t>
   </si>
   <si>
@@ -1553,9 +1487,6 @@
     <t>6302155180080</t>
   </si>
   <si>
-    <t>31 Apricot Way, Westridge, M/Plain</t>
-  </si>
-  <si>
     <t>6702045207086</t>
   </si>
   <si>
@@ -1658,12 +1589,6 @@
     <t>9305075343081</t>
   </si>
   <si>
-    <t>MALE</t>
-  </si>
-  <si>
-    <t>COLOURED</t>
-  </si>
-  <si>
     <t>Glen</t>
   </si>
   <si>
@@ -1679,9 +1604,6 @@
     <t>6902225185082</t>
   </si>
   <si>
-    <t>42 Bronze Street Vanguard Estate</t>
-  </si>
-  <si>
     <t>basildv@mweb.co.za</t>
   </si>
   <si>
@@ -1691,9 +1613,6 @@
     <t>8501195233084</t>
   </si>
   <si>
-    <t>20 Goud Street, Vanguard Estate</t>
-  </si>
-  <si>
     <t>jason.isaacs@hotmail.co.za</t>
   </si>
   <si>
@@ -1727,9 +1646,6 @@
     <t>6703065207089</t>
   </si>
   <si>
-    <t>51 Bronze Street Vanguard Estate</t>
-  </si>
-  <si>
     <t>DSA-140202</t>
   </si>
   <si>
@@ -1772,9 +1688,6 @@
     <t>7304125122084</t>
   </si>
   <si>
-    <t>13 Boeschoten Rd, Gleemoor</t>
-  </si>
-  <si>
     <t>craig180williams@gmail.com</t>
   </si>
   <si>
@@ -1967,9 +1880,6 @@
     <t>1976-02-21</t>
   </si>
   <si>
-    <t>7 angora Close, Westridge Mitchells Plain, 7785</t>
-  </si>
-  <si>
     <t>7602215129087</t>
   </si>
   <si>
@@ -2006,9 +1916,6 @@
     <t>7405205257086</t>
   </si>
   <si>
-    <t>10 Marne Road Strandfontein</t>
-  </si>
-  <si>
     <t>0677090499</t>
   </si>
   <si>
@@ -2030,9 +1937,6 @@
     <t>6310080136085</t>
   </si>
   <si>
-    <t>14 Verdun Way Strandfontein</t>
-  </si>
-  <si>
     <t>0638015911</t>
   </si>
   <si>
@@ -2042,9 +1946,6 @@
     <t>6704125204082</t>
   </si>
   <si>
-    <t>6 Frigate Close Strandfontein</t>
-  </si>
-  <si>
     <t>0842534652</t>
   </si>
   <si>
@@ -2240,12 +2141,6 @@
     <t>1982-01-07</t>
   </si>
   <si>
-    <t>15 Nantes Close Westridge</t>
-  </si>
-  <si>
-    <t>91 Berlin Square, Strandfontein Village,</t>
-  </si>
-  <si>
     <t xml:space="preserve">Johnniel </t>
   </si>
   <si>
@@ -2297,9 +2192,6 @@
     <t>EH</t>
   </si>
   <si>
-    <t>53 Strelitzia Street Vredenburg</t>
-  </si>
-  <si>
     <t>1967-09-28</t>
   </si>
   <si>
@@ -2315,9 +2207,6 @@
     <t>1954-11-14</t>
   </si>
   <si>
-    <t>WHITE</t>
-  </si>
-  <si>
     <t>0752679976</t>
   </si>
   <si>
@@ -2375,9 +2264,6 @@
     <t>5412155094081</t>
   </si>
   <si>
-    <t>27 Anzio Crescent, Strandfontein Village, 7798</t>
-  </si>
-  <si>
     <t>0817532140</t>
   </si>
   <si>
@@ -2393,9 +2279,6 @@
     <t>8802275058080</t>
   </si>
   <si>
-    <t>Delft The Hague</t>
-  </si>
-  <si>
     <t>0848096003</t>
   </si>
   <si>
@@ -2495,9 +2378,6 @@
     <t>1988-09-22</t>
   </si>
   <si>
-    <t>1 Caen Road Strandfontien Village</t>
-  </si>
-  <si>
     <t>0718478732</t>
   </si>
   <si>
@@ -2585,9 +2465,6 @@
     <t>Chesley</t>
   </si>
   <si>
-    <t>32 Shepherd Way, Westridge, Mitchell's Plain</t>
-  </si>
-  <si>
     <t>5503135006086</t>
   </si>
   <si>
@@ -2609,9 +2486,6 @@
     <t>1964-04-05</t>
   </si>
   <si>
-    <t>23B Jasmine Street Bonteheuwel 7764</t>
-  </si>
-  <si>
     <t>DSA-230265</t>
   </si>
   <si>
@@ -2712,6 +2586,126 @@
   </si>
   <si>
     <t>V/D Westhuizen</t>
+  </si>
+  <si>
+    <t>Guardians</t>
+  </si>
+  <si>
+    <t>Brisdel</t>
+  </si>
+  <si>
+    <t>Voorbrug, Delft</t>
+  </si>
+  <si>
+    <t>149 Harvester Way, Westridge</t>
+  </si>
+  <si>
+    <t>23B Jasmine Street, Bonteheuwel</t>
+  </si>
+  <si>
+    <t>31 Apricot Way, Westridge, Mitchells Plain</t>
+  </si>
+  <si>
+    <t>42 Bronze Street, Vanguard Estate</t>
+  </si>
+  <si>
+    <t>30 Marsh Cresent, Weltevreden Village, Mitchells Plain</t>
+  </si>
+  <si>
+    <t>30 Marsh Cresent Highlands Village, Mitchells Plain</t>
+  </si>
+  <si>
+    <t>7 angora Close, Westridge, Mitchells Plain</t>
+  </si>
+  <si>
+    <t>91 Berlin Square, Strandfontein Village</t>
+  </si>
+  <si>
+    <t>15 Nantes Close, Westridge</t>
+  </si>
+  <si>
+    <t>14 Verdun Way, Strandfontein</t>
+  </si>
+  <si>
+    <t>10 Marne Road, Strandfontein</t>
+  </si>
+  <si>
+    <t>38 Lansport Road, Hanover Park</t>
+  </si>
+  <si>
+    <t>20 Goud Road, Vanguard Estate</t>
+  </si>
+  <si>
+    <t>29 Milano Crescent, San Remo</t>
+  </si>
+  <si>
+    <t>6 Frigate Close, Strandfontein</t>
+  </si>
+  <si>
+    <t>27 Anzio Crescent, Strandfontein Village</t>
+  </si>
+  <si>
+    <t>11 Moses Kottler, New Woodlands</t>
+  </si>
+  <si>
+    <t>3 Culloden Close, Strandfontein</t>
+  </si>
+  <si>
+    <t>8 Glider Street, Beacon Valley, Mitchells Plain</t>
+  </si>
+  <si>
+    <t>68 Bloem Street, Goodwood</t>
+  </si>
+  <si>
+    <t>29 Clyde Street, Bayview</t>
+  </si>
+  <si>
+    <t>2 Durr Road, Greenhaven</t>
+  </si>
+  <si>
+    <t>7 Chelsea Road, London Village</t>
+  </si>
+  <si>
+    <t>68 Mitchel Avenue, Woodlands, Mitchells Plain</t>
+  </si>
+  <si>
+    <t>51 Viscount Road, Rocklands, Mitchells Plain</t>
+  </si>
+  <si>
+    <t>16 Amandal Close, Westridge</t>
+  </si>
+  <si>
+    <t>51 Bronze Street, Vanguard Estate</t>
+  </si>
+  <si>
+    <t>1 Caen Road, Strandfontien Village</t>
+  </si>
+  <si>
+    <t>32 Shepherd Way, Westridge, Mitchells Plain</t>
+  </si>
+  <si>
+    <t>The Hague, Delft</t>
+  </si>
+  <si>
+    <t>36 Missouri Crescent, Portlands</t>
+  </si>
+  <si>
+    <t>158 Downberg Road, Hanover Park</t>
+  </si>
+  <si>
+    <t>24 Blinkbaar Street, Eastridge</t>
+  </si>
+  <si>
+    <t>53 Strelitzia Street, Vredenburg</t>
+  </si>
+  <si>
+    <t>51 Siversands Road, Westridge</t>
+  </si>
+  <si>
+    <t>13 Boeschoten Road, Gleemoor</t>
+  </si>
+  <si>
+    <t>28 Primrose Street, Newfields Village</t>
   </si>
 </sst>
 </file>
@@ -3174,6 +3168,12 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3188,12 +3188,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="17">
@@ -3216,16 +3210,6 @@
     <cellStyle name="Normal 8" xfId="14" xr:uid="{4EABBA24-76A8-4352-B39A-B5112A27DA65}"/>
   </cellStyles>
   <dxfs count="19">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -3326,6 +3310,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4302,66 +4296,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
     </row>
     <row r="2" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>235</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
+      <c r="A2" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
     </row>
     <row r="3" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
     </row>
     <row r="6" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47" t="s">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="47"/>
+      <c r="D8" s="42"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
@@ -4392,7 +4386,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>28</v>
@@ -4404,7 +4398,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>17</v>
@@ -4436,7 +4430,7 @@
         <v>18</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>18</v>
@@ -4454,33 +4448,33 @@
       <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="48"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47" t="s">
+      <c r="B18" s="42"/>
+      <c r="C18" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="47"/>
+      <c r="D18" s="42"/>
     </row>
     <row r="19" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>49</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4494,7 +4488,7 @@
         <v>27</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4502,13 +4496,13 @@
         <v>28</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4516,7 +4510,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>17</v>
@@ -4548,13 +4542,13 @@
         <v>18</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4562,30 +4556,30 @@
         <v>29</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
     </row>
     <row r="28" spans="1:4" s="2" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="47" t="s">
+      <c r="A28" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47" t="s">
+      <c r="B28" s="42"/>
+      <c r="C28" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="47"/>
+      <c r="D28" s="42"/>
     </row>
     <row r="29" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
@@ -4598,7 +4592,7 @@
         <v>49</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4620,13 +4614,13 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4638,7 +4632,7 @@
         <v>17</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4666,13 +4660,13 @@
         <v>18</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4680,13 +4674,13 @@
         <v>29</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4697,6 +4691,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="A18:B18"/>
@@ -4705,12 +4705,6 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B26" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -4758,7 +4752,7 @@
   <sheetData>
     <row r="1" spans="1:20" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>33</v>
@@ -4797,7 +4791,7 @@
         <v>14</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="O1" s="10" t="s">
         <v>15</v>
@@ -4820,7 +4814,7 @@
     </row>
     <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="B2" s="34" t="s">
         <v>59</v>
@@ -4838,13 +4832,13 @@
         <v>131</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H2" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="J2" s="35" t="s">
         <v>120</v>
@@ -4854,27 +4848,27 @@
       </c>
       <c r="L2" s="35"/>
       <c r="M2" s="35" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="N2" s="36">
         <v>18768</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
       <c r="R2" s="35" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="S2" s="37"/>
       <c r="T2" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="B3" s="34" t="s">
         <v>59</v>
@@ -4892,43 +4886,43 @@
         <v>131</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H3" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="J3" s="34" t="s">
         <v>82</v>
       </c>
       <c r="K3" s="34" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="L3" s="34"/>
       <c r="M3" s="35" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="N3" s="36">
         <v>21633</v>
       </c>
       <c r="O3" s="34" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="P3" s="34"/>
       <c r="Q3" s="34"/>
       <c r="R3" s="35" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="S3" s="38"/>
       <c r="T3" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
-        <v>566</v>
+        <v>537</v>
       </c>
       <c r="B4" s="34" t="s">
         <v>59</v>
@@ -4940,49 +4934,49 @@
         <v>61</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H4" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I4" s="34" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="J4" s="34" t="s">
         <v>74</v>
       </c>
       <c r="K4" s="34" t="s">
-        <v>565</v>
+        <v>536</v>
       </c>
       <c r="L4" s="34"/>
       <c r="M4" s="35" t="s">
-        <v>572</v>
+        <v>542</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>573</v>
+        <v>543</v>
       </c>
       <c r="O4" s="34" t="s">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="P4" s="34"/>
       <c r="Q4" s="34"/>
       <c r="R4" s="35" t="s">
-        <v>634</v>
+        <v>601</v>
       </c>
       <c r="S4" s="38"/>
       <c r="T4" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>558</v>
+        <v>529</v>
       </c>
       <c r="B5" s="34" t="s">
         <v>59</v>
@@ -4994,51 +4988,51 @@
         <v>61</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H5" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I5" s="35" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="J5" s="35" t="s">
         <v>73</v>
       </c>
       <c r="K5" s="35" t="s">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="L5" s="35" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
       <c r="M5" s="35" t="s">
-        <v>536</v>
+        <v>507</v>
       </c>
       <c r="N5" s="36">
         <v>34958</v>
       </c>
       <c r="O5" s="34" t="s">
-        <v>537</v>
+        <v>508</v>
       </c>
       <c r="P5" s="35"/>
       <c r="Q5" s="35"/>
       <c r="R5" s="35" t="s">
-        <v>635</v>
+        <v>602</v>
       </c>
       <c r="S5" s="35"/>
       <c r="T5" s="35" t="s">
-        <v>508</v>
+        <v>777</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="B6" s="34" t="s">
         <v>59</v>
@@ -5056,7 +5050,7 @@
         <v>131</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H6" s="34" t="s">
         <v>63</v>
@@ -5072,27 +5066,27 @@
       </c>
       <c r="L6" s="34"/>
       <c r="M6" s="35" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="N6" s="36">
         <v>20787</v>
       </c>
       <c r="O6" s="34" t="s">
-        <v>176</v>
+        <v>779</v>
       </c>
       <c r="P6" s="34"/>
       <c r="Q6" s="34"/>
       <c r="R6" s="35" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="S6" s="38"/>
       <c r="T6" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>59</v>
@@ -5110,7 +5104,7 @@
         <v>131</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H7" s="34" t="s">
         <v>63</v>
@@ -5124,27 +5118,27 @@
       </c>
       <c r="L7" s="34"/>
       <c r="M7" s="35" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="N7" s="36">
         <v>30024</v>
       </c>
       <c r="O7" s="34" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P7" s="34"/>
       <c r="Q7" s="34"/>
       <c r="R7" s="35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="S7" s="38"/>
       <c r="T7" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
-        <v>690</v>
+        <v>653</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>59</v>
@@ -5162,43 +5156,43 @@
         <v>131</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H8" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I8" s="35" t="s">
-        <v>613</v>
+        <v>580</v>
       </c>
       <c r="J8" s="35" t="s">
         <v>74</v>
       </c>
       <c r="K8" s="35" t="s">
-        <v>691</v>
+        <v>654</v>
       </c>
       <c r="L8" s="35"/>
       <c r="M8" s="35" t="s">
-        <v>692</v>
+        <v>655</v>
       </c>
       <c r="N8" s="36" t="s">
-        <v>701</v>
+        <v>664</v>
       </c>
       <c r="O8" s="34" t="s">
-        <v>693</v>
+        <v>656</v>
       </c>
       <c r="P8" s="35"/>
       <c r="Q8" s="35"/>
       <c r="R8" s="35" t="s">
-        <v>694</v>
+        <v>657</v>
       </c>
       <c r="S8" s="35"/>
       <c r="T8" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
-        <v>612</v>
+        <v>579</v>
       </c>
       <c r="B9" s="34" t="s">
         <v>59</v>
@@ -5216,43 +5210,43 @@
         <v>131</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H9" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>613</v>
+        <v>580</v>
       </c>
       <c r="J9" s="34" t="s">
         <v>73</v>
       </c>
       <c r="K9" s="34" t="s">
-        <v>614</v>
+        <v>581</v>
       </c>
       <c r="L9" s="34"/>
       <c r="M9" s="35" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
       <c r="N9" s="36">
         <v>23651</v>
       </c>
       <c r="O9" s="34" t="s">
-        <v>616</v>
+        <v>583</v>
       </c>
       <c r="P9" s="34"/>
       <c r="Q9" s="34"/>
       <c r="R9" s="35" t="s">
-        <v>617</v>
+        <v>584</v>
       </c>
       <c r="S9" s="38"/>
       <c r="T9" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>59</v>
@@ -5270,7 +5264,7 @@
         <v>131</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H10" s="34" t="s">
         <v>63</v>
@@ -5286,27 +5280,27 @@
       </c>
       <c r="L10" s="34"/>
       <c r="M10" s="35" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="N10" s="36">
         <v>24982</v>
       </c>
       <c r="O10" s="34" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P10" s="34"/>
       <c r="Q10" s="34"/>
       <c r="R10" s="34" t="s">
-        <v>636</v>
+        <v>603</v>
       </c>
       <c r="S10" s="35"/>
       <c r="T10" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>439</v>
+        <v>416</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>59</v>
@@ -5324,47 +5318,47 @@
         <v>131</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H11" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I11" s="35" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="K11" s="35" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="L11" s="35" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="M11" s="35" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="N11" s="36">
         <v>26677</v>
       </c>
       <c r="O11" s="34" t="s">
-        <v>423</v>
+        <v>780</v>
       </c>
       <c r="P11" s="35"/>
       <c r="Q11" s="35"/>
       <c r="R11" s="35" t="s">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="S11" s="35" t="s">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="T11" s="38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
-        <v>762</v>
+        <v>722</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>59</v>
@@ -5382,43 +5376,43 @@
         <v>131</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H12" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
       <c r="J12" s="34" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="K12" s="34" t="s">
-        <v>756</v>
+        <v>716</v>
       </c>
       <c r="L12" s="34"/>
       <c r="M12" s="35" t="s">
-        <v>757</v>
+        <v>717</v>
       </c>
       <c r="N12" s="36" t="s">
-        <v>758</v>
+        <v>718</v>
       </c>
       <c r="O12" s="34" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="P12" s="34"/>
       <c r="Q12" s="34"/>
       <c r="R12" s="35" t="s">
-        <v>760</v>
+        <v>720</v>
       </c>
       <c r="S12" s="39"/>
       <c r="T12" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="35" t="s">
-        <v>763</v>
+        <v>723</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>59</v>
@@ -5436,43 +5430,43 @@
         <v>131</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H13" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
       <c r="J13" s="34" t="s">
         <v>108</v>
       </c>
       <c r="K13" s="34" t="s">
-        <v>752</v>
+        <v>712</v>
       </c>
       <c r="L13" s="34"/>
       <c r="M13" s="35" t="s">
-        <v>753</v>
+        <v>713</v>
       </c>
       <c r="N13" s="36" t="s">
-        <v>754</v>
+        <v>714</v>
       </c>
       <c r="O13" s="34" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="P13" s="34"/>
       <c r="Q13" s="34"/>
       <c r="R13" s="35" t="s">
-        <v>759</v>
+        <v>719</v>
       </c>
       <c r="S13" s="39"/>
       <c r="T13" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>761</v>
+        <v>721</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>59</v>
@@ -5490,43 +5484,43 @@
         <v>131</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H14" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
       <c r="J14" s="34" t="s">
         <v>73</v>
       </c>
       <c r="K14" s="34" t="s">
-        <v>755</v>
+        <v>715</v>
       </c>
       <c r="L14" s="34"/>
       <c r="M14" s="35" t="s">
-        <v>749</v>
+        <v>709</v>
       </c>
       <c r="N14" s="36" t="s">
-        <v>750</v>
+        <v>710</v>
       </c>
       <c r="O14" s="34" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="P14" s="34"/>
       <c r="Q14" s="34"/>
       <c r="R14" s="35" t="s">
-        <v>751</v>
+        <v>711</v>
       </c>
       <c r="S14" s="39"/>
       <c r="T14" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
-        <v>522</v>
+        <v>493</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>59</v>
@@ -5544,43 +5538,43 @@
         <v>131</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H15" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I15" s="34" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
       <c r="J15" s="34" t="s">
-        <v>463</v>
+        <v>440</v>
       </c>
       <c r="K15" s="34" t="s">
-        <v>464</v>
+        <v>441</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="35" t="s">
-        <v>466</v>
+        <v>443</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>748</v>
+        <v>708</v>
       </c>
       <c r="O15" s="34" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="P15" s="34"/>
       <c r="Q15" s="34"/>
       <c r="R15" s="35" t="s">
-        <v>742</v>
+        <v>703</v>
       </c>
       <c r="S15" s="39"/>
       <c r="T15" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B16" s="34" t="s">
         <v>59</v>
@@ -5598,7 +5592,7 @@
         <v>131</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H16" s="34" t="s">
         <v>63</v>
@@ -5614,27 +5608,27 @@
       </c>
       <c r="L16" s="34"/>
       <c r="M16" s="35" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="N16" s="36">
         <v>23212</v>
       </c>
       <c r="O16" s="34" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="P16" s="34"/>
       <c r="Q16" s="34"/>
       <c r="R16" s="35" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="S16" s="39"/>
       <c r="T16" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
-        <v>460</v>
+        <v>437</v>
       </c>
       <c r="B17" s="34" t="s">
         <v>59</v>
@@ -5652,45 +5646,45 @@
         <v>131</v>
       </c>
       <c r="G17" s="35" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H17" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I17" s="35" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="J17" s="35" t="s">
         <v>68</v>
       </c>
       <c r="K17" s="35" t="s">
-        <v>456</v>
+        <v>433</v>
       </c>
       <c r="L17" s="35" t="s">
-        <v>455</v>
+        <v>432</v>
       </c>
       <c r="M17" s="35" t="s">
-        <v>457</v>
+        <v>434</v>
       </c>
       <c r="N17" s="36">
         <v>28381</v>
       </c>
       <c r="O17" s="35" t="s">
-        <v>458</v>
+        <v>435</v>
       </c>
       <c r="P17" s="35"/>
       <c r="Q17" s="35"/>
       <c r="R17" s="35" t="s">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="S17" s="37"/>
       <c r="T17" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
-        <v>562</v>
+        <v>533</v>
       </c>
       <c r="B18" s="34" t="s">
         <v>59</v>
@@ -5708,41 +5702,41 @@
         <v>131</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H18" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I18" s="34" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="J18" s="34" t="s">
         <v>108</v>
       </c>
       <c r="K18" s="34" t="s">
-        <v>552</v>
+        <v>523</v>
       </c>
       <c r="L18" s="34"/>
       <c r="M18" s="35" t="s">
-        <v>554</v>
+        <v>525</v>
       </c>
       <c r="N18" s="36">
         <v>37912</v>
       </c>
       <c r="O18" s="34" t="s">
-        <v>553</v>
+        <v>524</v>
       </c>
       <c r="P18" s="34"/>
       <c r="Q18" s="34"/>
       <c r="R18" s="35"/>
       <c r="S18" s="39"/>
       <c r="T18" s="38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="B19" s="34" t="s">
         <v>59</v>
@@ -5760,45 +5754,45 @@
         <v>131</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H19" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I19" s="34" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="J19" s="34" t="s">
         <v>84</v>
       </c>
       <c r="K19" s="34" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="L19" s="34"/>
       <c r="M19" s="35" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="N19" s="36">
         <v>23337</v>
       </c>
       <c r="O19" s="34" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="P19" s="34"/>
       <c r="Q19" s="34"/>
       <c r="R19" s="35" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="S19" s="38" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="T19" s="38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>560</v>
+        <v>531</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>59</v>
@@ -5816,23 +5810,23 @@
         <v>131</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H20" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I20" s="35" t="s">
-        <v>555</v>
+        <v>526</v>
       </c>
       <c r="J20" s="35" t="s">
         <v>75</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>556</v>
+        <v>527</v>
       </c>
       <c r="L20" s="35"/>
       <c r="M20" s="35" t="s">
-        <v>557</v>
+        <v>528</v>
       </c>
       <c r="N20" s="36">
         <v>25927</v>
@@ -5843,12 +5837,12 @@
       <c r="R20" s="35"/>
       <c r="S20" s="35"/>
       <c r="T20" s="38" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>59</v>
@@ -5866,7 +5860,7 @@
         <v>131</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H21" s="34" t="s">
         <v>63</v>
@@ -5882,25 +5876,25 @@
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="35" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="N21" s="36">
         <v>21575</v>
       </c>
       <c r="O21" s="34" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="P21" s="34"/>
       <c r="Q21" s="34"/>
       <c r="R21" s="35"/>
       <c r="S21" s="38"/>
       <c r="T21" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
-        <v>523</v>
+        <v>494</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>59</v>
@@ -5918,43 +5912,43 @@
         <v>131</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H22" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I22" s="34" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="J22" s="34" t="s">
         <v>83</v>
       </c>
       <c r="K22" s="34" t="s">
-        <v>525</v>
+        <v>496</v>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="35" t="s">
-        <v>526</v>
+        <v>497</v>
       </c>
       <c r="N22" s="36">
         <v>27616</v>
       </c>
       <c r="O22" s="34" t="s">
-        <v>527</v>
+        <v>498</v>
       </c>
       <c r="P22" s="34"/>
       <c r="Q22" s="34"/>
       <c r="R22" s="35" t="s">
-        <v>528</v>
+        <v>499</v>
       </c>
       <c r="S22" s="39"/>
       <c r="T22" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
-        <v>798</v>
+        <v>756</v>
       </c>
       <c r="B23" s="34" t="s">
         <v>59</v>
@@ -5972,41 +5966,41 @@
         <v>131</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H23" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I23" s="34" t="s">
-        <v>780</v>
+        <v>739</v>
       </c>
       <c r="J23" s="34" t="s">
         <v>86</v>
       </c>
       <c r="K23" s="34" t="s">
-        <v>781</v>
+        <v>740</v>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="35" t="s">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="N23" s="36" t="s">
-        <v>783</v>
+        <v>742</v>
       </c>
       <c r="O23" s="34" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="P23" s="34"/>
       <c r="Q23" s="34"/>
       <c r="R23" s="35"/>
       <c r="S23" s="38"/>
       <c r="T23" s="38" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="34" t="s">
-        <v>728</v>
+        <v>689</v>
       </c>
       <c r="B24" s="34" t="s">
         <v>59</v>
@@ -6024,43 +6018,43 @@
         <v>131</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H24" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I24" s="34" t="s">
-        <v>730</v>
+        <v>691</v>
       </c>
       <c r="J24" s="34" t="s">
         <v>74</v>
       </c>
       <c r="K24" s="34" t="s">
-        <v>731</v>
+        <v>692</v>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="35" t="s">
-        <v>733</v>
+        <v>694</v>
       </c>
       <c r="N24" s="36" t="s">
-        <v>735</v>
+        <v>696</v>
       </c>
       <c r="O24" s="34" t="s">
-        <v>737</v>
+        <v>698</v>
       </c>
       <c r="P24" s="34"/>
       <c r="Q24" s="34"/>
       <c r="R24" s="35" t="s">
-        <v>741</v>
+        <v>702</v>
       </c>
       <c r="S24" s="39"/>
       <c r="T24" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
-        <v>729</v>
+        <v>690</v>
       </c>
       <c r="B25" s="34" t="s">
         <v>59</v>
@@ -6078,43 +6072,43 @@
         <v>131</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H25" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I25" s="34" t="s">
-        <v>730</v>
+        <v>691</v>
       </c>
       <c r="J25" s="34" t="s">
         <v>74</v>
       </c>
       <c r="K25" s="34" t="s">
-        <v>732</v>
+        <v>693</v>
       </c>
       <c r="L25" s="34"/>
       <c r="M25" s="35" t="s">
-        <v>734</v>
+        <v>695</v>
       </c>
       <c r="N25" s="36" t="s">
-        <v>736</v>
+        <v>697</v>
       </c>
       <c r="O25" s="34" t="s">
-        <v>737</v>
+        <v>698</v>
       </c>
       <c r="P25" s="34"/>
       <c r="Q25" s="34"/>
       <c r="R25" s="35" t="s">
-        <v>740</v>
+        <v>701</v>
       </c>
       <c r="S25" s="39"/>
       <c r="T25" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="B26" s="34" t="s">
         <v>59</v>
@@ -6132,7 +6126,7 @@
         <v>131</v>
       </c>
       <c r="G26" s="35" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H26" s="35" t="s">
         <v>63</v>
@@ -6144,33 +6138,33 @@
         <v>71</v>
       </c>
       <c r="K26" s="35" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="L26" s="35" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="M26" s="35" t="s">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="N26" s="36">
         <v>23057</v>
       </c>
       <c r="O26" s="35" t="s">
-        <v>432</v>
+        <v>782</v>
       </c>
       <c r="P26" s="35"/>
       <c r="Q26" s="35"/>
       <c r="R26" s="35" t="s">
-        <v>631</v>
+        <v>598</v>
       </c>
       <c r="S26" s="37"/>
       <c r="T26" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="B27" s="34" t="s">
         <v>59</v>
@@ -6182,51 +6176,51 @@
         <v>61</v>
       </c>
       <c r="E27" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F27" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G27" s="35" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H27" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I27" s="35" t="s">
-        <v>471</v>
+        <v>446</v>
       </c>
       <c r="J27" s="35" t="s">
         <v>68</v>
       </c>
       <c r="K27" s="35" t="s">
-        <v>472</v>
+        <v>447</v>
       </c>
       <c r="L27" s="35"/>
       <c r="M27" s="35" t="s">
-        <v>473</v>
+        <v>448</v>
       </c>
       <c r="N27" s="36">
         <v>25256</v>
       </c>
       <c r="O27" s="35" t="s">
-        <v>474</v>
+        <v>783</v>
       </c>
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="35" t="s">
-        <v>633</v>
+        <v>600</v>
       </c>
       <c r="S27" s="37" t="s">
-        <v>475</v>
-      </c>
-      <c r="T27" s="37" t="s">
-        <v>508</v>
+        <v>449</v>
+      </c>
+      <c r="T27" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="34" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="B28" s="34" t="s">
         <v>59</v>
@@ -6238,19 +6232,19 @@
         <v>61</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F28" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I28" s="35" t="s">
-        <v>667</v>
+        <v>632</v>
       </c>
       <c r="J28" s="35" t="s">
         <v>75</v>
@@ -6259,30 +6253,30 @@
         <v>76</v>
       </c>
       <c r="L28" s="35" t="s">
-        <v>668</v>
+        <v>633</v>
       </c>
       <c r="M28" s="35" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="N28" s="36" t="s">
-        <v>682</v>
+        <v>646</v>
       </c>
       <c r="O28" s="34" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="35" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
       <c r="S28" s="35"/>
-      <c r="T28" s="38" t="s">
-        <v>508</v>
+      <c r="T28" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="34" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B29" s="34" t="s">
         <v>59</v>
@@ -6300,45 +6294,45 @@
         <v>131</v>
       </c>
       <c r="G29" s="35" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H29" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I29" s="35" t="s">
-        <v>815</v>
+        <v>773</v>
       </c>
       <c r="J29" s="35" t="s">
         <v>90</v>
       </c>
       <c r="K29" s="35" t="s">
-        <v>802</v>
+        <v>760</v>
       </c>
       <c r="L29" s="35"/>
       <c r="M29" s="35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N29" s="36">
         <v>22633</v>
       </c>
       <c r="O29" s="35" t="s">
-        <v>160</v>
+        <v>231</v>
       </c>
       <c r="P29" s="35"/>
       <c r="Q29" s="35"/>
       <c r="R29" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="S29" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="T29" s="35" t="s">
         <v>161</v>
-      </c>
-      <c r="S29" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="T29" s="35" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="35" t="s">
-        <v>800</v>
+        <v>758</v>
       </c>
       <c r="B30" s="34" t="s">
         <v>59</v>
@@ -6356,43 +6350,43 @@
         <v>131</v>
       </c>
       <c r="G30" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H30" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>767</v>
+        <v>727</v>
       </c>
       <c r="J30" s="35" t="s">
         <v>108</v>
       </c>
       <c r="K30" s="35" t="s">
-        <v>768</v>
+        <v>728</v>
       </c>
       <c r="L30" s="35"/>
       <c r="M30" s="35" t="s">
-        <v>771</v>
+        <v>731</v>
       </c>
       <c r="N30" s="36" t="s">
-        <v>772</v>
+        <v>732</v>
       </c>
       <c r="O30" s="34" t="s">
-        <v>769</v>
+        <v>729</v>
       </c>
       <c r="P30" s="35"/>
       <c r="Q30" s="35"/>
       <c r="R30" s="35" t="s">
-        <v>770</v>
+        <v>730</v>
       </c>
       <c r="S30" s="35"/>
       <c r="T30" s="35" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="35" t="s">
-        <v>764</v>
+        <v>724</v>
       </c>
       <c r="B31" s="34" t="s">
         <v>59</v>
@@ -6410,43 +6404,43 @@
         <v>131</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H31" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I31" s="34" t="s">
-        <v>724</v>
+        <v>685</v>
       </c>
       <c r="J31" s="34" t="s">
         <v>86</v>
       </c>
       <c r="K31" s="34" t="s">
-        <v>738</v>
+        <v>699</v>
       </c>
       <c r="L31" s="34"/>
       <c r="M31" s="35" t="s">
-        <v>725</v>
+        <v>686</v>
       </c>
       <c r="N31" s="36" t="s">
-        <v>726</v>
+        <v>687</v>
       </c>
       <c r="O31" s="34" t="s">
-        <v>727</v>
+        <v>688</v>
       </c>
       <c r="P31" s="34"/>
       <c r="Q31" s="34"/>
       <c r="R31" s="35" t="s">
-        <v>739</v>
+        <v>700</v>
       </c>
       <c r="S31" s="38"/>
       <c r="T31" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="B32" s="34" t="s">
         <v>59</v>
@@ -6464,7 +6458,7 @@
         <v>131</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>63</v>
@@ -6476,35 +6470,35 @@
         <v>71</v>
       </c>
       <c r="K32" s="35" t="s">
-        <v>426</v>
+        <v>405</v>
       </c>
       <c r="L32" s="35" t="s">
-        <v>426</v>
+        <v>405</v>
       </c>
       <c r="M32" s="35" t="s">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="N32" s="36">
         <v>30282</v>
       </c>
       <c r="O32" s="34" t="s">
-        <v>428</v>
+        <v>784</v>
       </c>
       <c r="P32" s="35"/>
       <c r="Q32" s="35"/>
       <c r="R32" s="35" t="s">
-        <v>429</v>
+        <v>407</v>
       </c>
       <c r="S32" s="35" t="s">
-        <v>430</v>
+        <v>408</v>
       </c>
       <c r="T32" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B33" s="34" t="s">
         <v>59</v>
@@ -6522,7 +6516,7 @@
         <v>131</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H33" s="34" t="s">
         <v>63</v>
@@ -6534,33 +6528,33 @@
         <v>133</v>
       </c>
       <c r="K33" s="35" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="L33" s="35"/>
       <c r="M33" s="35" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="N33" s="36">
         <v>27970</v>
       </c>
       <c r="O33" s="34" t="s">
-        <v>214</v>
+        <v>785</v>
       </c>
       <c r="P33" s="35"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="35" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="S33" s="35" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="T33" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
-        <v>575</v>
+        <v>545</v>
       </c>
       <c r="B34" s="34" t="s">
         <v>59</v>
@@ -6572,49 +6566,49 @@
         <v>61</v>
       </c>
       <c r="E34" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F34" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H34" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I34" s="35" t="s">
-        <v>567</v>
+        <v>538</v>
       </c>
       <c r="J34" s="35" t="s">
         <v>108</v>
       </c>
       <c r="K34" s="35" t="s">
-        <v>568</v>
+        <v>539</v>
       </c>
       <c r="L34" s="35"/>
       <c r="M34" s="35" t="s">
-        <v>571</v>
+        <v>541</v>
       </c>
       <c r="N34" s="36" t="s">
-        <v>569</v>
+        <v>540</v>
       </c>
       <c r="O34" s="34" t="s">
-        <v>570</v>
+        <v>786</v>
       </c>
       <c r="P34" s="35"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="35" t="s">
-        <v>629</v>
+        <v>596</v>
       </c>
       <c r="S34" s="35"/>
       <c r="T34" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="35" t="s">
-        <v>715</v>
+        <v>676</v>
       </c>
       <c r="B35" s="34" t="s">
         <v>59</v>
@@ -6629,46 +6623,46 @@
         <v>62</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H35" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>664</v>
+        <v>629</v>
       </c>
       <c r="J35" s="35" t="s">
         <v>75</v>
       </c>
       <c r="K35" s="35" t="s">
-        <v>663</v>
+        <v>628</v>
       </c>
       <c r="L35" s="35"/>
       <c r="M35" s="35" t="s">
-        <v>655</v>
+        <v>622</v>
       </c>
       <c r="N35" s="36" t="s">
-        <v>659</v>
+        <v>626</v>
       </c>
       <c r="O35" s="34" t="s">
-        <v>662</v>
+        <v>787</v>
       </c>
       <c r="P35" s="35"/>
       <c r="Q35" s="35"/>
       <c r="R35" s="35" t="s">
-        <v>665</v>
+        <v>630</v>
       </c>
       <c r="S35" s="35"/>
       <c r="T35" s="38" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
-        <v>640</v>
+        <v>607</v>
       </c>
       <c r="B36" s="34" t="s">
         <v>59</v>
@@ -6680,49 +6674,49 @@
         <v>61</v>
       </c>
       <c r="E36" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F36" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H36" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I36" s="34" t="s">
-        <v>507</v>
+        <v>478</v>
       </c>
       <c r="J36" s="34" t="s">
         <v>75</v>
       </c>
       <c r="K36" s="34" t="s">
-        <v>618</v>
+        <v>585</v>
       </c>
       <c r="L36" s="34"/>
       <c r="M36" s="35" t="s">
-        <v>637</v>
+        <v>604</v>
       </c>
       <c r="N36" s="36">
         <v>38935</v>
       </c>
       <c r="O36" s="34" t="s">
-        <v>619</v>
+        <v>586</v>
       </c>
       <c r="P36" s="34"/>
       <c r="Q36" s="34"/>
       <c r="R36" s="35" t="s">
-        <v>620</v>
+        <v>587</v>
       </c>
       <c r="S36" s="39"/>
-      <c r="T36" s="38" t="s">
-        <v>508</v>
+      <c r="T36" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
-        <v>671</v>
+        <v>636</v>
       </c>
       <c r="B37" s="34" t="s">
         <v>59</v>
@@ -6734,19 +6728,19 @@
         <v>61</v>
       </c>
       <c r="E37" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F37" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G37" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H37" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I37" s="35" t="s">
-        <v>507</v>
+        <v>478</v>
       </c>
       <c r="J37" s="35" t="s">
         <v>75</v>
@@ -6755,30 +6749,30 @@
         <v>76</v>
       </c>
       <c r="L37" s="35" t="s">
-        <v>672</v>
+        <v>637</v>
       </c>
       <c r="M37" s="35" t="s">
-        <v>673</v>
+        <v>638</v>
       </c>
       <c r="N37" s="36" t="s">
-        <v>683</v>
+        <v>647</v>
       </c>
       <c r="O37" s="34" t="s">
-        <v>619</v>
+        <v>586</v>
       </c>
       <c r="P37" s="35"/>
       <c r="Q37" s="35"/>
       <c r="R37" s="35" t="s">
-        <v>674</v>
+        <v>639</v>
       </c>
       <c r="S37" s="35"/>
-      <c r="T37" s="38" t="s">
-        <v>508</v>
+      <c r="T37" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="34" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B38" s="34" t="s">
         <v>59</v>
@@ -6796,7 +6790,7 @@
         <v>131</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H38" s="34" t="s">
         <v>63</v>
@@ -6812,27 +6806,27 @@
       </c>
       <c r="L38" s="34"/>
       <c r="M38" s="35" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="N38" s="36">
         <v>27347</v>
       </c>
       <c r="O38" s="34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P38" s="34"/>
       <c r="Q38" s="34"/>
       <c r="R38" s="35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S38" s="39"/>
       <c r="T38" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="35" t="s">
-        <v>765</v>
+        <v>725</v>
       </c>
       <c r="B39" s="34" t="s">
         <v>59</v>
@@ -6844,51 +6838,51 @@
         <v>61</v>
       </c>
       <c r="E39" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G39" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H39" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I39" s="34" t="s">
-        <v>814</v>
+        <v>772</v>
       </c>
       <c r="J39" s="34" t="s">
-        <v>717</v>
+        <v>678</v>
       </c>
       <c r="K39" s="34" t="s">
-        <v>804</v>
+        <v>762</v>
       </c>
       <c r="L39" s="34" t="s">
-        <v>718</v>
+        <v>679</v>
       </c>
       <c r="M39" s="35" t="s">
-        <v>719</v>
+        <v>680</v>
       </c>
       <c r="N39" s="36" t="s">
-        <v>720</v>
+        <v>681</v>
       </c>
       <c r="O39" s="34" t="s">
-        <v>721</v>
+        <v>682</v>
       </c>
       <c r="P39" s="34"/>
       <c r="Q39" s="34"/>
       <c r="R39" s="35" t="s">
-        <v>722</v>
+        <v>683</v>
       </c>
       <c r="S39" s="39"/>
       <c r="T39" s="38" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="34" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B40" s="34" t="s">
         <v>59</v>
@@ -6906,7 +6900,7 @@
         <v>131</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H40" s="34" t="s">
         <v>63</v>
@@ -6918,31 +6912,31 @@
         <v>142</v>
       </c>
       <c r="K40" s="35" t="s">
-        <v>803</v>
+        <v>761</v>
       </c>
       <c r="L40" s="35"/>
       <c r="M40" s="35" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="N40" s="36">
         <v>22941</v>
       </c>
       <c r="O40" s="34" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="P40" s="35"/>
       <c r="Q40" s="35"/>
       <c r="R40" s="35" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="S40" s="35"/>
       <c r="T40" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="34" t="s">
-        <v>607</v>
+        <v>574</v>
       </c>
       <c r="B41" s="34" t="s">
         <v>59</v>
@@ -6960,13 +6954,13 @@
         <v>131</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H41" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I41" s="35" t="s">
-        <v>608</v>
+        <v>575</v>
       </c>
       <c r="J41" s="35" t="s">
         <v>86</v>
@@ -6976,27 +6970,27 @@
       </c>
       <c r="L41" s="35"/>
       <c r="M41" s="35" t="s">
-        <v>609</v>
+        <v>576</v>
       </c>
       <c r="N41" s="36">
         <v>30209</v>
       </c>
       <c r="O41" s="34" t="s">
-        <v>610</v>
+        <v>577</v>
       </c>
       <c r="P41" s="35"/>
       <c r="Q41" s="35"/>
       <c r="R41" s="35" t="s">
-        <v>611</v>
+        <v>578</v>
       </c>
       <c r="S41" s="35"/>
       <c r="T41" s="38" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="35" t="s">
-        <v>716</v>
+        <v>677</v>
       </c>
       <c r="B42" s="34" t="s">
         <v>59</v>
@@ -7011,46 +7005,46 @@
         <v>62</v>
       </c>
       <c r="F42" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G42" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H42" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I42" s="35" t="s">
-        <v>656</v>
+        <v>623</v>
       </c>
       <c r="J42" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K42" s="35" t="s">
-        <v>657</v>
+        <v>624</v>
       </c>
       <c r="L42" s="35"/>
       <c r="M42" s="35" t="s">
-        <v>658</v>
+        <v>625</v>
       </c>
       <c r="N42" s="36" t="s">
-        <v>660</v>
+        <v>627</v>
       </c>
       <c r="O42" s="34" t="s">
-        <v>661</v>
+        <v>788</v>
       </c>
       <c r="P42" s="35"/>
       <c r="Q42" s="35"/>
       <c r="R42" s="35" t="s">
-        <v>666</v>
+        <v>631</v>
       </c>
       <c r="S42" s="35"/>
       <c r="T42" s="38" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="34" t="s">
-        <v>586</v>
+        <v>555</v>
       </c>
       <c r="B43" s="34" t="s">
         <v>59</v>
@@ -7068,45 +7062,45 @@
         <v>131</v>
       </c>
       <c r="G43" s="35" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H43" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I43" s="35" t="s">
-        <v>587</v>
+        <v>556</v>
       </c>
       <c r="J43" s="35" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="K43" s="35" t="s">
-        <v>588</v>
+        <v>557</v>
       </c>
       <c r="L43" s="35" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="M43" s="35" t="s">
-        <v>590</v>
+        <v>559</v>
       </c>
       <c r="N43" s="36">
         <v>23292</v>
       </c>
       <c r="O43" s="35" t="s">
-        <v>591</v>
+        <v>789</v>
       </c>
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
       <c r="R43" s="35" t="s">
-        <v>592</v>
+        <v>560</v>
       </c>
       <c r="S43" s="35"/>
       <c r="T43" s="35" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="34" t="s">
-        <v>641</v>
+        <v>608</v>
       </c>
       <c r="B44" s="34" t="s">
         <v>59</v>
@@ -7124,48 +7118,48 @@
         <v>131</v>
       </c>
       <c r="G44" s="34" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H44" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I44" s="34" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="J44" s="34" t="s">
         <v>82</v>
       </c>
       <c r="K44" s="34" t="s">
-        <v>598</v>
+        <v>565</v>
       </c>
       <c r="L44" s="34" t="s">
-        <v>599</v>
+        <v>566</v>
       </c>
       <c r="M44" s="35" t="s">
-        <v>600</v>
+        <v>567</v>
       </c>
       <c r="N44" s="36">
         <v>29846</v>
       </c>
       <c r="O44" s="34" t="s">
-        <v>583</v>
+        <v>790</v>
       </c>
       <c r="P44" s="34"/>
       <c r="Q44" s="34"/>
       <c r="R44" s="35" t="s">
-        <v>577</v>
+        <v>547</v>
       </c>
       <c r="S44" s="39" t="s">
-        <v>601</v>
+        <v>568</v>
       </c>
       <c r="T44" s="38" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
       <c r="U44" s="32"/>
     </row>
     <row r="45" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="34" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="B45" s="34" t="s">
         <v>59</v>
@@ -7183,43 +7177,43 @@
         <v>131</v>
       </c>
       <c r="G45" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H45" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I45" s="34" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="J45" s="34" t="s">
         <v>65</v>
       </c>
       <c r="K45" s="34" t="s">
-        <v>805</v>
+        <v>763</v>
       </c>
       <c r="L45" s="34"/>
       <c r="M45" s="35" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="N45" s="36">
         <v>26758</v>
       </c>
       <c r="O45" s="34" t="s">
-        <v>292</v>
+        <v>791</v>
       </c>
       <c r="P45" s="34"/>
       <c r="Q45" s="34"/>
       <c r="R45" s="35" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="S45" s="39"/>
       <c r="T45" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="34" t="s">
-        <v>476</v>
+        <v>450</v>
       </c>
       <c r="B46" s="34" t="s">
         <v>59</v>
@@ -7231,19 +7225,19 @@
         <v>61</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F46" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G46" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H46" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I46" s="34" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="J46" s="34" t="s">
         <v>75</v>
@@ -7253,29 +7247,29 @@
       </c>
       <c r="L46" s="34"/>
       <c r="M46" s="35" t="s">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="N46" s="36">
         <v>31066</v>
       </c>
       <c r="O46" s="34" t="s">
-        <v>478</v>
+        <v>792</v>
       </c>
       <c r="P46" s="34"/>
       <c r="Q46" s="34"/>
       <c r="R46" s="35" t="s">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="S46" s="39" t="s">
-        <v>479</v>
-      </c>
-      <c r="T46" s="38" t="s">
-        <v>508</v>
+        <v>452</v>
+      </c>
+      <c r="T46" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="34" t="s">
-        <v>579</v>
+        <v>549</v>
       </c>
       <c r="B47" s="34" t="s">
         <v>59</v>
@@ -7293,47 +7287,47 @@
         <v>131</v>
       </c>
       <c r="G47" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H47" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I47" s="34" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="J47" s="34" t="s">
         <v>112</v>
       </c>
       <c r="K47" s="34" t="s">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="L47" s="34" t="s">
-        <v>581</v>
+        <v>551</v>
       </c>
       <c r="M47" s="35" t="s">
-        <v>582</v>
+        <v>552</v>
       </c>
       <c r="N47" s="36">
         <v>27169</v>
       </c>
       <c r="O47" s="34" t="s">
-        <v>583</v>
+        <v>790</v>
       </c>
       <c r="P47" s="34"/>
       <c r="Q47" s="34"/>
       <c r="R47" s="35" t="s">
-        <v>584</v>
+        <v>553</v>
       </c>
       <c r="S47" s="39" t="s">
-        <v>585</v>
+        <v>554</v>
       </c>
       <c r="T47" s="38" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="34" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="B48" s="34" t="s">
         <v>59</v>
@@ -7351,25 +7345,25 @@
         <v>131</v>
       </c>
       <c r="G48" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H48" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I48" s="34" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="J48" s="34" t="s">
         <v>82</v>
       </c>
       <c r="K48" s="34" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="L48" s="34" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="M48" s="35" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="N48" s="36">
         <v>25576</v>
@@ -7380,12 +7374,12 @@
       <c r="R48" s="35"/>
       <c r="S48" s="39"/>
       <c r="T48" s="38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="34" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="B49" s="34" t="s">
         <v>59</v>
@@ -7403,7 +7397,7 @@
         <v>131</v>
       </c>
       <c r="G49" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H49" s="34" t="s">
         <v>63</v>
@@ -7412,36 +7406,36 @@
         <v>126</v>
       </c>
       <c r="J49" s="34" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="K49" s="34" t="s">
-        <v>806</v>
+        <v>764</v>
       </c>
       <c r="L49" s="34"/>
       <c r="M49" s="35" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="N49" s="36">
         <v>23532</v>
       </c>
       <c r="O49" s="34" t="s">
-        <v>312</v>
+        <v>793</v>
       </c>
       <c r="P49" s="34"/>
       <c r="Q49" s="34"/>
       <c r="R49" s="35" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="S49" s="39" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="T49" s="38" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="50" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="34" t="s">
-        <v>642</v>
+        <v>609</v>
       </c>
       <c r="B50" s="34" t="s">
         <v>59</v>
@@ -7459,7 +7453,7 @@
         <v>131</v>
       </c>
       <c r="G50" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H50" s="34" t="s">
         <v>63</v>
@@ -7474,32 +7468,32 @@
         <v>107</v>
       </c>
       <c r="L50" s="34" t="s">
-        <v>593</v>
+        <v>561</v>
       </c>
       <c r="M50" s="35" t="s">
-        <v>594</v>
+        <v>562</v>
       </c>
       <c r="N50" s="36">
         <v>24574</v>
       </c>
       <c r="O50" s="34" t="s">
-        <v>595</v>
+        <v>794</v>
       </c>
       <c r="P50" s="34"/>
       <c r="Q50" s="34"/>
       <c r="R50" s="35" t="s">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="S50" s="39" t="s">
-        <v>597</v>
+        <v>564</v>
       </c>
       <c r="T50" s="38" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="51" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="34" t="s">
-        <v>703</v>
+        <v>666</v>
       </c>
       <c r="B51" s="34" t="s">
         <v>59</v>
@@ -7517,7 +7511,7 @@
         <v>131</v>
       </c>
       <c r="G51" s="34" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="H51" s="34" t="s">
         <v>63</v>
@@ -7529,33 +7523,33 @@
         <v>86</v>
       </c>
       <c r="K51" s="34" t="s">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="L51" s="34" t="s">
-        <v>704</v>
+        <v>667</v>
       </c>
       <c r="M51" s="35" t="s">
-        <v>705</v>
+        <v>668</v>
       </c>
       <c r="N51" s="36">
         <v>20073</v>
       </c>
       <c r="O51" s="34" t="s">
-        <v>706</v>
+        <v>795</v>
       </c>
       <c r="P51" s="34"/>
       <c r="Q51" s="34"/>
       <c r="R51" s="35" t="s">
-        <v>707</v>
+        <v>669</v>
       </c>
       <c r="S51" s="39"/>
       <c r="T51" s="38" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="52" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="34" t="s">
-        <v>563</v>
+        <v>534</v>
       </c>
       <c r="B52" s="34" t="s">
         <v>59</v>
@@ -7573,7 +7567,7 @@
         <v>131</v>
       </c>
       <c r="G52" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H52" s="34" t="s">
         <v>63</v>
@@ -7585,29 +7579,29 @@
         <v>75</v>
       </c>
       <c r="K52" s="34" t="s">
-        <v>550</v>
+        <v>521</v>
       </c>
       <c r="L52" s="34"/>
       <c r="M52" s="35" t="s">
-        <v>551</v>
+        <v>522</v>
       </c>
       <c r="N52" s="36">
         <v>40077</v>
       </c>
       <c r="O52" s="34" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="P52" s="34"/>
       <c r="Q52" s="34"/>
       <c r="R52" s="35"/>
       <c r="S52" s="39"/>
       <c r="T52" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="53" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="34" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="B53" s="34" t="s">
         <v>59</v>
@@ -7625,7 +7619,7 @@
         <v>131</v>
       </c>
       <c r="G53" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H53" s="34" t="s">
         <v>63</v>
@@ -7641,27 +7635,27 @@
       </c>
       <c r="L53" s="34"/>
       <c r="M53" s="35" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="N53" s="36">
         <v>24906</v>
       </c>
       <c r="O53" s="34" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="P53" s="34"/>
       <c r="Q53" s="34"/>
       <c r="R53" s="35" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="S53" s="39"/>
       <c r="T53" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="34" t="s">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="B54" s="34" t="s">
         <v>59</v>
@@ -7673,13 +7667,13 @@
         <v>61</v>
       </c>
       <c r="E54" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F54" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G54" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H54" s="34" t="s">
         <v>63</v>
@@ -7691,33 +7685,33 @@
         <v>71</v>
       </c>
       <c r="K54" s="34" t="s">
-        <v>481</v>
+        <v>454</v>
       </c>
       <c r="L54" s="34"/>
       <c r="M54" s="35" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="N54" s="36">
         <v>23023</v>
       </c>
       <c r="O54" s="34" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="P54" s="34"/>
       <c r="Q54" s="34"/>
       <c r="R54" s="35" t="s">
-        <v>632</v>
+        <v>599</v>
       </c>
       <c r="S54" s="39" t="s">
-        <v>484</v>
-      </c>
-      <c r="T54" s="38" t="s">
-        <v>508</v>
+        <v>457</v>
+      </c>
+      <c r="T54" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="55" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="34" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="B55" s="34" t="s">
         <v>59</v>
@@ -7735,7 +7729,7 @@
         <v>131</v>
       </c>
       <c r="G55" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H55" s="34" t="s">
         <v>63</v>
@@ -7747,33 +7741,33 @@
         <v>75</v>
       </c>
       <c r="K55" s="34" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="L55" s="34"/>
       <c r="M55" s="35" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="N55" s="36">
         <v>23467</v>
       </c>
       <c r="O55" s="34" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="P55" s="34"/>
       <c r="Q55" s="34"/>
       <c r="R55" s="35" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="S55" s="39" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="T55" s="38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="34" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B56" s="34" t="s">
         <v>59</v>
@@ -7791,7 +7785,7 @@
         <v>131</v>
       </c>
       <c r="G56" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H56" s="34" t="s">
         <v>63</v>
@@ -7806,30 +7800,30 @@
         <v>134</v>
       </c>
       <c r="L56" s="34" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="M56" s="35" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="N56" s="36">
         <v>27622</v>
       </c>
       <c r="O56" s="34" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="P56" s="34"/>
       <c r="Q56" s="34"/>
       <c r="R56" s="35" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="S56" s="39"/>
       <c r="T56" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="34" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="B57" s="34" t="s">
         <v>59</v>
@@ -7847,7 +7841,7 @@
         <v>131</v>
       </c>
       <c r="G57" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H57" s="34" t="s">
         <v>63</v>
@@ -7859,13 +7853,13 @@
         <v>83</v>
       </c>
       <c r="K57" s="34" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="L57" s="34" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="M57" s="35" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="N57" s="36">
         <v>22700</v>
@@ -7876,12 +7870,12 @@
       <c r="R57" s="35"/>
       <c r="S57" s="39"/>
       <c r="T57" s="38" t="s">
-        <v>461</v>
+        <v>778</v>
       </c>
     </row>
     <row r="58" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="34" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="B58" s="34" t="s">
         <v>59</v>
@@ -7899,7 +7893,7 @@
         <v>131</v>
       </c>
       <c r="G58" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H58" s="34" t="s">
         <v>63</v>
@@ -7908,36 +7902,36 @@
         <v>109</v>
       </c>
       <c r="J58" s="34" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="K58" s="34" t="s">
-        <v>807</v>
+        <v>765</v>
       </c>
       <c r="L58" s="34"/>
       <c r="M58" s="35" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="N58" s="36">
         <v>30254</v>
       </c>
       <c r="O58" s="34" t="s">
-        <v>324</v>
+        <v>796</v>
       </c>
       <c r="P58" s="34"/>
       <c r="Q58" s="34"/>
       <c r="R58" s="35" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="S58" s="39" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="T58" s="38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="34" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="B59" s="34" t="s">
         <v>59</v>
@@ -7955,45 +7949,45 @@
         <v>131</v>
       </c>
       <c r="G59" s="34" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H59" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I59" s="34" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="J59" s="34" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="K59" s="34" t="s">
-        <v>808</v>
+        <v>766</v>
       </c>
       <c r="L59" s="34"/>
       <c r="M59" s="35" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="N59" s="36">
         <v>27776</v>
       </c>
       <c r="O59" s="34" t="s">
-        <v>319</v>
+        <v>797</v>
       </c>
       <c r="P59" s="34"/>
       <c r="Q59" s="34"/>
       <c r="R59" s="35" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="S59" s="39" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="T59" s="38" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="60" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="34" t="s">
-        <v>442</v>
+        <v>419</v>
       </c>
       <c r="B60" s="34" t="s">
         <v>59</v>
@@ -8011,7 +8005,7 @@
         <v>131</v>
       </c>
       <c r="G60" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H60" s="34" t="s">
         <v>63</v>
@@ -8029,7 +8023,7 @@
         <v>69</v>
       </c>
       <c r="M60" s="35" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="N60" s="36">
         <v>30538</v>
@@ -8040,12 +8034,12 @@
       <c r="R60" s="35"/>
       <c r="S60" s="39"/>
       <c r="T60" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="61" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="34" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="B61" s="34" t="s">
         <v>59</v>
@@ -8063,13 +8057,13 @@
         <v>131</v>
       </c>
       <c r="G61" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H61" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I61" s="34" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="J61" s="34" t="s">
         <v>82</v>
@@ -8081,7 +8075,7 @@
         <v>97</v>
       </c>
       <c r="M61" s="35" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="N61" s="36">
         <v>25896</v>
@@ -8092,12 +8086,12 @@
       <c r="R61" s="35"/>
       <c r="S61" s="39"/>
       <c r="T61" s="38" t="s">
-        <v>461</v>
+        <v>778</v>
       </c>
     </row>
     <row r="62" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="34" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="B62" s="34" t="s">
         <v>59</v>
@@ -8115,43 +8109,43 @@
         <v>131</v>
       </c>
       <c r="G62" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H62" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I62" s="34" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="J62" s="34" t="s">
         <v>65</v>
       </c>
       <c r="K62" s="34" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="L62" s="34"/>
       <c r="M62" s="35" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="N62" s="36">
         <v>25993</v>
       </c>
       <c r="O62" s="34" t="s">
-        <v>336</v>
+        <v>798</v>
       </c>
       <c r="P62" s="34"/>
       <c r="Q62" s="34"/>
       <c r="R62" s="35" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="S62" s="39"/>
       <c r="T62" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="34" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="B63" s="34" t="s">
         <v>59</v>
@@ -8169,7 +8163,7 @@
         <v>131</v>
       </c>
       <c r="G63" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H63" s="34" t="s">
         <v>63</v>
@@ -8181,33 +8175,33 @@
         <v>92</v>
       </c>
       <c r="K63" s="34" t="s">
-        <v>809</v>
+        <v>767</v>
       </c>
       <c r="L63" s="34"/>
       <c r="M63" s="35" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N63" s="36">
         <v>25881</v>
       </c>
       <c r="O63" s="34" t="s">
-        <v>165</v>
+        <v>799</v>
       </c>
       <c r="P63" s="34"/>
       <c r="Q63" s="34"/>
       <c r="R63" s="35" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="S63" s="39" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T63" s="38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="34" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="B64" s="34" t="s">
         <v>59</v>
@@ -8225,47 +8219,47 @@
         <v>131</v>
       </c>
       <c r="G64" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H64" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I64" s="34" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="J64" s="34" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="K64" s="34" t="s">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="L64" s="34" t="s">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="M64" s="35" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="N64" s="36">
         <v>30157</v>
       </c>
       <c r="O64" s="34" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="P64" s="34"/>
       <c r="Q64" s="34"/>
       <c r="R64" s="35" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="S64" s="39" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="T64" s="38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="34" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="B65" s="34" t="s">
         <v>59</v>
@@ -8283,45 +8277,45 @@
         <v>131</v>
       </c>
       <c r="G65" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H65" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I65" s="34" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="J65" s="34" t="s">
         <v>75</v>
       </c>
       <c r="K65" s="34" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="L65" s="34"/>
       <c r="M65" s="35" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="N65" s="36">
         <v>34772</v>
       </c>
       <c r="O65" s="34" t="s">
-        <v>363</v>
+        <v>800</v>
       </c>
       <c r="P65" s="34"/>
       <c r="Q65" s="34"/>
       <c r="R65" s="35" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="S65" s="39" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="T65" s="38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="34" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="B66" s="34" t="s">
         <v>59</v>
@@ -8339,45 +8333,45 @@
         <v>131</v>
       </c>
       <c r="G66" s="35" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H66" s="35" t="s">
         <v>63</v>
       </c>
       <c r="I66" s="35" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="J66" s="35" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="K66" s="35" t="s">
-        <v>810</v>
+        <v>768</v>
       </c>
       <c r="L66" s="35"/>
       <c r="M66" s="35" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="N66" s="36">
         <v>23605</v>
       </c>
       <c r="O66" s="35" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="P66" s="35"/>
       <c r="Q66" s="35"/>
       <c r="R66" s="35" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="S66" s="37" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="T66" s="37" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="34" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="B67" s="34" t="s">
         <v>59</v>
@@ -8395,7 +8389,7 @@
         <v>131</v>
       </c>
       <c r="G67" s="34" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H67" s="34" t="s">
         <v>63</v>
@@ -8407,33 +8401,33 @@
         <v>94</v>
       </c>
       <c r="K67" s="34" t="s">
-        <v>811</v>
+        <v>769</v>
       </c>
       <c r="L67" s="34"/>
       <c r="M67" s="35" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N67" s="36">
         <v>22431</v>
       </c>
       <c r="O67" s="34" t="s">
-        <v>169</v>
+        <v>801</v>
       </c>
       <c r="P67" s="34"/>
       <c r="Q67" s="34"/>
       <c r="R67" s="35" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="S67" s="39" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="T67" s="38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="34" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="B68" s="34" t="s">
         <v>59</v>
@@ -8451,7 +8445,7 @@
         <v>131</v>
       </c>
       <c r="G68" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H68" s="34" t="s">
         <v>63</v>
@@ -8467,27 +8461,27 @@
       </c>
       <c r="L68" s="35"/>
       <c r="M68" s="35" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="N68" s="36">
         <v>23105</v>
       </c>
       <c r="O68" s="34" t="s">
-        <v>206</v>
+        <v>802</v>
       </c>
       <c r="P68" s="35"/>
       <c r="Q68" s="35"/>
       <c r="R68" s="35" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S68" s="35"/>
       <c r="T68" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="34" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B69" s="34" t="s">
         <v>59</v>
@@ -8505,7 +8499,7 @@
         <v>131</v>
       </c>
       <c r="G69" s="34" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H69" s="34" t="s">
         <v>63</v>
@@ -8521,27 +8515,27 @@
       </c>
       <c r="L69" s="35"/>
       <c r="M69" s="35" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="N69" s="36">
         <v>36383</v>
       </c>
       <c r="O69" s="34" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
       <c r="R69" s="35" t="s">
-        <v>622</v>
+        <v>589</v>
       </c>
       <c r="S69" s="35"/>
       <c r="T69" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="34" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="B70" s="34" t="s">
         <v>59</v>
@@ -8559,7 +8553,7 @@
         <v>131</v>
       </c>
       <c r="G70" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H70" s="34" t="s">
         <v>63</v>
@@ -8575,27 +8569,27 @@
       </c>
       <c r="L70" s="35"/>
       <c r="M70" s="35" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="N70" s="36">
         <v>33831</v>
       </c>
       <c r="O70" s="34" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="P70" s="35"/>
       <c r="Q70" s="35"/>
       <c r="R70" s="35" t="s">
-        <v>623</v>
+        <v>590</v>
       </c>
       <c r="S70" s="35"/>
       <c r="T70" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="71" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="34" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="B71" s="34" t="s">
         <v>59</v>
@@ -8613,7 +8607,7 @@
         <v>131</v>
       </c>
       <c r="G71" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H71" s="34" t="s">
         <v>63</v>
@@ -8625,31 +8619,31 @@
         <v>86</v>
       </c>
       <c r="K71" s="35" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="L71" s="35"/>
       <c r="M71" s="35" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="N71" s="36">
         <v>30287</v>
       </c>
       <c r="O71" s="34" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="P71" s="35"/>
       <c r="Q71" s="35"/>
       <c r="R71" s="35" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="S71" s="35"/>
       <c r="T71" s="38" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="34" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="B72" s="34" t="s">
         <v>59</v>
@@ -8667,7 +8661,7 @@
         <v>131</v>
       </c>
       <c r="G72" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H72" s="34" t="s">
         <v>63</v>
@@ -8683,27 +8677,27 @@
       </c>
       <c r="L72" s="35"/>
       <c r="M72" s="35" t="s">
-        <v>521</v>
+        <v>492</v>
       </c>
       <c r="N72" s="36">
         <v>26138</v>
       </c>
       <c r="O72" s="34" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="P72" s="35"/>
       <c r="Q72" s="35"/>
       <c r="R72" s="35" t="s">
-        <v>624</v>
+        <v>591</v>
       </c>
       <c r="S72" s="35"/>
       <c r="T72" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="73" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="34" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="B73" s="34" t="s">
         <v>59</v>
@@ -8721,7 +8715,7 @@
         <v>131</v>
       </c>
       <c r="G73" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H73" s="34" t="s">
         <v>63</v>
@@ -8737,27 +8731,27 @@
       </c>
       <c r="L73" s="35"/>
       <c r="M73" s="35" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="N73" s="36">
         <v>32984</v>
       </c>
       <c r="O73" s="34" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="P73" s="35"/>
       <c r="Q73" s="35"/>
       <c r="R73" s="35" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="S73" s="35"/>
       <c r="T73" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="74" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="34" t="s">
-        <v>561</v>
+        <v>532</v>
       </c>
       <c r="B74" s="34" t="s">
         <v>59</v>
@@ -8769,51 +8763,51 @@
         <v>61</v>
       </c>
       <c r="E74" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F74" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G74" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H74" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I74" s="35" t="s">
-        <v>538</v>
+        <v>509</v>
       </c>
       <c r="J74" s="35" t="s">
         <v>108</v>
       </c>
       <c r="K74" s="35" t="s">
-        <v>539</v>
+        <v>510</v>
       </c>
       <c r="L74" s="35" t="s">
-        <v>540</v>
+        <v>511</v>
       </c>
       <c r="M74" s="35" t="s">
-        <v>541</v>
+        <v>512</v>
       </c>
       <c r="N74" s="36">
         <v>23098</v>
       </c>
       <c r="O74" s="34" t="s">
-        <v>542</v>
+        <v>513</v>
       </c>
       <c r="P74" s="35"/>
       <c r="Q74" s="35"/>
       <c r="R74" s="35" t="s">
-        <v>543</v>
+        <v>514</v>
       </c>
       <c r="S74" s="35"/>
-      <c r="T74" s="38" t="s">
-        <v>508</v>
+      <c r="T74" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="75" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="34" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="B75" s="34" t="s">
         <v>59</v>
@@ -8831,45 +8825,45 @@
         <v>131</v>
       </c>
       <c r="G75" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H75" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I75" s="35" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="J75" s="35" t="s">
         <v>83</v>
       </c>
       <c r="K75" s="35" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="L75" s="35"/>
       <c r="M75" s="35" t="s">
-        <v>444</v>
+        <v>421</v>
       </c>
       <c r="N75" s="36">
         <v>25389</v>
       </c>
       <c r="O75" s="34" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="P75" s="35"/>
       <c r="Q75" s="35"/>
       <c r="R75" s="35" t="s">
-        <v>446</v>
+        <v>423</v>
       </c>
       <c r="S75" s="35" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
       <c r="T75" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="76" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="34" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B76" s="34" t="s">
         <v>59</v>
@@ -8887,7 +8881,7 @@
         <v>131</v>
       </c>
       <c r="G76" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H76" s="34" t="s">
         <v>63</v>
@@ -8903,27 +8897,27 @@
       </c>
       <c r="L76" s="35"/>
       <c r="M76" s="35" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="N76" s="36">
         <v>29006</v>
       </c>
       <c r="O76" s="34" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="P76" s="35"/>
       <c r="Q76" s="35"/>
       <c r="R76" s="35" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="S76" s="35"/>
       <c r="T76" s="38" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="34" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="B77" s="34" t="s">
         <v>59</v>
@@ -8941,7 +8935,7 @@
         <v>131</v>
       </c>
       <c r="G77" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H77" s="34" t="s">
         <v>63</v>
@@ -8957,27 +8951,27 @@
       </c>
       <c r="L77" s="35"/>
       <c r="M77" s="35" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="N77" s="36">
         <v>21024</v>
       </c>
       <c r="O77" s="34" t="s">
-        <v>228</v>
+        <v>803</v>
       </c>
       <c r="P77" s="35"/>
       <c r="Q77" s="35"/>
       <c r="R77" s="35" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="S77" s="35"/>
       <c r="T77" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="78" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="34" t="s">
-        <v>799</v>
+        <v>757</v>
       </c>
       <c r="B78" s="34" t="s">
         <v>59</v>
@@ -8995,7 +8989,7 @@
         <v>131</v>
       </c>
       <c r="G78" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H78" s="34" t="s">
         <v>63</v>
@@ -9004,34 +8998,34 @@
         <v>137</v>
       </c>
       <c r="J78" s="34" t="s">
-        <v>791</v>
+        <v>749</v>
       </c>
       <c r="K78" s="34" t="s">
-        <v>792</v>
+        <v>750</v>
       </c>
       <c r="L78" s="34"/>
       <c r="M78" s="35" t="s">
-        <v>793</v>
+        <v>751</v>
       </c>
       <c r="N78" s="36" t="s">
-        <v>795</v>
+        <v>753</v>
       </c>
       <c r="O78" s="34" t="s">
-        <v>796</v>
+        <v>754</v>
       </c>
       <c r="P78" s="34"/>
       <c r="Q78" s="34"/>
       <c r="R78" s="35" t="s">
-        <v>797</v>
+        <v>755</v>
       </c>
       <c r="S78" s="38"/>
       <c r="T78" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="79" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="34" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B79" s="34" t="s">
         <v>59</v>
@@ -9049,7 +9043,7 @@
         <v>131</v>
       </c>
       <c r="G79" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H79" s="34" t="s">
         <v>63</v>
@@ -9061,31 +9055,31 @@
         <v>138</v>
       </c>
       <c r="K79" s="35" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="L79" s="35"/>
       <c r="M79" s="35" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="N79" s="36">
         <v>19757</v>
       </c>
       <c r="O79" s="34" t="s">
-        <v>225</v>
+        <v>804</v>
       </c>
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
       <c r="R79" s="35" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="S79" s="35"/>
       <c r="T79" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="80" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="34" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="B80" s="34" t="s">
         <v>59</v>
@@ -9103,43 +9097,43 @@
         <v>131</v>
       </c>
       <c r="G80" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H80" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I80" s="35" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="J80" s="35" t="s">
         <v>75</v>
       </c>
       <c r="K80" s="35" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="L80" s="35"/>
       <c r="M80" s="35" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="N80" s="36">
         <v>30337</v>
       </c>
       <c r="O80" s="34" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
       <c r="R80" s="35" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="S80" s="35"/>
       <c r="T80" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:21" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="34" t="s">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="B81" s="34" t="s">
         <v>59</v>
@@ -9157,25 +9151,25 @@
         <v>131</v>
       </c>
       <c r="G81" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H81" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I81" s="35" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="J81" s="35" t="s">
         <v>65</v>
       </c>
       <c r="K81" s="35" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="L81" s="35" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="M81" s="35" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="N81" s="36">
         <v>29821</v>
@@ -9186,13 +9180,13 @@
       <c r="R81" s="35"/>
       <c r="S81" s="35"/>
       <c r="T81" s="38" t="s">
-        <v>461</v>
+        <v>778</v>
       </c>
       <c r="U81" s="27"/>
     </row>
     <row r="82" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="34" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="B82" s="34" t="s">
         <v>59</v>
@@ -9210,7 +9204,7 @@
         <v>131</v>
       </c>
       <c r="G82" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H82" s="34" t="s">
         <v>63</v>
@@ -9232,23 +9226,23 @@
         <v>27213</v>
       </c>
       <c r="O82" s="34" t="s">
-        <v>144</v>
+        <v>805</v>
       </c>
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
       <c r="R82" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="S82" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="S82" s="35" t="s">
+      <c r="T82" s="38" t="s">
         <v>146</v>
-      </c>
-      <c r="T82" s="38" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="83" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="34" t="s">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="B83" s="34" t="s">
         <v>59</v>
@@ -9266,25 +9260,25 @@
         <v>131</v>
       </c>
       <c r="G83" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H83" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I83" s="35" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="J83" s="35" t="s">
         <v>74</v>
       </c>
       <c r="K83" s="35" t="s">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="L83" s="35" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="M83" s="35" t="s">
-        <v>433</v>
+        <v>410</v>
       </c>
       <c r="N83" s="36">
         <v>24507</v>
@@ -9293,16 +9287,16 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
       <c r="R83" s="35" t="s">
-        <v>625</v>
+        <v>592</v>
       </c>
       <c r="S83" s="35"/>
       <c r="T83" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="34" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B84" s="34" t="s">
         <v>59</v>
@@ -9320,7 +9314,7 @@
         <v>131</v>
       </c>
       <c r="G84" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H84" s="34" t="s">
         <v>63</v>
@@ -9332,33 +9326,33 @@
         <v>136</v>
       </c>
       <c r="K84" s="35" t="s">
-        <v>812</v>
+        <v>770</v>
       </c>
       <c r="L84" s="35"/>
       <c r="M84" s="35" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="N84" s="36">
         <v>29328</v>
       </c>
       <c r="O84" s="34" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
       <c r="R84" s="35" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="S84" s="35" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="T84" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="85" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="34" t="s">
-        <v>654</v>
+        <v>621</v>
       </c>
       <c r="B85" s="34" t="s">
         <v>59</v>
@@ -9376,7 +9370,7 @@
         <v>131</v>
       </c>
       <c r="G85" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H85" s="34" t="s">
         <v>63</v>
@@ -9385,32 +9379,32 @@
         <v>135</v>
       </c>
       <c r="J85" s="35" t="s">
-        <v>651</v>
+        <v>618</v>
       </c>
       <c r="K85" s="35" t="s">
-        <v>652</v>
+        <v>619</v>
       </c>
       <c r="L85" s="35"/>
       <c r="M85" s="35" t="s">
-        <v>653</v>
+        <v>620</v>
       </c>
       <c r="N85" s="36">
         <v>40905</v>
       </c>
       <c r="O85" s="34" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
       <c r="R85" s="35"/>
       <c r="S85" s="35"/>
       <c r="T85" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="34" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B86" s="34" t="s">
         <v>59</v>
@@ -9428,7 +9422,7 @@
         <v>131</v>
       </c>
       <c r="G86" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H86" s="34" t="s">
         <v>63</v>
@@ -9444,29 +9438,29 @@
       </c>
       <c r="L86" s="35"/>
       <c r="M86" s="35" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="N86" s="36">
         <v>27907</v>
       </c>
       <c r="O86" s="34" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
       <c r="R86" s="35" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="S86" s="35" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="T86" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="87" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="34" t="s">
-        <v>559</v>
+        <v>530</v>
       </c>
       <c r="B87" s="34" t="s">
         <v>59</v>
@@ -9478,51 +9472,51 @@
         <v>61</v>
       </c>
       <c r="E87" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G87" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H87" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I87" s="35" t="s">
-        <v>529</v>
+        <v>500</v>
       </c>
       <c r="J87" s="35" t="s">
         <v>122</v>
       </c>
       <c r="K87" s="35" t="s">
-        <v>530</v>
+        <v>501</v>
       </c>
       <c r="L87" s="35" t="s">
-        <v>531</v>
+        <v>502</v>
       </c>
       <c r="M87" s="35" t="s">
-        <v>532</v>
+        <v>503</v>
       </c>
       <c r="N87" s="36" t="s">
-        <v>684</v>
+        <v>648</v>
       </c>
       <c r="O87" s="34" t="s">
-        <v>533</v>
+        <v>504</v>
       </c>
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
       <c r="R87" s="35" t="s">
-        <v>675</v>
+        <v>640</v>
       </c>
       <c r="S87" s="35"/>
-      <c r="T87" s="38" t="s">
-        <v>508</v>
+      <c r="T87" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="88" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="34" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B88" s="34" t="s">
         <v>59</v>
@@ -9540,43 +9534,43 @@
         <v>131</v>
       </c>
       <c r="G88" s="34" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H88" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I88" s="35" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="J88" s="35" t="s">
         <v>82</v>
       </c>
       <c r="K88" s="35" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="L88" s="35"/>
       <c r="M88" s="35" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="N88" s="36">
         <v>23497</v>
       </c>
       <c r="O88" s="34" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
       <c r="R88" s="35" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="S88" s="35"/>
       <c r="T88" s="38" t="s">
-        <v>461</v>
+        <v>778</v>
       </c>
     </row>
     <row r="89" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="34" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="B89" s="34" t="s">
         <v>59</v>
@@ -9588,51 +9582,51 @@
         <v>61</v>
       </c>
       <c r="E89" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F89" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G89" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H89" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I89" s="35" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="J89" s="35" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="K89" s="35" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="L89" s="35" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="M89" s="35" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="N89" s="36">
         <v>24537</v>
       </c>
       <c r="O89" s="34" t="s">
-        <v>490</v>
+        <v>806</v>
       </c>
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
       <c r="R89" s="35" t="s">
-        <v>630</v>
+        <v>597</v>
       </c>
       <c r="S89" s="35"/>
-      <c r="T89" s="38" t="s">
-        <v>508</v>
+      <c r="T89" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="90" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="35" t="s">
-        <v>766</v>
+        <v>726</v>
       </c>
       <c r="B90" s="34" t="s">
         <v>59</v>
@@ -9644,49 +9638,49 @@
         <v>61</v>
       </c>
       <c r="E90" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F90" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G90" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H90" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I90" s="34" t="s">
-        <v>723</v>
+        <v>684</v>
       </c>
       <c r="J90" s="34" t="s">
         <v>86</v>
       </c>
       <c r="K90" s="34" t="s">
-        <v>743</v>
+        <v>704</v>
       </c>
       <c r="L90" s="34"/>
       <c r="M90" s="35" t="s">
-        <v>744</v>
+        <v>705</v>
       </c>
       <c r="N90" s="36" t="s">
-        <v>745</v>
+        <v>706</v>
       </c>
       <c r="O90" s="34" t="s">
-        <v>746</v>
+        <v>807</v>
       </c>
       <c r="P90" s="34"/>
       <c r="Q90" s="34"/>
       <c r="R90" s="35" t="s">
-        <v>747</v>
+        <v>707</v>
       </c>
       <c r="S90" s="39"/>
       <c r="T90" s="38" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="91" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="35" t="s">
-        <v>801</v>
+        <v>759</v>
       </c>
       <c r="B91" s="34" t="s">
         <v>59</v>
@@ -9704,43 +9698,43 @@
         <v>131</v>
       </c>
       <c r="G91" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H91" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I91" s="35" t="s">
-        <v>773</v>
+        <v>733</v>
       </c>
       <c r="J91" s="35" t="s">
-        <v>774</v>
+        <v>734</v>
       </c>
       <c r="K91" s="35" t="s">
-        <v>775</v>
+        <v>735</v>
       </c>
       <c r="L91" s="35"/>
       <c r="M91" s="35" t="s">
-        <v>777</v>
+        <v>736</v>
       </c>
       <c r="N91" s="36" t="s">
-        <v>778</v>
+        <v>737</v>
       </c>
       <c r="O91" s="34" t="s">
-        <v>776</v>
+        <v>808</v>
       </c>
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
       <c r="R91" s="35" t="s">
-        <v>779</v>
+        <v>738</v>
       </c>
       <c r="S91" s="35"/>
       <c r="T91" s="35" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="34" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B92" s="34" t="s">
         <v>59</v>
@@ -9758,7 +9752,7 @@
         <v>131</v>
       </c>
       <c r="G92" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H92" s="34" t="s">
         <v>63</v>
@@ -9774,27 +9768,27 @@
       </c>
       <c r="L92" s="35"/>
       <c r="M92" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N92" s="36">
         <v>31298</v>
       </c>
       <c r="O92" s="34" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
       <c r="R92" s="35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S92" s="35"/>
       <c r="T92" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="34" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="B93" s="34" t="s">
         <v>59</v>
@@ -9812,7 +9806,7 @@
         <v>131</v>
       </c>
       <c r="G93" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H93" s="34" t="s">
         <v>63</v>
@@ -9828,27 +9822,27 @@
       </c>
       <c r="L93" s="35"/>
       <c r="M93" s="35" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="N93" s="36">
         <v>28101</v>
       </c>
       <c r="O93" s="34" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
       <c r="R93" s="35" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="S93" s="35"/>
       <c r="T93" s="38" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="94" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="34" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="B94" s="34" t="s">
         <v>59</v>
@@ -9866,7 +9860,7 @@
         <v>131</v>
       </c>
       <c r="G94" s="34" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H94" s="34" t="s">
         <v>63</v>
@@ -9878,11 +9872,11 @@
         <v>81</v>
       </c>
       <c r="K94" s="35" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="L94" s="35"/>
       <c r="M94" s="35" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="N94" s="36">
         <v>30156</v>
@@ -9891,16 +9885,16 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
       <c r="R94" s="35" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="S94" s="35"/>
       <c r="T94" s="38" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="95" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="34" t="s">
-        <v>644</v>
+        <v>611</v>
       </c>
       <c r="B95" s="34" t="s">
         <v>59</v>
@@ -9915,46 +9909,46 @@
         <v>62</v>
       </c>
       <c r="F95" s="35" t="s">
-        <v>645</v>
+        <v>612</v>
       </c>
       <c r="G95" s="34" t="s">
-        <v>678</v>
+        <v>643</v>
       </c>
       <c r="H95" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I95" s="35" t="s">
-        <v>646</v>
+        <v>613</v>
       </c>
       <c r="J95" s="35" t="s">
         <v>84</v>
       </c>
       <c r="K95" s="35" t="s">
-        <v>647</v>
+        <v>614</v>
       </c>
       <c r="L95" s="35"/>
       <c r="M95" s="35" t="s">
-        <v>648</v>
+        <v>615</v>
       </c>
       <c r="N95" s="36">
         <v>33667</v>
       </c>
       <c r="O95" s="34" t="s">
-        <v>649</v>
+        <v>616</v>
       </c>
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
       <c r="R95" s="35" t="s">
-        <v>650</v>
+        <v>617</v>
       </c>
       <c r="S95" s="35"/>
       <c r="T95" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="96" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="34" t="s">
-        <v>564</v>
+        <v>535</v>
       </c>
       <c r="B96" s="34" t="s">
         <v>59</v>
@@ -9966,49 +9960,49 @@
         <v>61</v>
       </c>
       <c r="E96" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F96" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G96" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H96" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I96" s="35" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
       <c r="J96" s="35" t="s">
         <v>74</v>
       </c>
       <c r="K96" s="35" t="s">
-        <v>545</v>
+        <v>516</v>
       </c>
       <c r="L96" s="35"/>
       <c r="M96" s="35" t="s">
-        <v>546</v>
+        <v>517</v>
       </c>
       <c r="N96" s="36" t="s">
-        <v>547</v>
+        <v>518</v>
       </c>
       <c r="O96" s="34" t="s">
-        <v>548</v>
+        <v>519</v>
       </c>
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
       <c r="R96" s="35" t="s">
-        <v>549</v>
+        <v>520</v>
       </c>
       <c r="S96" s="35"/>
       <c r="T96" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="97" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="34" t="s">
-        <v>491</v>
+        <v>463</v>
       </c>
       <c r="B97" s="34" t="s">
         <v>59</v>
@@ -10020,53 +10014,53 @@
         <v>61</v>
       </c>
       <c r="E97" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F97" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G97" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H97" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I97" s="35" t="s">
-        <v>492</v>
+        <v>464</v>
       </c>
       <c r="J97" s="35" t="s">
         <v>75</v>
       </c>
       <c r="K97" s="35" t="s">
-        <v>493</v>
+        <v>465</v>
       </c>
       <c r="L97" s="35" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="M97" s="35" t="s">
-        <v>494</v>
+        <v>466</v>
       </c>
       <c r="N97" s="36">
         <v>34298</v>
       </c>
       <c r="O97" s="34" t="s">
-        <v>495</v>
+        <v>467</v>
       </c>
       <c r="P97" s="35"/>
       <c r="Q97" s="35"/>
       <c r="R97" s="35" t="s">
-        <v>496</v>
+        <v>468</v>
       </c>
       <c r="S97" s="35" t="s">
-        <v>497</v>
-      </c>
-      <c r="T97" s="38" t="s">
-        <v>508</v>
+        <v>469</v>
+      </c>
+      <c r="T97" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="98" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="34" t="s">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="B98" s="34" t="s">
         <v>59</v>
@@ -10078,51 +10072,51 @@
         <v>61</v>
       </c>
       <c r="E98" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F98" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G98" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H98" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I98" s="35" t="s">
-        <v>492</v>
+        <v>464</v>
       </c>
       <c r="J98" s="35" t="s">
         <v>84</v>
       </c>
       <c r="K98" s="35" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="L98" s="35"/>
       <c r="M98" s="35" t="s">
-        <v>500</v>
+        <v>472</v>
       </c>
       <c r="N98" s="36">
         <v>29452</v>
       </c>
       <c r="O98" s="34" t="s">
-        <v>501</v>
+        <v>473</v>
       </c>
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
       <c r="R98" s="35" t="s">
-        <v>627</v>
+        <v>594</v>
       </c>
       <c r="S98" s="35" t="s">
-        <v>502</v>
-      </c>
-      <c r="T98" s="38" t="s">
-        <v>508</v>
+        <v>474</v>
+      </c>
+      <c r="T98" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="99" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="34" t="s">
-        <v>785</v>
+        <v>743</v>
       </c>
       <c r="B99" s="34" t="s">
         <v>59</v>
@@ -10140,43 +10134,43 @@
         <v>131</v>
       </c>
       <c r="G99" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H99" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I99" s="34" t="s">
-        <v>786</v>
+        <v>744</v>
       </c>
       <c r="J99" s="34" t="s">
         <v>83</v>
       </c>
       <c r="K99" s="34" t="s">
-        <v>787</v>
+        <v>745</v>
       </c>
       <c r="L99" s="34"/>
       <c r="M99" s="35" t="s">
-        <v>788</v>
+        <v>746</v>
       </c>
       <c r="N99" s="36" t="s">
-        <v>794</v>
+        <v>752</v>
       </c>
       <c r="O99" s="34" t="s">
-        <v>789</v>
+        <v>747</v>
       </c>
       <c r="P99" s="34"/>
       <c r="Q99" s="34"/>
       <c r="R99" s="35" t="s">
-        <v>790</v>
+        <v>748</v>
       </c>
       <c r="S99" s="38"/>
       <c r="T99" s="38" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="100" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="34" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="B100" s="34" t="s">
         <v>59</v>
@@ -10191,48 +10185,48 @@
         <v>62</v>
       </c>
       <c r="F100" s="35" t="s">
-        <v>686</v>
+        <v>612</v>
       </c>
       <c r="G100" s="34" t="s">
-        <v>678</v>
+        <v>643</v>
       </c>
       <c r="H100" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I100" s="35" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="J100" s="35" t="s">
         <v>71</v>
       </c>
       <c r="K100" s="35" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="L100" s="35" t="s">
-        <v>676</v>
+        <v>641</v>
       </c>
       <c r="M100" s="35" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="N100" s="36" t="s">
-        <v>685</v>
+        <v>649</v>
       </c>
       <c r="O100" s="34" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
       <c r="R100" s="35" t="s">
-        <v>621</v>
+        <v>588</v>
       </c>
       <c r="S100" s="35"/>
-      <c r="T100" s="38" t="s">
-        <v>508</v>
+      <c r="T100" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="101" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="34" t="s">
-        <v>708</v>
+        <v>670</v>
       </c>
       <c r="B101" s="34" t="s">
         <v>59</v>
@@ -10250,43 +10244,43 @@
         <v>131</v>
       </c>
       <c r="G101" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H101" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I101" s="35" t="s">
-        <v>709</v>
+        <v>671</v>
       </c>
       <c r="J101" s="35" t="s">
         <v>73</v>
       </c>
       <c r="K101" s="35" t="s">
-        <v>710</v>
+        <v>672</v>
       </c>
       <c r="L101" s="35"/>
       <c r="M101" s="35" t="s">
-        <v>711</v>
+        <v>673</v>
       </c>
       <c r="N101" s="36">
         <v>32200</v>
       </c>
       <c r="O101" s="34" t="s">
-        <v>712</v>
+        <v>809</v>
       </c>
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
       <c r="R101" s="35" t="s">
-        <v>713</v>
+        <v>674</v>
       </c>
       <c r="S101" s="35"/>
       <c r="T101" s="38" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="102" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="34" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="B102" s="34" t="s">
         <v>59</v>
@@ -10304,43 +10298,43 @@
         <v>131</v>
       </c>
       <c r="G102" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H102" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I102" s="35" t="s">
-        <v>816</v>
+        <v>774</v>
       </c>
       <c r="J102" s="35" t="s">
         <v>65</v>
       </c>
       <c r="K102" s="35" t="s">
-        <v>813</v>
+        <v>771</v>
       </c>
       <c r="L102" s="35"/>
       <c r="M102" s="35" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="N102" s="36">
         <v>28570</v>
       </c>
       <c r="O102" s="34" t="s">
-        <v>295</v>
+        <v>810</v>
       </c>
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
       <c r="R102" s="35" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="S102" s="35"/>
       <c r="T102" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="34" t="s">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="B103" s="34" t="s">
         <v>59</v>
@@ -10358,43 +10352,43 @@
         <v>131</v>
       </c>
       <c r="G103" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H103" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I103" s="35" t="s">
-        <v>816</v>
+        <v>774</v>
       </c>
       <c r="J103" s="35" t="s">
         <v>75</v>
       </c>
       <c r="K103" s="35" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="L103" s="35"/>
       <c r="M103" s="35" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="N103" s="36">
         <v>33544</v>
       </c>
       <c r="O103" s="34" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
       <c r="R103" s="35" t="s">
-        <v>454</v>
+        <v>431</v>
       </c>
       <c r="S103" s="35"/>
       <c r="T103" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="34" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="B104" s="34" t="s">
         <v>59</v>
@@ -10412,7 +10406,7 @@
         <v>131</v>
       </c>
       <c r="G104" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H104" s="34" t="s">
         <v>63</v>
@@ -10421,38 +10415,38 @@
         <v>101</v>
       </c>
       <c r="J104" s="35" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="K104" s="35" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="L104" s="35" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="M104" s="35" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="N104" s="36">
         <v>25204</v>
       </c>
       <c r="O104" s="34" t="s">
-        <v>417</v>
+        <v>811</v>
       </c>
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
       <c r="R104" s="35" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="S104" s="35" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="T104" s="38" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="105" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="34" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B105" s="34" t="s">
         <v>59</v>
@@ -10470,7 +10464,7 @@
         <v>131</v>
       </c>
       <c r="G105" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H105" s="34" t="s">
         <v>63</v>
@@ -10486,25 +10480,25 @@
       </c>
       <c r="L105" s="35"/>
       <c r="M105" s="35" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="N105" s="36">
         <v>26134</v>
       </c>
       <c r="O105" s="34" t="s">
-        <v>179</v>
+        <v>812</v>
       </c>
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
       <c r="R105" s="35"/>
       <c r="S105" s="35"/>
       <c r="T105" s="38" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="106" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="34" t="s">
-        <v>643</v>
+        <v>610</v>
       </c>
       <c r="B106" s="34" t="s">
         <v>59</v>
@@ -10522,45 +10516,45 @@
         <v>131</v>
       </c>
       <c r="G106" s="34" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="H106" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I106" s="35" t="s">
-        <v>602</v>
+        <v>569</v>
       </c>
       <c r="J106" s="35" t="s">
-        <v>817</v>
+        <v>775</v>
       </c>
       <c r="K106" s="35" t="s">
-        <v>603</v>
+        <v>570</v>
       </c>
       <c r="L106" s="35" t="s">
-        <v>603</v>
+        <v>570</v>
       </c>
       <c r="M106" s="35" t="s">
-        <v>604</v>
+        <v>571</v>
       </c>
       <c r="N106" s="36">
         <v>31906</v>
       </c>
       <c r="O106" s="34" t="s">
-        <v>605</v>
+        <v>572</v>
       </c>
       <c r="P106" s="35"/>
       <c r="Q106" s="35"/>
       <c r="R106" s="35" t="s">
-        <v>606</v>
+        <v>573</v>
       </c>
       <c r="S106" s="35"/>
       <c r="T106" s="38" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="107" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="34" t="s">
-        <v>677</v>
+        <v>642</v>
       </c>
       <c r="B107" s="34" t="s">
         <v>59</v>
@@ -10572,49 +10566,49 @@
         <v>61</v>
       </c>
       <c r="E107" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F107" s="35" t="s">
-        <v>686</v>
+        <v>612</v>
       </c>
       <c r="G107" s="34" t="s">
-        <v>678</v>
+        <v>643</v>
       </c>
       <c r="H107" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I107" s="35" t="s">
-        <v>818</v>
+        <v>776</v>
       </c>
       <c r="J107" s="35" t="s">
-        <v>679</v>
+        <v>644</v>
       </c>
       <c r="K107" s="35" t="s">
-        <v>656</v>
+        <v>623</v>
       </c>
       <c r="L107" s="35"/>
       <c r="M107" s="35" t="s">
-        <v>688</v>
+        <v>651</v>
       </c>
       <c r="N107" s="36" t="s">
-        <v>689</v>
+        <v>652</v>
       </c>
       <c r="O107" s="34" t="s">
-        <v>680</v>
+        <v>813</v>
       </c>
       <c r="P107" s="35"/>
       <c r="Q107" s="35"/>
       <c r="R107" s="35" t="s">
-        <v>687</v>
+        <v>650</v>
       </c>
       <c r="S107" s="35"/>
       <c r="T107" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="108" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="34" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="B108" s="34" t="s">
         <v>59</v>
@@ -10629,10 +10623,10 @@
         <v>77</v>
       </c>
       <c r="F108" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G108" s="34" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H108" s="34" t="s">
         <v>63</v>
@@ -10648,27 +10642,27 @@
       </c>
       <c r="L108" s="35"/>
       <c r="M108" s="35" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="N108" s="36" t="s">
-        <v>681</v>
+        <v>645</v>
       </c>
       <c r="O108" s="34" t="s">
-        <v>189</v>
+        <v>814</v>
       </c>
       <c r="P108" s="35"/>
       <c r="Q108" s="35"/>
       <c r="R108" s="35" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="S108" s="35"/>
       <c r="T108" s="38" t="s">
-        <v>461</v>
+        <v>778</v>
       </c>
     </row>
     <row r="109" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="34" t="s">
-        <v>714</v>
+        <v>675</v>
       </c>
       <c r="B109" s="34" t="s">
         <v>59</v>
@@ -10680,51 +10674,51 @@
         <v>61</v>
       </c>
       <c r="E109" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F109" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G109" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H109" s="34" t="s">
         <v>63</v>
       </c>
       <c r="I109" s="35" t="s">
-        <v>695</v>
+        <v>658</v>
       </c>
       <c r="J109" s="35" t="s">
-        <v>651</v>
+        <v>618</v>
       </c>
       <c r="K109" s="35" t="s">
-        <v>696</v>
+        <v>659</v>
       </c>
       <c r="L109" s="35" t="s">
-        <v>697</v>
+        <v>660</v>
       </c>
       <c r="M109" s="35" t="s">
-        <v>700</v>
+        <v>663</v>
       </c>
       <c r="N109" s="36" t="s">
-        <v>702</v>
+        <v>665</v>
       </c>
       <c r="O109" s="34" t="s">
-        <v>698</v>
+        <v>661</v>
       </c>
       <c r="P109" s="35"/>
       <c r="Q109" s="35"/>
       <c r="R109" s="35" t="s">
-        <v>699</v>
+        <v>662</v>
       </c>
       <c r="S109" s="35"/>
-      <c r="T109" s="38" t="s">
-        <v>508</v>
+      <c r="T109" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="110" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="34" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
       <c r="B110" s="34" t="s">
         <v>59</v>
@@ -10736,13 +10730,13 @@
         <v>61</v>
       </c>
       <c r="E110" s="35" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="F110" s="35" t="s">
-        <v>468</v>
+        <v>131</v>
       </c>
       <c r="G110" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H110" s="34" t="s">
         <v>63</v>
@@ -10754,33 +10748,33 @@
         <v>71</v>
       </c>
       <c r="K110" s="35" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="L110" s="35"/>
       <c r="M110" s="35" t="s">
-        <v>504</v>
+        <v>476</v>
       </c>
       <c r="N110" s="36">
         <v>26766</v>
       </c>
       <c r="O110" s="34" t="s">
-        <v>505</v>
+        <v>815</v>
       </c>
       <c r="P110" s="35"/>
       <c r="Q110" s="35"/>
       <c r="R110" s="35" t="s">
-        <v>628</v>
+        <v>595</v>
       </c>
       <c r="S110" s="35" t="s">
-        <v>506</v>
-      </c>
-      <c r="T110" s="38" t="s">
-        <v>508</v>
+        <v>477</v>
+      </c>
+      <c r="T110" s="35" t="s">
+        <v>777</v>
       </c>
     </row>
     <row r="111" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="34" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B111" s="34" t="s">
         <v>59</v>
@@ -10798,7 +10792,7 @@
         <v>131</v>
       </c>
       <c r="G111" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H111" s="34" t="s">
         <v>63</v>
@@ -10814,27 +10808,27 @@
       </c>
       <c r="L111" s="35"/>
       <c r="M111" s="35" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="N111" s="36">
         <v>24263</v>
       </c>
       <c r="O111" s="34" t="s">
-        <v>212</v>
+        <v>816</v>
       </c>
       <c r="P111" s="35"/>
       <c r="Q111" s="35"/>
       <c r="R111" s="35" t="s">
-        <v>626</v>
+        <v>593</v>
       </c>
       <c r="S111" s="35"/>
       <c r="T111" s="38" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="112" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="34" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="B112" s="34" t="s">
         <v>59</v>
@@ -10852,7 +10846,7 @@
         <v>131</v>
       </c>
       <c r="G112" s="34" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H112" s="34" t="s">
         <v>63</v>
@@ -10868,27 +10862,27 @@
       </c>
       <c r="L112" s="35"/>
       <c r="M112" s="35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N112" s="36">
         <v>29464</v>
       </c>
       <c r="O112" s="34" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P112" s="35"/>
       <c r="Q112" s="35"/>
       <c r="R112" s="35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S112" s="35"/>
       <c r="T112" s="38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" sort="0"/>
-  <autoFilter ref="A1:T106" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:T112" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U115">
     <sortCondition ref="I2:I16998"/>
     <sortCondition ref="K2:K16998"/>
@@ -10897,7 +10891,7 @@
   <conditionalFormatting sqref="A113:A1048576 A1">
     <cfRule type="duplicateValues" dxfId="17" priority="591"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H101:H106 H2:H93">
+  <conditionalFormatting sqref="H2:H93 H101:H106">
     <cfRule type="containsText" dxfId="16" priority="22" operator="containsText" text="Inactive - ADS">
       <formula>NOT(ISERROR(SEARCH("Inactive - ADS",H2)))</formula>
     </cfRule>
@@ -10927,34 +10921,34 @@
       <formula>LEN(M1)&lt;&gt;13</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M93">
+    <cfRule type="duplicateValues" dxfId="10" priority="670"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M2:M112">
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>LEN(M2)&lt;13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M94">
-    <cfRule type="duplicateValues" dxfId="9" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M95:M96">
-    <cfRule type="duplicateValues" dxfId="8" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M97:M100">
-    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M101:M106">
-    <cfRule type="duplicateValues" dxfId="6" priority="652"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="652"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M107:M110">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M111:M112">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M113:M65093 M1">
-    <cfRule type="duplicateValues" dxfId="3" priority="648" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M93">
-    <cfRule type="duplicateValues" dxfId="0" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="648" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -11078,12 +11072,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="M1 M18:M65486">
-    <cfRule type="expression" dxfId="2" priority="560" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="560" stopIfTrue="1">
       <formula>LEN(M1)&lt;&gt;13</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M18:M65486 M1">
-    <cfRule type="duplicateValues" dxfId="1" priority="559" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="559" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11121,102 +11115,102 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>639</v>
+        <v>606</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>638</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
-        <v>461</v>
+        <v>438</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>510</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>516</v>
+        <v>487</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>512</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>508</v>
+        <v>479</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>518</v>
+        <v>489</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>517</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>513</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="30" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>514</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
-        <v>509</v>
+        <v>480</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>520</v>
+        <v>491</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>515</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
       <c r="B10"/>
       <c r="C10" s="31" t="s">
-        <v>577</v>
+        <v>547</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>578</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">

--- a/import-files/WC-CTN-O(1).xlsx
+++ b/import-files/WC-CTN-O(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B253B18-2F04-4927-8942-1667FAD25EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B63422-A3B6-4EF8-AAF2-31460DBA0346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="730">
   <si>
     <t>Membership No.</t>
   </si>
@@ -6320,7 +6320,9 @@
       <c r="Q61" s="3"/>
       <c r="R61" s="4"/>
       <c r="S61" s="3"/>
-      <c r="T61" s="8"/>
+      <c r="T61" s="8" t="s">
+        <v>97</v>
+      </c>
       <c r="U61" s="7"/>
       <c r="V61" s="7"/>
       <c r="W61" s="7"/>
@@ -34348,7 +34350,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:T113" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="H102:H107 H2:H94">
+  <conditionalFormatting sqref="H2:H94 H102:H107">
     <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Inactive - ADS">
       <formula>NOT(ISERROR(SEARCH(("Inactive - ADS"),(H2))))</formula>
     </cfRule>
